--- a/public/plantilla-concurso.xlsx
+++ b/public/plantilla-concurso.xlsx
@@ -138,13 +138,6 @@
         </r>
       </text>
     </comment>
-    <comment ref="G1" authorId="0">
-      <text>
-        <r>
-          <t>Opcional: enlace a una canción de Spotify.</t>
-        </r>
-      </text>
-    </comment>
   </commentList>
 </comments>
 </file>
@@ -194,13 +187,6 @@
       </text>
     </comment>
     <comment ref="E1" authorId="0">
-      <text>
-        <r>
-          <t>Opcional: enlace de Spotify. Se pausa sola cuando alguien pulsa.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="G1" authorId="0">
       <text>
         <r>
           <t>Solo para ti.</t>
@@ -284,7 +270,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="139">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="134">
   <si>
     <t>CÓMO RELLENAR ESTA PLANTILLA</t>
   </si>
@@ -316,9 +302,6 @@
     <t>6. Puntos: un número (por acierto) o una lista por puestos, como 3,2,1 (1º, 2º y 3º).</t>
   </si>
   <si>
-    <t>7. Canciones: copia el enlace de Spotify (Compartir → Copiar enlace de la canción).</t>
-  </si>
-  <si>
     <t>Para cargarla: en el portátil, pantalla de preparación → "Cargar concurso" → elige este archivo.</t>
   </si>
   <si>
@@ -346,9 +329,6 @@
     <t>El presentador juega</t>
   </si>
   <si>
-    <t>Música de entrada</t>
-  </si>
-  <si>
     <t>Calentamiento</t>
   </si>
   <si>
@@ -436,9 +416,6 @@
     <t>Sí</t>
   </si>
   <si>
-    <t>https://open.spotify.com/track/4uLU6hMCjMI75M1A2tKUQC</t>
-  </si>
-  <si>
     <t>Equipo</t>
   </si>
   <si>
@@ -499,12 +476,6 @@
     <t>Mostrar en tele</t>
   </si>
   <si>
-    <t>Canción</t>
-  </si>
-  <si>
-    <t>Desde segundo</t>
-  </si>
-  <si>
     <t>Notas</t>
   </si>
   <si>
@@ -520,13 +491,13 @@
     <t>Ocho</t>
   </si>
   <si>
-    <t>¿Qué canción es?</t>
-  </si>
-  <si>
-    <t>Mr. Brightside</t>
-  </si>
-  <si>
-    <t>Suena 20 s</t>
+    <t>🎵 ¿Qué canción suena?</t>
+  </si>
+  <si>
+    <t>Mr. Brightside (The Killers)</t>
+  </si>
+  <si>
+    <t>Pon la canción tú desde tu música</t>
   </si>
   <si>
     <t>A</t>
@@ -1101,7 +1072,7 @@
   <sheetPr>
     <tabColor rgb="FF111111"/>
   </sheetPr>
-  <dimension ref="A1:A15"/>
+  <dimension ref="A1:A14"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="110" customWidth="1"/>
@@ -1159,12 +1130,12 @@
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>10</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
@@ -1175,11 +1146,6 @@
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>12</v>
-      </c>
-    </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A15" s="2" t="s">
-        <v>13</v>
       </c>
     </row>
   </sheetData>
@@ -1205,53 +1171,53 @@
   <sheetData>
     <row r="1" ht="30" customHeight="1" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B2" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="C2">
         <v>910</v>
       </c>
       <c r="D2" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="E2" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B3" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="C3">
         <v>120</v>
       </c>
       <c r="D3" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="E3" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25"/>
@@ -1487,38 +1453,38 @@
   <sheetData>
     <row r="1" ht="30" customHeight="1" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B2">
         <v>10</v>
       </c>
       <c r="C2" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B3">
         <v>15</v>
       </c>
       <c r="C3" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="D3">
         <v>3</v>
@@ -1526,13 +1492,13 @@
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B4">
         <v>7</v>
       </c>
       <c r="C4" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25"/>
@@ -1767,24 +1733,24 @@
   <sheetData>
     <row r="1" ht="30" customHeight="1" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B2">
         <v>3</v>
       </c>
       <c r="C2" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25"/>
@@ -2023,56 +1989,56 @@
   <sheetData>
     <row r="1" ht="30" customHeight="1" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="C1" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="F1" s="3" t="s">
         <v>17</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>127</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>18</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B2" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="C2" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="D2" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="E2" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B3" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="C3" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="D3" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="E3" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -2307,7 +2273,7 @@
   <sheetPr>
     <tabColor rgb="FFFFD400"/>
   </sheetPr>
-  <dimension ref="A1:G200"/>
+  <dimension ref="A1:F200"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
@@ -2315,192 +2281,185 @@
     <col min="4" max="4" width="50" customWidth="1"/>
     <col min="5" max="5" width="10" customWidth="1"/>
     <col min="6" max="6" width="12" customWidth="1"/>
-    <col min="7" max="7" width="46" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" ht="30" customHeight="1" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B1" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="C1" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="D1" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="E1" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="F1" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="F1" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="G1" s="3" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
       <c r="B2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D2" t="s">
         <v>21</v>
-      </c>
-      <c r="C2" t="s">
-        <v>22</v>
-      </c>
-      <c r="D2" t="s">
-        <v>23</v>
       </c>
       <c r="E2">
         <v>1</v>
       </c>
       <c r="F2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
       <c r="B3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C3" t="s">
+        <v>24</v>
+      </c>
+      <c r="D3" t="s">
         <v>25</v>
-      </c>
-      <c r="C3" t="s">
-        <v>26</v>
-      </c>
-      <c r="D3" t="s">
-        <v>27</v>
       </c>
       <c r="E3">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>3</v>
       </c>
       <c r="B4" t="s">
+        <v>26</v>
+      </c>
+      <c r="C4" t="s">
+        <v>27</v>
+      </c>
+      <c r="D4" t="s">
         <v>28</v>
-      </c>
-      <c r="C4" t="s">
-        <v>29</v>
-      </c>
-      <c r="D4" t="s">
-        <v>30</v>
       </c>
       <c r="E4">
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>4</v>
       </c>
       <c r="B5" t="s">
+        <v>29</v>
+      </c>
+      <c r="C5" t="s">
+        <v>30</v>
+      </c>
+      <c r="D5" t="s">
         <v>31</v>
-      </c>
-      <c r="C5" t="s">
-        <v>32</v>
-      </c>
-      <c r="D5" t="s">
-        <v>33</v>
       </c>
       <c r="E5">
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>5</v>
       </c>
       <c r="B6" t="s">
+        <v>32</v>
+      </c>
+      <c r="C6" t="s">
+        <v>33</v>
+      </c>
+      <c r="D6" t="s">
         <v>34</v>
       </c>
-      <c r="C6" t="s">
+      <c r="E6" t="s">
         <v>35</v>
       </c>
-      <c r="D6" t="s">
-        <v>36</v>
-      </c>
-      <c r="E6" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>6</v>
       </c>
       <c r="B7" t="s">
+        <v>36</v>
+      </c>
+      <c r="C7" t="s">
+        <v>37</v>
+      </c>
+      <c r="D7" t="s">
         <v>38</v>
       </c>
-      <c r="C7" t="s">
-        <v>39</v>
-      </c>
-      <c r="D7" t="s">
-        <v>40</v>
-      </c>
       <c r="E7" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>7</v>
       </c>
       <c r="B8" t="s">
+        <v>39</v>
+      </c>
+      <c r="C8" t="s">
+        <v>40</v>
+      </c>
+      <c r="D8" t="s">
         <v>41</v>
       </c>
-      <c r="C8" t="s">
-        <v>42</v>
-      </c>
-      <c r="D8" t="s">
-        <v>43</v>
-      </c>
       <c r="E8" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C9" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D9" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="E9">
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>9</v>
       </c>
       <c r="B10" t="s">
+        <v>44</v>
+      </c>
+      <c r="C10" t="s">
+        <v>45</v>
+      </c>
+      <c r="D10" t="s">
         <v>46</v>
-      </c>
-      <c r="C10" t="s">
-        <v>47</v>
-      </c>
-      <c r="D10" t="s">
-        <v>48</v>
       </c>
       <c r="E10">
         <v>3</v>
       </c>
       <c r="F10" t="s">
-        <v>49</v>
-      </c>
-      <c r="G10" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
     </row>
     <row r="11" spans="3:6" x14ac:dyDescent="0.25"/>
@@ -2728,26 +2687,26 @@
   <sheetData>
     <row r="1" ht="30" customHeight="1" spans="1:2" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="B2" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="B3" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
     </row>
     <row r="4" spans="2:2" x14ac:dyDescent="0.25"/>
@@ -2976,23 +2935,23 @@
   <sheetData>
     <row r="1" ht="30" customHeight="1" spans="1:2" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="B2" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="B3">
         <v>1</v>
@@ -3000,7 +2959,7 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="B4">
         <v>1</v>
@@ -3008,7 +2967,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="B5">
         <v>1</v>
@@ -3016,7 +2975,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="B6">
         <v>1</v>
@@ -3024,7 +2983,7 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -3032,15 +2991,15 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="B8" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="B9">
         <v>20</v>
@@ -3057,90 +3016,76 @@
   <sheetPr>
     <tabColor rgb="FFE53935"/>
   </sheetPr>
-  <dimension ref="A1:G200"/>
+  <dimension ref="A1:E200"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="24" customWidth="1"/>
     <col min="2" max="2" width="50" customWidth="1"/>
     <col min="3" max="3" width="30" customWidth="1"/>
     <col min="4" max="4" width="10" customWidth="1"/>
-    <col min="5" max="5" width="46" customWidth="1"/>
-    <col min="6" max="6" width="10" customWidth="1"/>
-    <col min="7" max="7" width="30" customWidth="1"/>
+    <col min="5" max="5" width="30" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" ht="30" customHeight="1" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B1" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="E1" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="C1" s="3" t="s">
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B2" t="s">
         <v>69</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="C2" t="s">
         <v>70</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="D2" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B3" t="s">
         <v>71</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="C3" t="s">
         <v>72</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="D3" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B4" t="s">
         <v>73</v>
       </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>21</v>
-      </c>
-      <c r="B2" t="s">
+      <c r="C4" t="s">
         <v>74</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D4" t="s">
+        <v>47</v>
+      </c>
+      <c r="E4" t="s">
         <v>75</v>
-      </c>
-      <c r="D2" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>21</v>
-      </c>
-      <c r="B3" t="s">
-        <v>76</v>
-      </c>
-      <c r="C3" t="s">
-        <v>77</v>
-      </c>
-      <c r="D3" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>21</v>
-      </c>
-      <c r="B4" t="s">
-        <v>78</v>
-      </c>
-      <c r="C4" t="s">
-        <v>79</v>
-      </c>
-      <c r="D4" t="s">
-        <v>24</v>
-      </c>
-      <c r="E4" t="s">
-        <v>50</v>
-      </c>
-      <c r="F4">
-        <v>0</v>
-      </c>
-      <c r="G4" t="s">
-        <v>80</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25"/>
@@ -3377,74 +3322,74 @@
   <sheetData>
     <row r="1" ht="30" customHeight="1" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="C1" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="H1" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="I1" s="3" t="s">
         <v>82</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="G1" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="H1" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="I1" s="3" t="s">
-        <v>87</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B2" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="C2" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="D2" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="E2" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="F2" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="G2" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B3" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="C3" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="D3" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="E3" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="G3" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="H3">
         <v>15</v>
@@ -3683,35 +3628,35 @@
   <sheetData>
     <row r="1" ht="30" customHeight="1" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B2" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="C2" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B3" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="C3" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25"/>
@@ -3947,39 +3892,39 @@
   <sheetData>
     <row r="1" ht="30" customHeight="1" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B2" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="C2" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="D2" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="E2" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="F2">
         <v>2</v>
@@ -4218,26 +4163,26 @@
   <sheetData>
     <row r="1" ht="30" customHeight="1" spans="1:2" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B2" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B3" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25"/>

--- a/public/plantilla-concurso.xlsx
+++ b/public/plantilla-concurso.xlsx
@@ -138,6 +138,13 @@
         </r>
       </text>
     </comment>
+    <comment ref="G1" authorId="0">
+      <text>
+        <r>
+          <t>Decorado de Halloween de la tele en esta sección. Vacío = uno distinto en cada sección.</t>
+        </r>
+      </text>
+    </comment>
   </commentList>
 </comments>
 </file>
@@ -270,7 +277,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="134">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="136">
   <si>
     <t>CÓMO RELLENAR ESTA PLANTILLA</t>
   </si>
@@ -329,6 +336,9 @@
     <t>El presentador juega</t>
   </si>
   <si>
+    <t>Entorno</t>
+  </si>
+  <si>
     <t>Calentamiento</t>
   </si>
   <si>
@@ -414,6 +424,9 @@
   </si>
   <si>
     <t>Sí</t>
+  </si>
+  <si>
+    <t>Noche de luna</t>
   </si>
   <si>
     <t>Equipo</t>
@@ -1174,50 +1187,50 @@
         <v>14</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B2" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="C2">
         <v>910</v>
       </c>
       <c r="D2" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="E2" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B3" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="C3">
         <v>120</v>
       </c>
       <c r="D3" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="E3" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25"/>
@@ -1456,35 +1469,35 @@
         <v>14</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B2">
         <v>10</v>
       </c>
       <c r="C2" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B3">
         <v>15</v>
       </c>
       <c r="C3" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="D3">
         <v>3</v>
@@ -1492,13 +1505,13 @@
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B4">
         <v>7</v>
       </c>
       <c r="C4" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25"/>
@@ -1736,21 +1749,21 @@
         <v>14</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B2">
         <v>3</v>
       </c>
       <c r="C2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25"/>
@@ -1992,16 +2005,16 @@
         <v>14</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="C1" s="3" t="s">
         <v>16</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="F1" s="3" t="s">
         <v>17</v>
@@ -2009,36 +2022,36 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="C2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="D2" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="E2" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B3" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="C3" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="D3" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="E3" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -2273,7 +2286,7 @@
   <sheetPr>
     <tabColor rgb="FFFFD400"/>
   </sheetPr>
-  <dimension ref="A1:F200"/>
+  <dimension ref="A1:G200"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
@@ -2281,9 +2294,10 @@
     <col min="4" max="4" width="50" customWidth="1"/>
     <col min="5" max="5" width="10" customWidth="1"/>
     <col min="6" max="6" width="12" customWidth="1"/>
+    <col min="7" max="7" width="22" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" ht="30" customHeight="1" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>13</v>
       </c>
@@ -2302,358 +2316,364 @@
       <c r="F1" s="3" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G1" s="3" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E2">
         <v>1</v>
       </c>
       <c r="F2" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C3" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E3">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E4">
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C5" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D5" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E5">
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C6" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D6" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E6" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>6</v>
       </c>
       <c r="B7" t="s">
+        <v>37</v>
+      </c>
+      <c r="C7" t="s">
+        <v>38</v>
+      </c>
+      <c r="D7" t="s">
+        <v>39</v>
+      </c>
+      <c r="E7" t="s">
         <v>36</v>
       </c>
-      <c r="C7" t="s">
-        <v>37</v>
-      </c>
-      <c r="D7" t="s">
-        <v>38</v>
-      </c>
-      <c r="E7" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C8" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D8" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E8" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C9" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D9" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E9">
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C10" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D10" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E10">
         <v>3</v>
       </c>
       <c r="F10" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="11" spans="3:6" x14ac:dyDescent="0.25"/>
-    <row r="12" spans="3:6" x14ac:dyDescent="0.25"/>
-    <row r="13" spans="3:6" x14ac:dyDescent="0.25"/>
-    <row r="14" spans="3:6" x14ac:dyDescent="0.25"/>
-    <row r="15" spans="3:6" x14ac:dyDescent="0.25"/>
-    <row r="16" spans="3:6" x14ac:dyDescent="0.25"/>
-    <row r="17" spans="3:6" x14ac:dyDescent="0.25"/>
-    <row r="18" spans="3:6" x14ac:dyDescent="0.25"/>
-    <row r="19" spans="3:6" x14ac:dyDescent="0.25"/>
-    <row r="20" spans="3:6" x14ac:dyDescent="0.25"/>
-    <row r="21" spans="3:6" x14ac:dyDescent="0.25"/>
-    <row r="22" spans="3:6" x14ac:dyDescent="0.25"/>
-    <row r="23" spans="3:6" x14ac:dyDescent="0.25"/>
-    <row r="24" spans="3:6" x14ac:dyDescent="0.25"/>
-    <row r="25" spans="3:6" x14ac:dyDescent="0.25"/>
-    <row r="26" spans="3:6" x14ac:dyDescent="0.25"/>
-    <row r="27" spans="3:6" x14ac:dyDescent="0.25"/>
-    <row r="28" spans="3:6" x14ac:dyDescent="0.25"/>
-    <row r="29" spans="3:6" x14ac:dyDescent="0.25"/>
-    <row r="30" spans="3:6" x14ac:dyDescent="0.25"/>
-    <row r="31" spans="3:6" x14ac:dyDescent="0.25"/>
-    <row r="32" spans="3:6" x14ac:dyDescent="0.25"/>
-    <row r="33" spans="3:6" x14ac:dyDescent="0.25"/>
-    <row r="34" spans="3:6" x14ac:dyDescent="0.25"/>
-    <row r="35" spans="3:6" x14ac:dyDescent="0.25"/>
-    <row r="36" spans="3:6" x14ac:dyDescent="0.25"/>
-    <row r="37" spans="3:6" x14ac:dyDescent="0.25"/>
-    <row r="38" spans="3:6" x14ac:dyDescent="0.25"/>
-    <row r="39" spans="3:6" x14ac:dyDescent="0.25"/>
-    <row r="40" spans="3:6" x14ac:dyDescent="0.25"/>
-    <row r="41" spans="3:6" x14ac:dyDescent="0.25"/>
-    <row r="42" spans="3:6" x14ac:dyDescent="0.25"/>
-    <row r="43" spans="3:6" x14ac:dyDescent="0.25"/>
-    <row r="44" spans="3:6" x14ac:dyDescent="0.25"/>
-    <row r="45" spans="3:6" x14ac:dyDescent="0.25"/>
-    <row r="46" spans="3:6" x14ac:dyDescent="0.25"/>
-    <row r="47" spans="3:6" x14ac:dyDescent="0.25"/>
-    <row r="48" spans="3:6" x14ac:dyDescent="0.25"/>
-    <row r="49" spans="3:6" x14ac:dyDescent="0.25"/>
-    <row r="50" spans="3:6" x14ac:dyDescent="0.25"/>
-    <row r="51" spans="3:6" x14ac:dyDescent="0.25"/>
-    <row r="52" spans="3:6" x14ac:dyDescent="0.25"/>
-    <row r="53" spans="3:6" x14ac:dyDescent="0.25"/>
-    <row r="54" spans="3:6" x14ac:dyDescent="0.25"/>
-    <row r="55" spans="3:6" x14ac:dyDescent="0.25"/>
-    <row r="56" spans="3:6" x14ac:dyDescent="0.25"/>
-    <row r="57" spans="3:6" x14ac:dyDescent="0.25"/>
-    <row r="58" spans="3:6" x14ac:dyDescent="0.25"/>
-    <row r="59" spans="3:6" x14ac:dyDescent="0.25"/>
-    <row r="60" spans="3:6" x14ac:dyDescent="0.25"/>
-    <row r="61" spans="3:6" x14ac:dyDescent="0.25"/>
-    <row r="62" spans="3:6" x14ac:dyDescent="0.25"/>
-    <row r="63" spans="3:6" x14ac:dyDescent="0.25"/>
-    <row r="64" spans="3:6" x14ac:dyDescent="0.25"/>
-    <row r="65" spans="3:6" x14ac:dyDescent="0.25"/>
-    <row r="66" spans="3:6" x14ac:dyDescent="0.25"/>
-    <row r="67" spans="3:6" x14ac:dyDescent="0.25"/>
-    <row r="68" spans="3:6" x14ac:dyDescent="0.25"/>
-    <row r="69" spans="3:6" x14ac:dyDescent="0.25"/>
-    <row r="70" spans="3:6" x14ac:dyDescent="0.25"/>
-    <row r="71" spans="3:6" x14ac:dyDescent="0.25"/>
-    <row r="72" spans="3:6" x14ac:dyDescent="0.25"/>
-    <row r="73" spans="3:6" x14ac:dyDescent="0.25"/>
-    <row r="74" spans="3:6" x14ac:dyDescent="0.25"/>
-    <row r="75" spans="3:6" x14ac:dyDescent="0.25"/>
-    <row r="76" spans="3:6" x14ac:dyDescent="0.25"/>
-    <row r="77" spans="3:6" x14ac:dyDescent="0.25"/>
-    <row r="78" spans="3:6" x14ac:dyDescent="0.25"/>
-    <row r="79" spans="3:6" x14ac:dyDescent="0.25"/>
-    <row r="80" spans="3:6" x14ac:dyDescent="0.25"/>
-    <row r="81" spans="3:6" x14ac:dyDescent="0.25"/>
-    <row r="82" spans="3:6" x14ac:dyDescent="0.25"/>
-    <row r="83" spans="3:6" x14ac:dyDescent="0.25"/>
-    <row r="84" spans="3:6" x14ac:dyDescent="0.25"/>
-    <row r="85" spans="3:6" x14ac:dyDescent="0.25"/>
-    <row r="86" spans="3:6" x14ac:dyDescent="0.25"/>
-    <row r="87" spans="3:6" x14ac:dyDescent="0.25"/>
-    <row r="88" spans="3:6" x14ac:dyDescent="0.25"/>
-    <row r="89" spans="3:6" x14ac:dyDescent="0.25"/>
-    <row r="90" spans="3:6" x14ac:dyDescent="0.25"/>
-    <row r="91" spans="3:6" x14ac:dyDescent="0.25"/>
-    <row r="92" spans="3:6" x14ac:dyDescent="0.25"/>
-    <row r="93" spans="3:6" x14ac:dyDescent="0.25"/>
-    <row r="94" spans="3:6" x14ac:dyDescent="0.25"/>
-    <row r="95" spans="3:6" x14ac:dyDescent="0.25"/>
-    <row r="96" spans="3:6" x14ac:dyDescent="0.25"/>
-    <row r="97" spans="3:6" x14ac:dyDescent="0.25"/>
-    <row r="98" spans="3:6" x14ac:dyDescent="0.25"/>
-    <row r="99" spans="3:6" x14ac:dyDescent="0.25"/>
-    <row r="100" spans="3:6" x14ac:dyDescent="0.25"/>
-    <row r="101" spans="3:6" x14ac:dyDescent="0.25"/>
-    <row r="102" spans="3:6" x14ac:dyDescent="0.25"/>
-    <row r="103" spans="3:6" x14ac:dyDescent="0.25"/>
-    <row r="104" spans="3:6" x14ac:dyDescent="0.25"/>
-    <row r="105" spans="3:6" x14ac:dyDescent="0.25"/>
-    <row r="106" spans="3:6" x14ac:dyDescent="0.25"/>
-    <row r="107" spans="3:6" x14ac:dyDescent="0.25"/>
-    <row r="108" spans="3:6" x14ac:dyDescent="0.25"/>
-    <row r="109" spans="3:6" x14ac:dyDescent="0.25"/>
-    <row r="110" spans="3:6" x14ac:dyDescent="0.25"/>
-    <row r="111" spans="3:6" x14ac:dyDescent="0.25"/>
-    <row r="112" spans="3:6" x14ac:dyDescent="0.25"/>
-    <row r="113" spans="3:6" x14ac:dyDescent="0.25"/>
-    <row r="114" spans="3:6" x14ac:dyDescent="0.25"/>
-    <row r="115" spans="3:6" x14ac:dyDescent="0.25"/>
-    <row r="116" spans="3:6" x14ac:dyDescent="0.25"/>
-    <row r="117" spans="3:6" x14ac:dyDescent="0.25"/>
-    <row r="118" spans="3:6" x14ac:dyDescent="0.25"/>
-    <row r="119" spans="3:6" x14ac:dyDescent="0.25"/>
-    <row r="120" spans="3:6" x14ac:dyDescent="0.25"/>
-    <row r="121" spans="3:6" x14ac:dyDescent="0.25"/>
-    <row r="122" spans="3:6" x14ac:dyDescent="0.25"/>
-    <row r="123" spans="3:6" x14ac:dyDescent="0.25"/>
-    <row r="124" spans="3:6" x14ac:dyDescent="0.25"/>
-    <row r="125" spans="3:6" x14ac:dyDescent="0.25"/>
-    <row r="126" spans="3:6" x14ac:dyDescent="0.25"/>
-    <row r="127" spans="3:6" x14ac:dyDescent="0.25"/>
-    <row r="128" spans="3:6" x14ac:dyDescent="0.25"/>
-    <row r="129" spans="3:6" x14ac:dyDescent="0.25"/>
-    <row r="130" spans="3:6" x14ac:dyDescent="0.25"/>
-    <row r="131" spans="3:6" x14ac:dyDescent="0.25"/>
-    <row r="132" spans="3:6" x14ac:dyDescent="0.25"/>
-    <row r="133" spans="3:6" x14ac:dyDescent="0.25"/>
-    <row r="134" spans="3:6" x14ac:dyDescent="0.25"/>
-    <row r="135" spans="3:6" x14ac:dyDescent="0.25"/>
-    <row r="136" spans="3:6" x14ac:dyDescent="0.25"/>
-    <row r="137" spans="3:6" x14ac:dyDescent="0.25"/>
-    <row r="138" spans="3:6" x14ac:dyDescent="0.25"/>
-    <row r="139" spans="3:6" x14ac:dyDescent="0.25"/>
-    <row r="140" spans="3:6" x14ac:dyDescent="0.25"/>
-    <row r="141" spans="3:6" x14ac:dyDescent="0.25"/>
-    <row r="142" spans="3:6" x14ac:dyDescent="0.25"/>
-    <row r="143" spans="3:6" x14ac:dyDescent="0.25"/>
-    <row r="144" spans="3:6" x14ac:dyDescent="0.25"/>
-    <row r="145" spans="3:6" x14ac:dyDescent="0.25"/>
-    <row r="146" spans="3:6" x14ac:dyDescent="0.25"/>
-    <row r="147" spans="3:6" x14ac:dyDescent="0.25"/>
-    <row r="148" spans="3:6" x14ac:dyDescent="0.25"/>
-    <row r="149" spans="3:6" x14ac:dyDescent="0.25"/>
-    <row r="150" spans="3:6" x14ac:dyDescent="0.25"/>
-    <row r="151" spans="3:6" x14ac:dyDescent="0.25"/>
-    <row r="152" spans="3:6" x14ac:dyDescent="0.25"/>
-    <row r="153" spans="3:6" x14ac:dyDescent="0.25"/>
-    <row r="154" spans="3:6" x14ac:dyDescent="0.25"/>
-    <row r="155" spans="3:6" x14ac:dyDescent="0.25"/>
-    <row r="156" spans="3:6" x14ac:dyDescent="0.25"/>
-    <row r="157" spans="3:6" x14ac:dyDescent="0.25"/>
-    <row r="158" spans="3:6" x14ac:dyDescent="0.25"/>
-    <row r="159" spans="3:6" x14ac:dyDescent="0.25"/>
-    <row r="160" spans="3:6" x14ac:dyDescent="0.25"/>
-    <row r="161" spans="3:6" x14ac:dyDescent="0.25"/>
-    <row r="162" spans="3:6" x14ac:dyDescent="0.25"/>
-    <row r="163" spans="3:6" x14ac:dyDescent="0.25"/>
-    <row r="164" spans="3:6" x14ac:dyDescent="0.25"/>
-    <row r="165" spans="3:6" x14ac:dyDescent="0.25"/>
-    <row r="166" spans="3:6" x14ac:dyDescent="0.25"/>
-    <row r="167" spans="3:6" x14ac:dyDescent="0.25"/>
-    <row r="168" spans="3:6" x14ac:dyDescent="0.25"/>
-    <row r="169" spans="3:6" x14ac:dyDescent="0.25"/>
-    <row r="170" spans="3:6" x14ac:dyDescent="0.25"/>
-    <row r="171" spans="3:6" x14ac:dyDescent="0.25"/>
-    <row r="172" spans="3:6" x14ac:dyDescent="0.25"/>
-    <row r="173" spans="3:6" x14ac:dyDescent="0.25"/>
-    <row r="174" spans="3:6" x14ac:dyDescent="0.25"/>
-    <row r="175" spans="3:6" x14ac:dyDescent="0.25"/>
-    <row r="176" spans="3:6" x14ac:dyDescent="0.25"/>
-    <row r="177" spans="3:6" x14ac:dyDescent="0.25"/>
-    <row r="178" spans="3:6" x14ac:dyDescent="0.25"/>
-    <row r="179" spans="3:6" x14ac:dyDescent="0.25"/>
-    <row r="180" spans="3:6" x14ac:dyDescent="0.25"/>
-    <row r="181" spans="3:6" x14ac:dyDescent="0.25"/>
-    <row r="182" spans="3:6" x14ac:dyDescent="0.25"/>
-    <row r="183" spans="3:6" x14ac:dyDescent="0.25"/>
-    <row r="184" spans="3:6" x14ac:dyDescent="0.25"/>
-    <row r="185" spans="3:6" x14ac:dyDescent="0.25"/>
-    <row r="186" spans="3:6" x14ac:dyDescent="0.25"/>
-    <row r="187" spans="3:6" x14ac:dyDescent="0.25"/>
-    <row r="188" spans="3:6" x14ac:dyDescent="0.25"/>
-    <row r="189" spans="3:6" x14ac:dyDescent="0.25"/>
-    <row r="190" spans="3:6" x14ac:dyDescent="0.25"/>
-    <row r="191" spans="3:6" x14ac:dyDescent="0.25"/>
-    <row r="192" spans="3:6" x14ac:dyDescent="0.25"/>
-    <row r="193" spans="3:6" x14ac:dyDescent="0.25"/>
-    <row r="194" spans="3:6" x14ac:dyDescent="0.25"/>
-    <row r="195" spans="3:6" x14ac:dyDescent="0.25"/>
-    <row r="196" spans="3:6" x14ac:dyDescent="0.25"/>
-    <row r="197" spans="3:6" x14ac:dyDescent="0.25"/>
-    <row r="198" spans="3:6" x14ac:dyDescent="0.25"/>
-    <row r="199" spans="3:6" x14ac:dyDescent="0.25"/>
-    <row r="200" spans="3:6" x14ac:dyDescent="0.25"/>
+        <v>48</v>
+      </c>
+      <c r="G10" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="11" spans="3:7" x14ac:dyDescent="0.25"/>
+    <row r="12" spans="3:7" x14ac:dyDescent="0.25"/>
+    <row r="13" spans="3:7" x14ac:dyDescent="0.25"/>
+    <row r="14" spans="3:7" x14ac:dyDescent="0.25"/>
+    <row r="15" spans="3:7" x14ac:dyDescent="0.25"/>
+    <row r="16" spans="3:7" x14ac:dyDescent="0.25"/>
+    <row r="17" spans="3:7" x14ac:dyDescent="0.25"/>
+    <row r="18" spans="3:7" x14ac:dyDescent="0.25"/>
+    <row r="19" spans="3:7" x14ac:dyDescent="0.25"/>
+    <row r="20" spans="3:7" x14ac:dyDescent="0.25"/>
+    <row r="21" spans="3:7" x14ac:dyDescent="0.25"/>
+    <row r="22" spans="3:7" x14ac:dyDescent="0.25"/>
+    <row r="23" spans="3:7" x14ac:dyDescent="0.25"/>
+    <row r="24" spans="3:7" x14ac:dyDescent="0.25"/>
+    <row r="25" spans="3:7" x14ac:dyDescent="0.25"/>
+    <row r="26" spans="3:7" x14ac:dyDescent="0.25"/>
+    <row r="27" spans="3:7" x14ac:dyDescent="0.25"/>
+    <row r="28" spans="3:7" x14ac:dyDescent="0.25"/>
+    <row r="29" spans="3:7" x14ac:dyDescent="0.25"/>
+    <row r="30" spans="3:7" x14ac:dyDescent="0.25"/>
+    <row r="31" spans="3:7" x14ac:dyDescent="0.25"/>
+    <row r="32" spans="3:7" x14ac:dyDescent="0.25"/>
+    <row r="33" spans="3:7" x14ac:dyDescent="0.25"/>
+    <row r="34" spans="3:7" x14ac:dyDescent="0.25"/>
+    <row r="35" spans="3:7" x14ac:dyDescent="0.25"/>
+    <row r="36" spans="3:7" x14ac:dyDescent="0.25"/>
+    <row r="37" spans="3:7" x14ac:dyDescent="0.25"/>
+    <row r="38" spans="3:7" x14ac:dyDescent="0.25"/>
+    <row r="39" spans="3:7" x14ac:dyDescent="0.25"/>
+    <row r="40" spans="3:7" x14ac:dyDescent="0.25"/>
+    <row r="41" spans="3:7" x14ac:dyDescent="0.25"/>
+    <row r="42" spans="3:7" x14ac:dyDescent="0.25"/>
+    <row r="43" spans="3:7" x14ac:dyDescent="0.25"/>
+    <row r="44" spans="3:7" x14ac:dyDescent="0.25"/>
+    <row r="45" spans="3:7" x14ac:dyDescent="0.25"/>
+    <row r="46" spans="3:7" x14ac:dyDescent="0.25"/>
+    <row r="47" spans="3:7" x14ac:dyDescent="0.25"/>
+    <row r="48" spans="3:7" x14ac:dyDescent="0.25"/>
+    <row r="49" spans="3:7" x14ac:dyDescent="0.25"/>
+    <row r="50" spans="3:7" x14ac:dyDescent="0.25"/>
+    <row r="51" spans="3:7" x14ac:dyDescent="0.25"/>
+    <row r="52" spans="3:7" x14ac:dyDescent="0.25"/>
+    <row r="53" spans="3:7" x14ac:dyDescent="0.25"/>
+    <row r="54" spans="3:7" x14ac:dyDescent="0.25"/>
+    <row r="55" spans="3:7" x14ac:dyDescent="0.25"/>
+    <row r="56" spans="3:7" x14ac:dyDescent="0.25"/>
+    <row r="57" spans="3:7" x14ac:dyDescent="0.25"/>
+    <row r="58" spans="3:7" x14ac:dyDescent="0.25"/>
+    <row r="59" spans="3:7" x14ac:dyDescent="0.25"/>
+    <row r="60" spans="3:7" x14ac:dyDescent="0.25"/>
+    <row r="61" spans="3:7" x14ac:dyDescent="0.25"/>
+    <row r="62" spans="3:7" x14ac:dyDescent="0.25"/>
+    <row r="63" spans="3:7" x14ac:dyDescent="0.25"/>
+    <row r="64" spans="3:7" x14ac:dyDescent="0.25"/>
+    <row r="65" spans="3:7" x14ac:dyDescent="0.25"/>
+    <row r="66" spans="3:7" x14ac:dyDescent="0.25"/>
+    <row r="67" spans="3:7" x14ac:dyDescent="0.25"/>
+    <row r="68" spans="3:7" x14ac:dyDescent="0.25"/>
+    <row r="69" spans="3:7" x14ac:dyDescent="0.25"/>
+    <row r="70" spans="3:7" x14ac:dyDescent="0.25"/>
+    <row r="71" spans="3:7" x14ac:dyDescent="0.25"/>
+    <row r="72" spans="3:7" x14ac:dyDescent="0.25"/>
+    <row r="73" spans="3:7" x14ac:dyDescent="0.25"/>
+    <row r="74" spans="3:7" x14ac:dyDescent="0.25"/>
+    <row r="75" spans="3:7" x14ac:dyDescent="0.25"/>
+    <row r="76" spans="3:7" x14ac:dyDescent="0.25"/>
+    <row r="77" spans="3:7" x14ac:dyDescent="0.25"/>
+    <row r="78" spans="3:7" x14ac:dyDescent="0.25"/>
+    <row r="79" spans="3:7" x14ac:dyDescent="0.25"/>
+    <row r="80" spans="3:7" x14ac:dyDescent="0.25"/>
+    <row r="81" spans="3:7" x14ac:dyDescent="0.25"/>
+    <row r="82" spans="3:7" x14ac:dyDescent="0.25"/>
+    <row r="83" spans="3:7" x14ac:dyDescent="0.25"/>
+    <row r="84" spans="3:7" x14ac:dyDescent="0.25"/>
+    <row r="85" spans="3:7" x14ac:dyDescent="0.25"/>
+    <row r="86" spans="3:7" x14ac:dyDescent="0.25"/>
+    <row r="87" spans="3:7" x14ac:dyDescent="0.25"/>
+    <row r="88" spans="3:7" x14ac:dyDescent="0.25"/>
+    <row r="89" spans="3:7" x14ac:dyDescent="0.25"/>
+    <row r="90" spans="3:7" x14ac:dyDescent="0.25"/>
+    <row r="91" spans="3:7" x14ac:dyDescent="0.25"/>
+    <row r="92" spans="3:7" x14ac:dyDescent="0.25"/>
+    <row r="93" spans="3:7" x14ac:dyDescent="0.25"/>
+    <row r="94" spans="3:7" x14ac:dyDescent="0.25"/>
+    <row r="95" spans="3:7" x14ac:dyDescent="0.25"/>
+    <row r="96" spans="3:7" x14ac:dyDescent="0.25"/>
+    <row r="97" spans="3:7" x14ac:dyDescent="0.25"/>
+    <row r="98" spans="3:7" x14ac:dyDescent="0.25"/>
+    <row r="99" spans="3:7" x14ac:dyDescent="0.25"/>
+    <row r="100" spans="3:7" x14ac:dyDescent="0.25"/>
+    <row r="101" spans="3:7" x14ac:dyDescent="0.25"/>
+    <row r="102" spans="3:7" x14ac:dyDescent="0.25"/>
+    <row r="103" spans="3:7" x14ac:dyDescent="0.25"/>
+    <row r="104" spans="3:7" x14ac:dyDescent="0.25"/>
+    <row r="105" spans="3:7" x14ac:dyDescent="0.25"/>
+    <row r="106" spans="3:7" x14ac:dyDescent="0.25"/>
+    <row r="107" spans="3:7" x14ac:dyDescent="0.25"/>
+    <row r="108" spans="3:7" x14ac:dyDescent="0.25"/>
+    <row r="109" spans="3:7" x14ac:dyDescent="0.25"/>
+    <row r="110" spans="3:7" x14ac:dyDescent="0.25"/>
+    <row r="111" spans="3:7" x14ac:dyDescent="0.25"/>
+    <row r="112" spans="3:7" x14ac:dyDescent="0.25"/>
+    <row r="113" spans="3:7" x14ac:dyDescent="0.25"/>
+    <row r="114" spans="3:7" x14ac:dyDescent="0.25"/>
+    <row r="115" spans="3:7" x14ac:dyDescent="0.25"/>
+    <row r="116" spans="3:7" x14ac:dyDescent="0.25"/>
+    <row r="117" spans="3:7" x14ac:dyDescent="0.25"/>
+    <row r="118" spans="3:7" x14ac:dyDescent="0.25"/>
+    <row r="119" spans="3:7" x14ac:dyDescent="0.25"/>
+    <row r="120" spans="3:7" x14ac:dyDescent="0.25"/>
+    <row r="121" spans="3:7" x14ac:dyDescent="0.25"/>
+    <row r="122" spans="3:7" x14ac:dyDescent="0.25"/>
+    <row r="123" spans="3:7" x14ac:dyDescent="0.25"/>
+    <row r="124" spans="3:7" x14ac:dyDescent="0.25"/>
+    <row r="125" spans="3:7" x14ac:dyDescent="0.25"/>
+    <row r="126" spans="3:7" x14ac:dyDescent="0.25"/>
+    <row r="127" spans="3:7" x14ac:dyDescent="0.25"/>
+    <row r="128" spans="3:7" x14ac:dyDescent="0.25"/>
+    <row r="129" spans="3:7" x14ac:dyDescent="0.25"/>
+    <row r="130" spans="3:7" x14ac:dyDescent="0.25"/>
+    <row r="131" spans="3:7" x14ac:dyDescent="0.25"/>
+    <row r="132" spans="3:7" x14ac:dyDescent="0.25"/>
+    <row r="133" spans="3:7" x14ac:dyDescent="0.25"/>
+    <row r="134" spans="3:7" x14ac:dyDescent="0.25"/>
+    <row r="135" spans="3:7" x14ac:dyDescent="0.25"/>
+    <row r="136" spans="3:7" x14ac:dyDescent="0.25"/>
+    <row r="137" spans="3:7" x14ac:dyDescent="0.25"/>
+    <row r="138" spans="3:7" x14ac:dyDescent="0.25"/>
+    <row r="139" spans="3:7" x14ac:dyDescent="0.25"/>
+    <row r="140" spans="3:7" x14ac:dyDescent="0.25"/>
+    <row r="141" spans="3:7" x14ac:dyDescent="0.25"/>
+    <row r="142" spans="3:7" x14ac:dyDescent="0.25"/>
+    <row r="143" spans="3:7" x14ac:dyDescent="0.25"/>
+    <row r="144" spans="3:7" x14ac:dyDescent="0.25"/>
+    <row r="145" spans="3:7" x14ac:dyDescent="0.25"/>
+    <row r="146" spans="3:7" x14ac:dyDescent="0.25"/>
+    <row r="147" spans="3:7" x14ac:dyDescent="0.25"/>
+    <row r="148" spans="3:7" x14ac:dyDescent="0.25"/>
+    <row r="149" spans="3:7" x14ac:dyDescent="0.25"/>
+    <row r="150" spans="3:7" x14ac:dyDescent="0.25"/>
+    <row r="151" spans="3:7" x14ac:dyDescent="0.25"/>
+    <row r="152" spans="3:7" x14ac:dyDescent="0.25"/>
+    <row r="153" spans="3:7" x14ac:dyDescent="0.25"/>
+    <row r="154" spans="3:7" x14ac:dyDescent="0.25"/>
+    <row r="155" spans="3:7" x14ac:dyDescent="0.25"/>
+    <row r="156" spans="3:7" x14ac:dyDescent="0.25"/>
+    <row r="157" spans="3:7" x14ac:dyDescent="0.25"/>
+    <row r="158" spans="3:7" x14ac:dyDescent="0.25"/>
+    <row r="159" spans="3:7" x14ac:dyDescent="0.25"/>
+    <row r="160" spans="3:7" x14ac:dyDescent="0.25"/>
+    <row r="161" spans="3:7" x14ac:dyDescent="0.25"/>
+    <row r="162" spans="3:7" x14ac:dyDescent="0.25"/>
+    <row r="163" spans="3:7" x14ac:dyDescent="0.25"/>
+    <row r="164" spans="3:7" x14ac:dyDescent="0.25"/>
+    <row r="165" spans="3:7" x14ac:dyDescent="0.25"/>
+    <row r="166" spans="3:7" x14ac:dyDescent="0.25"/>
+    <row r="167" spans="3:7" x14ac:dyDescent="0.25"/>
+    <row r="168" spans="3:7" x14ac:dyDescent="0.25"/>
+    <row r="169" spans="3:7" x14ac:dyDescent="0.25"/>
+    <row r="170" spans="3:7" x14ac:dyDescent="0.25"/>
+    <row r="171" spans="3:7" x14ac:dyDescent="0.25"/>
+    <row r="172" spans="3:7" x14ac:dyDescent="0.25"/>
+    <row r="173" spans="3:7" x14ac:dyDescent="0.25"/>
+    <row r="174" spans="3:7" x14ac:dyDescent="0.25"/>
+    <row r="175" spans="3:7" x14ac:dyDescent="0.25"/>
+    <row r="176" spans="3:7" x14ac:dyDescent="0.25"/>
+    <row r="177" spans="3:7" x14ac:dyDescent="0.25"/>
+    <row r="178" spans="3:7" x14ac:dyDescent="0.25"/>
+    <row r="179" spans="3:7" x14ac:dyDescent="0.25"/>
+    <row r="180" spans="3:7" x14ac:dyDescent="0.25"/>
+    <row r="181" spans="3:7" x14ac:dyDescent="0.25"/>
+    <row r="182" spans="3:7" x14ac:dyDescent="0.25"/>
+    <row r="183" spans="3:7" x14ac:dyDescent="0.25"/>
+    <row r="184" spans="3:7" x14ac:dyDescent="0.25"/>
+    <row r="185" spans="3:7" x14ac:dyDescent="0.25"/>
+    <row r="186" spans="3:7" x14ac:dyDescent="0.25"/>
+    <row r="187" spans="3:7" x14ac:dyDescent="0.25"/>
+    <row r="188" spans="3:7" x14ac:dyDescent="0.25"/>
+    <row r="189" spans="3:7" x14ac:dyDescent="0.25"/>
+    <row r="190" spans="3:7" x14ac:dyDescent="0.25"/>
+    <row r="191" spans="3:7" x14ac:dyDescent="0.25"/>
+    <row r="192" spans="3:7" x14ac:dyDescent="0.25"/>
+    <row r="193" spans="3:7" x14ac:dyDescent="0.25"/>
+    <row r="194" spans="3:7" x14ac:dyDescent="0.25"/>
+    <row r="195" spans="3:7" x14ac:dyDescent="0.25"/>
+    <row r="196" spans="3:7" x14ac:dyDescent="0.25"/>
+    <row r="197" spans="3:7" x14ac:dyDescent="0.25"/>
+    <row r="198" spans="3:7" x14ac:dyDescent="0.25"/>
+    <row r="199" spans="3:7" x14ac:dyDescent="0.25"/>
+    <row r="200" spans="3:7" x14ac:dyDescent="0.25"/>
   </sheetData>
-  <dataValidations count="4">
+  <dataValidations count="6">
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="warning" errorTitle="Valor no previsto" error="Elige un valor de la lista." sqref="C10:C200">
       <formula1>"Pulsador,Test,Verdad o mentira,Dos verdades y una mentira,Votación,Estimación,Parar el contador,Duelo de reflejos,Libre"</formula1>
     </dataValidation>
@@ -2665,6 +2685,12 @@
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="warning" errorTitle="Valor no previsto" error="Elige un valor de la lista." sqref="F2:F200">
       <formula1>"Sí,No"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="warning" errorTitle="Valor no previsto" error="Elige un valor de la lista." sqref="G10:G200">
+      <formula1>"Noche de luna,Cementerio,Bosque encantado,Huerto de calabazas,Laboratorio,Mansión encantada,Telaraña,Aquelarre,Cripta helada,Tormenta"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="warning" errorTitle="Valor no previsto" error="Elige un valor de la lista." sqref="G2:G200">
+      <formula1>"Noche de luna,Cementerio,Bosque encantado,Huerto de calabazas,Laboratorio,Mansión encantada,Telaraña,Aquelarre,Cripta helada,Tormenta"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2687,26 +2713,26 @@
   <sheetData>
     <row r="1" ht="30" customHeight="1" spans="1:2" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
     <row r="4" spans="2:2" x14ac:dyDescent="0.25"/>
@@ -2935,23 +2961,23 @@
   <sheetData>
     <row r="1" ht="30" customHeight="1" spans="1:2" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B3">
         <v>1</v>
@@ -2959,7 +2985,7 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B4">
         <v>1</v>
@@ -2967,7 +2993,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="B5">
         <v>1</v>
@@ -2975,7 +3001,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B6">
         <v>1</v>
@@ -2983,7 +3009,7 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -2991,15 +3017,15 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="B8" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="B9">
         <v>20</v>
@@ -3031,61 +3057,61 @@
         <v>14</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C2" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B3" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C3" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="D3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B4" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C4" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D4" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E4" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25"/>
@@ -3325,71 +3351,71 @@
         <v>14</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B2" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C2" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="D2" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="E2" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="F2" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="G2" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B3" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C3" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="D3" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="E3" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="G3" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="H3">
         <v>15</v>
@@ -3631,32 +3657,32 @@
         <v>14</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B2" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="C2" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B3" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="C3" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25"/>
@@ -3895,36 +3921,36 @@
         <v>14</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="C1" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="F1" s="3" t="s">
         <v>98</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>96</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B2" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="C2" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="D2" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="E2" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="F2">
         <v>2</v>
@@ -4166,23 +4192,23 @@
         <v>14</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B2" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B3" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25"/>

--- a/public/plantilla-concurso.xlsx
+++ b/public/plantilla-concurso.xlsx
@@ -141,6 +141,13 @@
     <comment ref="G1" authorId="0">
       <text>
         <r>
+          <t>Sí: cada pregunta la responde un solo jugador de cada equipo. Al empezar la sección, el portavoz de cada equipo elige el orden en su móvil (de la pregunta más fácil a la más difícil). Solo Verdad o mentira, Estimación y Parar el contador, y con equipos. El Test (millonario) siempre va por turnos: un concursante cada vez, alternando equipos.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="H1" authorId="0">
+      <text>
+        <r>
           <t>Decorado de Halloween de la tele en esta sección. Vacío = uno distinto en cada sección.</t>
         </r>
       </text>
@@ -220,13 +227,6 @@
     <comment ref="H1" authorId="0">
       <text>
         <r>
-          <t>Vacío = el de Ajustes.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="I1" authorId="0">
-      <text>
-        <r>
           <t>Opcional: dirección web de una imagen.</t>
         </r>
       </text>
@@ -277,7 +277,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="136">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="147">
   <si>
     <t>CÓMO RELLENAR ESTA PLANTILLA</t>
   </si>
@@ -291,7 +291,10 @@
     <t>2. Equipos: uno por fila con su color. Si la dejas vacía, se juega sin equipos.</t>
   </si>
   <si>
-    <t>3. Ajustes: título, comodines por equipo (o por jugador si no hay equipos) y puntos por defecto.</t>
+    <t>3. Ajustes: título, comodines del Test (50:50, Público y Llamada) por equipo (o por jugador sin equipos) y puntos.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   El Test se juega como «¿Quién quiere ser millonario?»: un concursante cada vez; ordena sus preguntas de fácil a difícil.</t>
   </si>
   <si>
     <t>4. Cada tipo de sección tiene su pestaña. En la columna "Sección" escribe (o elige) el nombre de la sección</t>
@@ -336,6 +339,9 @@
     <t>El presentador juega</t>
   </si>
   <si>
+    <t>Por turnos</t>
+  </si>
+  <si>
     <t>Entorno</t>
   </si>
   <si>
@@ -357,7 +363,7 @@
     <t>Test</t>
   </si>
   <si>
-    <t>Cuatro respuestas, solo una buena.</t>
+    <t>¿Quién quiere ser millonario? Uno cada vez; vuestro portavoz decide el orden.</t>
   </si>
   <si>
     <t>¿Verdad o mentira?</t>
@@ -462,7 +468,7 @@
     <t>Comodín 50 %</t>
   </si>
   <si>
-    <t>Comodín Doble</t>
+    <t>Comodín Llamada</t>
   </si>
   <si>
     <t>Comodín Público</t>
@@ -528,12 +534,21 @@
     <t>Correcta</t>
   </si>
   <si>
-    <t>Segundos</t>
-  </si>
-  <si>
     <t>Imagen</t>
   </si>
   <si>
+    <t>¿Cuántos lados tiene un hexágono?</t>
+  </si>
+  <si>
+    <t>Cinco</t>
+  </si>
+  <si>
+    <t>Seis</t>
+  </si>
+  <si>
+    <t>Siete</t>
+  </si>
+  <si>
     <t>¿En qué año llegó el hombre a la Luna?</t>
   </si>
   <si>
@@ -549,6 +564,21 @@
     <t>1975</t>
   </si>
   <si>
+    <t>¿Cuál es la capital de provincia española que está a más altura?</t>
+  </si>
+  <si>
+    <t>Cuenca</t>
+  </si>
+  <si>
+    <t>Badajoz</t>
+  </si>
+  <si>
+    <t>Jaén</t>
+  </si>
+  <si>
+    <t>Ávila</t>
+  </si>
+  <si>
     <t>¿Cuál es el planeta más grande?</t>
   </si>
   <si>
@@ -559,6 +589,9 @@
   </si>
   <si>
     <t>Júpiter</t>
+  </si>
+  <si>
+    <t>Urano</t>
   </si>
   <si>
     <t>Afirmación</t>
@@ -1085,7 +1118,7 @@
   <sheetPr>
     <tabColor rgb="FF111111"/>
   </sheetPr>
-  <dimension ref="A1:A14"/>
+  <dimension ref="A1:A15"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="110" customWidth="1"/>
@@ -1143,12 +1176,12 @@
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>10</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
@@ -1159,6 +1192,11 @@
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>12</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A15" s="2" t="s">
+        <v>13</v>
       </c>
     </row>
   </sheetData>
@@ -1184,53 +1222,53 @@
   <sheetData>
     <row r="1" ht="30" customHeight="1" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>109</v>
+        <v>120</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>110</v>
+        <v>121</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B2" t="s">
-        <v>111</v>
+        <v>122</v>
       </c>
       <c r="C2">
         <v>910</v>
       </c>
       <c r="D2" t="s">
-        <v>112</v>
+        <v>123</v>
       </c>
       <c r="E2" t="s">
-        <v>113</v>
+        <v>124</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B3" t="s">
-        <v>114</v>
+        <v>125</v>
       </c>
       <c r="C3">
         <v>120</v>
       </c>
       <c r="D3" t="s">
-        <v>115</v>
+        <v>126</v>
       </c>
       <c r="E3" t="s">
-        <v>116</v>
+        <v>127</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25"/>
@@ -1466,38 +1504,38 @@
   <sheetData>
     <row r="1" ht="30" customHeight="1" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>117</v>
+        <v>128</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>118</v>
+        <v>129</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>119</v>
+        <v>130</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B2">
         <v>10</v>
       </c>
       <c r="C2" t="s">
-        <v>120</v>
+        <v>131</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B3">
         <v>15</v>
       </c>
       <c r="C3" t="s">
-        <v>121</v>
+        <v>132</v>
       </c>
       <c r="D3">
         <v>3</v>
@@ -1505,13 +1543,13 @@
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B4">
         <v>7</v>
       </c>
       <c r="C4" t="s">
-        <v>122</v>
+        <v>133</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25"/>
@@ -1746,24 +1784,24 @@
   <sheetData>
     <row r="1" ht="30" customHeight="1" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>123</v>
+        <v>134</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>124</v>
+        <v>135</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B2">
         <v>3</v>
       </c>
       <c r="C2" t="s">
-        <v>125</v>
+        <v>136</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25"/>
@@ -2002,56 +2040,56 @@
   <sheetData>
     <row r="1" ht="30" customHeight="1" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>126</v>
+        <v>137</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>127</v>
+        <v>138</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B2" t="s">
-        <v>128</v>
+        <v>139</v>
       </c>
       <c r="C2" t="s">
-        <v>129</v>
+        <v>140</v>
       </c>
       <c r="D2" t="s">
-        <v>130</v>
+        <v>141</v>
       </c>
       <c r="E2" t="s">
-        <v>131</v>
+        <v>142</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B3" t="s">
-        <v>132</v>
+        <v>143</v>
       </c>
       <c r="C3" t="s">
-        <v>133</v>
+        <v>144</v>
       </c>
       <c r="D3" t="s">
-        <v>134</v>
+        <v>145</v>
       </c>
       <c r="E3" t="s">
-        <v>135</v>
+        <v>146</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -2286,7 +2324,7 @@
   <sheetPr>
     <tabColor rgb="FFFFD400"/>
   </sheetPr>
-  <dimension ref="A1:G200"/>
+  <dimension ref="A1:H200"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
@@ -2294,384 +2332,388 @@
     <col min="4" max="4" width="50" customWidth="1"/>
     <col min="5" max="5" width="10" customWidth="1"/>
     <col min="6" max="6" width="12" customWidth="1"/>
-    <col min="7" max="7" width="22" customWidth="1"/>
+    <col min="7" max="7" width="11" customWidth="1"/>
+    <col min="8" max="8" width="22" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" ht="30" customHeight="1" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+        <v>20</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D2" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="E2">
         <v>1</v>
       </c>
       <c r="F2" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D3" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E3">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C4" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D4" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="E4">
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C5" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D5" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E5">
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C6" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D6" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="E6" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C7" t="s">
+        <v>40</v>
+      </c>
+      <c r="D7" t="s">
+        <v>41</v>
+      </c>
+      <c r="E7" t="s">
         <v>38</v>
       </c>
-      <c r="D7" t="s">
-        <v>39</v>
-      </c>
-      <c r="E7" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C8" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D8" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E8" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C9" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D9" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="E9">
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C10" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="D10" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="E10">
         <v>3</v>
       </c>
       <c r="F10" t="s">
-        <v>48</v>
-      </c>
-      <c r="G10" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="11" spans="3:7" x14ac:dyDescent="0.25"/>
-    <row r="12" spans="3:7" x14ac:dyDescent="0.25"/>
-    <row r="13" spans="3:7" x14ac:dyDescent="0.25"/>
-    <row r="14" spans="3:7" x14ac:dyDescent="0.25"/>
-    <row r="15" spans="3:7" x14ac:dyDescent="0.25"/>
-    <row r="16" spans="3:7" x14ac:dyDescent="0.25"/>
-    <row r="17" spans="3:7" x14ac:dyDescent="0.25"/>
-    <row r="18" spans="3:7" x14ac:dyDescent="0.25"/>
-    <row r="19" spans="3:7" x14ac:dyDescent="0.25"/>
-    <row r="20" spans="3:7" x14ac:dyDescent="0.25"/>
-    <row r="21" spans="3:7" x14ac:dyDescent="0.25"/>
-    <row r="22" spans="3:7" x14ac:dyDescent="0.25"/>
-    <row r="23" spans="3:7" x14ac:dyDescent="0.25"/>
-    <row r="24" spans="3:7" x14ac:dyDescent="0.25"/>
-    <row r="25" spans="3:7" x14ac:dyDescent="0.25"/>
-    <row r="26" spans="3:7" x14ac:dyDescent="0.25"/>
-    <row r="27" spans="3:7" x14ac:dyDescent="0.25"/>
-    <row r="28" spans="3:7" x14ac:dyDescent="0.25"/>
-    <row r="29" spans="3:7" x14ac:dyDescent="0.25"/>
-    <row r="30" spans="3:7" x14ac:dyDescent="0.25"/>
-    <row r="31" spans="3:7" x14ac:dyDescent="0.25"/>
-    <row r="32" spans="3:7" x14ac:dyDescent="0.25"/>
-    <row r="33" spans="3:7" x14ac:dyDescent="0.25"/>
-    <row r="34" spans="3:7" x14ac:dyDescent="0.25"/>
-    <row r="35" spans="3:7" x14ac:dyDescent="0.25"/>
-    <row r="36" spans="3:7" x14ac:dyDescent="0.25"/>
-    <row r="37" spans="3:7" x14ac:dyDescent="0.25"/>
-    <row r="38" spans="3:7" x14ac:dyDescent="0.25"/>
-    <row r="39" spans="3:7" x14ac:dyDescent="0.25"/>
-    <row r="40" spans="3:7" x14ac:dyDescent="0.25"/>
-    <row r="41" spans="3:7" x14ac:dyDescent="0.25"/>
-    <row r="42" spans="3:7" x14ac:dyDescent="0.25"/>
-    <row r="43" spans="3:7" x14ac:dyDescent="0.25"/>
-    <row r="44" spans="3:7" x14ac:dyDescent="0.25"/>
-    <row r="45" spans="3:7" x14ac:dyDescent="0.25"/>
-    <row r="46" spans="3:7" x14ac:dyDescent="0.25"/>
-    <row r="47" spans="3:7" x14ac:dyDescent="0.25"/>
-    <row r="48" spans="3:7" x14ac:dyDescent="0.25"/>
-    <row r="49" spans="3:7" x14ac:dyDescent="0.25"/>
-    <row r="50" spans="3:7" x14ac:dyDescent="0.25"/>
-    <row r="51" spans="3:7" x14ac:dyDescent="0.25"/>
-    <row r="52" spans="3:7" x14ac:dyDescent="0.25"/>
-    <row r="53" spans="3:7" x14ac:dyDescent="0.25"/>
-    <row r="54" spans="3:7" x14ac:dyDescent="0.25"/>
-    <row r="55" spans="3:7" x14ac:dyDescent="0.25"/>
-    <row r="56" spans="3:7" x14ac:dyDescent="0.25"/>
-    <row r="57" spans="3:7" x14ac:dyDescent="0.25"/>
-    <row r="58" spans="3:7" x14ac:dyDescent="0.25"/>
-    <row r="59" spans="3:7" x14ac:dyDescent="0.25"/>
-    <row r="60" spans="3:7" x14ac:dyDescent="0.25"/>
-    <row r="61" spans="3:7" x14ac:dyDescent="0.25"/>
-    <row r="62" spans="3:7" x14ac:dyDescent="0.25"/>
-    <row r="63" spans="3:7" x14ac:dyDescent="0.25"/>
-    <row r="64" spans="3:7" x14ac:dyDescent="0.25"/>
-    <row r="65" spans="3:7" x14ac:dyDescent="0.25"/>
-    <row r="66" spans="3:7" x14ac:dyDescent="0.25"/>
-    <row r="67" spans="3:7" x14ac:dyDescent="0.25"/>
-    <row r="68" spans="3:7" x14ac:dyDescent="0.25"/>
-    <row r="69" spans="3:7" x14ac:dyDescent="0.25"/>
-    <row r="70" spans="3:7" x14ac:dyDescent="0.25"/>
-    <row r="71" spans="3:7" x14ac:dyDescent="0.25"/>
-    <row r="72" spans="3:7" x14ac:dyDescent="0.25"/>
-    <row r="73" spans="3:7" x14ac:dyDescent="0.25"/>
-    <row r="74" spans="3:7" x14ac:dyDescent="0.25"/>
-    <row r="75" spans="3:7" x14ac:dyDescent="0.25"/>
-    <row r="76" spans="3:7" x14ac:dyDescent="0.25"/>
-    <row r="77" spans="3:7" x14ac:dyDescent="0.25"/>
-    <row r="78" spans="3:7" x14ac:dyDescent="0.25"/>
-    <row r="79" spans="3:7" x14ac:dyDescent="0.25"/>
-    <row r="80" spans="3:7" x14ac:dyDescent="0.25"/>
-    <row r="81" spans="3:7" x14ac:dyDescent="0.25"/>
-    <row r="82" spans="3:7" x14ac:dyDescent="0.25"/>
-    <row r="83" spans="3:7" x14ac:dyDescent="0.25"/>
-    <row r="84" spans="3:7" x14ac:dyDescent="0.25"/>
-    <row r="85" spans="3:7" x14ac:dyDescent="0.25"/>
-    <row r="86" spans="3:7" x14ac:dyDescent="0.25"/>
-    <row r="87" spans="3:7" x14ac:dyDescent="0.25"/>
-    <row r="88" spans="3:7" x14ac:dyDescent="0.25"/>
-    <row r="89" spans="3:7" x14ac:dyDescent="0.25"/>
-    <row r="90" spans="3:7" x14ac:dyDescent="0.25"/>
-    <row r="91" spans="3:7" x14ac:dyDescent="0.25"/>
-    <row r="92" spans="3:7" x14ac:dyDescent="0.25"/>
-    <row r="93" spans="3:7" x14ac:dyDescent="0.25"/>
-    <row r="94" spans="3:7" x14ac:dyDescent="0.25"/>
-    <row r="95" spans="3:7" x14ac:dyDescent="0.25"/>
-    <row r="96" spans="3:7" x14ac:dyDescent="0.25"/>
-    <row r="97" spans="3:7" x14ac:dyDescent="0.25"/>
-    <row r="98" spans="3:7" x14ac:dyDescent="0.25"/>
-    <row r="99" spans="3:7" x14ac:dyDescent="0.25"/>
-    <row r="100" spans="3:7" x14ac:dyDescent="0.25"/>
-    <row r="101" spans="3:7" x14ac:dyDescent="0.25"/>
-    <row r="102" spans="3:7" x14ac:dyDescent="0.25"/>
-    <row r="103" spans="3:7" x14ac:dyDescent="0.25"/>
-    <row r="104" spans="3:7" x14ac:dyDescent="0.25"/>
-    <row r="105" spans="3:7" x14ac:dyDescent="0.25"/>
-    <row r="106" spans="3:7" x14ac:dyDescent="0.25"/>
-    <row r="107" spans="3:7" x14ac:dyDescent="0.25"/>
-    <row r="108" spans="3:7" x14ac:dyDescent="0.25"/>
-    <row r="109" spans="3:7" x14ac:dyDescent="0.25"/>
-    <row r="110" spans="3:7" x14ac:dyDescent="0.25"/>
-    <row r="111" spans="3:7" x14ac:dyDescent="0.25"/>
-    <row r="112" spans="3:7" x14ac:dyDescent="0.25"/>
-    <row r="113" spans="3:7" x14ac:dyDescent="0.25"/>
-    <row r="114" spans="3:7" x14ac:dyDescent="0.25"/>
-    <row r="115" spans="3:7" x14ac:dyDescent="0.25"/>
-    <row r="116" spans="3:7" x14ac:dyDescent="0.25"/>
-    <row r="117" spans="3:7" x14ac:dyDescent="0.25"/>
-    <row r="118" spans="3:7" x14ac:dyDescent="0.25"/>
-    <row r="119" spans="3:7" x14ac:dyDescent="0.25"/>
-    <row r="120" spans="3:7" x14ac:dyDescent="0.25"/>
-    <row r="121" spans="3:7" x14ac:dyDescent="0.25"/>
-    <row r="122" spans="3:7" x14ac:dyDescent="0.25"/>
-    <row r="123" spans="3:7" x14ac:dyDescent="0.25"/>
-    <row r="124" spans="3:7" x14ac:dyDescent="0.25"/>
-    <row r="125" spans="3:7" x14ac:dyDescent="0.25"/>
-    <row r="126" spans="3:7" x14ac:dyDescent="0.25"/>
-    <row r="127" spans="3:7" x14ac:dyDescent="0.25"/>
-    <row r="128" spans="3:7" x14ac:dyDescent="0.25"/>
-    <row r="129" spans="3:7" x14ac:dyDescent="0.25"/>
-    <row r="130" spans="3:7" x14ac:dyDescent="0.25"/>
-    <row r="131" spans="3:7" x14ac:dyDescent="0.25"/>
-    <row r="132" spans="3:7" x14ac:dyDescent="0.25"/>
-    <row r="133" spans="3:7" x14ac:dyDescent="0.25"/>
-    <row r="134" spans="3:7" x14ac:dyDescent="0.25"/>
-    <row r="135" spans="3:7" x14ac:dyDescent="0.25"/>
-    <row r="136" spans="3:7" x14ac:dyDescent="0.25"/>
-    <row r="137" spans="3:7" x14ac:dyDescent="0.25"/>
-    <row r="138" spans="3:7" x14ac:dyDescent="0.25"/>
-    <row r="139" spans="3:7" x14ac:dyDescent="0.25"/>
-    <row r="140" spans="3:7" x14ac:dyDescent="0.25"/>
-    <row r="141" spans="3:7" x14ac:dyDescent="0.25"/>
-    <row r="142" spans="3:7" x14ac:dyDescent="0.25"/>
-    <row r="143" spans="3:7" x14ac:dyDescent="0.25"/>
-    <row r="144" spans="3:7" x14ac:dyDescent="0.25"/>
-    <row r="145" spans="3:7" x14ac:dyDescent="0.25"/>
-    <row r="146" spans="3:7" x14ac:dyDescent="0.25"/>
-    <row r="147" spans="3:7" x14ac:dyDescent="0.25"/>
-    <row r="148" spans="3:7" x14ac:dyDescent="0.25"/>
-    <row r="149" spans="3:7" x14ac:dyDescent="0.25"/>
-    <row r="150" spans="3:7" x14ac:dyDescent="0.25"/>
-    <row r="151" spans="3:7" x14ac:dyDescent="0.25"/>
-    <row r="152" spans="3:7" x14ac:dyDescent="0.25"/>
-    <row r="153" spans="3:7" x14ac:dyDescent="0.25"/>
-    <row r="154" spans="3:7" x14ac:dyDescent="0.25"/>
-    <row r="155" spans="3:7" x14ac:dyDescent="0.25"/>
-    <row r="156" spans="3:7" x14ac:dyDescent="0.25"/>
-    <row r="157" spans="3:7" x14ac:dyDescent="0.25"/>
-    <row r="158" spans="3:7" x14ac:dyDescent="0.25"/>
-    <row r="159" spans="3:7" x14ac:dyDescent="0.25"/>
-    <row r="160" spans="3:7" x14ac:dyDescent="0.25"/>
-    <row r="161" spans="3:7" x14ac:dyDescent="0.25"/>
-    <row r="162" spans="3:7" x14ac:dyDescent="0.25"/>
-    <row r="163" spans="3:7" x14ac:dyDescent="0.25"/>
-    <row r="164" spans="3:7" x14ac:dyDescent="0.25"/>
-    <row r="165" spans="3:7" x14ac:dyDescent="0.25"/>
-    <row r="166" spans="3:7" x14ac:dyDescent="0.25"/>
-    <row r="167" spans="3:7" x14ac:dyDescent="0.25"/>
-    <row r="168" spans="3:7" x14ac:dyDescent="0.25"/>
-    <row r="169" spans="3:7" x14ac:dyDescent="0.25"/>
-    <row r="170" spans="3:7" x14ac:dyDescent="0.25"/>
-    <row r="171" spans="3:7" x14ac:dyDescent="0.25"/>
-    <row r="172" spans="3:7" x14ac:dyDescent="0.25"/>
-    <row r="173" spans="3:7" x14ac:dyDescent="0.25"/>
-    <row r="174" spans="3:7" x14ac:dyDescent="0.25"/>
-    <row r="175" spans="3:7" x14ac:dyDescent="0.25"/>
-    <row r="176" spans="3:7" x14ac:dyDescent="0.25"/>
-    <row r="177" spans="3:7" x14ac:dyDescent="0.25"/>
-    <row r="178" spans="3:7" x14ac:dyDescent="0.25"/>
-    <row r="179" spans="3:7" x14ac:dyDescent="0.25"/>
-    <row r="180" spans="3:7" x14ac:dyDescent="0.25"/>
-    <row r="181" spans="3:7" x14ac:dyDescent="0.25"/>
-    <row r="182" spans="3:7" x14ac:dyDescent="0.25"/>
-    <row r="183" spans="3:7" x14ac:dyDescent="0.25"/>
-    <row r="184" spans="3:7" x14ac:dyDescent="0.25"/>
-    <row r="185" spans="3:7" x14ac:dyDescent="0.25"/>
-    <row r="186" spans="3:7" x14ac:dyDescent="0.25"/>
-    <row r="187" spans="3:7" x14ac:dyDescent="0.25"/>
-    <row r="188" spans="3:7" x14ac:dyDescent="0.25"/>
-    <row r="189" spans="3:7" x14ac:dyDescent="0.25"/>
-    <row r="190" spans="3:7" x14ac:dyDescent="0.25"/>
-    <row r="191" spans="3:7" x14ac:dyDescent="0.25"/>
-    <row r="192" spans="3:7" x14ac:dyDescent="0.25"/>
-    <row r="193" spans="3:7" x14ac:dyDescent="0.25"/>
-    <row r="194" spans="3:7" x14ac:dyDescent="0.25"/>
-    <row r="195" spans="3:7" x14ac:dyDescent="0.25"/>
-    <row r="196" spans="3:7" x14ac:dyDescent="0.25"/>
-    <row r="197" spans="3:7" x14ac:dyDescent="0.25"/>
-    <row r="198" spans="3:7" x14ac:dyDescent="0.25"/>
-    <row r="199" spans="3:7" x14ac:dyDescent="0.25"/>
-    <row r="200" spans="3:7" x14ac:dyDescent="0.25"/>
+        <v>50</v>
+      </c>
+      <c r="H10" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="11" spans="3:8" x14ac:dyDescent="0.25"/>
+    <row r="12" spans="3:8" x14ac:dyDescent="0.25"/>
+    <row r="13" spans="3:8" x14ac:dyDescent="0.25"/>
+    <row r="14" spans="3:8" x14ac:dyDescent="0.25"/>
+    <row r="15" spans="3:8" x14ac:dyDescent="0.25"/>
+    <row r="16" spans="3:8" x14ac:dyDescent="0.25"/>
+    <row r="17" spans="3:8" x14ac:dyDescent="0.25"/>
+    <row r="18" spans="3:8" x14ac:dyDescent="0.25"/>
+    <row r="19" spans="3:8" x14ac:dyDescent="0.25"/>
+    <row r="20" spans="3:8" x14ac:dyDescent="0.25"/>
+    <row r="21" spans="3:8" x14ac:dyDescent="0.25"/>
+    <row r="22" spans="3:8" x14ac:dyDescent="0.25"/>
+    <row r="23" spans="3:8" x14ac:dyDescent="0.25"/>
+    <row r="24" spans="3:8" x14ac:dyDescent="0.25"/>
+    <row r="25" spans="3:8" x14ac:dyDescent="0.25"/>
+    <row r="26" spans="3:8" x14ac:dyDescent="0.25"/>
+    <row r="27" spans="3:8" x14ac:dyDescent="0.25"/>
+    <row r="28" spans="3:8" x14ac:dyDescent="0.25"/>
+    <row r="29" spans="3:8" x14ac:dyDescent="0.25"/>
+    <row r="30" spans="3:8" x14ac:dyDescent="0.25"/>
+    <row r="31" spans="3:8" x14ac:dyDescent="0.25"/>
+    <row r="32" spans="3:8" x14ac:dyDescent="0.25"/>
+    <row r="33" spans="3:8" x14ac:dyDescent="0.25"/>
+    <row r="34" spans="3:8" x14ac:dyDescent="0.25"/>
+    <row r="35" spans="3:8" x14ac:dyDescent="0.25"/>
+    <row r="36" spans="3:8" x14ac:dyDescent="0.25"/>
+    <row r="37" spans="3:8" x14ac:dyDescent="0.25"/>
+    <row r="38" spans="3:8" x14ac:dyDescent="0.25"/>
+    <row r="39" spans="3:8" x14ac:dyDescent="0.25"/>
+    <row r="40" spans="3:8" x14ac:dyDescent="0.25"/>
+    <row r="41" spans="3:8" x14ac:dyDescent="0.25"/>
+    <row r="42" spans="3:8" x14ac:dyDescent="0.25"/>
+    <row r="43" spans="3:8" x14ac:dyDescent="0.25"/>
+    <row r="44" spans="3:8" x14ac:dyDescent="0.25"/>
+    <row r="45" spans="3:8" x14ac:dyDescent="0.25"/>
+    <row r="46" spans="3:8" x14ac:dyDescent="0.25"/>
+    <row r="47" spans="3:8" x14ac:dyDescent="0.25"/>
+    <row r="48" spans="3:8" x14ac:dyDescent="0.25"/>
+    <row r="49" spans="3:8" x14ac:dyDescent="0.25"/>
+    <row r="50" spans="3:8" x14ac:dyDescent="0.25"/>
+    <row r="51" spans="3:8" x14ac:dyDescent="0.25"/>
+    <row r="52" spans="3:8" x14ac:dyDescent="0.25"/>
+    <row r="53" spans="3:8" x14ac:dyDescent="0.25"/>
+    <row r="54" spans="3:8" x14ac:dyDescent="0.25"/>
+    <row r="55" spans="3:8" x14ac:dyDescent="0.25"/>
+    <row r="56" spans="3:8" x14ac:dyDescent="0.25"/>
+    <row r="57" spans="3:8" x14ac:dyDescent="0.25"/>
+    <row r="58" spans="3:8" x14ac:dyDescent="0.25"/>
+    <row r="59" spans="3:8" x14ac:dyDescent="0.25"/>
+    <row r="60" spans="3:8" x14ac:dyDescent="0.25"/>
+    <row r="61" spans="3:8" x14ac:dyDescent="0.25"/>
+    <row r="62" spans="3:8" x14ac:dyDescent="0.25"/>
+    <row r="63" spans="3:8" x14ac:dyDescent="0.25"/>
+    <row r="64" spans="3:8" x14ac:dyDescent="0.25"/>
+    <row r="65" spans="3:8" x14ac:dyDescent="0.25"/>
+    <row r="66" spans="3:8" x14ac:dyDescent="0.25"/>
+    <row r="67" spans="3:8" x14ac:dyDescent="0.25"/>
+    <row r="68" spans="3:8" x14ac:dyDescent="0.25"/>
+    <row r="69" spans="3:8" x14ac:dyDescent="0.25"/>
+    <row r="70" spans="3:8" x14ac:dyDescent="0.25"/>
+    <row r="71" spans="3:8" x14ac:dyDescent="0.25"/>
+    <row r="72" spans="3:8" x14ac:dyDescent="0.25"/>
+    <row r="73" spans="3:8" x14ac:dyDescent="0.25"/>
+    <row r="74" spans="3:8" x14ac:dyDescent="0.25"/>
+    <row r="75" spans="3:8" x14ac:dyDescent="0.25"/>
+    <row r="76" spans="3:8" x14ac:dyDescent="0.25"/>
+    <row r="77" spans="3:8" x14ac:dyDescent="0.25"/>
+    <row r="78" spans="3:8" x14ac:dyDescent="0.25"/>
+    <row r="79" spans="3:8" x14ac:dyDescent="0.25"/>
+    <row r="80" spans="3:8" x14ac:dyDescent="0.25"/>
+    <row r="81" spans="3:8" x14ac:dyDescent="0.25"/>
+    <row r="82" spans="3:8" x14ac:dyDescent="0.25"/>
+    <row r="83" spans="3:8" x14ac:dyDescent="0.25"/>
+    <row r="84" spans="3:8" x14ac:dyDescent="0.25"/>
+    <row r="85" spans="3:8" x14ac:dyDescent="0.25"/>
+    <row r="86" spans="3:8" x14ac:dyDescent="0.25"/>
+    <row r="87" spans="3:8" x14ac:dyDescent="0.25"/>
+    <row r="88" spans="3:8" x14ac:dyDescent="0.25"/>
+    <row r="89" spans="3:8" x14ac:dyDescent="0.25"/>
+    <row r="90" spans="3:8" x14ac:dyDescent="0.25"/>
+    <row r="91" spans="3:8" x14ac:dyDescent="0.25"/>
+    <row r="92" spans="3:8" x14ac:dyDescent="0.25"/>
+    <row r="93" spans="3:8" x14ac:dyDescent="0.25"/>
+    <row r="94" spans="3:8" x14ac:dyDescent="0.25"/>
+    <row r="95" spans="3:8" x14ac:dyDescent="0.25"/>
+    <row r="96" spans="3:8" x14ac:dyDescent="0.25"/>
+    <row r="97" spans="3:8" x14ac:dyDescent="0.25"/>
+    <row r="98" spans="3:8" x14ac:dyDescent="0.25"/>
+    <row r="99" spans="3:8" x14ac:dyDescent="0.25"/>
+    <row r="100" spans="3:8" x14ac:dyDescent="0.25"/>
+    <row r="101" spans="3:8" x14ac:dyDescent="0.25"/>
+    <row r="102" spans="3:8" x14ac:dyDescent="0.25"/>
+    <row r="103" spans="3:8" x14ac:dyDescent="0.25"/>
+    <row r="104" spans="3:8" x14ac:dyDescent="0.25"/>
+    <row r="105" spans="3:8" x14ac:dyDescent="0.25"/>
+    <row r="106" spans="3:8" x14ac:dyDescent="0.25"/>
+    <row r="107" spans="3:8" x14ac:dyDescent="0.25"/>
+    <row r="108" spans="3:8" x14ac:dyDescent="0.25"/>
+    <row r="109" spans="3:8" x14ac:dyDescent="0.25"/>
+    <row r="110" spans="3:8" x14ac:dyDescent="0.25"/>
+    <row r="111" spans="3:8" x14ac:dyDescent="0.25"/>
+    <row r="112" spans="3:8" x14ac:dyDescent="0.25"/>
+    <row r="113" spans="3:8" x14ac:dyDescent="0.25"/>
+    <row r="114" spans="3:8" x14ac:dyDescent="0.25"/>
+    <row r="115" spans="3:8" x14ac:dyDescent="0.25"/>
+    <row r="116" spans="3:8" x14ac:dyDescent="0.25"/>
+    <row r="117" spans="3:8" x14ac:dyDescent="0.25"/>
+    <row r="118" spans="3:8" x14ac:dyDescent="0.25"/>
+    <row r="119" spans="3:8" x14ac:dyDescent="0.25"/>
+    <row r="120" spans="3:8" x14ac:dyDescent="0.25"/>
+    <row r="121" spans="3:8" x14ac:dyDescent="0.25"/>
+    <row r="122" spans="3:8" x14ac:dyDescent="0.25"/>
+    <row r="123" spans="3:8" x14ac:dyDescent="0.25"/>
+    <row r="124" spans="3:8" x14ac:dyDescent="0.25"/>
+    <row r="125" spans="3:8" x14ac:dyDescent="0.25"/>
+    <row r="126" spans="3:8" x14ac:dyDescent="0.25"/>
+    <row r="127" spans="3:8" x14ac:dyDescent="0.25"/>
+    <row r="128" spans="3:8" x14ac:dyDescent="0.25"/>
+    <row r="129" spans="3:8" x14ac:dyDescent="0.25"/>
+    <row r="130" spans="3:8" x14ac:dyDescent="0.25"/>
+    <row r="131" spans="3:8" x14ac:dyDescent="0.25"/>
+    <row r="132" spans="3:8" x14ac:dyDescent="0.25"/>
+    <row r="133" spans="3:8" x14ac:dyDescent="0.25"/>
+    <row r="134" spans="3:8" x14ac:dyDescent="0.25"/>
+    <row r="135" spans="3:8" x14ac:dyDescent="0.25"/>
+    <row r="136" spans="3:8" x14ac:dyDescent="0.25"/>
+    <row r="137" spans="3:8" x14ac:dyDescent="0.25"/>
+    <row r="138" spans="3:8" x14ac:dyDescent="0.25"/>
+    <row r="139" spans="3:8" x14ac:dyDescent="0.25"/>
+    <row r="140" spans="3:8" x14ac:dyDescent="0.25"/>
+    <row r="141" spans="3:8" x14ac:dyDescent="0.25"/>
+    <row r="142" spans="3:8" x14ac:dyDescent="0.25"/>
+    <row r="143" spans="3:8" x14ac:dyDescent="0.25"/>
+    <row r="144" spans="3:8" x14ac:dyDescent="0.25"/>
+    <row r="145" spans="3:8" x14ac:dyDescent="0.25"/>
+    <row r="146" spans="3:8" x14ac:dyDescent="0.25"/>
+    <row r="147" spans="3:8" x14ac:dyDescent="0.25"/>
+    <row r="148" spans="3:8" x14ac:dyDescent="0.25"/>
+    <row r="149" spans="3:8" x14ac:dyDescent="0.25"/>
+    <row r="150" spans="3:8" x14ac:dyDescent="0.25"/>
+    <row r="151" spans="3:8" x14ac:dyDescent="0.25"/>
+    <row r="152" spans="3:8" x14ac:dyDescent="0.25"/>
+    <row r="153" spans="3:8" x14ac:dyDescent="0.25"/>
+    <row r="154" spans="3:8" x14ac:dyDescent="0.25"/>
+    <row r="155" spans="3:8" x14ac:dyDescent="0.25"/>
+    <row r="156" spans="3:8" x14ac:dyDescent="0.25"/>
+    <row r="157" spans="3:8" x14ac:dyDescent="0.25"/>
+    <row r="158" spans="3:8" x14ac:dyDescent="0.25"/>
+    <row r="159" spans="3:8" x14ac:dyDescent="0.25"/>
+    <row r="160" spans="3:8" x14ac:dyDescent="0.25"/>
+    <row r="161" spans="3:8" x14ac:dyDescent="0.25"/>
+    <row r="162" spans="3:8" x14ac:dyDescent="0.25"/>
+    <row r="163" spans="3:8" x14ac:dyDescent="0.25"/>
+    <row r="164" spans="3:8" x14ac:dyDescent="0.25"/>
+    <row r="165" spans="3:8" x14ac:dyDescent="0.25"/>
+    <row r="166" spans="3:8" x14ac:dyDescent="0.25"/>
+    <row r="167" spans="3:8" x14ac:dyDescent="0.25"/>
+    <row r="168" spans="3:8" x14ac:dyDescent="0.25"/>
+    <row r="169" spans="3:8" x14ac:dyDescent="0.25"/>
+    <row r="170" spans="3:8" x14ac:dyDescent="0.25"/>
+    <row r="171" spans="3:8" x14ac:dyDescent="0.25"/>
+    <row r="172" spans="3:8" x14ac:dyDescent="0.25"/>
+    <row r="173" spans="3:8" x14ac:dyDescent="0.25"/>
+    <row r="174" spans="3:8" x14ac:dyDescent="0.25"/>
+    <row r="175" spans="3:8" x14ac:dyDescent="0.25"/>
+    <row r="176" spans="3:8" x14ac:dyDescent="0.25"/>
+    <row r="177" spans="3:8" x14ac:dyDescent="0.25"/>
+    <row r="178" spans="3:8" x14ac:dyDescent="0.25"/>
+    <row r="179" spans="3:8" x14ac:dyDescent="0.25"/>
+    <row r="180" spans="3:8" x14ac:dyDescent="0.25"/>
+    <row r="181" spans="3:8" x14ac:dyDescent="0.25"/>
+    <row r="182" spans="3:8" x14ac:dyDescent="0.25"/>
+    <row r="183" spans="3:8" x14ac:dyDescent="0.25"/>
+    <row r="184" spans="3:8" x14ac:dyDescent="0.25"/>
+    <row r="185" spans="3:8" x14ac:dyDescent="0.25"/>
+    <row r="186" spans="3:8" x14ac:dyDescent="0.25"/>
+    <row r="187" spans="3:8" x14ac:dyDescent="0.25"/>
+    <row r="188" spans="3:8" x14ac:dyDescent="0.25"/>
+    <row r="189" spans="3:8" x14ac:dyDescent="0.25"/>
+    <row r="190" spans="3:8" x14ac:dyDescent="0.25"/>
+    <row r="191" spans="3:8" x14ac:dyDescent="0.25"/>
+    <row r="192" spans="3:8" x14ac:dyDescent="0.25"/>
+    <row r="193" spans="3:8" x14ac:dyDescent="0.25"/>
+    <row r="194" spans="3:8" x14ac:dyDescent="0.25"/>
+    <row r="195" spans="3:8" x14ac:dyDescent="0.25"/>
+    <row r="196" spans="3:8" x14ac:dyDescent="0.25"/>
+    <row r="197" spans="3:8" x14ac:dyDescent="0.25"/>
+    <row r="198" spans="3:8" x14ac:dyDescent="0.25"/>
+    <row r="199" spans="3:8" x14ac:dyDescent="0.25"/>
+    <row r="200" spans="3:8" x14ac:dyDescent="0.25"/>
   </sheetData>
   <dataValidations count="6">
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="warning" errorTitle="Valor no previsto" error="Elige un valor de la lista." sqref="C10:C200">
@@ -2680,17 +2722,17 @@
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="warning" errorTitle="Valor no previsto" error="Elige un valor de la lista." sqref="C2:C200">
       <formula1>"Pulsador,Test,Verdad o mentira,Dos verdades y una mentira,Votación,Estimación,Parar el contador,Duelo de reflejos,Libre"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="warning" errorTitle="Valor no previsto" error="Elige un valor de la lista." sqref="F10:F200">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="warning" errorTitle="Valor no previsto" error="Elige un valor de la lista." sqref="F10:G200">
       <formula1>"Sí,No"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="warning" errorTitle="Valor no previsto" error="Elige un valor de la lista." sqref="F2:F200">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="warning" errorTitle="Valor no previsto" error="Elige un valor de la lista." sqref="F2:G200">
       <formula1>"Sí,No"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="warning" errorTitle="Valor no previsto" error="Elige un valor de la lista." sqref="G10:G200">
-      <formula1>"Noche de luna,Cementerio,Bosque encantado,Huerto de calabazas,Laboratorio,Mansión encantada,Telaraña,Aquelarre,Cripta helada,Tormenta"</formula1>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="warning" errorTitle="Valor no previsto" error="Elige un valor de la lista." sqref="H10:H200">
+      <formula1>"Noche de luna,Cementerio,Bosque encantado,Huerto de calabazas,Laboratorio,Mansión encantada,Telaraña,Aquelarre,Cripta helada,Tormenta,Plató millonario"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="warning" errorTitle="Valor no previsto" error="Elige un valor de la lista." sqref="G2:G200">
-      <formula1>"Noche de luna,Cementerio,Bosque encantado,Huerto de calabazas,Laboratorio,Mansión encantada,Telaraña,Aquelarre,Cripta helada,Tormenta"</formula1>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="warning" errorTitle="Valor no previsto" error="Elige un valor de la lista." sqref="H2:H200">
+      <formula1>"Noche de luna,Cementerio,Bosque encantado,Huerto de calabazas,Laboratorio,Mansión encantada,Telaraña,Aquelarre,Cripta helada,Tormenta,Plató millonario"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2713,26 +2755,26 @@
   <sheetData>
     <row r="1" ht="30" customHeight="1" spans="1:2" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B3" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
     <row r="4" spans="2:2" x14ac:dyDescent="0.25"/>
@@ -2961,23 +3003,23 @@
   <sheetData>
     <row r="1" ht="30" customHeight="1" spans="1:2" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B2" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="B3">
         <v>1</v>
@@ -2985,7 +3027,7 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B4">
         <v>1</v>
@@ -2993,7 +3035,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="B5">
         <v>1</v>
@@ -3001,7 +3043,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="B6">
         <v>1</v>
@@ -3009,7 +3051,7 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -3017,15 +3059,15 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="B8" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="B9">
         <v>20</v>
@@ -3054,64 +3096,64 @@
   <sheetData>
     <row r="1" ht="30" customHeight="1" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B2" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="D2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B3" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C3" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D3" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B4" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C4" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="D4" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="E4" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25"/>
@@ -3336,71 +3378,68 @@
   <sheetPr>
     <tabColor rgb="FF2E7D32"/>
   </sheetPr>
-  <dimension ref="A1:I200"/>
+  <dimension ref="A1:H200"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="24" customWidth="1"/>
     <col min="2" max="2" width="50" customWidth="1"/>
     <col min="3" max="6" width="22" customWidth="1"/>
-    <col min="7" max="8" width="10" customWidth="1"/>
-    <col min="9" max="9" width="40" customWidth="1"/>
+    <col min="7" max="7" width="10" customWidth="1"/>
+    <col min="8" max="8" width="40" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" ht="30" customHeight="1" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="F1" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B2" t="s">
+        <v>86</v>
+      </c>
+      <c r="C2" t="s">
+        <v>87</v>
+      </c>
+      <c r="D2" t="s">
+        <v>88</v>
+      </c>
+      <c r="E2" t="s">
+        <v>89</v>
+      </c>
+      <c r="F2" t="s">
+        <v>76</v>
+      </c>
+      <c r="G2" t="s">
         <v>81</v>
       </c>
-      <c r="G1" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="H1" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="I1" s="3" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>24</v>
-      </c>
-      <c r="B2" t="s">
-        <v>85</v>
-      </c>
-      <c r="C2" t="s">
-        <v>86</v>
-      </c>
-      <c r="D2" t="s">
-        <v>87</v>
-      </c>
-      <c r="E2" t="s">
-        <v>88</v>
-      </c>
-      <c r="F2" t="s">
-        <v>89</v>
-      </c>
-      <c r="G2" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B3" t="s">
         <v>90</v>
@@ -3414,15 +3453,59 @@
       <c r="E3" t="s">
         <v>93</v>
       </c>
+      <c r="F3" t="s">
+        <v>94</v>
+      </c>
       <c r="G3" t="s">
-        <v>80</v>
-      </c>
-      <c r="H3">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25"/>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25"/>
+        <v>81</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>26</v>
+      </c>
+      <c r="B4" t="s">
+        <v>95</v>
+      </c>
+      <c r="C4" t="s">
+        <v>96</v>
+      </c>
+      <c r="D4" t="s">
+        <v>97</v>
+      </c>
+      <c r="E4" t="s">
+        <v>98</v>
+      </c>
+      <c r="F4" t="s">
+        <v>99</v>
+      </c>
+      <c r="G4" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>26</v>
+      </c>
+      <c r="B5" t="s">
+        <v>100</v>
+      </c>
+      <c r="C5" t="s">
+        <v>101</v>
+      </c>
+      <c r="D5" t="s">
+        <v>102</v>
+      </c>
+      <c r="E5" t="s">
+        <v>103</v>
+      </c>
+      <c r="F5" t="s">
+        <v>104</v>
+      </c>
+      <c r="G5" t="s">
+        <v>82</v>
+      </c>
+    </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25"/>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25"/>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25"/>
@@ -3654,35 +3737,35 @@
   <sheetData>
     <row r="1" ht="30" customHeight="1" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>94</v>
+        <v>105</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B2" t="s">
-        <v>95</v>
+        <v>106</v>
       </c>
       <c r="C2" t="s">
-        <v>96</v>
+        <v>107</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B3" t="s">
-        <v>97</v>
+        <v>108</v>
       </c>
       <c r="C3" t="s">
-        <v>98</v>
+        <v>109</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25"/>
@@ -3918,39 +4001,39 @@
   <sheetData>
     <row r="1" ht="30" customHeight="1" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>99</v>
+        <v>110</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>100</v>
+        <v>111</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>101</v>
+        <v>112</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>102</v>
+        <v>113</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>98</v>
+        <v>109</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B2" t="s">
-        <v>103</v>
+        <v>114</v>
       </c>
       <c r="C2" t="s">
-        <v>104</v>
+        <v>115</v>
       </c>
       <c r="D2" t="s">
-        <v>105</v>
+        <v>116</v>
       </c>
       <c r="E2" t="s">
-        <v>106</v>
+        <v>117</v>
       </c>
       <c r="F2">
         <v>2</v>
@@ -4189,26 +4272,26 @@
   <sheetData>
     <row r="1" ht="30" customHeight="1" spans="1:2" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B2" t="s">
-        <v>107</v>
+        <v>118</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B3" t="s">
-        <v>108</v>
+        <v>119</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25"/>

--- a/public/plantilla-concurso.xlsx
+++ b/public/plantilla-concurso.xlsx
@@ -227,6 +227,13 @@
     <comment ref="H1" authorId="0">
       <text>
         <r>
+          <t>Su música y sus puntos (columna Puntos de la pestaña Concurso: fácil, media, difícil, p. ej. 1,3,5). Vacía = por tercios.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="I1" authorId="0">
+      <text>
+        <r>
           <t>Opcional: dirección web de una imagen.</t>
         </r>
       </text>
@@ -277,7 +284,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="147">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="220" uniqueCount="162">
   <si>
     <t>CÓMO RELLENAR ESTA PLANTILLA</t>
   </si>
@@ -366,6 +373,9 @@
     <t>¿Quién quiere ser millonario? Uno cada vez; vuestro portavoz decide el orden.</t>
   </si>
   <si>
+    <t>1,3,5</t>
+  </si>
+  <si>
     <t>¿Verdad o mentira?</t>
   </si>
   <si>
@@ -534,6 +544,9 @@
     <t>Correcta</t>
   </si>
   <si>
+    <t>Dificultad</t>
+  </si>
+  <si>
     <t>Imagen</t>
   </si>
   <si>
@@ -549,6 +562,24 @@
     <t>Siete</t>
   </si>
   <si>
+    <t>Fácil</t>
+  </si>
+  <si>
+    <t>¿De qué color es el caballo blanco de Santiago?</t>
+  </si>
+  <si>
+    <t>Negro</t>
+  </si>
+  <si>
+    <t>Marrón</t>
+  </si>
+  <si>
+    <t>Blanco</t>
+  </si>
+  <si>
+    <t>Gris</t>
+  </si>
+  <si>
     <t>¿En qué año llegó el hombre a la Luna?</t>
   </si>
   <si>
@@ -564,6 +595,24 @@
     <t>1975</t>
   </si>
   <si>
+    <t>Media</t>
+  </si>
+  <si>
+    <t>¿Cuál es el planeta más grande?</t>
+  </si>
+  <si>
+    <t>Saturno</t>
+  </si>
+  <si>
+    <t>Neptuno</t>
+  </si>
+  <si>
+    <t>Júpiter</t>
+  </si>
+  <si>
+    <t>Urano</t>
+  </si>
+  <si>
     <t>¿Cuál es la capital de provincia española que está a más altura?</t>
   </si>
   <si>
@@ -579,19 +628,22 @@
     <t>Ávila</t>
   </si>
   <si>
-    <t>¿Cuál es el planeta más grande?</t>
-  </si>
-  <si>
-    <t>Saturno</t>
-  </si>
-  <si>
-    <t>Neptuno</t>
-  </si>
-  <si>
-    <t>Júpiter</t>
-  </si>
-  <si>
-    <t>Urano</t>
+    <t>Difícil</t>
+  </si>
+  <si>
+    <t>¿Qué elemento químico tiene el símbolo W?</t>
+  </si>
+  <si>
+    <t>Wolframio</t>
+  </si>
+  <si>
+    <t>Vanadio</t>
+  </si>
+  <si>
+    <t>Osmio</t>
+  </si>
+  <si>
+    <t>Wiconio</t>
   </si>
   <si>
     <t>Afirmación</t>
@@ -1225,50 +1277,50 @@
         <v>15</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>120</v>
+        <v>135</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>121</v>
+        <v>136</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B2" t="s">
-        <v>122</v>
+        <v>137</v>
       </c>
       <c r="C2">
         <v>910</v>
       </c>
       <c r="D2" t="s">
-        <v>123</v>
+        <v>138</v>
       </c>
       <c r="E2" t="s">
-        <v>124</v>
+        <v>139</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B3" t="s">
-        <v>125</v>
+        <v>140</v>
       </c>
       <c r="C3">
         <v>120</v>
       </c>
       <c r="D3" t="s">
-        <v>126</v>
+        <v>141</v>
       </c>
       <c r="E3" t="s">
-        <v>127</v>
+        <v>142</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25"/>
@@ -1507,35 +1559,35 @@
         <v>15</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>128</v>
+        <v>143</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>129</v>
+        <v>144</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>130</v>
+        <v>145</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B2">
         <v>10</v>
       </c>
       <c r="C2" t="s">
-        <v>131</v>
+        <v>146</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B3">
         <v>15</v>
       </c>
       <c r="C3" t="s">
-        <v>132</v>
+        <v>147</v>
       </c>
       <c r="D3">
         <v>3</v>
@@ -1543,13 +1595,13 @@
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B4">
         <v>7</v>
       </c>
       <c r="C4" t="s">
-        <v>133</v>
+        <v>148</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25"/>
@@ -1787,21 +1839,21 @@
         <v>15</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>134</v>
+        <v>149</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>135</v>
+        <v>150</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B2">
         <v>3</v>
       </c>
       <c r="C2" t="s">
-        <v>136</v>
+        <v>151</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25"/>
@@ -2043,16 +2095,16 @@
         <v>15</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>137</v>
+        <v>152</v>
       </c>
       <c r="C1" s="3" t="s">
         <v>17</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>138</v>
+        <v>153</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>135</v>
+        <v>150</v>
       </c>
       <c r="F1" s="3" t="s">
         <v>18</v>
@@ -2060,36 +2112,36 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B2" t="s">
-        <v>139</v>
+        <v>154</v>
       </c>
       <c r="C2" t="s">
-        <v>140</v>
+        <v>155</v>
       </c>
       <c r="D2" t="s">
-        <v>141</v>
+        <v>156</v>
       </c>
       <c r="E2" t="s">
-        <v>142</v>
+        <v>157</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B3" t="s">
-        <v>143</v>
+        <v>158</v>
       </c>
       <c r="C3" t="s">
-        <v>144</v>
+        <v>159</v>
       </c>
       <c r="D3" t="s">
-        <v>145</v>
+        <v>160</v>
       </c>
       <c r="E3" t="s">
-        <v>146</v>
+        <v>161</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -2395,8 +2447,8 @@
       <c r="D3" t="s">
         <v>28</v>
       </c>
-      <c r="E3">
-        <v>2</v>
+      <c r="E3" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
@@ -2404,13 +2456,13 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D4" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E4">
         <v>1</v>
@@ -2421,13 +2473,13 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C5" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D5" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E5">
         <v>1</v>
@@ -2438,16 +2490,16 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C6" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D6" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
@@ -2455,16 +2507,16 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
+        <v>40</v>
+      </c>
+      <c r="C7" t="s">
+        <v>41</v>
+      </c>
+      <c r="D7" t="s">
+        <v>42</v>
+      </c>
+      <c r="E7" t="s">
         <v>39</v>
-      </c>
-      <c r="C7" t="s">
-        <v>40</v>
-      </c>
-      <c r="D7" t="s">
-        <v>41</v>
-      </c>
-      <c r="E7" t="s">
-        <v>38</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
@@ -2472,16 +2524,16 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C8" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D8" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E8" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
@@ -2489,13 +2541,13 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C9" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D9" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E9">
         <v>1</v>
@@ -2506,22 +2558,22 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C10" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D10" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E10">
         <v>3</v>
       </c>
       <c r="F10" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H10" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="11" spans="3:8" x14ac:dyDescent="0.25"/>
@@ -2755,26 +2807,26 @@
   <sheetData>
     <row r="1" ht="30" customHeight="1" spans="1:2" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="4" spans="2:2" x14ac:dyDescent="0.25"/>
@@ -3003,23 +3055,23 @@
   <sheetData>
     <row r="1" ht="30" customHeight="1" spans="1:2" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B3">
         <v>1</v>
@@ -3027,7 +3079,7 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B4">
         <v>1</v>
@@ -3035,7 +3087,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B5">
         <v>1</v>
@@ -3043,7 +3095,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B6">
         <v>1</v>
@@ -3051,7 +3103,7 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -3059,15 +3111,15 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B8" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B9">
         <v>20</v>
@@ -3099,16 +3151,16 @@
         <v>15</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
@@ -3116,13 +3168,13 @@
         <v>22</v>
       </c>
       <c r="B2" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
@@ -3130,13 +3182,13 @@
         <v>22</v>
       </c>
       <c r="B3" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D3" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
@@ -3144,16 +3196,16 @@
         <v>22</v>
       </c>
       <c r="B4" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C4" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D4" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25"/>
@@ -3378,331 +3430,397 @@
   <sheetPr>
     <tabColor rgb="FF2E7D32"/>
   </sheetPr>
-  <dimension ref="A1:H200"/>
+  <dimension ref="A1:I200"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="24" customWidth="1"/>
     <col min="2" max="2" width="50" customWidth="1"/>
     <col min="3" max="6" width="22" customWidth="1"/>
     <col min="7" max="7" width="10" customWidth="1"/>
-    <col min="8" max="8" width="40" customWidth="1"/>
+    <col min="8" max="8" width="12" customWidth="1"/>
+    <col min="9" max="9" width="40" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" ht="30" customHeight="1" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>15</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+        <v>86</v>
+      </c>
+      <c r="I1" s="3" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>26</v>
       </c>
       <c r="B2" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C2" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="D2" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="E2" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="F2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G2" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+        <v>82</v>
+      </c>
+      <c r="H2" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>26</v>
       </c>
       <c r="B3" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="C3" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="D3" t="s">
+        <v>95</v>
+      </c>
+      <c r="E3" t="s">
+        <v>96</v>
+      </c>
+      <c r="F3" t="s">
+        <v>97</v>
+      </c>
+      <c r="G3" t="s">
+        <v>83</v>
+      </c>
+      <c r="H3" t="s">
         <v>92</v>
       </c>
-      <c r="E3" t="s">
-        <v>93</v>
-      </c>
-      <c r="F3" t="s">
-        <v>94</v>
-      </c>
-      <c r="G3" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>26</v>
       </c>
       <c r="B4" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="C4" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="D4" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="E4" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="F4" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="G4" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+        <v>82</v>
+      </c>
+      <c r="H4" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>26</v>
       </c>
       <c r="B5" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="C5" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="D5" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="E5" t="s">
+        <v>107</v>
+      </c>
+      <c r="F5" t="s">
+        <v>108</v>
+      </c>
+      <c r="G5" t="s">
+        <v>83</v>
+      </c>
+      <c r="H5" t="s">
         <v>103</v>
       </c>
-      <c r="F5" t="s">
-        <v>104</v>
-      </c>
-      <c r="G5" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25"/>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25"/>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25"/>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25"/>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25"/>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25"/>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25"/>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25"/>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25"/>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25"/>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25"/>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25"/>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25"/>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25"/>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25"/>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25"/>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25"/>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25"/>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25"/>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.25"/>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.25"/>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.25"/>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.25"/>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.25"/>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.25"/>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.25"/>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.25"/>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.25"/>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.25"/>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.25"/>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.25"/>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.25"/>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.25"/>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.25"/>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.25"/>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.25"/>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.25"/>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.25"/>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.25"/>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.25"/>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.25"/>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.25"/>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.25"/>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.25"/>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.25"/>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.25"/>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.25"/>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.25"/>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.25"/>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.25"/>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.25"/>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.25"/>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.25"/>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.25"/>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.25"/>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.25"/>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.25"/>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.25"/>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.25"/>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.25"/>
-    <row r="66" spans="1:7" x14ac:dyDescent="0.25"/>
-    <row r="67" spans="1:7" x14ac:dyDescent="0.25"/>
-    <row r="68" spans="1:7" x14ac:dyDescent="0.25"/>
-    <row r="69" spans="1:7" x14ac:dyDescent="0.25"/>
-    <row r="70" spans="1:7" x14ac:dyDescent="0.25"/>
-    <row r="71" spans="1:7" x14ac:dyDescent="0.25"/>
-    <row r="72" spans="1:7" x14ac:dyDescent="0.25"/>
-    <row r="73" spans="1:7" x14ac:dyDescent="0.25"/>
-    <row r="74" spans="1:7" x14ac:dyDescent="0.25"/>
-    <row r="75" spans="1:7" x14ac:dyDescent="0.25"/>
-    <row r="76" spans="1:7" x14ac:dyDescent="0.25"/>
-    <row r="77" spans="1:7" x14ac:dyDescent="0.25"/>
-    <row r="78" spans="1:7" x14ac:dyDescent="0.25"/>
-    <row r="79" spans="1:7" x14ac:dyDescent="0.25"/>
-    <row r="80" spans="1:7" x14ac:dyDescent="0.25"/>
-    <row r="81" spans="1:7" x14ac:dyDescent="0.25"/>
-    <row r="82" spans="1:7" x14ac:dyDescent="0.25"/>
-    <row r="83" spans="1:7" x14ac:dyDescent="0.25"/>
-    <row r="84" spans="1:7" x14ac:dyDescent="0.25"/>
-    <row r="85" spans="1:7" x14ac:dyDescent="0.25"/>
-    <row r="86" spans="1:7" x14ac:dyDescent="0.25"/>
-    <row r="87" spans="1:7" x14ac:dyDescent="0.25"/>
-    <row r="88" spans="1:7" x14ac:dyDescent="0.25"/>
-    <row r="89" spans="1:7" x14ac:dyDescent="0.25"/>
-    <row r="90" spans="1:7" x14ac:dyDescent="0.25"/>
-    <row r="91" spans="1:7" x14ac:dyDescent="0.25"/>
-    <row r="92" spans="1:7" x14ac:dyDescent="0.25"/>
-    <row r="93" spans="1:7" x14ac:dyDescent="0.25"/>
-    <row r="94" spans="1:7" x14ac:dyDescent="0.25"/>
-    <row r="95" spans="1:7" x14ac:dyDescent="0.25"/>
-    <row r="96" spans="1:7" x14ac:dyDescent="0.25"/>
-    <row r="97" spans="1:7" x14ac:dyDescent="0.25"/>
-    <row r="98" spans="1:7" x14ac:dyDescent="0.25"/>
-    <row r="99" spans="1:7" x14ac:dyDescent="0.25"/>
-    <row r="100" spans="1:7" x14ac:dyDescent="0.25"/>
-    <row r="101" spans="1:7" x14ac:dyDescent="0.25"/>
-    <row r="102" spans="1:7" x14ac:dyDescent="0.25"/>
-    <row r="103" spans="1:7" x14ac:dyDescent="0.25"/>
-    <row r="104" spans="1:7" x14ac:dyDescent="0.25"/>
-    <row r="105" spans="1:7" x14ac:dyDescent="0.25"/>
-    <row r="106" spans="1:7" x14ac:dyDescent="0.25"/>
-    <row r="107" spans="1:7" x14ac:dyDescent="0.25"/>
-    <row r="108" spans="1:7" x14ac:dyDescent="0.25"/>
-    <row r="109" spans="1:7" x14ac:dyDescent="0.25"/>
-    <row r="110" spans="1:7" x14ac:dyDescent="0.25"/>
-    <row r="111" spans="1:7" x14ac:dyDescent="0.25"/>
-    <row r="112" spans="1:7" x14ac:dyDescent="0.25"/>
-    <row r="113" spans="1:7" x14ac:dyDescent="0.25"/>
-    <row r="114" spans="1:7" x14ac:dyDescent="0.25"/>
-    <row r="115" spans="1:7" x14ac:dyDescent="0.25"/>
-    <row r="116" spans="1:7" x14ac:dyDescent="0.25"/>
-    <row r="117" spans="1:7" x14ac:dyDescent="0.25"/>
-    <row r="118" spans="1:7" x14ac:dyDescent="0.25"/>
-    <row r="119" spans="1:7" x14ac:dyDescent="0.25"/>
-    <row r="120" spans="1:7" x14ac:dyDescent="0.25"/>
-    <row r="121" spans="1:7" x14ac:dyDescent="0.25"/>
-    <row r="122" spans="1:7" x14ac:dyDescent="0.25"/>
-    <row r="123" spans="1:7" x14ac:dyDescent="0.25"/>
-    <row r="124" spans="1:7" x14ac:dyDescent="0.25"/>
-    <row r="125" spans="1:7" x14ac:dyDescent="0.25"/>
-    <row r="126" spans="1:7" x14ac:dyDescent="0.25"/>
-    <row r="127" spans="1:7" x14ac:dyDescent="0.25"/>
-    <row r="128" spans="1:7" x14ac:dyDescent="0.25"/>
-    <row r="129" spans="1:7" x14ac:dyDescent="0.25"/>
-    <row r="130" spans="1:7" x14ac:dyDescent="0.25"/>
-    <row r="131" spans="1:7" x14ac:dyDescent="0.25"/>
-    <row r="132" spans="1:7" x14ac:dyDescent="0.25"/>
-    <row r="133" spans="1:7" x14ac:dyDescent="0.25"/>
-    <row r="134" spans="1:7" x14ac:dyDescent="0.25"/>
-    <row r="135" spans="1:7" x14ac:dyDescent="0.25"/>
-    <row r="136" spans="1:7" x14ac:dyDescent="0.25"/>
-    <row r="137" spans="1:7" x14ac:dyDescent="0.25"/>
-    <row r="138" spans="1:7" x14ac:dyDescent="0.25"/>
-    <row r="139" spans="1:7" x14ac:dyDescent="0.25"/>
-    <row r="140" spans="1:7" x14ac:dyDescent="0.25"/>
-    <row r="141" spans="1:7" x14ac:dyDescent="0.25"/>
-    <row r="142" spans="1:7" x14ac:dyDescent="0.25"/>
-    <row r="143" spans="1:7" x14ac:dyDescent="0.25"/>
-    <row r="144" spans="1:7" x14ac:dyDescent="0.25"/>
-    <row r="145" spans="1:7" x14ac:dyDescent="0.25"/>
-    <row r="146" spans="1:7" x14ac:dyDescent="0.25"/>
-    <row r="147" spans="1:7" x14ac:dyDescent="0.25"/>
-    <row r="148" spans="1:7" x14ac:dyDescent="0.25"/>
-    <row r="149" spans="1:7" x14ac:dyDescent="0.25"/>
-    <row r="150" spans="1:7" x14ac:dyDescent="0.25"/>
-    <row r="151" spans="1:7" x14ac:dyDescent="0.25"/>
-    <row r="152" spans="1:7" x14ac:dyDescent="0.25"/>
-    <row r="153" spans="1:7" x14ac:dyDescent="0.25"/>
-    <row r="154" spans="1:7" x14ac:dyDescent="0.25"/>
-    <row r="155" spans="1:7" x14ac:dyDescent="0.25"/>
-    <row r="156" spans="1:7" x14ac:dyDescent="0.25"/>
-    <row r="157" spans="1:7" x14ac:dyDescent="0.25"/>
-    <row r="158" spans="1:7" x14ac:dyDescent="0.25"/>
-    <row r="159" spans="1:7" x14ac:dyDescent="0.25"/>
-    <row r="160" spans="1:7" x14ac:dyDescent="0.25"/>
-    <row r="161" spans="1:7" x14ac:dyDescent="0.25"/>
-    <row r="162" spans="1:7" x14ac:dyDescent="0.25"/>
-    <row r="163" spans="1:7" x14ac:dyDescent="0.25"/>
-    <row r="164" spans="1:7" x14ac:dyDescent="0.25"/>
-    <row r="165" spans="1:7" x14ac:dyDescent="0.25"/>
-    <row r="166" spans="1:7" x14ac:dyDescent="0.25"/>
-    <row r="167" spans="1:7" x14ac:dyDescent="0.25"/>
-    <row r="168" spans="1:7" x14ac:dyDescent="0.25"/>
-    <row r="169" spans="1:7" x14ac:dyDescent="0.25"/>
-    <row r="170" spans="1:7" x14ac:dyDescent="0.25"/>
-    <row r="171" spans="1:7" x14ac:dyDescent="0.25"/>
-    <row r="172" spans="1:7" x14ac:dyDescent="0.25"/>
-    <row r="173" spans="1:7" x14ac:dyDescent="0.25"/>
-    <row r="174" spans="1:7" x14ac:dyDescent="0.25"/>
-    <row r="175" spans="1:7" x14ac:dyDescent="0.25"/>
-    <row r="176" spans="1:7" x14ac:dyDescent="0.25"/>
-    <row r="177" spans="1:7" x14ac:dyDescent="0.25"/>
-    <row r="178" spans="1:7" x14ac:dyDescent="0.25"/>
-    <row r="179" spans="1:7" x14ac:dyDescent="0.25"/>
-    <row r="180" spans="1:7" x14ac:dyDescent="0.25"/>
-    <row r="181" spans="1:7" x14ac:dyDescent="0.25"/>
-    <row r="182" spans="1:7" x14ac:dyDescent="0.25"/>
-    <row r="183" spans="1:7" x14ac:dyDescent="0.25"/>
-    <row r="184" spans="1:7" x14ac:dyDescent="0.25"/>
-    <row r="185" spans="1:7" x14ac:dyDescent="0.25"/>
-    <row r="186" spans="1:7" x14ac:dyDescent="0.25"/>
-    <row r="187" spans="1:7" x14ac:dyDescent="0.25"/>
-    <row r="188" spans="1:7" x14ac:dyDescent="0.25"/>
-    <row r="189" spans="1:7" x14ac:dyDescent="0.25"/>
-    <row r="190" spans="1:7" x14ac:dyDescent="0.25"/>
-    <row r="191" spans="1:7" x14ac:dyDescent="0.25"/>
-    <row r="192" spans="1:7" x14ac:dyDescent="0.25"/>
-    <row r="193" spans="1:7" x14ac:dyDescent="0.25"/>
-    <row r="194" spans="1:7" x14ac:dyDescent="0.25"/>
-    <row r="195" spans="1:7" x14ac:dyDescent="0.25"/>
-    <row r="196" spans="1:7" x14ac:dyDescent="0.25"/>
-    <row r="197" spans="1:7" x14ac:dyDescent="0.25"/>
-    <row r="198" spans="1:7" x14ac:dyDescent="0.25"/>
-    <row r="199" spans="1:7" x14ac:dyDescent="0.25"/>
-    <row r="200" spans="1:7" x14ac:dyDescent="0.25"/>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>26</v>
+      </c>
+      <c r="B6" t="s">
+        <v>109</v>
+      </c>
+      <c r="C6" t="s">
+        <v>110</v>
+      </c>
+      <c r="D6" t="s">
+        <v>111</v>
+      </c>
+      <c r="E6" t="s">
+        <v>112</v>
+      </c>
+      <c r="F6" t="s">
+        <v>113</v>
+      </c>
+      <c r="G6" t="s">
+        <v>84</v>
+      </c>
+      <c r="H6" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>26</v>
+      </c>
+      <c r="B7" t="s">
+        <v>115</v>
+      </c>
+      <c r="C7" t="s">
+        <v>116</v>
+      </c>
+      <c r="D7" t="s">
+        <v>117</v>
+      </c>
+      <c r="E7" t="s">
+        <v>118</v>
+      </c>
+      <c r="F7" t="s">
+        <v>119</v>
+      </c>
+      <c r="G7" t="s">
+        <v>81</v>
+      </c>
+      <c r="H7" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="49" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="50" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="51" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="52" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="53" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="54" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="55" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="56" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="57" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="58" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="59" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="60" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="61" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="62" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="63" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="64" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="65" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="66" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="67" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="68" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="69" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="70" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="71" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="72" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="73" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="74" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="75" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="76" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="77" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="78" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="79" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="80" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="81" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="82" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="83" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="84" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="85" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="86" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="87" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="88" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="89" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="90" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="91" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="92" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="93" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="94" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="95" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="96" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="97" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="98" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="99" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="100" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="101" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="102" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="103" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="104" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="105" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="106" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="107" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="108" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="109" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="110" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="111" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="112" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="113" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="114" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="115" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="116" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="117" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="118" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="119" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="120" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="121" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="122" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="123" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="124" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="125" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="126" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="127" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="128" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="129" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="130" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="131" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="132" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="133" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="134" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="135" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="136" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="137" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="138" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="139" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="140" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="141" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="142" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="143" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="144" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="145" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="146" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="147" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="148" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="149" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="150" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="151" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="152" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="153" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="154" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="155" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="156" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="157" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="158" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="159" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="160" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="161" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="162" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="163" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="164" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="165" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="166" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="167" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="168" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="169" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="170" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="171" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="172" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="173" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="174" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="175" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="176" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="177" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="178" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="179" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="180" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="181" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="182" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="183" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="184" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="185" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="186" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="187" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="188" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="189" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="190" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="191" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="192" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="193" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="194" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="195" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="196" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="197" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="198" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="199" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="200" spans="1:8" x14ac:dyDescent="0.25"/>
   </sheetData>
-  <dataValidations count="4">
+  <dataValidations count="6">
     <dataValidation type="list" allowBlank="1" errorStyle="warning" errorTitle="Valor no previsto" error="Elige un valor de la lista." sqref="A10:A200">
       <formula1>Concurso!$B$2:$B$100</formula1>
     </dataValidation>
@@ -3714,6 +3832,12 @@
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="warning" errorTitle="Valor no previsto" error="Elige un valor de la lista." sqref="G2:G200">
       <formula1>"A,B,C,D"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="warning" errorTitle="Valor no previsto" error="Elige un valor de la lista." sqref="H10:H200">
+      <formula1>"Fácil,Media,Difícil"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="warning" errorTitle="Valor no previsto" error="Elige un valor de la lista." sqref="H2:H200">
+      <formula1>"Fácil,Media,Difícil"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3740,32 +3864,32 @@
         <v>15</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>105</v>
+        <v>120</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B2" t="s">
-        <v>106</v>
+        <v>121</v>
       </c>
       <c r="C2" t="s">
-        <v>107</v>
+        <v>122</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B3" t="s">
-        <v>108</v>
+        <v>123</v>
       </c>
       <c r="C3" t="s">
-        <v>109</v>
+        <v>124</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25"/>
@@ -4004,36 +4128,36 @@
         <v>15</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>110</v>
+        <v>125</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>111</v>
+        <v>126</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>112</v>
+        <v>127</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>113</v>
+        <v>128</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>109</v>
+        <v>124</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B2" t="s">
-        <v>114</v>
+        <v>129</v>
       </c>
       <c r="C2" t="s">
-        <v>115</v>
+        <v>130</v>
       </c>
       <c r="D2" t="s">
-        <v>116</v>
+        <v>131</v>
       </c>
       <c r="E2" t="s">
-        <v>117</v>
+        <v>132</v>
       </c>
       <c r="F2">
         <v>2</v>
@@ -4275,23 +4399,23 @@
         <v>15</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B2" t="s">
-        <v>118</v>
+        <v>133</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B3" t="s">
-        <v>119</v>
+        <v>134</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25"/>

--- a/public/plantilla-concurso.xlsx
+++ b/public/plantilla-concurso.xlsx
@@ -17,13 +17,17 @@
     <sheet sheetId="11" name="Contador" state="visible" r:id="rId14"/>
     <sheet sheetId="12" name="Reflejos" state="visible" r:id="rId15"/>
     <sheet sheetId="13" name="Libre" state="visible" r:id="rId16"/>
+    <sheet sheetId="14" name="Palabras" state="visible" r:id="rId17"/>
+    <sheet sheetId="15" name="Agitar" state="visible" r:id="rId18"/>
+    <sheet sheetId="16" name="Apuesta" state="visible" r:id="rId19"/>
+    <sheet sheetId="17" name="Castigos" state="visible" r:id="rId20"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="296" uniqueCount="241">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="591" uniqueCount="432">
   <si>
     <t>EMPIEZA AQUÍ</t>
   </si>
@@ -49,6 +53,9 @@
     <t>3.  «Equipos»: uno por fila con su color (sin filas = sin equipos). «Ajustes»: el título y poco más.</t>
   </si>
   <si>
+    <t xml:space="preserve">     «Castigos»: opciones para el equipo que pierda (todos votan 3 al empezar; al final, la ruleta elige). Sin filas = sin castigo.</t>
+  </si>
+  <si>
     <t>4.  Guárdala como .xlsx y cárgala en la tele («Cargar concurso» o dentro de la carpeta del concurso).</t>
   </si>
   <si>
@@ -58,6 +65,9 @@
     <t>Para cambiar algo después: edita la celda y vuelve a cargar el archivo. Las filas que ya hay son ejemplos: cámbialas o bórralas.</t>
   </si>
   <si>
+    <t>¿Esta noche no os apetece algún juego? Mejor que borrarlo: en la preparación de la tele, quita su casilla en «¿Qué juegos jugamos?».</t>
+  </si>
+  <si>
     <t>En el Test, la respuesta buena se pinta de verde según la letra de «Correcta»: así ves de un vistazo que está bien.</t>
   </si>
   <si>
@@ -157,6 +167,33 @@
     <t>Pruebas físicas o lo que quieras («Fit o Fat»); tú das los puntos.</t>
   </si>
   <si>
+    <t>Palabras secretas</t>
+  </si>
+  <si>
+    <t>pestaña «Palabras»</t>
+  </si>
+  <si>
+    <t>Mímica, Tabú, descríbelo o tararéalo: uno del equipo la hace y los suyos adivinan.</t>
+  </si>
+  <si>
+    <t>Agita el móvil</t>
+  </si>
+  <si>
+    <t>pestaña «Agitar»</t>
+  </si>
+  <si>
+    <t>Carrera: gana quien más agite el móvil en los segundos que digas.</t>
+  </si>
+  <si>
+    <t>La gran apuesta</t>
+  </si>
+  <si>
+    <t>pestaña «Apuesta»</t>
+  </si>
+  <si>
+    <t>Para el final: cada equipo apuesta sus puntos y luego responde.</t>
+  </si>
+  <si>
     <t>Orden</t>
   </si>
   <si>
@@ -196,7 +233,7 @@
     <t>↳ Opcional: una frase que sale en la tele al presentarla.</t>
   </si>
   <si>
-    <t>↳ Por acierto (p. ej. 1). Por puestos: 3,2,1. Test: fácil, media, difícil (1,3,5).</t>
+    <t>↳ Por acierto (p. ej. 1). Por puestos: 3,2,1. Test: fácil, media, difícil (2,5,10). Palabras: por palabra.</t>
   </si>
   <si>
     <t>↳ Vacío = lo normal del tipo.</t>
@@ -211,7 +248,7 @@
     <t>Calentamiento</t>
   </si>
   <si>
-    <t>El primero que pulse, responde.</t>
+    <t>El primero que pulse, responde. ¡Ojo con pulsar antes de tiempo!</t>
   </si>
   <si>
     <t>No</t>
@@ -223,13 +260,16 @@
     <t>¿Quién quiere ser millonario? Uno cada vez; vuestro portavoz decide el orden.</t>
   </si>
   <si>
-    <t>1,3,5</t>
+    <t>2,5,10</t>
   </si>
   <si>
     <t>¿Verdad o mentira?</t>
   </si>
   <si>
-    <t>¿Te lo crees o no?</t>
+    <t>¿Te lo crees o no? Todos a la vez.</t>
+  </si>
+  <si>
+    <t>Mímica, Tabú y canciones: haz que tu equipo adivine todas las que pueda.</t>
   </si>
   <si>
     <t>¿Quién es más probable…?</t>
@@ -241,12 +281,18 @@
     <t>Calcula</t>
   </si>
   <si>
-    <t>El que más se acerque.</t>
+    <t>El que más se acerque. En algunas, sin pasarse.</t>
   </si>
   <si>
     <t>3,2,1</t>
   </si>
   <si>
+    <t>¡Agita hasta que te duela el brazo!</t>
+  </si>
+  <si>
+    <t>Sí</t>
+  </si>
+  <si>
     <t>Reloj interno</t>
   </si>
   <si>
@@ -268,12 +314,12 @@
     <t>Pruebas físicas.</t>
   </si>
   <si>
-    <t>Sí</t>
-  </si>
-  <si>
     <t>Noche de luna</t>
   </si>
   <si>
+    <t>Apostad lo que tenéis. Aquí se decide todo.</t>
+  </si>
+  <si>
     <t>Equipo</t>
   </si>
   <si>
@@ -286,13 +332,13 @@
     <t>↳ Opcional. Cada equipo, uno distinto.</t>
   </si>
   <si>
-    <t>Los Rojos</t>
+    <t>Zombies</t>
   </si>
   <si>
     <t>Rojo</t>
   </si>
   <si>
-    <t>Los Azules</t>
+    <t>Hombres Lobo</t>
   </si>
   <si>
     <t>Azul</t>
@@ -367,6 +413,18 @@
     <t>Tiempo para responder en Verdad o mentira, Votación… (la Estimación tiene 10 más).</t>
   </si>
   <si>
+    <t>Segundos por turno (Palabras)</t>
+  </si>
+  <si>
+    <t>Palabras secretas: cuánto dura cada turno.</t>
+  </si>
+  <si>
+    <t>Turnos por equipo (Palabras)</t>
+  </si>
+  <si>
+    <t>Palabras secretas: cuántas veces sale cada equipo (cada vez, otro de sus jugadores).</t>
+  </si>
+  <si>
     <t>Pregunta</t>
   </si>
   <si>
@@ -394,27 +452,72 @@
     <t>↳ Vacía = la única sección de este tipo. Si hay varias, elige a cuál va cada fila.</t>
   </si>
   <si>
-    <t>¿Cuál es el río más largo de España?</t>
+    <t>¿Cuántas patas tiene una araña?</t>
+  </si>
+  <si>
+    <t>Ocho</t>
+  </si>
+  <si>
+    <t>¿Qué hortaliza se vacía para hacer la linterna de Halloween?</t>
+  </si>
+  <si>
+    <t>La calabaza</t>
+  </si>
+  <si>
+    <t>¿Cómo se llama el conde vampiro de la novela de Bram Stoker?</t>
+  </si>
+  <si>
+    <t>Drácula</t>
+  </si>
+  <si>
+    <t>¿De qué metal tiene que ser la bala para matar a un hombre lobo?</t>
+  </si>
+  <si>
+    <t>De plata</t>
+  </si>
+  <si>
+    <t>¿Cuál es el río más largo de la península ibérica?</t>
   </si>
   <si>
     <t>El Tajo</t>
   </si>
   <si>
-    <t>¿Cuántas patas tiene una araña?</t>
-  </si>
-  <si>
-    <t>Ocho</t>
+    <t>El Ebro es el más largo que va entero por España</t>
+  </si>
+  <si>
+    <t>¿Cómo se llama el científico que crea al monstruo en la novela de Mary Shelley?</t>
+  </si>
+  <si>
+    <t>Víctor Frankenstein</t>
+  </si>
+  <si>
+    <t>El monstruo no tiene nombre</t>
+  </si>
+  <si>
+    <t>¿Qué fiesta celta, de origen irlandés, dio lugar a Halloween?</t>
+  </si>
+  <si>
+    <t>Samhain</t>
+  </si>
+  <si>
+    <t>Vale «la de los celtas» si lo explican</t>
   </si>
   <si>
     <t>🎵 ¿Qué canción suena?</t>
   </si>
   <si>
-    <t>Mr. Brightside (The Killers)</t>
+    <t>Thriller (Michael Jackson)</t>
   </si>
   <si>
     <t>Pon la canción tú desde tu música</t>
   </si>
   <si>
+    <t>🎵 ¿De qué película es esta canción?</t>
+  </si>
+  <si>
+    <t>Los Cazafantasmas</t>
+  </si>
+  <si>
     <t>A</t>
   </si>
   <si>
@@ -475,19 +578,49 @@
     <t>Fácil</t>
   </si>
   <si>
-    <t>¿De qué color es el caballo blanco de Santiago?</t>
-  </si>
-  <si>
-    <t>Negro</t>
-  </si>
-  <si>
-    <t>Marrón</t>
-  </si>
-  <si>
-    <t>Blanco</t>
-  </si>
-  <si>
-    <t>Gris</t>
+    <t>¿Qué usan las brujas de los cuentos para volar?</t>
+  </si>
+  <si>
+    <t>Una escoba</t>
+  </si>
+  <si>
+    <t>Una alfombra</t>
+  </si>
+  <si>
+    <t>Un paraguas</t>
+  </si>
+  <si>
+    <t>Una nube</t>
+  </si>
+  <si>
+    <t>¿Qué planeta es conocido como «el planeta rojo»?</t>
+  </si>
+  <si>
+    <t>Venus</t>
+  </si>
+  <si>
+    <t>Marte</t>
+  </si>
+  <si>
+    <t>Júpiter</t>
+  </si>
+  <si>
+    <t>Mercurio</t>
+  </si>
+  <si>
+    <t>¿Qué animal es Simba en «El rey león»?</t>
+  </si>
+  <si>
+    <t>Un tigre</t>
+  </si>
+  <si>
+    <t>Un guepardo</t>
+  </si>
+  <si>
+    <t>Un león</t>
+  </si>
+  <si>
+    <t>Un lobo</t>
   </si>
   <si>
     <t>¿En qué año llegó el hombre a la Luna?</t>
@@ -508,7 +641,7 @@
     <t>Media</t>
   </si>
   <si>
-    <t>¿Cuál es el planeta más grande?</t>
+    <t>¿Cuál es el planeta más grande del sistema solar?</t>
   </si>
   <si>
     <t>Saturno</t>
@@ -517,22 +650,49 @@
     <t>Neptuno</t>
   </si>
   <si>
-    <t>Júpiter</t>
-  </si>
-  <si>
     <t>Urano</t>
   </si>
   <si>
-    <t>¿Cuál es la capital de provincia española que está a más altura?</t>
+    <t>¿Quién escribió «Frankenstein»?</t>
+  </si>
+  <si>
+    <t>Bram Stoker</t>
+  </si>
+  <si>
+    <t>Mary Shelley</t>
+  </si>
+  <si>
+    <t>Edgar Allan Poe</t>
+  </si>
+  <si>
+    <t>H. P. Lovecraft</t>
+  </si>
+  <si>
+    <t>¿Quién dirigió la película «Psicosis» (1960)?</t>
+  </si>
+  <si>
+    <t>Stanley Kubrick</t>
+  </si>
+  <si>
+    <t>Steven Spielberg</t>
+  </si>
+  <si>
+    <t>John Carpenter</t>
+  </si>
+  <si>
+    <t>Alfred Hitchcock</t>
+  </si>
+  <si>
+    <t>¿Cuál es la capital de provincia española que está a más altitud?</t>
   </si>
   <si>
     <t>Cuenca</t>
   </si>
   <si>
-    <t>Badajoz</t>
-  </si>
-  <si>
-    <t>Jaén</t>
+    <t>Soria</t>
+  </si>
+  <si>
+    <t>Teruel</t>
   </si>
   <si>
     <t>Ávila</t>
@@ -553,7 +713,37 @@
     <t>Osmio</t>
   </si>
   <si>
-    <t>Wiconio</t>
+    <t>Teluro</t>
+  </si>
+  <si>
+    <t>¿Cuántos huesos tiene el cuerpo de un adulto?</t>
+  </si>
+  <si>
+    <t>186</t>
+  </si>
+  <si>
+    <t>206</t>
+  </si>
+  <si>
+    <t>226</t>
+  </si>
+  <si>
+    <t>256</t>
+  </si>
+  <si>
+    <t>¿En qué año se estrenó «La noche de Halloween», de John Carpenter?</t>
+  </si>
+  <si>
+    <t>1974</t>
+  </si>
+  <si>
+    <t>1978</t>
+  </si>
+  <si>
+    <t>1982</t>
+  </si>
+  <si>
+    <t>1986</t>
   </si>
   <si>
     <t>Afirmación</t>
@@ -577,6 +767,24 @@
     <t>Mentira</t>
   </si>
   <si>
+    <t>Los murciélagos son ciegos.</t>
+  </si>
+  <si>
+    <t>Para los botánicos, la calabaza es una fruta.</t>
+  </si>
+  <si>
+    <t>La miel bien cerrada no se estropea nunca.</t>
+  </si>
+  <si>
+    <t>En Japón y en Escocia, un gato negro trae buena suerte.</t>
+  </si>
+  <si>
+    <t>Bram Stoker viajó a Transilvania para escribir «Drácula».</t>
+  </si>
+  <si>
+    <t>Un rayo nunca cae dos veces en el mismo sitio.</t>
+  </si>
+  <si>
     <t>Sobre quién</t>
   </si>
   <si>
@@ -589,10 +797,10 @@
     <t>Frase 3</t>
   </si>
   <si>
-    <t>↳ El jugador (su nombre, como entre). No vota.</t>
-  </si>
-  <si>
-    <t>↳ Tres frases sobre él…</t>
+    <t>↳ Un jugador (su nombre, como entre: no vota) o un personaje famoso.</t>
+  </si>
+  <si>
+    <t>↳ Tres frases…</t>
   </si>
   <si>
     <t>↳ …dos verdad…</t>
@@ -616,6 +824,75 @@
     <t>Tengo tres hermanos.</t>
   </si>
   <si>
+    <t>Drácula (la novela)</t>
+  </si>
+  <si>
+    <t>Puede convertirse en lobo y en murciélago.</t>
+  </si>
+  <si>
+    <t>No se refleja en los espejos.</t>
+  </si>
+  <si>
+    <t>Muere de un disparo con una bala de plata.</t>
+  </si>
+  <si>
+    <t>El monstruo de Frankenstein</t>
+  </si>
+  <si>
+    <t>En la novela tiene tornillos en el cuello.</t>
+  </si>
+  <si>
+    <t>En la novela no tiene nombre.</t>
+  </si>
+  <si>
+    <t>Mary Shelley empezó a escribirlo con 18 años.</t>
+  </si>
+  <si>
+    <t>Harry Potter</t>
+  </si>
+  <si>
+    <t>Su cumpleaños es el 31 de julio.</t>
+  </si>
+  <si>
+    <t>Su patronus es un lobo.</t>
+  </si>
+  <si>
+    <t>Su varita lleva una pluma de fénix.</t>
+  </si>
+  <si>
+    <t>Pesadilla antes de Navidad</t>
+  </si>
+  <si>
+    <t>Jack Skellington es el rey de Halloween.</t>
+  </si>
+  <si>
+    <t>Su perro fantasma se llama Zero.</t>
+  </si>
+  <si>
+    <t>La dirigió Tim Burton.</t>
+  </si>
+  <si>
+    <t>Su cuartel es un antiguo parque de bomberos.</t>
+  </si>
+  <si>
+    <t>Cazan fantasmas en Chicago.</t>
+  </si>
+  <si>
+    <t>La película es de 1984.</t>
+  </si>
+  <si>
+    <t>Stephen King</t>
+  </si>
+  <si>
+    <t>Escribió «It».</t>
+  </si>
+  <si>
+    <t>Escribió «El exorcista».</t>
+  </si>
+  <si>
+    <t>Nació en Maine (Estados Unidos).</t>
+  </si>
+  <si>
     <t>↳ «¿Quién es más probable que…?»: todos votan a un jugador.</t>
   </si>
   <si>
@@ -625,6 +902,24 @@
     <t>¿Quién es más probable que sobreviva a un apocalipsis zombi?</t>
   </si>
   <si>
+    <t>¿Quién es más probable que sea el primero en morir en una película de miedo?</t>
+  </si>
+  <si>
+    <t>¿Quién es más probable que se coma los caramelos de Halloween antes de que llegue nadie?</t>
+  </si>
+  <si>
+    <t>¿Quién es más probable que grite en el pasaje del terror?</t>
+  </si>
+  <si>
+    <t>¿Quién es más probable que se haga amigo del fantasma de su casa?</t>
+  </si>
+  <si>
+    <t>¿Quién es más probable que repita disfraz todos los años?</t>
+  </si>
+  <si>
+    <t>¿Quién es más probable que invoque a un demonio por leer en voz alta un libro raro?</t>
+  </si>
+  <si>
     <t>Unidad</t>
   </si>
   <si>
@@ -652,15 +947,45 @@
     <t>Más cercano</t>
   </si>
   <si>
-    <t>¿Cuánto cuesta un kilo de jamón ibérico de bellota?</t>
-  </si>
-  <si>
-    <t>€</t>
+    <t>¿Cuántos kilos pesaba la calabaza más pesada del mundo (récord de 2023)?</t>
+  </si>
+  <si>
+    <t>kg</t>
+  </si>
+  <si>
+    <t>¿En qué año se publicó «Drácula», de Bram Stoker?</t>
+  </si>
+  <si>
+    <t>¿Cuántos metros mide la Torre Eiffel (con sus antenas)?</t>
+  </si>
+  <si>
+    <t>m</t>
+  </si>
+  <si>
+    <t>¿Cuántas teclas tiene un piano normal?</t>
+  </si>
+  <si>
+    <t>teclas</t>
   </si>
   <si>
     <t>Sin pasarse</t>
   </si>
   <si>
+    <t>¿Cuántos kilómetros hay en línea recta de Madrid a Barcelona?</t>
+  </si>
+  <si>
+    <t>¿Cuántos años vivió Edgar Allan Poe?</t>
+  </si>
+  <si>
+    <t>años</t>
+  </si>
+  <si>
+    <t>¿Cuántos dientes tiene un adulto, con las muelas del juicio?</t>
+  </si>
+  <si>
+    <t>dientes</t>
+  </si>
+  <si>
     <t>Objetivo (s)</t>
   </si>
   <si>
@@ -703,6 +1028,9 @@
     <t>Todos</t>
   </si>
   <si>
+    <t>Duelo</t>
+  </si>
+  <si>
     <t>Prueba</t>
   </si>
   <si>
@@ -746,6 +1074,255 @@
   </si>
   <si>
     <t>Equipos</t>
+  </si>
+  <si>
+    <t>Sentadillas</t>
+  </si>
+  <si>
+    <t>Más sentadillas en un minuto (bajando hasta abajo).</t>
+  </si>
+  <si>
+    <t>La silla invisible</t>
+  </si>
+  <si>
+    <t>Espalda en la pared, como sentado en una silla. Gana el último.</t>
+  </si>
+  <si>
+    <t>Flamenco a ciegas</t>
+  </si>
+  <si>
+    <t>A la pata coja y con los ojos cerrados. Gana el último en apoyar el pie.</t>
+  </si>
+  <si>
+    <t>La momia</t>
+  </si>
+  <si>
+    <t>Envolved a un compañero en papel higiénico en un minuto. Gana la mejor momia.</t>
+  </si>
+  <si>
+    <t>Ninguna</t>
+  </si>
+  <si>
+    <t>Manzana colgante</t>
+  </si>
+  <si>
+    <t>Muerde la manzana que cuelga de un hilo, sin manos.</t>
+  </si>
+  <si>
+    <t>Burpees</t>
+  </si>
+  <si>
+    <t>Más burpees en 30 segundos, entre todo el equipo.</t>
+  </si>
+  <si>
+    <t>Palabra</t>
+  </si>
+  <si>
+    <t>Prohibidas</t>
+  </si>
+  <si>
+    <t>↳ Lo que hay que adivinar. Solo la ven quien la hace y el equipo rival.</t>
+  </si>
+  <si>
+    <t>↳ Tabú: las que no se pueden decir, separadas por comas.</t>
+  </si>
+  <si>
+    <t>↳ Vacío = Tabú si hay prohibidas; si no, Mímica.</t>
+  </si>
+  <si>
+    <t>Calabaza</t>
+  </si>
+  <si>
+    <t>Halloween, naranja, vela, cara</t>
+  </si>
+  <si>
+    <t>Tabú</t>
+  </si>
+  <si>
+    <t>Vampiro</t>
+  </si>
+  <si>
+    <t>Sangre, Drácula, colmillos, murciélago</t>
+  </si>
+  <si>
+    <t>Fantasma</t>
+  </si>
+  <si>
+    <t>Sábana, espíritu, casa encantada, susto</t>
+  </si>
+  <si>
+    <t>Bruja</t>
+  </si>
+  <si>
+    <t>Escoba, caldero, sombrero, hechizo</t>
+  </si>
+  <si>
+    <t>Telaraña</t>
+  </si>
+  <si>
+    <t>Araña, hilo, red, tejer</t>
+  </si>
+  <si>
+    <t>Esqueleto</t>
+  </si>
+  <si>
+    <t>Huesos, calavera, cuerpo, muerto</t>
+  </si>
+  <si>
+    <t>Cementerio</t>
+  </si>
+  <si>
+    <t>Tumba, muertos, lápida, enterrar</t>
+  </si>
+  <si>
+    <t>Murciélago</t>
+  </si>
+  <si>
+    <t>Vampiro, volar, cueva, noche</t>
+  </si>
+  <si>
+    <t>Caramelo</t>
+  </si>
+  <si>
+    <t>Dulce, azúcar, chuche, truco o trato</t>
+  </si>
+  <si>
+    <t>Luna llena</t>
+  </si>
+  <si>
+    <t>Noche, lobo, redonda, cielo</t>
+  </si>
+  <si>
+    <t>Hombre lobo</t>
+  </si>
+  <si>
+    <t>Mímica</t>
+  </si>
+  <si>
+    <t>Momia</t>
+  </si>
+  <si>
+    <t>Zombi</t>
+  </si>
+  <si>
+    <t>Tallar una calabaza</t>
+  </si>
+  <si>
+    <t>Pedir caramelos</t>
+  </si>
+  <si>
+    <t>Volar en escoba</t>
+  </si>
+  <si>
+    <t>Ver una peli de miedo</t>
+  </si>
+  <si>
+    <t>Salir de un ataúd</t>
+  </si>
+  <si>
+    <t>Gato negro</t>
+  </si>
+  <si>
+    <t>Poción</t>
+  </si>
+  <si>
+    <t>Descríbelo</t>
+  </si>
+  <si>
+    <t>Disfraz</t>
+  </si>
+  <si>
+    <t>Escalofrío</t>
+  </si>
+  <si>
+    <t>Casa encantada</t>
+  </si>
+  <si>
+    <t>Ataúd</t>
+  </si>
+  <si>
+    <t>Thriller</t>
+  </si>
+  <si>
+    <t>Tararéalo</t>
+  </si>
+  <si>
+    <t>La familia Addams</t>
+  </si>
+  <si>
+    <t>Tiburón</t>
+  </si>
+  <si>
+    <t>Piratas del Caribe</t>
+  </si>
+  <si>
+    <t>Cumpleaños feliz</t>
+  </si>
+  <si>
+    <t>Segundos</t>
+  </si>
+  <si>
+    <t>↳ Cuánto dura cada carrera (de 3 a 60). Una fila = una carrera.</t>
+  </si>
+  <si>
+    <t>↳ Mejor difícil: cada equipo apuesta antes de verla.</t>
+  </si>
+  <si>
+    <t>¿Qué famoso escapista murió un 31 de octubre, noche de Halloween?</t>
+  </si>
+  <si>
+    <t>Harry Houdini</t>
+  </si>
+  <si>
+    <t>David Copperfield</t>
+  </si>
+  <si>
+    <t>Charles Chaplin</t>
+  </si>
+  <si>
+    <t>Bela Lugosi</t>
+  </si>
+  <si>
+    <t>¿Qué actor fue Drácula en la película de 1931?</t>
+  </si>
+  <si>
+    <t>Boris Karloff</t>
+  </si>
+  <si>
+    <t>Christopher Lee</t>
+  </si>
+  <si>
+    <t>Vincent Price</t>
+  </si>
+  <si>
+    <t>Castigo</t>
+  </si>
+  <si>
+    <t>↳ Uno por fila. Al empezar se votan 3; al final, la ruleta elige el del equipo que pierda.</t>
+  </si>
+  <si>
+    <t>Bailar «Thriller» entera delante de todos</t>
+  </si>
+  <si>
+    <t>Servir las bebidas a los ganadores el resto de la noche</t>
+  </si>
+  <si>
+    <t>Llevar el disfraz que elijan los ganadores hasta el final de la fiesta</t>
+  </si>
+  <si>
+    <t>Fregar todos los platos de la cena</t>
+  </si>
+  <si>
+    <t>Declarar su amor a una calabaza, de rodillas y con drama</t>
+  </si>
+  <si>
+    <t>Cantar la canción que elijan los ganadores</t>
+  </si>
+  <si>
+    <t>Imitar a cada ganador durante 30 segundos</t>
+  </si>
+  <si>
+    <t>Contar un chiste malo a cada ganador hasta que se ría</t>
   </si>
 </sst>
 </file>
@@ -863,7 +1440,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="12">
+  <dxfs count="16">
     <dxf>
       <font>
         <b/>
@@ -993,6 +1570,50 @@
       <fill>
         <patternFill patternType="solid">
           <bgColor rgb="FFFFCDD2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF1B5E20"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFC8E6C9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF1B5E20"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFC8E6C9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF1B5E20"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFC8E6C9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF1B5E20"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFC8E6C9"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1334,7 +1955,7 @@
   <sheetPr>
     <tabColor rgb="FFFF8A1F"/>
   </sheetPr>
-  <dimension ref="A1:C26"/>
+  <dimension ref="A1:C31"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
@@ -1383,23 +2004,23 @@
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A9" s="4" t="s">
+      <c r="A9" s="3" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A10" s="3" t="s">
+      <c r="A10" s="4" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>10</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
@@ -1414,122 +2035,165 @@
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A16" s="3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A17" s="3" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A16" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="B17" s="6" t="s">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A18" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C17" s="6" t="s">
+    </row>
+    <row r="19" spans="1:3" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="6" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A18" s="7" t="s">
+      <c r="B19" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="B18" t="s">
+      <c r="C19" s="6" t="s">
         <v>18</v>
-      </c>
-      <c r="C18" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A19" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="B19" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="C19" s="9" t="s">
-        <v>22</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" s="7" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="C20" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" s="8" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="C21" s="9" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" s="7" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="B22" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="C22" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" s="8" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="B23" s="9" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="C23" s="9" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" s="7" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="B24" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="C24" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" s="8" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="B25" s="9" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="C25" s="9" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="B26" t="s">
+        <v>38</v>
+      </c>
+      <c r="C26" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A27" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="B27" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="B26" t="s">
+      <c r="C27" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="C26" t="s">
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A28" s="7" t="s">
         <v>43</v>
+      </c>
+      <c r="B28" t="s">
+        <v>44</v>
+      </c>
+      <c r="C28" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A29" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="B29" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="C29" s="9" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A30" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="B30" t="s">
+        <v>50</v>
+      </c>
+      <c r="C30" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A31" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="B31" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="C31" s="9" t="s">
+        <v>54</v>
       </c>
     </row>
   </sheetData>
@@ -1555,108 +2219,154 @@
   <sheetData>
     <row r="1" ht="30" customHeight="1" spans="1:5" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="10" t="s">
-        <v>114</v>
+        <v>132</v>
       </c>
       <c r="B1" s="10" t="s">
-        <v>115</v>
+        <v>133</v>
       </c>
       <c r="C1" s="10" t="s">
-        <v>200</v>
+        <v>297</v>
       </c>
       <c r="D1" s="10" t="s">
-        <v>201</v>
+        <v>298</v>
       </c>
       <c r="E1" s="10" t="s">
-        <v>45</v>
+        <v>56</v>
       </c>
     </row>
     <row r="2" ht="42" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="11" t="s">
-        <v>202</v>
+        <v>299</v>
       </c>
       <c r="B2" s="11" t="s">
-        <v>203</v>
+        <v>300</v>
       </c>
       <c r="C2" s="11" t="s">
-        <v>204</v>
+        <v>301</v>
       </c>
       <c r="D2" s="11" t="s">
-        <v>205</v>
+        <v>302</v>
       </c>
       <c r="E2" s="11" t="s">
-        <v>122</v>
+        <v>140</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="14" t="s">
-        <v>206</v>
+        <v>303</v>
       </c>
       <c r="B3" s="12">
         <v>910</v>
       </c>
       <c r="C3" s="12" t="s">
-        <v>207</v>
+        <v>304</v>
       </c>
       <c r="D3" s="12" t="s">
-        <v>208</v>
+        <v>305</v>
       </c>
       <c r="E3" s="12"/>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="14" t="s">
-        <v>209</v>
+        <v>306</v>
       </c>
       <c r="B4" s="12">
-        <v>120</v>
+        <v>1247</v>
       </c>
       <c r="C4" s="12" t="s">
-        <v>210</v>
+        <v>307</v>
       </c>
       <c r="D4" s="12" t="s">
-        <v>211</v>
+        <v>305</v>
       </c>
       <c r="E4" s="12"/>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" s="14"/>
-      <c r="B5" s="12"/>
+      <c r="A5" s="14" t="s">
+        <v>308</v>
+      </c>
+      <c r="B5" s="12">
+        <v>1897</v>
+      </c>
       <c r="C5" s="12"/>
-      <c r="D5" s="12"/>
+      <c r="D5" s="12" t="s">
+        <v>305</v>
+      </c>
       <c r="E5" s="12"/>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" s="14"/>
-      <c r="B6" s="12"/>
-      <c r="C6" s="12"/>
-      <c r="D6" s="12"/>
+      <c r="A6" s="14" t="s">
+        <v>309</v>
+      </c>
+      <c r="B6" s="12">
+        <v>330</v>
+      </c>
+      <c r="C6" s="12" t="s">
+        <v>310</v>
+      </c>
+      <c r="D6" s="12" t="s">
+        <v>305</v>
+      </c>
       <c r="E6" s="12"/>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" s="14"/>
-      <c r="B7" s="12"/>
-      <c r="C7" s="12"/>
-      <c r="D7" s="12"/>
+      <c r="A7" s="14" t="s">
+        <v>311</v>
+      </c>
+      <c r="B7" s="12">
+        <v>88</v>
+      </c>
+      <c r="C7" s="12" t="s">
+        <v>312</v>
+      </c>
+      <c r="D7" s="12" t="s">
+        <v>313</v>
+      </c>
       <c r="E7" s="12"/>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A8" s="14"/>
-      <c r="B8" s="12"/>
-      <c r="C8" s="12"/>
-      <c r="D8" s="12"/>
+      <c r="A8" s="14" t="s">
+        <v>314</v>
+      </c>
+      <c r="B8" s="12">
+        <v>505</v>
+      </c>
+      <c r="C8" s="12" t="s">
+        <v>304</v>
+      </c>
+      <c r="D8" s="12" t="s">
+        <v>305</v>
+      </c>
       <c r="E8" s="12"/>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A9" s="14"/>
-      <c r="B9" s="12"/>
-      <c r="C9" s="12"/>
-      <c r="D9" s="12"/>
+      <c r="A9" s="14" t="s">
+        <v>315</v>
+      </c>
+      <c r="B9" s="12">
+        <v>40</v>
+      </c>
+      <c r="C9" s="12" t="s">
+        <v>316</v>
+      </c>
+      <c r="D9" s="12" t="s">
+        <v>313</v>
+      </c>
       <c r="E9" s="12"/>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A10" s="14"/>
-      <c r="B10" s="12"/>
-      <c r="C10" s="12"/>
-      <c r="D10" s="12"/>
+      <c r="A10" s="14" t="s">
+        <v>317</v>
+      </c>
+      <c r="B10" s="12">
+        <v>32</v>
+      </c>
+      <c r="C10" s="12" t="s">
+        <v>318</v>
+      </c>
+      <c r="D10" s="12" t="s">
+        <v>313</v>
+      </c>
       <c r="E10" s="12"/>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
@@ -3024,30 +3734,30 @@
   <sheetData>
     <row r="1" ht="30" customHeight="1" spans="1:4" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="10" t="s">
-        <v>212</v>
+        <v>319</v>
       </c>
       <c r="B1" s="10" t="s">
-        <v>213</v>
+        <v>320</v>
       </c>
       <c r="C1" s="10" t="s">
-        <v>214</v>
+        <v>321</v>
       </c>
       <c r="D1" s="10" t="s">
-        <v>45</v>
+        <v>56</v>
       </c>
     </row>
     <row r="2" ht="42" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="11" t="s">
-        <v>215</v>
+        <v>322</v>
       </c>
       <c r="B2" s="11" t="s">
-        <v>216</v>
+        <v>323</v>
       </c>
       <c r="C2" s="11" t="s">
-        <v>217</v>
+        <v>324</v>
       </c>
       <c r="D2" s="11" t="s">
-        <v>122</v>
+        <v>140</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -3055,7 +3765,7 @@
         <v>10</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>218</v>
+        <v>325</v>
       </c>
       <c r="C3" s="12"/>
       <c r="D3" s="12"/>
@@ -3065,7 +3775,7 @@
         <v>15</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>219</v>
+        <v>326</v>
       </c>
       <c r="C4" s="12">
         <v>3</v>
@@ -3077,20 +3787,30 @@
         <v>7</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>220</v>
+        <v>327</v>
       </c>
       <c r="C5" s="12"/>
       <c r="D5" s="12"/>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6" s="12"/>
-      <c r="B6" s="12"/>
-      <c r="C6" s="12"/>
+      <c r="A6" s="12">
+        <v>12</v>
+      </c>
+      <c r="B6" s="12" t="s">
+        <v>326</v>
+      </c>
+      <c r="C6" s="12">
+        <v>5</v>
+      </c>
       <c r="D6" s="12"/>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A7" s="12"/>
-      <c r="B7" s="12"/>
+      <c r="A7" s="12">
+        <v>20</v>
+      </c>
+      <c r="B7" s="12" t="s">
+        <v>327</v>
+      </c>
       <c r="C7" s="12"/>
       <c r="D7" s="12"/>
     </row>
@@ -4287,24 +5007,24 @@
   <sheetData>
     <row r="1" ht="30" customHeight="1" spans="1:3" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="10" t="s">
-        <v>221</v>
+        <v>328</v>
       </c>
       <c r="B1" s="10" t="s">
-        <v>222</v>
+        <v>329</v>
       </c>
       <c r="C1" s="10" t="s">
-        <v>45</v>
+        <v>56</v>
       </c>
     </row>
     <row r="2" ht="42" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="11" t="s">
-        <v>223</v>
+        <v>330</v>
       </c>
       <c r="B2" s="11" t="s">
-        <v>224</v>
+        <v>331</v>
       </c>
       <c r="C2" s="11" t="s">
-        <v>122</v>
+        <v>140</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -4312,18 +5032,26 @@
         <v>3</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>225</v>
+        <v>332</v>
       </c>
       <c r="C3" s="12"/>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" s="12"/>
-      <c r="B4" s="12"/>
+      <c r="A4" s="12">
+        <v>2</v>
+      </c>
+      <c r="B4" s="12" t="s">
+        <v>333</v>
+      </c>
       <c r="C4" s="12"/>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" s="12"/>
-      <c r="B5" s="12"/>
+      <c r="A5" s="12">
+        <v>3</v>
+      </c>
+      <c r="B5" s="12" t="s">
+        <v>332</v>
+      </c>
       <c r="C5" s="12"/>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
@@ -5338,72 +6066,72 @@
   <sheetData>
     <row r="1" ht="30" customHeight="1" spans="1:6" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="10" t="s">
-        <v>226</v>
+        <v>334</v>
       </c>
       <c r="B1" s="10" t="s">
-        <v>47</v>
+        <v>58</v>
       </c>
       <c r="C1" s="10" t="s">
-        <v>227</v>
+        <v>335</v>
       </c>
       <c r="D1" s="10" t="s">
-        <v>222</v>
+        <v>329</v>
       </c>
       <c r="E1" s="10" t="s">
-        <v>48</v>
+        <v>59</v>
       </c>
       <c r="F1" s="10" t="s">
-        <v>45</v>
+        <v>56</v>
       </c>
     </row>
     <row r="2" ht="42" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="11" t="s">
-        <v>228</v>
+        <v>336</v>
       </c>
       <c r="B2" s="11" t="s">
-        <v>229</v>
+        <v>337</v>
       </c>
       <c r="C2" s="11" t="s">
-        <v>230</v>
+        <v>338</v>
       </c>
       <c r="D2" s="11" t="s">
-        <v>231</v>
+        <v>339</v>
       </c>
       <c r="E2" s="11" t="s">
-        <v>232</v>
+        <v>340</v>
       </c>
       <c r="F2" s="11" t="s">
-        <v>122</v>
+        <v>140</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="12" t="s">
-        <v>233</v>
+        <v>341</v>
       </c>
       <c r="B3" s="14" t="s">
-        <v>234</v>
+        <v>342</v>
       </c>
       <c r="C3" s="12" t="s">
-        <v>235</v>
+        <v>343</v>
       </c>
       <c r="D3" s="12" t="s">
-        <v>236</v>
+        <v>344</v>
       </c>
       <c r="E3" s="12"/>
       <c r="F3" s="12"/>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="12" t="s">
-        <v>237</v>
+        <v>345</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>238</v>
+        <v>346</v>
       </c>
       <c r="C4" s="12" t="s">
-        <v>239</v>
+        <v>347</v>
       </c>
       <c r="D4" s="12" t="s">
-        <v>240</v>
+        <v>348</v>
       </c>
       <c r="E4" s="12">
         <v>5</v>
@@ -5411,51 +6139,103 @@
       <c r="F4" s="12"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="12"/>
-      <c r="B5" s="14"/>
-      <c r="C5" s="12"/>
-      <c r="D5" s="12"/>
+      <c r="A5" s="12" t="s">
+        <v>349</v>
+      </c>
+      <c r="B5" s="14" t="s">
+        <v>350</v>
+      </c>
+      <c r="C5" s="12" t="s">
+        <v>347</v>
+      </c>
+      <c r="D5" s="12" t="s">
+        <v>344</v>
+      </c>
       <c r="E5" s="12"/>
       <c r="F5" s="12"/>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="12"/>
-      <c r="B6" s="14"/>
-      <c r="C6" s="12"/>
-      <c r="D6" s="12"/>
+      <c r="A6" s="12" t="s">
+        <v>351</v>
+      </c>
+      <c r="B6" s="14" t="s">
+        <v>352</v>
+      </c>
+      <c r="C6" s="12" t="s">
+        <v>343</v>
+      </c>
+      <c r="D6" s="12" t="s">
+        <v>344</v>
+      </c>
       <c r="E6" s="12"/>
       <c r="F6" s="12"/>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="12"/>
-      <c r="B7" s="14"/>
-      <c r="C7" s="12"/>
-      <c r="D7" s="12"/>
+      <c r="A7" s="12" t="s">
+        <v>353</v>
+      </c>
+      <c r="B7" s="14" t="s">
+        <v>354</v>
+      </c>
+      <c r="C7" s="12" t="s">
+        <v>343</v>
+      </c>
+      <c r="D7" s="12" t="s">
+        <v>344</v>
+      </c>
       <c r="E7" s="12"/>
       <c r="F7" s="12"/>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="12"/>
-      <c r="B8" s="14"/>
-      <c r="C8" s="12"/>
-      <c r="D8" s="12"/>
-      <c r="E8" s="12"/>
+      <c r="A8" s="12" t="s">
+        <v>355</v>
+      </c>
+      <c r="B8" s="14" t="s">
+        <v>356</v>
+      </c>
+      <c r="C8" s="12" t="s">
+        <v>357</v>
+      </c>
+      <c r="D8" s="12" t="s">
+        <v>348</v>
+      </c>
+      <c r="E8" s="12">
+        <v>5</v>
+      </c>
       <c r="F8" s="12"/>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="12"/>
-      <c r="B9" s="14"/>
-      <c r="C9" s="12"/>
-      <c r="D9" s="12"/>
+      <c r="A9" s="12" t="s">
+        <v>358</v>
+      </c>
+      <c r="B9" s="14" t="s">
+        <v>359</v>
+      </c>
+      <c r="C9" s="12" t="s">
+        <v>343</v>
+      </c>
+      <c r="D9" s="12" t="s">
+        <v>344</v>
+      </c>
       <c r="E9" s="12"/>
       <c r="F9" s="12"/>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="12"/>
-      <c r="B10" s="14"/>
-      <c r="C10" s="12"/>
-      <c r="D10" s="12"/>
-      <c r="E10" s="12"/>
+      <c r="A10" s="12" t="s">
+        <v>360</v>
+      </c>
+      <c r="B10" s="14" t="s">
+        <v>361</v>
+      </c>
+      <c r="C10" s="12" t="s">
+        <v>347</v>
+      </c>
+      <c r="D10" s="12" t="s">
+        <v>348</v>
+      </c>
+      <c r="E10" s="12">
+        <v>5</v>
+      </c>
       <c r="F10" s="12"/>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
@@ -7004,6 +7784,4777 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <tabColor rgb="FFFF7043"/>
+  </sheetPr>
+  <dimension ref="A1:D200"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="26" customWidth="1"/>
+    <col min="2" max="2" width="46" customWidth="1"/>
+    <col min="3" max="3" width="13" customWidth="1"/>
+    <col min="4" max="4" width="22" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1" spans="1:4" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="10" t="s">
+        <v>362</v>
+      </c>
+      <c r="B1" s="10" t="s">
+        <v>363</v>
+      </c>
+      <c r="C1" s="10" t="s">
+        <v>320</v>
+      </c>
+      <c r="D1" s="10" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="2" ht="42" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" s="11" t="s">
+        <v>364</v>
+      </c>
+      <c r="B2" s="11" t="s">
+        <v>365</v>
+      </c>
+      <c r="C2" s="11" t="s">
+        <v>366</v>
+      </c>
+      <c r="D2" s="11" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" s="12" t="s">
+        <v>367</v>
+      </c>
+      <c r="B3" s="14" t="s">
+        <v>368</v>
+      </c>
+      <c r="C3" s="12" t="s">
+        <v>369</v>
+      </c>
+      <c r="D3" s="12"/>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" s="12" t="s">
+        <v>370</v>
+      </c>
+      <c r="B4" s="14" t="s">
+        <v>371</v>
+      </c>
+      <c r="C4" s="12" t="s">
+        <v>369</v>
+      </c>
+      <c r="D4" s="12"/>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" s="12" t="s">
+        <v>372</v>
+      </c>
+      <c r="B5" s="14" t="s">
+        <v>373</v>
+      </c>
+      <c r="C5" s="12" t="s">
+        <v>369</v>
+      </c>
+      <c r="D5" s="12"/>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" s="12" t="s">
+        <v>374</v>
+      </c>
+      <c r="B6" s="14" t="s">
+        <v>375</v>
+      </c>
+      <c r="C6" s="12" t="s">
+        <v>369</v>
+      </c>
+      <c r="D6" s="12"/>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7" s="12" t="s">
+        <v>376</v>
+      </c>
+      <c r="B7" s="14" t="s">
+        <v>377</v>
+      </c>
+      <c r="C7" s="12" t="s">
+        <v>369</v>
+      </c>
+      <c r="D7" s="12"/>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8" s="12" t="s">
+        <v>378</v>
+      </c>
+      <c r="B8" s="14" t="s">
+        <v>379</v>
+      </c>
+      <c r="C8" s="12" t="s">
+        <v>369</v>
+      </c>
+      <c r="D8" s="12"/>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9" s="12" t="s">
+        <v>380</v>
+      </c>
+      <c r="B9" s="14" t="s">
+        <v>381</v>
+      </c>
+      <c r="C9" s="12" t="s">
+        <v>369</v>
+      </c>
+      <c r="D9" s="12"/>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10" s="12" t="s">
+        <v>382</v>
+      </c>
+      <c r="B10" s="14" t="s">
+        <v>383</v>
+      </c>
+      <c r="C10" s="12" t="s">
+        <v>369</v>
+      </c>
+      <c r="D10" s="12"/>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A11" s="12" t="s">
+        <v>384</v>
+      </c>
+      <c r="B11" s="14" t="s">
+        <v>385</v>
+      </c>
+      <c r="C11" s="12" t="s">
+        <v>369</v>
+      </c>
+      <c r="D11" s="12"/>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A12" s="12" t="s">
+        <v>386</v>
+      </c>
+      <c r="B12" s="14" t="s">
+        <v>387</v>
+      </c>
+      <c r="C12" s="12" t="s">
+        <v>369</v>
+      </c>
+      <c r="D12" s="12"/>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A13" s="12" t="s">
+        <v>388</v>
+      </c>
+      <c r="B13" s="14"/>
+      <c r="C13" s="12" t="s">
+        <v>389</v>
+      </c>
+      <c r="D13" s="12"/>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A14" s="12" t="s">
+        <v>390</v>
+      </c>
+      <c r="B14" s="14"/>
+      <c r="C14" s="12" t="s">
+        <v>389</v>
+      </c>
+      <c r="D14" s="12"/>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A15" s="12" t="s">
+        <v>391</v>
+      </c>
+      <c r="B15" s="14"/>
+      <c r="C15" s="12" t="s">
+        <v>389</v>
+      </c>
+      <c r="D15" s="12"/>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A16" s="12" t="s">
+        <v>392</v>
+      </c>
+      <c r="B16" s="14"/>
+      <c r="C16" s="12" t="s">
+        <v>389</v>
+      </c>
+      <c r="D16" s="12"/>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A17" s="12" t="s">
+        <v>393</v>
+      </c>
+      <c r="B17" s="14"/>
+      <c r="C17" s="12" t="s">
+        <v>389</v>
+      </c>
+      <c r="D17" s="12"/>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A18" s="12" t="s">
+        <v>394</v>
+      </c>
+      <c r="B18" s="14"/>
+      <c r="C18" s="12" t="s">
+        <v>389</v>
+      </c>
+      <c r="D18" s="12"/>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A19" s="12" t="s">
+        <v>395</v>
+      </c>
+      <c r="B19" s="14"/>
+      <c r="C19" s="12" t="s">
+        <v>389</v>
+      </c>
+      <c r="D19" s="12"/>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A20" s="12" t="s">
+        <v>396</v>
+      </c>
+      <c r="B20" s="14"/>
+      <c r="C20" s="12" t="s">
+        <v>389</v>
+      </c>
+      <c r="D20" s="12"/>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A21" s="12" t="s">
+        <v>397</v>
+      </c>
+      <c r="B21" s="14"/>
+      <c r="C21" s="12" t="s">
+        <v>389</v>
+      </c>
+      <c r="D21" s="12"/>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A22" s="12" t="s">
+        <v>398</v>
+      </c>
+      <c r="B22" s="14"/>
+      <c r="C22" s="12" t="s">
+        <v>399</v>
+      </c>
+      <c r="D22" s="12"/>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A23" s="12" t="s">
+        <v>400</v>
+      </c>
+      <c r="B23" s="14"/>
+      <c r="C23" s="12" t="s">
+        <v>399</v>
+      </c>
+      <c r="D23" s="12"/>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A24" s="12" t="s">
+        <v>401</v>
+      </c>
+      <c r="B24" s="14"/>
+      <c r="C24" s="12" t="s">
+        <v>399</v>
+      </c>
+      <c r="D24" s="12"/>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A25" s="12" t="s">
+        <v>402</v>
+      </c>
+      <c r="B25" s="14"/>
+      <c r="C25" s="12" t="s">
+        <v>399</v>
+      </c>
+      <c r="D25" s="12"/>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A26" s="12" t="s">
+        <v>403</v>
+      </c>
+      <c r="B26" s="14"/>
+      <c r="C26" s="12" t="s">
+        <v>399</v>
+      </c>
+      <c r="D26" s="12"/>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A27" s="12" t="s">
+        <v>404</v>
+      </c>
+      <c r="B27" s="14"/>
+      <c r="C27" s="12" t="s">
+        <v>405</v>
+      </c>
+      <c r="D27" s="12"/>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A28" s="12" t="s">
+        <v>162</v>
+      </c>
+      <c r="B28" s="14"/>
+      <c r="C28" s="12" t="s">
+        <v>405</v>
+      </c>
+      <c r="D28" s="12"/>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A29" s="12" t="s">
+        <v>406</v>
+      </c>
+      <c r="B29" s="14"/>
+      <c r="C29" s="12" t="s">
+        <v>405</v>
+      </c>
+      <c r="D29" s="12"/>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A30" s="12" t="s">
+        <v>407</v>
+      </c>
+      <c r="B30" s="14"/>
+      <c r="C30" s="12" t="s">
+        <v>405</v>
+      </c>
+      <c r="D30" s="12"/>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A31" s="12" t="s">
+        <v>408</v>
+      </c>
+      <c r="B31" s="14"/>
+      <c r="C31" s="12" t="s">
+        <v>405</v>
+      </c>
+      <c r="D31" s="12"/>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A32" s="12" t="s">
+        <v>409</v>
+      </c>
+      <c r="B32" s="14"/>
+      <c r="C32" s="12" t="s">
+        <v>405</v>
+      </c>
+      <c r="D32" s="12"/>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A33" s="12"/>
+      <c r="B33" s="14"/>
+      <c r="C33" s="12"/>
+      <c r="D33" s="12"/>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A34" s="12"/>
+      <c r="B34" s="14"/>
+      <c r="C34" s="12"/>
+      <c r="D34" s="12"/>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A35" s="12"/>
+      <c r="B35" s="14"/>
+      <c r="C35" s="12"/>
+      <c r="D35" s="12"/>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A36" s="12"/>
+      <c r="B36" s="14"/>
+      <c r="C36" s="12"/>
+      <c r="D36" s="12"/>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A37" s="12"/>
+      <c r="B37" s="14"/>
+      <c r="C37" s="12"/>
+      <c r="D37" s="12"/>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A38" s="12"/>
+      <c r="B38" s="14"/>
+      <c r="C38" s="12"/>
+      <c r="D38" s="12"/>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A39" s="12"/>
+      <c r="B39" s="14"/>
+      <c r="C39" s="12"/>
+      <c r="D39" s="12"/>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A40" s="12"/>
+      <c r="B40" s="14"/>
+      <c r="C40" s="12"/>
+      <c r="D40" s="12"/>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A41" s="12"/>
+      <c r="B41" s="14"/>
+      <c r="C41" s="12"/>
+      <c r="D41" s="12"/>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A42" s="12"/>
+      <c r="B42" s="14"/>
+      <c r="C42" s="12"/>
+      <c r="D42" s="12"/>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A43" s="12"/>
+      <c r="B43" s="14"/>
+      <c r="C43" s="12"/>
+      <c r="D43" s="12"/>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A44" s="12"/>
+      <c r="B44" s="14"/>
+      <c r="C44" s="12"/>
+      <c r="D44" s="12"/>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A45" s="12"/>
+      <c r="B45" s="14"/>
+      <c r="C45" s="12"/>
+      <c r="D45" s="12"/>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A46" s="12"/>
+      <c r="B46" s="14"/>
+      <c r="C46" s="12"/>
+      <c r="D46" s="12"/>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A47" s="12"/>
+      <c r="B47" s="14"/>
+      <c r="C47" s="12"/>
+      <c r="D47" s="12"/>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A48" s="12"/>
+      <c r="B48" s="14"/>
+      <c r="C48" s="12"/>
+      <c r="D48" s="12"/>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A49" s="12"/>
+      <c r="B49" s="14"/>
+      <c r="C49" s="12"/>
+      <c r="D49" s="12"/>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A50" s="12"/>
+      <c r="B50" s="14"/>
+      <c r="C50" s="12"/>
+      <c r="D50" s="12"/>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A51" s="12"/>
+      <c r="B51" s="14"/>
+      <c r="C51" s="12"/>
+      <c r="D51" s="12"/>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A52" s="12"/>
+      <c r="B52" s="14"/>
+      <c r="C52" s="12"/>
+      <c r="D52" s="12"/>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A53" s="12"/>
+      <c r="B53" s="14"/>
+      <c r="C53" s="12"/>
+      <c r="D53" s="12"/>
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A54" s="12"/>
+      <c r="B54" s="14"/>
+      <c r="C54" s="12"/>
+      <c r="D54" s="12"/>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A55" s="12"/>
+      <c r="B55" s="14"/>
+      <c r="C55" s="12"/>
+      <c r="D55" s="12"/>
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A56" s="12"/>
+      <c r="B56" s="14"/>
+      <c r="C56" s="12"/>
+      <c r="D56" s="12"/>
+    </row>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A57" s="12"/>
+      <c r="B57" s="14"/>
+      <c r="C57" s="12"/>
+      <c r="D57" s="12"/>
+    </row>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A58" s="12"/>
+      <c r="B58" s="14"/>
+      <c r="C58" s="12"/>
+      <c r="D58" s="12"/>
+    </row>
+    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A59" s="12"/>
+      <c r="B59" s="14"/>
+      <c r="C59" s="12"/>
+      <c r="D59" s="12"/>
+    </row>
+    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A60" s="12"/>
+      <c r="B60" s="14"/>
+      <c r="C60" s="12"/>
+      <c r="D60" s="12"/>
+    </row>
+    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A61" s="12"/>
+      <c r="B61" s="14"/>
+      <c r="C61" s="12"/>
+      <c r="D61" s="12"/>
+    </row>
+    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A62" s="12"/>
+      <c r="B62" s="14"/>
+      <c r="C62" s="12"/>
+      <c r="D62" s="12"/>
+    </row>
+    <row r="63" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A63" s="12"/>
+      <c r="B63" s="14"/>
+      <c r="C63" s="12"/>
+      <c r="D63" s="12"/>
+    </row>
+    <row r="64" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A64" s="12"/>
+      <c r="B64" s="14"/>
+      <c r="C64" s="12"/>
+      <c r="D64" s="12"/>
+    </row>
+    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A65" s="12"/>
+      <c r="B65" s="14"/>
+      <c r="C65" s="12"/>
+      <c r="D65" s="12"/>
+    </row>
+    <row r="66" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A66" s="12"/>
+      <c r="B66" s="14"/>
+      <c r="C66" s="12"/>
+      <c r="D66" s="12"/>
+    </row>
+    <row r="67" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A67" s="12"/>
+      <c r="B67" s="14"/>
+      <c r="C67" s="12"/>
+      <c r="D67" s="12"/>
+    </row>
+    <row r="68" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A68" s="12"/>
+      <c r="B68" s="14"/>
+      <c r="C68" s="12"/>
+      <c r="D68" s="12"/>
+    </row>
+    <row r="69" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A69" s="12"/>
+      <c r="B69" s="14"/>
+      <c r="C69" s="12"/>
+      <c r="D69" s="12"/>
+    </row>
+    <row r="70" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A70" s="12"/>
+      <c r="B70" s="14"/>
+      <c r="C70" s="12"/>
+      <c r="D70" s="12"/>
+    </row>
+    <row r="71" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A71" s="12"/>
+      <c r="B71" s="14"/>
+      <c r="C71" s="12"/>
+      <c r="D71" s="12"/>
+    </row>
+    <row r="72" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A72" s="12"/>
+      <c r="B72" s="14"/>
+      <c r="C72" s="12"/>
+      <c r="D72" s="12"/>
+    </row>
+    <row r="73" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A73" s="12"/>
+      <c r="B73" s="14"/>
+      <c r="C73" s="12"/>
+      <c r="D73" s="12"/>
+    </row>
+    <row r="74" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A74" s="12"/>
+      <c r="B74" s="14"/>
+      <c r="C74" s="12"/>
+      <c r="D74" s="12"/>
+    </row>
+    <row r="75" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A75" s="12"/>
+      <c r="B75" s="14"/>
+      <c r="C75" s="12"/>
+      <c r="D75" s="12"/>
+    </row>
+    <row r="76" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A76" s="12"/>
+      <c r="B76" s="14"/>
+      <c r="C76" s="12"/>
+      <c r="D76" s="12"/>
+    </row>
+    <row r="77" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A77" s="12"/>
+      <c r="B77" s="14"/>
+      <c r="C77" s="12"/>
+      <c r="D77" s="12"/>
+    </row>
+    <row r="78" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A78" s="12"/>
+      <c r="B78" s="14"/>
+      <c r="C78" s="12"/>
+      <c r="D78" s="12"/>
+    </row>
+    <row r="79" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A79" s="12"/>
+      <c r="B79" s="14"/>
+      <c r="C79" s="12"/>
+      <c r="D79" s="12"/>
+    </row>
+    <row r="80" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A80" s="12"/>
+      <c r="B80" s="14"/>
+      <c r="C80" s="12"/>
+      <c r="D80" s="12"/>
+    </row>
+    <row r="81" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A81" s="12"/>
+      <c r="B81" s="14"/>
+      <c r="C81" s="12"/>
+      <c r="D81" s="12"/>
+    </row>
+    <row r="82" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A82" s="12"/>
+      <c r="B82" s="14"/>
+      <c r="C82" s="12"/>
+      <c r="D82" s="12"/>
+    </row>
+    <row r="83" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A83" s="12"/>
+      <c r="B83" s="14"/>
+      <c r="C83" s="12"/>
+      <c r="D83" s="12"/>
+    </row>
+    <row r="84" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A84" s="12"/>
+      <c r="B84" s="14"/>
+      <c r="C84" s="12"/>
+      <c r="D84" s="12"/>
+    </row>
+    <row r="85" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A85" s="12"/>
+      <c r="B85" s="14"/>
+      <c r="C85" s="12"/>
+      <c r="D85" s="12"/>
+    </row>
+    <row r="86" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A86" s="12"/>
+      <c r="B86" s="14"/>
+      <c r="C86" s="12"/>
+      <c r="D86" s="12"/>
+    </row>
+    <row r="87" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A87" s="12"/>
+      <c r="B87" s="14"/>
+      <c r="C87" s="12"/>
+      <c r="D87" s="12"/>
+    </row>
+    <row r="88" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A88" s="12"/>
+      <c r="B88" s="14"/>
+      <c r="C88" s="12"/>
+      <c r="D88" s="12"/>
+    </row>
+    <row r="89" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A89" s="12"/>
+      <c r="B89" s="14"/>
+      <c r="C89" s="12"/>
+      <c r="D89" s="12"/>
+    </row>
+    <row r="90" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A90" s="12"/>
+      <c r="B90" s="14"/>
+      <c r="C90" s="12"/>
+      <c r="D90" s="12"/>
+    </row>
+    <row r="91" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A91" s="12"/>
+      <c r="B91" s="14"/>
+      <c r="C91" s="12"/>
+      <c r="D91" s="12"/>
+    </row>
+    <row r="92" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A92" s="12"/>
+      <c r="B92" s="14"/>
+      <c r="C92" s="12"/>
+      <c r="D92" s="12"/>
+    </row>
+    <row r="93" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A93" s="12"/>
+      <c r="B93" s="14"/>
+      <c r="C93" s="12"/>
+      <c r="D93" s="12"/>
+    </row>
+    <row r="94" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A94" s="12"/>
+      <c r="B94" s="14"/>
+      <c r="C94" s="12"/>
+      <c r="D94" s="12"/>
+    </row>
+    <row r="95" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A95" s="12"/>
+      <c r="B95" s="14"/>
+      <c r="C95" s="12"/>
+      <c r="D95" s="12"/>
+    </row>
+    <row r="96" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A96" s="12"/>
+      <c r="B96" s="14"/>
+      <c r="C96" s="12"/>
+      <c r="D96" s="12"/>
+    </row>
+    <row r="97" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A97" s="12"/>
+      <c r="B97" s="14"/>
+      <c r="C97" s="12"/>
+      <c r="D97" s="12"/>
+    </row>
+    <row r="98" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A98" s="12"/>
+      <c r="B98" s="14"/>
+      <c r="C98" s="12"/>
+      <c r="D98" s="12"/>
+    </row>
+    <row r="99" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A99" s="12"/>
+      <c r="B99" s="14"/>
+      <c r="C99" s="12"/>
+      <c r="D99" s="12"/>
+    </row>
+    <row r="100" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A100" s="12"/>
+      <c r="B100" s="14"/>
+      <c r="C100" s="12"/>
+      <c r="D100" s="12"/>
+    </row>
+    <row r="101" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A101" s="12"/>
+      <c r="B101" s="14"/>
+      <c r="C101" s="12"/>
+      <c r="D101" s="12"/>
+    </row>
+    <row r="102" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A102" s="12"/>
+      <c r="B102" s="14"/>
+      <c r="C102" s="12"/>
+      <c r="D102" s="12"/>
+    </row>
+    <row r="103" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A103" s="12"/>
+      <c r="B103" s="14"/>
+      <c r="C103" s="12"/>
+      <c r="D103" s="12"/>
+    </row>
+    <row r="104" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A104" s="12"/>
+      <c r="B104" s="14"/>
+      <c r="C104" s="12"/>
+      <c r="D104" s="12"/>
+    </row>
+    <row r="105" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A105" s="12"/>
+      <c r="B105" s="14"/>
+      <c r="C105" s="12"/>
+      <c r="D105" s="12"/>
+    </row>
+    <row r="106" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A106" s="12"/>
+      <c r="B106" s="14"/>
+      <c r="C106" s="12"/>
+      <c r="D106" s="12"/>
+    </row>
+    <row r="107" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A107" s="12"/>
+      <c r="B107" s="14"/>
+      <c r="C107" s="12"/>
+      <c r="D107" s="12"/>
+    </row>
+    <row r="108" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A108" s="12"/>
+      <c r="B108" s="14"/>
+      <c r="C108" s="12"/>
+      <c r="D108" s="12"/>
+    </row>
+    <row r="109" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A109" s="12"/>
+      <c r="B109" s="14"/>
+      <c r="C109" s="12"/>
+      <c r="D109" s="12"/>
+    </row>
+    <row r="110" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A110" s="12"/>
+      <c r="B110" s="14"/>
+      <c r="C110" s="12"/>
+      <c r="D110" s="12"/>
+    </row>
+    <row r="111" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A111" s="12"/>
+      <c r="B111" s="14"/>
+      <c r="C111" s="12"/>
+      <c r="D111" s="12"/>
+    </row>
+    <row r="112" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A112" s="12"/>
+      <c r="B112" s="14"/>
+      <c r="C112" s="12"/>
+      <c r="D112" s="12"/>
+    </row>
+    <row r="113" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A113" s="12"/>
+      <c r="B113" s="14"/>
+      <c r="C113" s="12"/>
+      <c r="D113" s="12"/>
+    </row>
+    <row r="114" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A114" s="12"/>
+      <c r="B114" s="14"/>
+      <c r="C114" s="12"/>
+      <c r="D114" s="12"/>
+    </row>
+    <row r="115" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A115" s="12"/>
+      <c r="B115" s="14"/>
+      <c r="C115" s="12"/>
+      <c r="D115" s="12"/>
+    </row>
+    <row r="116" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A116" s="12"/>
+      <c r="B116" s="14"/>
+      <c r="C116" s="12"/>
+      <c r="D116" s="12"/>
+    </row>
+    <row r="117" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A117" s="12"/>
+      <c r="B117" s="14"/>
+      <c r="C117" s="12"/>
+      <c r="D117" s="12"/>
+    </row>
+    <row r="118" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A118" s="12"/>
+      <c r="B118" s="14"/>
+      <c r="C118" s="12"/>
+      <c r="D118" s="12"/>
+    </row>
+    <row r="119" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A119" s="12"/>
+      <c r="B119" s="14"/>
+      <c r="C119" s="12"/>
+      <c r="D119" s="12"/>
+    </row>
+    <row r="120" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A120" s="12"/>
+      <c r="B120" s="14"/>
+      <c r="C120" s="12"/>
+      <c r="D120" s="12"/>
+    </row>
+    <row r="121" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A121" s="12"/>
+      <c r="B121" s="14"/>
+      <c r="C121" s="12"/>
+      <c r="D121" s="12"/>
+    </row>
+    <row r="122" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A122" s="12"/>
+      <c r="B122" s="14"/>
+      <c r="C122" s="12"/>
+      <c r="D122" s="12"/>
+    </row>
+    <row r="123" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A123" s="12"/>
+      <c r="B123" s="14"/>
+      <c r="C123" s="12"/>
+      <c r="D123" s="12"/>
+    </row>
+    <row r="124" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A124" s="12"/>
+      <c r="B124" s="14"/>
+      <c r="C124" s="12"/>
+      <c r="D124" s="12"/>
+    </row>
+    <row r="125" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A125" s="12"/>
+      <c r="B125" s="14"/>
+      <c r="C125" s="12"/>
+      <c r="D125" s="12"/>
+    </row>
+    <row r="126" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A126" s="12"/>
+      <c r="B126" s="14"/>
+      <c r="C126" s="12"/>
+      <c r="D126" s="12"/>
+    </row>
+    <row r="127" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A127" s="12"/>
+      <c r="B127" s="14"/>
+      <c r="C127" s="12"/>
+      <c r="D127" s="12"/>
+    </row>
+    <row r="128" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A128" s="12"/>
+      <c r="B128" s="14"/>
+      <c r="C128" s="12"/>
+      <c r="D128" s="12"/>
+    </row>
+    <row r="129" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A129" s="12"/>
+      <c r="B129" s="14"/>
+      <c r="C129" s="12"/>
+      <c r="D129" s="12"/>
+    </row>
+    <row r="130" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A130" s="12"/>
+      <c r="B130" s="14"/>
+      <c r="C130" s="12"/>
+      <c r="D130" s="12"/>
+    </row>
+    <row r="131" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A131" s="12"/>
+      <c r="B131" s="14"/>
+      <c r="C131" s="12"/>
+      <c r="D131" s="12"/>
+    </row>
+    <row r="132" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A132" s="12"/>
+      <c r="B132" s="14"/>
+      <c r="C132" s="12"/>
+      <c r="D132" s="12"/>
+    </row>
+    <row r="133" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A133" s="12"/>
+      <c r="B133" s="14"/>
+      <c r="C133" s="12"/>
+      <c r="D133" s="12"/>
+    </row>
+    <row r="134" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A134" s="12"/>
+      <c r="B134" s="14"/>
+      <c r="C134" s="12"/>
+      <c r="D134" s="12"/>
+    </row>
+    <row r="135" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A135" s="12"/>
+      <c r="B135" s="14"/>
+      <c r="C135" s="12"/>
+      <c r="D135" s="12"/>
+    </row>
+    <row r="136" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A136" s="12"/>
+      <c r="B136" s="14"/>
+      <c r="C136" s="12"/>
+      <c r="D136" s="12"/>
+    </row>
+    <row r="137" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A137" s="12"/>
+      <c r="B137" s="14"/>
+      <c r="C137" s="12"/>
+      <c r="D137" s="12"/>
+    </row>
+    <row r="138" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A138" s="12"/>
+      <c r="B138" s="14"/>
+      <c r="C138" s="12"/>
+      <c r="D138" s="12"/>
+    </row>
+    <row r="139" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A139" s="12"/>
+      <c r="B139" s="14"/>
+      <c r="C139" s="12"/>
+      <c r="D139" s="12"/>
+    </row>
+    <row r="140" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A140" s="12"/>
+      <c r="B140" s="14"/>
+      <c r="C140" s="12"/>
+      <c r="D140" s="12"/>
+    </row>
+    <row r="141" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A141" s="12"/>
+      <c r="B141" s="14"/>
+      <c r="C141" s="12"/>
+      <c r="D141" s="12"/>
+    </row>
+    <row r="142" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A142" s="12"/>
+      <c r="B142" s="14"/>
+      <c r="C142" s="12"/>
+      <c r="D142" s="12"/>
+    </row>
+    <row r="143" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A143" s="12"/>
+      <c r="B143" s="14"/>
+      <c r="C143" s="12"/>
+      <c r="D143" s="12"/>
+    </row>
+    <row r="144" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A144" s="12"/>
+      <c r="B144" s="14"/>
+      <c r="C144" s="12"/>
+      <c r="D144" s="12"/>
+    </row>
+    <row r="145" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A145" s="12"/>
+      <c r="B145" s="14"/>
+      <c r="C145" s="12"/>
+      <c r="D145" s="12"/>
+    </row>
+    <row r="146" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A146" s="12"/>
+      <c r="B146" s="14"/>
+      <c r="C146" s="12"/>
+      <c r="D146" s="12"/>
+    </row>
+    <row r="147" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A147" s="12"/>
+      <c r="B147" s="14"/>
+      <c r="C147" s="12"/>
+      <c r="D147" s="12"/>
+    </row>
+    <row r="148" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A148" s="12"/>
+      <c r="B148" s="14"/>
+      <c r="C148" s="12"/>
+      <c r="D148" s="12"/>
+    </row>
+    <row r="149" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A149" s="12"/>
+      <c r="B149" s="14"/>
+      <c r="C149" s="12"/>
+      <c r="D149" s="12"/>
+    </row>
+    <row r="150" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A150" s="12"/>
+      <c r="B150" s="14"/>
+      <c r="C150" s="12"/>
+      <c r="D150" s="12"/>
+    </row>
+    <row r="151" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A151" s="12"/>
+      <c r="B151" s="14"/>
+      <c r="C151" s="12"/>
+      <c r="D151" s="12"/>
+    </row>
+    <row r="152" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A152" s="12"/>
+      <c r="B152" s="14"/>
+      <c r="C152" s="12"/>
+      <c r="D152" s="12"/>
+    </row>
+    <row r="153" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A153" s="12"/>
+      <c r="B153" s="14"/>
+      <c r="C153" s="12"/>
+      <c r="D153" s="12"/>
+    </row>
+    <row r="154" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A154" s="12"/>
+      <c r="B154" s="14"/>
+      <c r="C154" s="12"/>
+      <c r="D154" s="12"/>
+    </row>
+    <row r="155" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A155" s="12"/>
+      <c r="B155" s="14"/>
+      <c r="C155" s="12"/>
+      <c r="D155" s="12"/>
+    </row>
+    <row r="156" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A156" s="12"/>
+      <c r="B156" s="14"/>
+      <c r="C156" s="12"/>
+      <c r="D156" s="12"/>
+    </row>
+    <row r="157" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A157" s="12"/>
+      <c r="B157" s="14"/>
+      <c r="C157" s="12"/>
+      <c r="D157" s="12"/>
+    </row>
+    <row r="158" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A158" s="12"/>
+      <c r="B158" s="14"/>
+      <c r="C158" s="12"/>
+      <c r="D158" s="12"/>
+    </row>
+    <row r="159" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A159" s="12"/>
+      <c r="B159" s="14"/>
+      <c r="C159" s="12"/>
+      <c r="D159" s="12"/>
+    </row>
+    <row r="160" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A160" s="12"/>
+      <c r="B160" s="14"/>
+      <c r="C160" s="12"/>
+      <c r="D160" s="12"/>
+    </row>
+    <row r="161" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A161" s="12"/>
+      <c r="B161" s="14"/>
+      <c r="C161" s="12"/>
+      <c r="D161" s="12"/>
+    </row>
+    <row r="162" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A162" s="12"/>
+      <c r="B162" s="14"/>
+      <c r="C162" s="12"/>
+      <c r="D162" s="12"/>
+    </row>
+    <row r="163" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A163" s="12"/>
+      <c r="B163" s="14"/>
+      <c r="C163" s="12"/>
+      <c r="D163" s="12"/>
+    </row>
+    <row r="164" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A164" s="12"/>
+      <c r="B164" s="14"/>
+      <c r="C164" s="12"/>
+      <c r="D164" s="12"/>
+    </row>
+    <row r="165" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A165" s="12"/>
+      <c r="B165" s="14"/>
+      <c r="C165" s="12"/>
+      <c r="D165" s="12"/>
+    </row>
+    <row r="166" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A166" s="12"/>
+      <c r="B166" s="14"/>
+      <c r="C166" s="12"/>
+      <c r="D166" s="12"/>
+    </row>
+    <row r="167" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A167" s="12"/>
+      <c r="B167" s="14"/>
+      <c r="C167" s="12"/>
+      <c r="D167" s="12"/>
+    </row>
+    <row r="168" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A168" s="12"/>
+      <c r="B168" s="14"/>
+      <c r="C168" s="12"/>
+      <c r="D168" s="12"/>
+    </row>
+    <row r="169" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A169" s="12"/>
+      <c r="B169" s="14"/>
+      <c r="C169" s="12"/>
+      <c r="D169" s="12"/>
+    </row>
+    <row r="170" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A170" s="12"/>
+      <c r="B170" s="14"/>
+      <c r="C170" s="12"/>
+      <c r="D170" s="12"/>
+    </row>
+    <row r="171" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A171" s="12"/>
+      <c r="B171" s="14"/>
+      <c r="C171" s="12"/>
+      <c r="D171" s="12"/>
+    </row>
+    <row r="172" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A172" s="12"/>
+      <c r="B172" s="14"/>
+      <c r="C172" s="12"/>
+      <c r="D172" s="12"/>
+    </row>
+    <row r="173" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A173" s="12"/>
+      <c r="B173" s="14"/>
+      <c r="C173" s="12"/>
+      <c r="D173" s="12"/>
+    </row>
+    <row r="174" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A174" s="12"/>
+      <c r="B174" s="14"/>
+      <c r="C174" s="12"/>
+      <c r="D174" s="12"/>
+    </row>
+    <row r="175" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A175" s="12"/>
+      <c r="B175" s="14"/>
+      <c r="C175" s="12"/>
+      <c r="D175" s="12"/>
+    </row>
+    <row r="176" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A176" s="12"/>
+      <c r="B176" s="14"/>
+      <c r="C176" s="12"/>
+      <c r="D176" s="12"/>
+    </row>
+    <row r="177" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A177" s="12"/>
+      <c r="B177" s="14"/>
+      <c r="C177" s="12"/>
+      <c r="D177" s="12"/>
+    </row>
+    <row r="178" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A178" s="12"/>
+      <c r="B178" s="14"/>
+      <c r="C178" s="12"/>
+      <c r="D178" s="12"/>
+    </row>
+    <row r="179" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A179" s="12"/>
+      <c r="B179" s="14"/>
+      <c r="C179" s="12"/>
+      <c r="D179" s="12"/>
+    </row>
+    <row r="180" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A180" s="12"/>
+      <c r="B180" s="14"/>
+      <c r="C180" s="12"/>
+      <c r="D180" s="12"/>
+    </row>
+    <row r="181" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A181" s="12"/>
+      <c r="B181" s="14"/>
+      <c r="C181" s="12"/>
+      <c r="D181" s="12"/>
+    </row>
+    <row r="182" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A182" s="12"/>
+      <c r="B182" s="14"/>
+      <c r="C182" s="12"/>
+      <c r="D182" s="12"/>
+    </row>
+    <row r="183" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A183" s="12"/>
+      <c r="B183" s="14"/>
+      <c r="C183" s="12"/>
+      <c r="D183" s="12"/>
+    </row>
+    <row r="184" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A184" s="12"/>
+      <c r="B184" s="14"/>
+      <c r="C184" s="12"/>
+      <c r="D184" s="12"/>
+    </row>
+    <row r="185" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A185" s="12"/>
+      <c r="B185" s="14"/>
+      <c r="C185" s="12"/>
+      <c r="D185" s="12"/>
+    </row>
+    <row r="186" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A186" s="12"/>
+      <c r="B186" s="14"/>
+      <c r="C186" s="12"/>
+      <c r="D186" s="12"/>
+    </row>
+    <row r="187" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A187" s="12"/>
+      <c r="B187" s="14"/>
+      <c r="C187" s="12"/>
+      <c r="D187" s="12"/>
+    </row>
+    <row r="188" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A188" s="12"/>
+      <c r="B188" s="14"/>
+      <c r="C188" s="12"/>
+      <c r="D188" s="12"/>
+    </row>
+    <row r="189" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A189" s="12"/>
+      <c r="B189" s="14"/>
+      <c r="C189" s="12"/>
+      <c r="D189" s="12"/>
+    </row>
+    <row r="190" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A190" s="12"/>
+      <c r="B190" s="14"/>
+      <c r="C190" s="12"/>
+      <c r="D190" s="12"/>
+    </row>
+    <row r="191" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A191" s="12"/>
+      <c r="B191" s="14"/>
+      <c r="C191" s="12"/>
+      <c r="D191" s="12"/>
+    </row>
+    <row r="192" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A192" s="12"/>
+      <c r="B192" s="14"/>
+      <c r="C192" s="12"/>
+      <c r="D192" s="12"/>
+    </row>
+    <row r="193" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A193" s="12"/>
+      <c r="B193" s="14"/>
+      <c r="C193" s="12"/>
+      <c r="D193" s="12"/>
+    </row>
+    <row r="194" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A194" s="12"/>
+      <c r="B194" s="14"/>
+      <c r="C194" s="12"/>
+      <c r="D194" s="12"/>
+    </row>
+    <row r="195" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A195" s="12"/>
+      <c r="B195" s="14"/>
+      <c r="C195" s="12"/>
+      <c r="D195" s="12"/>
+    </row>
+    <row r="196" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A196" s="12"/>
+      <c r="B196" s="14"/>
+      <c r="C196" s="12"/>
+      <c r="D196" s="12"/>
+    </row>
+    <row r="197" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A197" s="12"/>
+      <c r="B197" s="14"/>
+      <c r="C197" s="12"/>
+      <c r="D197" s="12"/>
+    </row>
+    <row r="198" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A198" s="12"/>
+      <c r="B198" s="14"/>
+      <c r="C198" s="12"/>
+      <c r="D198" s="12"/>
+    </row>
+    <row r="199" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A199" s="12"/>
+      <c r="B199" s="14"/>
+      <c r="C199" s="12"/>
+      <c r="D199" s="12"/>
+    </row>
+    <row r="200" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A200" s="12"/>
+      <c r="B200" s="14"/>
+      <c r="C200" s="12"/>
+      <c r="D200" s="12"/>
+    </row>
+  </sheetData>
+  <dataValidations count="4">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="warning" errorTitle="Valor no previsto" error="Elige un valor de la lista." sqref="C10:C200">
+      <formula1>"Mímica,Tabú,Descríbelo,Tararéalo"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="warning" errorTitle="Valor no previsto" error="Elige un valor de la lista." sqref="C3:C200">
+      <formula1>"Mímica,Tabú,Descríbelo,Tararéalo"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" errorStyle="warning" errorTitle="Valor no previsto" error="Elige un valor de la lista." sqref="D10:D200">
+      <formula1>Concurso!$B$3:$B$100</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" errorStyle="warning" errorTitle="Valor no previsto" error="Elige un valor de la lista." sqref="D3:D200">
+      <formula1>Concurso!$B$3:$B$100</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <tabColor rgb="FF26A69A"/>
+  </sheetPr>
+  <dimension ref="A1:B200"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="12" customWidth="1"/>
+    <col min="2" max="2" width="22" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1" spans="1:2" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="10" t="s">
+        <v>410</v>
+      </c>
+      <c r="B1" s="10" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="2" ht="42" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" s="11" t="s">
+        <v>411</v>
+      </c>
+      <c r="B2" s="11" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" s="12">
+        <v>10</v>
+      </c>
+      <c r="B3" s="12"/>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" s="12">
+        <v>15</v>
+      </c>
+      <c r="B4" s="12"/>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" s="12"/>
+      <c r="B5" s="12"/>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" s="12"/>
+      <c r="B6" s="12"/>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" s="12"/>
+      <c r="B7" s="12"/>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" s="12"/>
+      <c r="B8" s="12"/>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" s="12"/>
+      <c r="B9" s="12"/>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" s="12"/>
+      <c r="B10" s="12"/>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" s="12"/>
+      <c r="B11" s="12"/>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12" s="12"/>
+      <c r="B12" s="12"/>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13" s="12"/>
+      <c r="B13" s="12"/>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A14" s="12"/>
+      <c r="B14" s="12"/>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A15" s="12"/>
+      <c r="B15" s="12"/>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A16" s="12"/>
+      <c r="B16" s="12"/>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A17" s="12"/>
+      <c r="B17" s="12"/>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A18" s="12"/>
+      <c r="B18" s="12"/>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A19" s="12"/>
+      <c r="B19" s="12"/>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A20" s="12"/>
+      <c r="B20" s="12"/>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A21" s="12"/>
+      <c r="B21" s="12"/>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A22" s="12"/>
+      <c r="B22" s="12"/>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A23" s="12"/>
+      <c r="B23" s="12"/>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A24" s="12"/>
+      <c r="B24" s="12"/>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A25" s="12"/>
+      <c r="B25" s="12"/>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A26" s="12"/>
+      <c r="B26" s="12"/>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A27" s="12"/>
+      <c r="B27" s="12"/>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A28" s="12"/>
+      <c r="B28" s="12"/>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A29" s="12"/>
+      <c r="B29" s="12"/>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A30" s="12"/>
+      <c r="B30" s="12"/>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A31" s="12"/>
+      <c r="B31" s="12"/>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A32" s="12"/>
+      <c r="B32" s="12"/>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A33" s="12"/>
+      <c r="B33" s="12"/>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A34" s="12"/>
+      <c r="B34" s="12"/>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A35" s="12"/>
+      <c r="B35" s="12"/>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A36" s="12"/>
+      <c r="B36" s="12"/>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A37" s="12"/>
+      <c r="B37" s="12"/>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A38" s="12"/>
+      <c r="B38" s="12"/>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A39" s="12"/>
+      <c r="B39" s="12"/>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A40" s="12"/>
+      <c r="B40" s="12"/>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A41" s="12"/>
+      <c r="B41" s="12"/>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A42" s="12"/>
+      <c r="B42" s="12"/>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A43" s="12"/>
+      <c r="B43" s="12"/>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A44" s="12"/>
+      <c r="B44" s="12"/>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A45" s="12"/>
+      <c r="B45" s="12"/>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A46" s="12"/>
+      <c r="B46" s="12"/>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A47" s="12"/>
+      <c r="B47" s="12"/>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A48" s="12"/>
+      <c r="B48" s="12"/>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A49" s="12"/>
+      <c r="B49" s="12"/>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A50" s="12"/>
+      <c r="B50" s="12"/>
+    </row>
+    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A51" s="12"/>
+      <c r="B51" s="12"/>
+    </row>
+    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A52" s="12"/>
+      <c r="B52" s="12"/>
+    </row>
+    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A53" s="12"/>
+      <c r="B53" s="12"/>
+    </row>
+    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A54" s="12"/>
+      <c r="B54" s="12"/>
+    </row>
+    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A55" s="12"/>
+      <c r="B55" s="12"/>
+    </row>
+    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A56" s="12"/>
+      <c r="B56" s="12"/>
+    </row>
+    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A57" s="12"/>
+      <c r="B57" s="12"/>
+    </row>
+    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A58" s="12"/>
+      <c r="B58" s="12"/>
+    </row>
+    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A59" s="12"/>
+      <c r="B59" s="12"/>
+    </row>
+    <row r="60" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A60" s="12"/>
+      <c r="B60" s="12"/>
+    </row>
+    <row r="61" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A61" s="12"/>
+      <c r="B61" s="12"/>
+    </row>
+    <row r="62" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A62" s="12"/>
+      <c r="B62" s="12"/>
+    </row>
+    <row r="63" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A63" s="12"/>
+      <c r="B63" s="12"/>
+    </row>
+    <row r="64" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A64" s="12"/>
+      <c r="B64" s="12"/>
+    </row>
+    <row r="65" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A65" s="12"/>
+      <c r="B65" s="12"/>
+    </row>
+    <row r="66" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A66" s="12"/>
+      <c r="B66" s="12"/>
+    </row>
+    <row r="67" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A67" s="12"/>
+      <c r="B67" s="12"/>
+    </row>
+    <row r="68" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A68" s="12"/>
+      <c r="B68" s="12"/>
+    </row>
+    <row r="69" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A69" s="12"/>
+      <c r="B69" s="12"/>
+    </row>
+    <row r="70" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A70" s="12"/>
+      <c r="B70" s="12"/>
+    </row>
+    <row r="71" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A71" s="12"/>
+      <c r="B71" s="12"/>
+    </row>
+    <row r="72" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A72" s="12"/>
+      <c r="B72" s="12"/>
+    </row>
+    <row r="73" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A73" s="12"/>
+      <c r="B73" s="12"/>
+    </row>
+    <row r="74" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A74" s="12"/>
+      <c r="B74" s="12"/>
+    </row>
+    <row r="75" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A75" s="12"/>
+      <c r="B75" s="12"/>
+    </row>
+    <row r="76" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A76" s="12"/>
+      <c r="B76" s="12"/>
+    </row>
+    <row r="77" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A77" s="12"/>
+      <c r="B77" s="12"/>
+    </row>
+    <row r="78" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A78" s="12"/>
+      <c r="B78" s="12"/>
+    </row>
+    <row r="79" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A79" s="12"/>
+      <c r="B79" s="12"/>
+    </row>
+    <row r="80" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A80" s="12"/>
+      <c r="B80" s="12"/>
+    </row>
+    <row r="81" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A81" s="12"/>
+      <c r="B81" s="12"/>
+    </row>
+    <row r="82" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A82" s="12"/>
+      <c r="B82" s="12"/>
+    </row>
+    <row r="83" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A83" s="12"/>
+      <c r="B83" s="12"/>
+    </row>
+    <row r="84" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A84" s="12"/>
+      <c r="B84" s="12"/>
+    </row>
+    <row r="85" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A85" s="12"/>
+      <c r="B85" s="12"/>
+    </row>
+    <row r="86" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A86" s="12"/>
+      <c r="B86" s="12"/>
+    </row>
+    <row r="87" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A87" s="12"/>
+      <c r="B87" s="12"/>
+    </row>
+    <row r="88" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A88" s="12"/>
+      <c r="B88" s="12"/>
+    </row>
+    <row r="89" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A89" s="12"/>
+      <c r="B89" s="12"/>
+    </row>
+    <row r="90" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A90" s="12"/>
+      <c r="B90" s="12"/>
+    </row>
+    <row r="91" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A91" s="12"/>
+      <c r="B91" s="12"/>
+    </row>
+    <row r="92" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A92" s="12"/>
+      <c r="B92" s="12"/>
+    </row>
+    <row r="93" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A93" s="12"/>
+      <c r="B93" s="12"/>
+    </row>
+    <row r="94" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A94" s="12"/>
+      <c r="B94" s="12"/>
+    </row>
+    <row r="95" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A95" s="12"/>
+      <c r="B95" s="12"/>
+    </row>
+    <row r="96" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A96" s="12"/>
+      <c r="B96" s="12"/>
+    </row>
+    <row r="97" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A97" s="12"/>
+      <c r="B97" s="12"/>
+    </row>
+    <row r="98" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A98" s="12"/>
+      <c r="B98" s="12"/>
+    </row>
+    <row r="99" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A99" s="12"/>
+      <c r="B99" s="12"/>
+    </row>
+    <row r="100" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A100" s="12"/>
+      <c r="B100" s="12"/>
+    </row>
+    <row r="101" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A101" s="12"/>
+      <c r="B101" s="12"/>
+    </row>
+    <row r="102" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A102" s="12"/>
+      <c r="B102" s="12"/>
+    </row>
+    <row r="103" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A103" s="12"/>
+      <c r="B103" s="12"/>
+    </row>
+    <row r="104" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A104" s="12"/>
+      <c r="B104" s="12"/>
+    </row>
+    <row r="105" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A105" s="12"/>
+      <c r="B105" s="12"/>
+    </row>
+    <row r="106" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A106" s="12"/>
+      <c r="B106" s="12"/>
+    </row>
+    <row r="107" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A107" s="12"/>
+      <c r="B107" s="12"/>
+    </row>
+    <row r="108" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A108" s="12"/>
+      <c r="B108" s="12"/>
+    </row>
+    <row r="109" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A109" s="12"/>
+      <c r="B109" s="12"/>
+    </row>
+    <row r="110" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A110" s="12"/>
+      <c r="B110" s="12"/>
+    </row>
+    <row r="111" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A111" s="12"/>
+      <c r="B111" s="12"/>
+    </row>
+    <row r="112" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A112" s="12"/>
+      <c r="B112" s="12"/>
+    </row>
+    <row r="113" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A113" s="12"/>
+      <c r="B113" s="12"/>
+    </row>
+    <row r="114" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A114" s="12"/>
+      <c r="B114" s="12"/>
+    </row>
+    <row r="115" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A115" s="12"/>
+      <c r="B115" s="12"/>
+    </row>
+    <row r="116" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A116" s="12"/>
+      <c r="B116" s="12"/>
+    </row>
+    <row r="117" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A117" s="12"/>
+      <c r="B117" s="12"/>
+    </row>
+    <row r="118" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A118" s="12"/>
+      <c r="B118" s="12"/>
+    </row>
+    <row r="119" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A119" s="12"/>
+      <c r="B119" s="12"/>
+    </row>
+    <row r="120" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A120" s="12"/>
+      <c r="B120" s="12"/>
+    </row>
+    <row r="121" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A121" s="12"/>
+      <c r="B121" s="12"/>
+    </row>
+    <row r="122" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A122" s="12"/>
+      <c r="B122" s="12"/>
+    </row>
+    <row r="123" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A123" s="12"/>
+      <c r="B123" s="12"/>
+    </row>
+    <row r="124" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A124" s="12"/>
+      <c r="B124" s="12"/>
+    </row>
+    <row r="125" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A125" s="12"/>
+      <c r="B125" s="12"/>
+    </row>
+    <row r="126" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A126" s="12"/>
+      <c r="B126" s="12"/>
+    </row>
+    <row r="127" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A127" s="12"/>
+      <c r="B127" s="12"/>
+    </row>
+    <row r="128" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A128" s="12"/>
+      <c r="B128" s="12"/>
+    </row>
+    <row r="129" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A129" s="12"/>
+      <c r="B129" s="12"/>
+    </row>
+    <row r="130" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A130" s="12"/>
+      <c r="B130" s="12"/>
+    </row>
+    <row r="131" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A131" s="12"/>
+      <c r="B131" s="12"/>
+    </row>
+    <row r="132" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A132" s="12"/>
+      <c r="B132" s="12"/>
+    </row>
+    <row r="133" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A133" s="12"/>
+      <c r="B133" s="12"/>
+    </row>
+    <row r="134" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A134" s="12"/>
+      <c r="B134" s="12"/>
+    </row>
+    <row r="135" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A135" s="12"/>
+      <c r="B135" s="12"/>
+    </row>
+    <row r="136" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A136" s="12"/>
+      <c r="B136" s="12"/>
+    </row>
+    <row r="137" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A137" s="12"/>
+      <c r="B137" s="12"/>
+    </row>
+    <row r="138" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A138" s="12"/>
+      <c r="B138" s="12"/>
+    </row>
+    <row r="139" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A139" s="12"/>
+      <c r="B139" s="12"/>
+    </row>
+    <row r="140" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A140" s="12"/>
+      <c r="B140" s="12"/>
+    </row>
+    <row r="141" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A141" s="12"/>
+      <c r="B141" s="12"/>
+    </row>
+    <row r="142" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A142" s="12"/>
+      <c r="B142" s="12"/>
+    </row>
+    <row r="143" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A143" s="12"/>
+      <c r="B143" s="12"/>
+    </row>
+    <row r="144" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A144" s="12"/>
+      <c r="B144" s="12"/>
+    </row>
+    <row r="145" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A145" s="12"/>
+      <c r="B145" s="12"/>
+    </row>
+    <row r="146" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A146" s="12"/>
+      <c r="B146" s="12"/>
+    </row>
+    <row r="147" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A147" s="12"/>
+      <c r="B147" s="12"/>
+    </row>
+    <row r="148" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A148" s="12"/>
+      <c r="B148" s="12"/>
+    </row>
+    <row r="149" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A149" s="12"/>
+      <c r="B149" s="12"/>
+    </row>
+    <row r="150" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A150" s="12"/>
+      <c r="B150" s="12"/>
+    </row>
+    <row r="151" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A151" s="12"/>
+      <c r="B151" s="12"/>
+    </row>
+    <row r="152" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A152" s="12"/>
+      <c r="B152" s="12"/>
+    </row>
+    <row r="153" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A153" s="12"/>
+      <c r="B153" s="12"/>
+    </row>
+    <row r="154" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A154" s="12"/>
+      <c r="B154" s="12"/>
+    </row>
+    <row r="155" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A155" s="12"/>
+      <c r="B155" s="12"/>
+    </row>
+    <row r="156" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A156" s="12"/>
+      <c r="B156" s="12"/>
+    </row>
+    <row r="157" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A157" s="12"/>
+      <c r="B157" s="12"/>
+    </row>
+    <row r="158" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A158" s="12"/>
+      <c r="B158" s="12"/>
+    </row>
+    <row r="159" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A159" s="12"/>
+      <c r="B159" s="12"/>
+    </row>
+    <row r="160" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A160" s="12"/>
+      <c r="B160" s="12"/>
+    </row>
+    <row r="161" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A161" s="12"/>
+      <c r="B161" s="12"/>
+    </row>
+    <row r="162" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A162" s="12"/>
+      <c r="B162" s="12"/>
+    </row>
+    <row r="163" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A163" s="12"/>
+      <c r="B163" s="12"/>
+    </row>
+    <row r="164" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A164" s="12"/>
+      <c r="B164" s="12"/>
+    </row>
+    <row r="165" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A165" s="12"/>
+      <c r="B165" s="12"/>
+    </row>
+    <row r="166" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A166" s="12"/>
+      <c r="B166" s="12"/>
+    </row>
+    <row r="167" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A167" s="12"/>
+      <c r="B167" s="12"/>
+    </row>
+    <row r="168" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A168" s="12"/>
+      <c r="B168" s="12"/>
+    </row>
+    <row r="169" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A169" s="12"/>
+      <c r="B169" s="12"/>
+    </row>
+    <row r="170" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A170" s="12"/>
+      <c r="B170" s="12"/>
+    </row>
+    <row r="171" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A171" s="12"/>
+      <c r="B171" s="12"/>
+    </row>
+    <row r="172" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A172" s="12"/>
+      <c r="B172" s="12"/>
+    </row>
+    <row r="173" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A173" s="12"/>
+      <c r="B173" s="12"/>
+    </row>
+    <row r="174" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A174" s="12"/>
+      <c r="B174" s="12"/>
+    </row>
+    <row r="175" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A175" s="12"/>
+      <c r="B175" s="12"/>
+    </row>
+    <row r="176" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A176" s="12"/>
+      <c r="B176" s="12"/>
+    </row>
+    <row r="177" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A177" s="12"/>
+      <c r="B177" s="12"/>
+    </row>
+    <row r="178" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A178" s="12"/>
+      <c r="B178" s="12"/>
+    </row>
+    <row r="179" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A179" s="12"/>
+      <c r="B179" s="12"/>
+    </row>
+    <row r="180" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A180" s="12"/>
+      <c r="B180" s="12"/>
+    </row>
+    <row r="181" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A181" s="12"/>
+      <c r="B181" s="12"/>
+    </row>
+    <row r="182" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A182" s="12"/>
+      <c r="B182" s="12"/>
+    </row>
+    <row r="183" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A183" s="12"/>
+      <c r="B183" s="12"/>
+    </row>
+    <row r="184" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A184" s="12"/>
+      <c r="B184" s="12"/>
+    </row>
+    <row r="185" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A185" s="12"/>
+      <c r="B185" s="12"/>
+    </row>
+    <row r="186" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A186" s="12"/>
+      <c r="B186" s="12"/>
+    </row>
+    <row r="187" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A187" s="12"/>
+      <c r="B187" s="12"/>
+    </row>
+    <row r="188" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A188" s="12"/>
+      <c r="B188" s="12"/>
+    </row>
+    <row r="189" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A189" s="12"/>
+      <c r="B189" s="12"/>
+    </row>
+    <row r="190" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A190" s="12"/>
+      <c r="B190" s="12"/>
+    </row>
+    <row r="191" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A191" s="12"/>
+      <c r="B191" s="12"/>
+    </row>
+    <row r="192" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A192" s="12"/>
+      <c r="B192" s="12"/>
+    </row>
+    <row r="193" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A193" s="12"/>
+      <c r="B193" s="12"/>
+    </row>
+    <row r="194" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A194" s="12"/>
+      <c r="B194" s="12"/>
+    </row>
+    <row r="195" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A195" s="12"/>
+      <c r="B195" s="12"/>
+    </row>
+    <row r="196" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A196" s="12"/>
+      <c r="B196" s="12"/>
+    </row>
+    <row r="197" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A197" s="12"/>
+      <c r="B197" s="12"/>
+    </row>
+    <row r="198" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A198" s="12"/>
+      <c r="B198" s="12"/>
+    </row>
+    <row r="199" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A199" s="12"/>
+      <c r="B199" s="12"/>
+    </row>
+    <row r="200" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A200" s="12"/>
+      <c r="B200" s="12"/>
+    </row>
+  </sheetData>
+  <dataValidations count="2">
+    <dataValidation type="list" allowBlank="1" errorStyle="warning" errorTitle="Valor no previsto" error="Elige un valor de la lista." sqref="B10:B200">
+      <formula1>Concurso!$B$3:$B$100</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" errorStyle="warning" errorTitle="Valor no previsto" error="Elige un valor de la lista." sqref="B3:B200">
+      <formula1>Concurso!$B$3:$B$100</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <tabColor rgb="FFFFB300"/>
+  </sheetPr>
+  <dimension ref="A1:G200"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="46" customWidth="1"/>
+    <col min="2" max="5" width="20" customWidth="1"/>
+    <col min="6" max="6" width="10" customWidth="1"/>
+    <col min="7" max="7" width="22" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="10" t="s">
+        <v>132</v>
+      </c>
+      <c r="B1" s="10" t="s">
+        <v>163</v>
+      </c>
+      <c r="C1" s="10" t="s">
+        <v>164</v>
+      </c>
+      <c r="D1" s="10" t="s">
+        <v>165</v>
+      </c>
+      <c r="E1" s="10" t="s">
+        <v>166</v>
+      </c>
+      <c r="F1" s="10" t="s">
+        <v>167</v>
+      </c>
+      <c r="G1" s="10" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="2" ht="42" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2" s="11" t="s">
+        <v>412</v>
+      </c>
+      <c r="B2" s="11" t="s">
+        <v>171</v>
+      </c>
+      <c r="C2" s="11" t="s">
+        <v>172</v>
+      </c>
+      <c r="D2" s="11" t="s">
+        <v>173</v>
+      </c>
+      <c r="E2" s="11" t="s">
+        <v>174</v>
+      </c>
+      <c r="F2" s="11" t="s">
+        <v>175</v>
+      </c>
+      <c r="G2" s="11" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3" s="14" t="s">
+        <v>413</v>
+      </c>
+      <c r="B3" s="14" t="s">
+        <v>414</v>
+      </c>
+      <c r="C3" s="14" t="s">
+        <v>415</v>
+      </c>
+      <c r="D3" s="14" t="s">
+        <v>416</v>
+      </c>
+      <c r="E3" s="14" t="s">
+        <v>417</v>
+      </c>
+      <c r="F3" s="12" t="s">
+        <v>163</v>
+      </c>
+      <c r="G3" s="12"/>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4" s="14" t="s">
+        <v>418</v>
+      </c>
+      <c r="B4" s="14" t="s">
+        <v>419</v>
+      </c>
+      <c r="C4" s="14" t="s">
+        <v>420</v>
+      </c>
+      <c r="D4" s="14" t="s">
+        <v>417</v>
+      </c>
+      <c r="E4" s="14" t="s">
+        <v>421</v>
+      </c>
+      <c r="F4" s="12" t="s">
+        <v>165</v>
+      </c>
+      <c r="G4" s="12"/>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5" s="14"/>
+      <c r="B5" s="14"/>
+      <c r="C5" s="14"/>
+      <c r="D5" s="14"/>
+      <c r="E5" s="14"/>
+      <c r="F5" s="12"/>
+      <c r="G5" s="12"/>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A6" s="14"/>
+      <c r="B6" s="14"/>
+      <c r="C6" s="14"/>
+      <c r="D6" s="14"/>
+      <c r="E6" s="14"/>
+      <c r="F6" s="12"/>
+      <c r="G6" s="12"/>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7" s="14"/>
+      <c r="B7" s="14"/>
+      <c r="C7" s="14"/>
+      <c r="D7" s="14"/>
+      <c r="E7" s="14"/>
+      <c r="F7" s="12"/>
+      <c r="G7" s="12"/>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A8" s="14"/>
+      <c r="B8" s="14"/>
+      <c r="C8" s="14"/>
+      <c r="D8" s="14"/>
+      <c r="E8" s="14"/>
+      <c r="F8" s="12"/>
+      <c r="G8" s="12"/>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A9" s="14"/>
+      <c r="B9" s="14"/>
+      <c r="C9" s="14"/>
+      <c r="D9" s="14"/>
+      <c r="E9" s="14"/>
+      <c r="F9" s="12"/>
+      <c r="G9" s="12"/>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A10" s="14"/>
+      <c r="B10" s="14"/>
+      <c r="C10" s="14"/>
+      <c r="D10" s="14"/>
+      <c r="E10" s="14"/>
+      <c r="F10" s="12"/>
+      <c r="G10" s="12"/>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A11" s="14"/>
+      <c r="B11" s="14"/>
+      <c r="C11" s="14"/>
+      <c r="D11" s="14"/>
+      <c r="E11" s="14"/>
+      <c r="F11" s="12"/>
+      <c r="G11" s="12"/>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A12" s="14"/>
+      <c r="B12" s="14"/>
+      <c r="C12" s="14"/>
+      <c r="D12" s="14"/>
+      <c r="E12" s="14"/>
+      <c r="F12" s="12"/>
+      <c r="G12" s="12"/>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A13" s="14"/>
+      <c r="B13" s="14"/>
+      <c r="C13" s="14"/>
+      <c r="D13" s="14"/>
+      <c r="E13" s="14"/>
+      <c r="F13" s="12"/>
+      <c r="G13" s="12"/>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A14" s="14"/>
+      <c r="B14" s="14"/>
+      <c r="C14" s="14"/>
+      <c r="D14" s="14"/>
+      <c r="E14" s="14"/>
+      <c r="F14" s="12"/>
+      <c r="G14" s="12"/>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A15" s="14"/>
+      <c r="B15" s="14"/>
+      <c r="C15" s="14"/>
+      <c r="D15" s="14"/>
+      <c r="E15" s="14"/>
+      <c r="F15" s="12"/>
+      <c r="G15" s="12"/>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A16" s="14"/>
+      <c r="B16" s="14"/>
+      <c r="C16" s="14"/>
+      <c r="D16" s="14"/>
+      <c r="E16" s="14"/>
+      <c r="F16" s="12"/>
+      <c r="G16" s="12"/>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A17" s="14"/>
+      <c r="B17" s="14"/>
+      <c r="C17" s="14"/>
+      <c r="D17" s="14"/>
+      <c r="E17" s="14"/>
+      <c r="F17" s="12"/>
+      <c r="G17" s="12"/>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A18" s="14"/>
+      <c r="B18" s="14"/>
+      <c r="C18" s="14"/>
+      <c r="D18" s="14"/>
+      <c r="E18" s="14"/>
+      <c r="F18" s="12"/>
+      <c r="G18" s="12"/>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A19" s="14"/>
+      <c r="B19" s="14"/>
+      <c r="C19" s="14"/>
+      <c r="D19" s="14"/>
+      <c r="E19" s="14"/>
+      <c r="F19" s="12"/>
+      <c r="G19" s="12"/>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A20" s="14"/>
+      <c r="B20" s="14"/>
+      <c r="C20" s="14"/>
+      <c r="D20" s="14"/>
+      <c r="E20" s="14"/>
+      <c r="F20" s="12"/>
+      <c r="G20" s="12"/>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A21" s="14"/>
+      <c r="B21" s="14"/>
+      <c r="C21" s="14"/>
+      <c r="D21" s="14"/>
+      <c r="E21" s="14"/>
+      <c r="F21" s="12"/>
+      <c r="G21" s="12"/>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A22" s="14"/>
+      <c r="B22" s="14"/>
+      <c r="C22" s="14"/>
+      <c r="D22" s="14"/>
+      <c r="E22" s="14"/>
+      <c r="F22" s="12"/>
+      <c r="G22" s="12"/>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A23" s="14"/>
+      <c r="B23" s="14"/>
+      <c r="C23" s="14"/>
+      <c r="D23" s="14"/>
+      <c r="E23" s="14"/>
+      <c r="F23" s="12"/>
+      <c r="G23" s="12"/>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A24" s="14"/>
+      <c r="B24" s="14"/>
+      <c r="C24" s="14"/>
+      <c r="D24" s="14"/>
+      <c r="E24" s="14"/>
+      <c r="F24" s="12"/>
+      <c r="G24" s="12"/>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A25" s="14"/>
+      <c r="B25" s="14"/>
+      <c r="C25" s="14"/>
+      <c r="D25" s="14"/>
+      <c r="E25" s="14"/>
+      <c r="F25" s="12"/>
+      <c r="G25" s="12"/>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A26" s="14"/>
+      <c r="B26" s="14"/>
+      <c r="C26" s="14"/>
+      <c r="D26" s="14"/>
+      <c r="E26" s="14"/>
+      <c r="F26" s="12"/>
+      <c r="G26" s="12"/>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A27" s="14"/>
+      <c r="B27" s="14"/>
+      <c r="C27" s="14"/>
+      <c r="D27" s="14"/>
+      <c r="E27" s="14"/>
+      <c r="F27" s="12"/>
+      <c r="G27" s="12"/>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A28" s="14"/>
+      <c r="B28" s="14"/>
+      <c r="C28" s="14"/>
+      <c r="D28" s="14"/>
+      <c r="E28" s="14"/>
+      <c r="F28" s="12"/>
+      <c r="G28" s="12"/>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A29" s="14"/>
+      <c r="B29" s="14"/>
+      <c r="C29" s="14"/>
+      <c r="D29" s="14"/>
+      <c r="E29" s="14"/>
+      <c r="F29" s="12"/>
+      <c r="G29" s="12"/>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A30" s="14"/>
+      <c r="B30" s="14"/>
+      <c r="C30" s="14"/>
+      <c r="D30" s="14"/>
+      <c r="E30" s="14"/>
+      <c r="F30" s="12"/>
+      <c r="G30" s="12"/>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A31" s="14"/>
+      <c r="B31" s="14"/>
+      <c r="C31" s="14"/>
+      <c r="D31" s="14"/>
+      <c r="E31" s="14"/>
+      <c r="F31" s="12"/>
+      <c r="G31" s="12"/>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A32" s="14"/>
+      <c r="B32" s="14"/>
+      <c r="C32" s="14"/>
+      <c r="D32" s="14"/>
+      <c r="E32" s="14"/>
+      <c r="F32" s="12"/>
+      <c r="G32" s="12"/>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A33" s="14"/>
+      <c r="B33" s="14"/>
+      <c r="C33" s="14"/>
+      <c r="D33" s="14"/>
+      <c r="E33" s="14"/>
+      <c r="F33" s="12"/>
+      <c r="G33" s="12"/>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A34" s="14"/>
+      <c r="B34" s="14"/>
+      <c r="C34" s="14"/>
+      <c r="D34" s="14"/>
+      <c r="E34" s="14"/>
+      <c r="F34" s="12"/>
+      <c r="G34" s="12"/>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A35" s="14"/>
+      <c r="B35" s="14"/>
+      <c r="C35" s="14"/>
+      <c r="D35" s="14"/>
+      <c r="E35" s="14"/>
+      <c r="F35" s="12"/>
+      <c r="G35" s="12"/>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A36" s="14"/>
+      <c r="B36" s="14"/>
+      <c r="C36" s="14"/>
+      <c r="D36" s="14"/>
+      <c r="E36" s="14"/>
+      <c r="F36" s="12"/>
+      <c r="G36" s="12"/>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A37" s="14"/>
+      <c r="B37" s="14"/>
+      <c r="C37" s="14"/>
+      <c r="D37" s="14"/>
+      <c r="E37" s="14"/>
+      <c r="F37" s="12"/>
+      <c r="G37" s="12"/>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A38" s="14"/>
+      <c r="B38" s="14"/>
+      <c r="C38" s="14"/>
+      <c r="D38" s="14"/>
+      <c r="E38" s="14"/>
+      <c r="F38" s="12"/>
+      <c r="G38" s="12"/>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A39" s="14"/>
+      <c r="B39" s="14"/>
+      <c r="C39" s="14"/>
+      <c r="D39" s="14"/>
+      <c r="E39" s="14"/>
+      <c r="F39" s="12"/>
+      <c r="G39" s="12"/>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A40" s="14"/>
+      <c r="B40" s="14"/>
+      <c r="C40" s="14"/>
+      <c r="D40" s="14"/>
+      <c r="E40" s="14"/>
+      <c r="F40" s="12"/>
+      <c r="G40" s="12"/>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A41" s="14"/>
+      <c r="B41" s="14"/>
+      <c r="C41" s="14"/>
+      <c r="D41" s="14"/>
+      <c r="E41" s="14"/>
+      <c r="F41" s="12"/>
+      <c r="G41" s="12"/>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A42" s="14"/>
+      <c r="B42" s="14"/>
+      <c r="C42" s="14"/>
+      <c r="D42" s="14"/>
+      <c r="E42" s="14"/>
+      <c r="F42" s="12"/>
+      <c r="G42" s="12"/>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A43" s="14"/>
+      <c r="B43" s="14"/>
+      <c r="C43" s="14"/>
+      <c r="D43" s="14"/>
+      <c r="E43" s="14"/>
+      <c r="F43" s="12"/>
+      <c r="G43" s="12"/>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A44" s="14"/>
+      <c r="B44" s="14"/>
+      <c r="C44" s="14"/>
+      <c r="D44" s="14"/>
+      <c r="E44" s="14"/>
+      <c r="F44" s="12"/>
+      <c r="G44" s="12"/>
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A45" s="14"/>
+      <c r="B45" s="14"/>
+      <c r="C45" s="14"/>
+      <c r="D45" s="14"/>
+      <c r="E45" s="14"/>
+      <c r="F45" s="12"/>
+      <c r="G45" s="12"/>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A46" s="14"/>
+      <c r="B46" s="14"/>
+      <c r="C46" s="14"/>
+      <c r="D46" s="14"/>
+      <c r="E46" s="14"/>
+      <c r="F46" s="12"/>
+      <c r="G46" s="12"/>
+    </row>
+    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A47" s="14"/>
+      <c r="B47" s="14"/>
+      <c r="C47" s="14"/>
+      <c r="D47" s="14"/>
+      <c r="E47" s="14"/>
+      <c r="F47" s="12"/>
+      <c r="G47" s="12"/>
+    </row>
+    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A48" s="14"/>
+      <c r="B48" s="14"/>
+      <c r="C48" s="14"/>
+      <c r="D48" s="14"/>
+      <c r="E48" s="14"/>
+      <c r="F48" s="12"/>
+      <c r="G48" s="12"/>
+    </row>
+    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A49" s="14"/>
+      <c r="B49" s="14"/>
+      <c r="C49" s="14"/>
+      <c r="D49" s="14"/>
+      <c r="E49" s="14"/>
+      <c r="F49" s="12"/>
+      <c r="G49" s="12"/>
+    </row>
+    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A50" s="14"/>
+      <c r="B50" s="14"/>
+      <c r="C50" s="14"/>
+      <c r="D50" s="14"/>
+      <c r="E50" s="14"/>
+      <c r="F50" s="12"/>
+      <c r="G50" s="12"/>
+    </row>
+    <row r="51" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A51" s="14"/>
+      <c r="B51" s="14"/>
+      <c r="C51" s="14"/>
+      <c r="D51" s="14"/>
+      <c r="E51" s="14"/>
+      <c r="F51" s="12"/>
+      <c r="G51" s="12"/>
+    </row>
+    <row r="52" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A52" s="14"/>
+      <c r="B52" s="14"/>
+      <c r="C52" s="14"/>
+      <c r="D52" s="14"/>
+      <c r="E52" s="14"/>
+      <c r="F52" s="12"/>
+      <c r="G52" s="12"/>
+    </row>
+    <row r="53" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A53" s="14"/>
+      <c r="B53" s="14"/>
+      <c r="C53" s="14"/>
+      <c r="D53" s="14"/>
+      <c r="E53" s="14"/>
+      <c r="F53" s="12"/>
+      <c r="G53" s="12"/>
+    </row>
+    <row r="54" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A54" s="14"/>
+      <c r="B54" s="14"/>
+      <c r="C54" s="14"/>
+      <c r="D54" s="14"/>
+      <c r="E54" s="14"/>
+      <c r="F54" s="12"/>
+      <c r="G54" s="12"/>
+    </row>
+    <row r="55" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A55" s="14"/>
+      <c r="B55" s="14"/>
+      <c r="C55" s="14"/>
+      <c r="D55" s="14"/>
+      <c r="E55" s="14"/>
+      <c r="F55" s="12"/>
+      <c r="G55" s="12"/>
+    </row>
+    <row r="56" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A56" s="14"/>
+      <c r="B56" s="14"/>
+      <c r="C56" s="14"/>
+      <c r="D56" s="14"/>
+      <c r="E56" s="14"/>
+      <c r="F56" s="12"/>
+      <c r="G56" s="12"/>
+    </row>
+    <row r="57" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A57" s="14"/>
+      <c r="B57" s="14"/>
+      <c r="C57" s="14"/>
+      <c r="D57" s="14"/>
+      <c r="E57" s="14"/>
+      <c r="F57" s="12"/>
+      <c r="G57" s="12"/>
+    </row>
+    <row r="58" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A58" s="14"/>
+      <c r="B58" s="14"/>
+      <c r="C58" s="14"/>
+      <c r="D58" s="14"/>
+      <c r="E58" s="14"/>
+      <c r="F58" s="12"/>
+      <c r="G58" s="12"/>
+    </row>
+    <row r="59" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A59" s="14"/>
+      <c r="B59" s="14"/>
+      <c r="C59" s="14"/>
+      <c r="D59" s="14"/>
+      <c r="E59" s="14"/>
+      <c r="F59" s="12"/>
+      <c r="G59" s="12"/>
+    </row>
+    <row r="60" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A60" s="14"/>
+      <c r="B60" s="14"/>
+      <c r="C60" s="14"/>
+      <c r="D60" s="14"/>
+      <c r="E60" s="14"/>
+      <c r="F60" s="12"/>
+      <c r="G60" s="12"/>
+    </row>
+    <row r="61" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A61" s="14"/>
+      <c r="B61" s="14"/>
+      <c r="C61" s="14"/>
+      <c r="D61" s="14"/>
+      <c r="E61" s="14"/>
+      <c r="F61" s="12"/>
+      <c r="G61" s="12"/>
+    </row>
+    <row r="62" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A62" s="14"/>
+      <c r="B62" s="14"/>
+      <c r="C62" s="14"/>
+      <c r="D62" s="14"/>
+      <c r="E62" s="14"/>
+      <c r="F62" s="12"/>
+      <c r="G62" s="12"/>
+    </row>
+    <row r="63" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A63" s="14"/>
+      <c r="B63" s="14"/>
+      <c r="C63" s="14"/>
+      <c r="D63" s="14"/>
+      <c r="E63" s="14"/>
+      <c r="F63" s="12"/>
+      <c r="G63" s="12"/>
+    </row>
+    <row r="64" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A64" s="14"/>
+      <c r="B64" s="14"/>
+      <c r="C64" s="14"/>
+      <c r="D64" s="14"/>
+      <c r="E64" s="14"/>
+      <c r="F64" s="12"/>
+      <c r="G64" s="12"/>
+    </row>
+    <row r="65" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A65" s="14"/>
+      <c r="B65" s="14"/>
+      <c r="C65" s="14"/>
+      <c r="D65" s="14"/>
+      <c r="E65" s="14"/>
+      <c r="F65" s="12"/>
+      <c r="G65" s="12"/>
+    </row>
+    <row r="66" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A66" s="14"/>
+      <c r="B66" s="14"/>
+      <c r="C66" s="14"/>
+      <c r="D66" s="14"/>
+      <c r="E66" s="14"/>
+      <c r="F66" s="12"/>
+      <c r="G66" s="12"/>
+    </row>
+    <row r="67" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A67" s="14"/>
+      <c r="B67" s="14"/>
+      <c r="C67" s="14"/>
+      <c r="D67" s="14"/>
+      <c r="E67" s="14"/>
+      <c r="F67" s="12"/>
+      <c r="G67" s="12"/>
+    </row>
+    <row r="68" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A68" s="14"/>
+      <c r="B68" s="14"/>
+      <c r="C68" s="14"/>
+      <c r="D68" s="14"/>
+      <c r="E68" s="14"/>
+      <c r="F68" s="12"/>
+      <c r="G68" s="12"/>
+    </row>
+    <row r="69" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A69" s="14"/>
+      <c r="B69" s="14"/>
+      <c r="C69" s="14"/>
+      <c r="D69" s="14"/>
+      <c r="E69" s="14"/>
+      <c r="F69" s="12"/>
+      <c r="G69" s="12"/>
+    </row>
+    <row r="70" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A70" s="14"/>
+      <c r="B70" s="14"/>
+      <c r="C70" s="14"/>
+      <c r="D70" s="14"/>
+      <c r="E70" s="14"/>
+      <c r="F70" s="12"/>
+      <c r="G70" s="12"/>
+    </row>
+    <row r="71" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A71" s="14"/>
+      <c r="B71" s="14"/>
+      <c r="C71" s="14"/>
+      <c r="D71" s="14"/>
+      <c r="E71" s="14"/>
+      <c r="F71" s="12"/>
+      <c r="G71" s="12"/>
+    </row>
+    <row r="72" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A72" s="14"/>
+      <c r="B72" s="14"/>
+      <c r="C72" s="14"/>
+      <c r="D72" s="14"/>
+      <c r="E72" s="14"/>
+      <c r="F72" s="12"/>
+      <c r="G72" s="12"/>
+    </row>
+    <row r="73" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A73" s="14"/>
+      <c r="B73" s="14"/>
+      <c r="C73" s="14"/>
+      <c r="D73" s="14"/>
+      <c r="E73" s="14"/>
+      <c r="F73" s="12"/>
+      <c r="G73" s="12"/>
+    </row>
+    <row r="74" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A74" s="14"/>
+      <c r="B74" s="14"/>
+      <c r="C74" s="14"/>
+      <c r="D74" s="14"/>
+      <c r="E74" s="14"/>
+      <c r="F74" s="12"/>
+      <c r="G74" s="12"/>
+    </row>
+    <row r="75" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A75" s="14"/>
+      <c r="B75" s="14"/>
+      <c r="C75" s="14"/>
+      <c r="D75" s="14"/>
+      <c r="E75" s="14"/>
+      <c r="F75" s="12"/>
+      <c r="G75" s="12"/>
+    </row>
+    <row r="76" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A76" s="14"/>
+      <c r="B76" s="14"/>
+      <c r="C76" s="14"/>
+      <c r="D76" s="14"/>
+      <c r="E76" s="14"/>
+      <c r="F76" s="12"/>
+      <c r="G76" s="12"/>
+    </row>
+    <row r="77" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A77" s="14"/>
+      <c r="B77" s="14"/>
+      <c r="C77" s="14"/>
+      <c r="D77" s="14"/>
+      <c r="E77" s="14"/>
+      <c r="F77" s="12"/>
+      <c r="G77" s="12"/>
+    </row>
+    <row r="78" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A78" s="14"/>
+      <c r="B78" s="14"/>
+      <c r="C78" s="14"/>
+      <c r="D78" s="14"/>
+      <c r="E78" s="14"/>
+      <c r="F78" s="12"/>
+      <c r="G78" s="12"/>
+    </row>
+    <row r="79" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A79" s="14"/>
+      <c r="B79" s="14"/>
+      <c r="C79" s="14"/>
+      <c r="D79" s="14"/>
+      <c r="E79" s="14"/>
+      <c r="F79" s="12"/>
+      <c r="G79" s="12"/>
+    </row>
+    <row r="80" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A80" s="14"/>
+      <c r="B80" s="14"/>
+      <c r="C80" s="14"/>
+      <c r="D80" s="14"/>
+      <c r="E80" s="14"/>
+      <c r="F80" s="12"/>
+      <c r="G80" s="12"/>
+    </row>
+    <row r="81" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A81" s="14"/>
+      <c r="B81" s="14"/>
+      <c r="C81" s="14"/>
+      <c r="D81" s="14"/>
+      <c r="E81" s="14"/>
+      <c r="F81" s="12"/>
+      <c r="G81" s="12"/>
+    </row>
+    <row r="82" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A82" s="14"/>
+      <c r="B82" s="14"/>
+      <c r="C82" s="14"/>
+      <c r="D82" s="14"/>
+      <c r="E82" s="14"/>
+      <c r="F82" s="12"/>
+      <c r="G82" s="12"/>
+    </row>
+    <row r="83" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A83" s="14"/>
+      <c r="B83" s="14"/>
+      <c r="C83" s="14"/>
+      <c r="D83" s="14"/>
+      <c r="E83" s="14"/>
+      <c r="F83" s="12"/>
+      <c r="G83" s="12"/>
+    </row>
+    <row r="84" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A84" s="14"/>
+      <c r="B84" s="14"/>
+      <c r="C84" s="14"/>
+      <c r="D84" s="14"/>
+      <c r="E84" s="14"/>
+      <c r="F84" s="12"/>
+      <c r="G84" s="12"/>
+    </row>
+    <row r="85" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A85" s="14"/>
+      <c r="B85" s="14"/>
+      <c r="C85" s="14"/>
+      <c r="D85" s="14"/>
+      <c r="E85" s="14"/>
+      <c r="F85" s="12"/>
+      <c r="G85" s="12"/>
+    </row>
+    <row r="86" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A86" s="14"/>
+      <c r="B86" s="14"/>
+      <c r="C86" s="14"/>
+      <c r="D86" s="14"/>
+      <c r="E86" s="14"/>
+      <c r="F86" s="12"/>
+      <c r="G86" s="12"/>
+    </row>
+    <row r="87" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A87" s="14"/>
+      <c r="B87" s="14"/>
+      <c r="C87" s="14"/>
+      <c r="D87" s="14"/>
+      <c r="E87" s="14"/>
+      <c r="F87" s="12"/>
+      <c r="G87" s="12"/>
+    </row>
+    <row r="88" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A88" s="14"/>
+      <c r="B88" s="14"/>
+      <c r="C88" s="14"/>
+      <c r="D88" s="14"/>
+      <c r="E88" s="14"/>
+      <c r="F88" s="12"/>
+      <c r="G88" s="12"/>
+    </row>
+    <row r="89" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A89" s="14"/>
+      <c r="B89" s="14"/>
+      <c r="C89" s="14"/>
+      <c r="D89" s="14"/>
+      <c r="E89" s="14"/>
+      <c r="F89" s="12"/>
+      <c r="G89" s="12"/>
+    </row>
+    <row r="90" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A90" s="14"/>
+      <c r="B90" s="14"/>
+      <c r="C90" s="14"/>
+      <c r="D90" s="14"/>
+      <c r="E90" s="14"/>
+      <c r="F90" s="12"/>
+      <c r="G90" s="12"/>
+    </row>
+    <row r="91" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A91" s="14"/>
+      <c r="B91" s="14"/>
+      <c r="C91" s="14"/>
+      <c r="D91" s="14"/>
+      <c r="E91" s="14"/>
+      <c r="F91" s="12"/>
+      <c r="G91" s="12"/>
+    </row>
+    <row r="92" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A92" s="14"/>
+      <c r="B92" s="14"/>
+      <c r="C92" s="14"/>
+      <c r="D92" s="14"/>
+      <c r="E92" s="14"/>
+      <c r="F92" s="12"/>
+      <c r="G92" s="12"/>
+    </row>
+    <row r="93" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A93" s="14"/>
+      <c r="B93" s="14"/>
+      <c r="C93" s="14"/>
+      <c r="D93" s="14"/>
+      <c r="E93" s="14"/>
+      <c r="F93" s="12"/>
+      <c r="G93" s="12"/>
+    </row>
+    <row r="94" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A94" s="14"/>
+      <c r="B94" s="14"/>
+      <c r="C94" s="14"/>
+      <c r="D94" s="14"/>
+      <c r="E94" s="14"/>
+      <c r="F94" s="12"/>
+      <c r="G94" s="12"/>
+    </row>
+    <row r="95" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A95" s="14"/>
+      <c r="B95" s="14"/>
+      <c r="C95" s="14"/>
+      <c r="D95" s="14"/>
+      <c r="E95" s="14"/>
+      <c r="F95" s="12"/>
+      <c r="G95" s="12"/>
+    </row>
+    <row r="96" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A96" s="14"/>
+      <c r="B96" s="14"/>
+      <c r="C96" s="14"/>
+      <c r="D96" s="14"/>
+      <c r="E96" s="14"/>
+      <c r="F96" s="12"/>
+      <c r="G96" s="12"/>
+    </row>
+    <row r="97" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A97" s="14"/>
+      <c r="B97" s="14"/>
+      <c r="C97" s="14"/>
+      <c r="D97" s="14"/>
+      <c r="E97" s="14"/>
+      <c r="F97" s="12"/>
+      <c r="G97" s="12"/>
+    </row>
+    <row r="98" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A98" s="14"/>
+      <c r="B98" s="14"/>
+      <c r="C98" s="14"/>
+      <c r="D98" s="14"/>
+      <c r="E98" s="14"/>
+      <c r="F98" s="12"/>
+      <c r="G98" s="12"/>
+    </row>
+    <row r="99" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A99" s="14"/>
+      <c r="B99" s="14"/>
+      <c r="C99" s="14"/>
+      <c r="D99" s="14"/>
+      <c r="E99" s="14"/>
+      <c r="F99" s="12"/>
+      <c r="G99" s="12"/>
+    </row>
+    <row r="100" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A100" s="14"/>
+      <c r="B100" s="14"/>
+      <c r="C100" s="14"/>
+      <c r="D100" s="14"/>
+      <c r="E100" s="14"/>
+      <c r="F100" s="12"/>
+      <c r="G100" s="12"/>
+    </row>
+    <row r="101" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A101" s="14"/>
+      <c r="B101" s="14"/>
+      <c r="C101" s="14"/>
+      <c r="D101" s="14"/>
+      <c r="E101" s="14"/>
+      <c r="F101" s="12"/>
+      <c r="G101" s="12"/>
+    </row>
+    <row r="102" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A102" s="14"/>
+      <c r="B102" s="14"/>
+      <c r="C102" s="14"/>
+      <c r="D102" s="14"/>
+      <c r="E102" s="14"/>
+      <c r="F102" s="12"/>
+      <c r="G102" s="12"/>
+    </row>
+    <row r="103" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A103" s="14"/>
+      <c r="B103" s="14"/>
+      <c r="C103" s="14"/>
+      <c r="D103" s="14"/>
+      <c r="E103" s="14"/>
+      <c r="F103" s="12"/>
+      <c r="G103" s="12"/>
+    </row>
+    <row r="104" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A104" s="14"/>
+      <c r="B104" s="14"/>
+      <c r="C104" s="14"/>
+      <c r="D104" s="14"/>
+      <c r="E104" s="14"/>
+      <c r="F104" s="12"/>
+      <c r="G104" s="12"/>
+    </row>
+    <row r="105" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A105" s="14"/>
+      <c r="B105" s="14"/>
+      <c r="C105" s="14"/>
+      <c r="D105" s="14"/>
+      <c r="E105" s="14"/>
+      <c r="F105" s="12"/>
+      <c r="G105" s="12"/>
+    </row>
+    <row r="106" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A106" s="14"/>
+      <c r="B106" s="14"/>
+      <c r="C106" s="14"/>
+      <c r="D106" s="14"/>
+      <c r="E106" s="14"/>
+      <c r="F106" s="12"/>
+      <c r="G106" s="12"/>
+    </row>
+    <row r="107" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A107" s="14"/>
+      <c r="B107" s="14"/>
+      <c r="C107" s="14"/>
+      <c r="D107" s="14"/>
+      <c r="E107" s="14"/>
+      <c r="F107" s="12"/>
+      <c r="G107" s="12"/>
+    </row>
+    <row r="108" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A108" s="14"/>
+      <c r="B108" s="14"/>
+      <c r="C108" s="14"/>
+      <c r="D108" s="14"/>
+      <c r="E108" s="14"/>
+      <c r="F108" s="12"/>
+      <c r="G108" s="12"/>
+    </row>
+    <row r="109" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A109" s="14"/>
+      <c r="B109" s="14"/>
+      <c r="C109" s="14"/>
+      <c r="D109" s="14"/>
+      <c r="E109" s="14"/>
+      <c r="F109" s="12"/>
+      <c r="G109" s="12"/>
+    </row>
+    <row r="110" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A110" s="14"/>
+      <c r="B110" s="14"/>
+      <c r="C110" s="14"/>
+      <c r="D110" s="14"/>
+      <c r="E110" s="14"/>
+      <c r="F110" s="12"/>
+      <c r="G110" s="12"/>
+    </row>
+    <row r="111" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A111" s="14"/>
+      <c r="B111" s="14"/>
+      <c r="C111" s="14"/>
+      <c r="D111" s="14"/>
+      <c r="E111" s="14"/>
+      <c r="F111" s="12"/>
+      <c r="G111" s="12"/>
+    </row>
+    <row r="112" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A112" s="14"/>
+      <c r="B112" s="14"/>
+      <c r="C112" s="14"/>
+      <c r="D112" s="14"/>
+      <c r="E112" s="14"/>
+      <c r="F112" s="12"/>
+      <c r="G112" s="12"/>
+    </row>
+    <row r="113" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A113" s="14"/>
+      <c r="B113" s="14"/>
+      <c r="C113" s="14"/>
+      <c r="D113" s="14"/>
+      <c r="E113" s="14"/>
+      <c r="F113" s="12"/>
+      <c r="G113" s="12"/>
+    </row>
+    <row r="114" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A114" s="14"/>
+      <c r="B114" s="14"/>
+      <c r="C114" s="14"/>
+      <c r="D114" s="14"/>
+      <c r="E114" s="14"/>
+      <c r="F114" s="12"/>
+      <c r="G114" s="12"/>
+    </row>
+    <row r="115" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A115" s="14"/>
+      <c r="B115" s="14"/>
+      <c r="C115" s="14"/>
+      <c r="D115" s="14"/>
+      <c r="E115" s="14"/>
+      <c r="F115" s="12"/>
+      <c r="G115" s="12"/>
+    </row>
+    <row r="116" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A116" s="14"/>
+      <c r="B116" s="14"/>
+      <c r="C116" s="14"/>
+      <c r="D116" s="14"/>
+      <c r="E116" s="14"/>
+      <c r="F116" s="12"/>
+      <c r="G116" s="12"/>
+    </row>
+    <row r="117" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A117" s="14"/>
+      <c r="B117" s="14"/>
+      <c r="C117" s="14"/>
+      <c r="D117" s="14"/>
+      <c r="E117" s="14"/>
+      <c r="F117" s="12"/>
+      <c r="G117" s="12"/>
+    </row>
+    <row r="118" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A118" s="14"/>
+      <c r="B118" s="14"/>
+      <c r="C118" s="14"/>
+      <c r="D118" s="14"/>
+      <c r="E118" s="14"/>
+      <c r="F118" s="12"/>
+      <c r="G118" s="12"/>
+    </row>
+    <row r="119" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A119" s="14"/>
+      <c r="B119" s="14"/>
+      <c r="C119" s="14"/>
+      <c r="D119" s="14"/>
+      <c r="E119" s="14"/>
+      <c r="F119" s="12"/>
+      <c r="G119" s="12"/>
+    </row>
+    <row r="120" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A120" s="14"/>
+      <c r="B120" s="14"/>
+      <c r="C120" s="14"/>
+      <c r="D120" s="14"/>
+      <c r="E120" s="14"/>
+      <c r="F120" s="12"/>
+      <c r="G120" s="12"/>
+    </row>
+    <row r="121" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A121" s="14"/>
+      <c r="B121" s="14"/>
+      <c r="C121" s="14"/>
+      <c r="D121" s="14"/>
+      <c r="E121" s="14"/>
+      <c r="F121" s="12"/>
+      <c r="G121" s="12"/>
+    </row>
+    <row r="122" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A122" s="14"/>
+      <c r="B122" s="14"/>
+      <c r="C122" s="14"/>
+      <c r="D122" s="14"/>
+      <c r="E122" s="14"/>
+      <c r="F122" s="12"/>
+      <c r="G122" s="12"/>
+    </row>
+    <row r="123" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A123" s="14"/>
+      <c r="B123" s="14"/>
+      <c r="C123" s="14"/>
+      <c r="D123" s="14"/>
+      <c r="E123" s="14"/>
+      <c r="F123" s="12"/>
+      <c r="G123" s="12"/>
+    </row>
+    <row r="124" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A124" s="14"/>
+      <c r="B124" s="14"/>
+      <c r="C124" s="14"/>
+      <c r="D124" s="14"/>
+      <c r="E124" s="14"/>
+      <c r="F124" s="12"/>
+      <c r="G124" s="12"/>
+    </row>
+    <row r="125" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A125" s="14"/>
+      <c r="B125" s="14"/>
+      <c r="C125" s="14"/>
+      <c r="D125" s="14"/>
+      <c r="E125" s="14"/>
+      <c r="F125" s="12"/>
+      <c r="G125" s="12"/>
+    </row>
+    <row r="126" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A126" s="14"/>
+      <c r="B126" s="14"/>
+      <c r="C126" s="14"/>
+      <c r="D126" s="14"/>
+      <c r="E126" s="14"/>
+      <c r="F126" s="12"/>
+      <c r="G126" s="12"/>
+    </row>
+    <row r="127" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A127" s="14"/>
+      <c r="B127" s="14"/>
+      <c r="C127" s="14"/>
+      <c r="D127" s="14"/>
+      <c r="E127" s="14"/>
+      <c r="F127" s="12"/>
+      <c r="G127" s="12"/>
+    </row>
+    <row r="128" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A128" s="14"/>
+      <c r="B128" s="14"/>
+      <c r="C128" s="14"/>
+      <c r="D128" s="14"/>
+      <c r="E128" s="14"/>
+      <c r="F128" s="12"/>
+      <c r="G128" s="12"/>
+    </row>
+    <row r="129" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A129" s="14"/>
+      <c r="B129" s="14"/>
+      <c r="C129" s="14"/>
+      <c r="D129" s="14"/>
+      <c r="E129" s="14"/>
+      <c r="F129" s="12"/>
+      <c r="G129" s="12"/>
+    </row>
+    <row r="130" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A130" s="14"/>
+      <c r="B130" s="14"/>
+      <c r="C130" s="14"/>
+      <c r="D130" s="14"/>
+      <c r="E130" s="14"/>
+      <c r="F130" s="12"/>
+      <c r="G130" s="12"/>
+    </row>
+    <row r="131" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A131" s="14"/>
+      <c r="B131" s="14"/>
+      <c r="C131" s="14"/>
+      <c r="D131" s="14"/>
+      <c r="E131" s="14"/>
+      <c r="F131" s="12"/>
+      <c r="G131" s="12"/>
+    </row>
+    <row r="132" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A132" s="14"/>
+      <c r="B132" s="14"/>
+      <c r="C132" s="14"/>
+      <c r="D132" s="14"/>
+      <c r="E132" s="14"/>
+      <c r="F132" s="12"/>
+      <c r="G132" s="12"/>
+    </row>
+    <row r="133" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A133" s="14"/>
+      <c r="B133" s="14"/>
+      <c r="C133" s="14"/>
+      <c r="D133" s="14"/>
+      <c r="E133" s="14"/>
+      <c r="F133" s="12"/>
+      <c r="G133" s="12"/>
+    </row>
+    <row r="134" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A134" s="14"/>
+      <c r="B134" s="14"/>
+      <c r="C134" s="14"/>
+      <c r="D134" s="14"/>
+      <c r="E134" s="14"/>
+      <c r="F134" s="12"/>
+      <c r="G134" s="12"/>
+    </row>
+    <row r="135" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A135" s="14"/>
+      <c r="B135" s="14"/>
+      <c r="C135" s="14"/>
+      <c r="D135" s="14"/>
+      <c r="E135" s="14"/>
+      <c r="F135" s="12"/>
+      <c r="G135" s="12"/>
+    </row>
+    <row r="136" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A136" s="14"/>
+      <c r="B136" s="14"/>
+      <c r="C136" s="14"/>
+      <c r="D136" s="14"/>
+      <c r="E136" s="14"/>
+      <c r="F136" s="12"/>
+      <c r="G136" s="12"/>
+    </row>
+    <row r="137" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A137" s="14"/>
+      <c r="B137" s="14"/>
+      <c r="C137" s="14"/>
+      <c r="D137" s="14"/>
+      <c r="E137" s="14"/>
+      <c r="F137" s="12"/>
+      <c r="G137" s="12"/>
+    </row>
+    <row r="138" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A138" s="14"/>
+      <c r="B138" s="14"/>
+      <c r="C138" s="14"/>
+      <c r="D138" s="14"/>
+      <c r="E138" s="14"/>
+      <c r="F138" s="12"/>
+      <c r="G138" s="12"/>
+    </row>
+    <row r="139" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A139" s="14"/>
+      <c r="B139" s="14"/>
+      <c r="C139" s="14"/>
+      <c r="D139" s="14"/>
+      <c r="E139" s="14"/>
+      <c r="F139" s="12"/>
+      <c r="G139" s="12"/>
+    </row>
+    <row r="140" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A140" s="14"/>
+      <c r="B140" s="14"/>
+      <c r="C140" s="14"/>
+      <c r="D140" s="14"/>
+      <c r="E140" s="14"/>
+      <c r="F140" s="12"/>
+      <c r="G140" s="12"/>
+    </row>
+    <row r="141" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A141" s="14"/>
+      <c r="B141" s="14"/>
+      <c r="C141" s="14"/>
+      <c r="D141" s="14"/>
+      <c r="E141" s="14"/>
+      <c r="F141" s="12"/>
+      <c r="G141" s="12"/>
+    </row>
+    <row r="142" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A142" s="14"/>
+      <c r="B142" s="14"/>
+      <c r="C142" s="14"/>
+      <c r="D142" s="14"/>
+      <c r="E142" s="14"/>
+      <c r="F142" s="12"/>
+      <c r="G142" s="12"/>
+    </row>
+    <row r="143" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A143" s="14"/>
+      <c r="B143" s="14"/>
+      <c r="C143" s="14"/>
+      <c r="D143" s="14"/>
+      <c r="E143" s="14"/>
+      <c r="F143" s="12"/>
+      <c r="G143" s="12"/>
+    </row>
+    <row r="144" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A144" s="14"/>
+      <c r="B144" s="14"/>
+      <c r="C144" s="14"/>
+      <c r="D144" s="14"/>
+      <c r="E144" s="14"/>
+      <c r="F144" s="12"/>
+      <c r="G144" s="12"/>
+    </row>
+    <row r="145" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A145" s="14"/>
+      <c r="B145" s="14"/>
+      <c r="C145" s="14"/>
+      <c r="D145" s="14"/>
+      <c r="E145" s="14"/>
+      <c r="F145" s="12"/>
+      <c r="G145" s="12"/>
+    </row>
+    <row r="146" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A146" s="14"/>
+      <c r="B146" s="14"/>
+      <c r="C146" s="14"/>
+      <c r="D146" s="14"/>
+      <c r="E146" s="14"/>
+      <c r="F146" s="12"/>
+      <c r="G146" s="12"/>
+    </row>
+    <row r="147" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A147" s="14"/>
+      <c r="B147" s="14"/>
+      <c r="C147" s="14"/>
+      <c r="D147" s="14"/>
+      <c r="E147" s="14"/>
+      <c r="F147" s="12"/>
+      <c r="G147" s="12"/>
+    </row>
+    <row r="148" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A148" s="14"/>
+      <c r="B148" s="14"/>
+      <c r="C148" s="14"/>
+      <c r="D148" s="14"/>
+      <c r="E148" s="14"/>
+      <c r="F148" s="12"/>
+      <c r="G148" s="12"/>
+    </row>
+    <row r="149" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A149" s="14"/>
+      <c r="B149" s="14"/>
+      <c r="C149" s="14"/>
+      <c r="D149" s="14"/>
+      <c r="E149" s="14"/>
+      <c r="F149" s="12"/>
+      <c r="G149" s="12"/>
+    </row>
+    <row r="150" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A150" s="14"/>
+      <c r="B150" s="14"/>
+      <c r="C150" s="14"/>
+      <c r="D150" s="14"/>
+      <c r="E150" s="14"/>
+      <c r="F150" s="12"/>
+      <c r="G150" s="12"/>
+    </row>
+    <row r="151" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A151" s="14"/>
+      <c r="B151" s="14"/>
+      <c r="C151" s="14"/>
+      <c r="D151" s="14"/>
+      <c r="E151" s="14"/>
+      <c r="F151" s="12"/>
+      <c r="G151" s="12"/>
+    </row>
+    <row r="152" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A152" s="14"/>
+      <c r="B152" s="14"/>
+      <c r="C152" s="14"/>
+      <c r="D152" s="14"/>
+      <c r="E152" s="14"/>
+      <c r="F152" s="12"/>
+      <c r="G152" s="12"/>
+    </row>
+    <row r="153" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A153" s="14"/>
+      <c r="B153" s="14"/>
+      <c r="C153" s="14"/>
+      <c r="D153" s="14"/>
+      <c r="E153" s="14"/>
+      <c r="F153" s="12"/>
+      <c r="G153" s="12"/>
+    </row>
+    <row r="154" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A154" s="14"/>
+      <c r="B154" s="14"/>
+      <c r="C154" s="14"/>
+      <c r="D154" s="14"/>
+      <c r="E154" s="14"/>
+      <c r="F154" s="12"/>
+      <c r="G154" s="12"/>
+    </row>
+    <row r="155" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A155" s="14"/>
+      <c r="B155" s="14"/>
+      <c r="C155" s="14"/>
+      <c r="D155" s="14"/>
+      <c r="E155" s="14"/>
+      <c r="F155" s="12"/>
+      <c r="G155" s="12"/>
+    </row>
+    <row r="156" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A156" s="14"/>
+      <c r="B156" s="14"/>
+      <c r="C156" s="14"/>
+      <c r="D156" s="14"/>
+      <c r="E156" s="14"/>
+      <c r="F156" s="12"/>
+      <c r="G156" s="12"/>
+    </row>
+    <row r="157" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A157" s="14"/>
+      <c r="B157" s="14"/>
+      <c r="C157" s="14"/>
+      <c r="D157" s="14"/>
+      <c r="E157" s="14"/>
+      <c r="F157" s="12"/>
+      <c r="G157" s="12"/>
+    </row>
+    <row r="158" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A158" s="14"/>
+      <c r="B158" s="14"/>
+      <c r="C158" s="14"/>
+      <c r="D158" s="14"/>
+      <c r="E158" s="14"/>
+      <c r="F158" s="12"/>
+      <c r="G158" s="12"/>
+    </row>
+    <row r="159" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A159" s="14"/>
+      <c r="B159" s="14"/>
+      <c r="C159" s="14"/>
+      <c r="D159" s="14"/>
+      <c r="E159" s="14"/>
+      <c r="F159" s="12"/>
+      <c r="G159" s="12"/>
+    </row>
+    <row r="160" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A160" s="14"/>
+      <c r="B160" s="14"/>
+      <c r="C160" s="14"/>
+      <c r="D160" s="14"/>
+      <c r="E160" s="14"/>
+      <c r="F160" s="12"/>
+      <c r="G160" s="12"/>
+    </row>
+    <row r="161" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A161" s="14"/>
+      <c r="B161" s="14"/>
+      <c r="C161" s="14"/>
+      <c r="D161" s="14"/>
+      <c r="E161" s="14"/>
+      <c r="F161" s="12"/>
+      <c r="G161" s="12"/>
+    </row>
+    <row r="162" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A162" s="14"/>
+      <c r="B162" s="14"/>
+      <c r="C162" s="14"/>
+      <c r="D162" s="14"/>
+      <c r="E162" s="14"/>
+      <c r="F162" s="12"/>
+      <c r="G162" s="12"/>
+    </row>
+    <row r="163" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A163" s="14"/>
+      <c r="B163" s="14"/>
+      <c r="C163" s="14"/>
+      <c r="D163" s="14"/>
+      <c r="E163" s="14"/>
+      <c r="F163" s="12"/>
+      <c r="G163" s="12"/>
+    </row>
+    <row r="164" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A164" s="14"/>
+      <c r="B164" s="14"/>
+      <c r="C164" s="14"/>
+      <c r="D164" s="14"/>
+      <c r="E164" s="14"/>
+      <c r="F164" s="12"/>
+      <c r="G164" s="12"/>
+    </row>
+    <row r="165" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A165" s="14"/>
+      <c r="B165" s="14"/>
+      <c r="C165" s="14"/>
+      <c r="D165" s="14"/>
+      <c r="E165" s="14"/>
+      <c r="F165" s="12"/>
+      <c r="G165" s="12"/>
+    </row>
+    <row r="166" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A166" s="14"/>
+      <c r="B166" s="14"/>
+      <c r="C166" s="14"/>
+      <c r="D166" s="14"/>
+      <c r="E166" s="14"/>
+      <c r="F166" s="12"/>
+      <c r="G166" s="12"/>
+    </row>
+    <row r="167" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A167" s="14"/>
+      <c r="B167" s="14"/>
+      <c r="C167" s="14"/>
+      <c r="D167" s="14"/>
+      <c r="E167" s="14"/>
+      <c r="F167" s="12"/>
+      <c r="G167" s="12"/>
+    </row>
+    <row r="168" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A168" s="14"/>
+      <c r="B168" s="14"/>
+      <c r="C168" s="14"/>
+      <c r="D168" s="14"/>
+      <c r="E168" s="14"/>
+      <c r="F168" s="12"/>
+      <c r="G168" s="12"/>
+    </row>
+    <row r="169" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A169" s="14"/>
+      <c r="B169" s="14"/>
+      <c r="C169" s="14"/>
+      <c r="D169" s="14"/>
+      <c r="E169" s="14"/>
+      <c r="F169" s="12"/>
+      <c r="G169" s="12"/>
+    </row>
+    <row r="170" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A170" s="14"/>
+      <c r="B170" s="14"/>
+      <c r="C170" s="14"/>
+      <c r="D170" s="14"/>
+      <c r="E170" s="14"/>
+      <c r="F170" s="12"/>
+      <c r="G170" s="12"/>
+    </row>
+    <row r="171" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A171" s="14"/>
+      <c r="B171" s="14"/>
+      <c r="C171" s="14"/>
+      <c r="D171" s="14"/>
+      <c r="E171" s="14"/>
+      <c r="F171" s="12"/>
+      <c r="G171" s="12"/>
+    </row>
+    <row r="172" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A172" s="14"/>
+      <c r="B172" s="14"/>
+      <c r="C172" s="14"/>
+      <c r="D172" s="14"/>
+      <c r="E172" s="14"/>
+      <c r="F172" s="12"/>
+      <c r="G172" s="12"/>
+    </row>
+    <row r="173" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A173" s="14"/>
+      <c r="B173" s="14"/>
+      <c r="C173" s="14"/>
+      <c r="D173" s="14"/>
+      <c r="E173" s="14"/>
+      <c r="F173" s="12"/>
+      <c r="G173" s="12"/>
+    </row>
+    <row r="174" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A174" s="14"/>
+      <c r="B174" s="14"/>
+      <c r="C174" s="14"/>
+      <c r="D174" s="14"/>
+      <c r="E174" s="14"/>
+      <c r="F174" s="12"/>
+      <c r="G174" s="12"/>
+    </row>
+    <row r="175" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A175" s="14"/>
+      <c r="B175" s="14"/>
+      <c r="C175" s="14"/>
+      <c r="D175" s="14"/>
+      <c r="E175" s="14"/>
+      <c r="F175" s="12"/>
+      <c r="G175" s="12"/>
+    </row>
+    <row r="176" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A176" s="14"/>
+      <c r="B176" s="14"/>
+      <c r="C176" s="14"/>
+      <c r="D176" s="14"/>
+      <c r="E176" s="14"/>
+      <c r="F176" s="12"/>
+      <c r="G176" s="12"/>
+    </row>
+    <row r="177" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A177" s="14"/>
+      <c r="B177" s="14"/>
+      <c r="C177" s="14"/>
+      <c r="D177" s="14"/>
+      <c r="E177" s="14"/>
+      <c r="F177" s="12"/>
+      <c r="G177" s="12"/>
+    </row>
+    <row r="178" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A178" s="14"/>
+      <c r="B178" s="14"/>
+      <c r="C178" s="14"/>
+      <c r="D178" s="14"/>
+      <c r="E178" s="14"/>
+      <c r="F178" s="12"/>
+      <c r="G178" s="12"/>
+    </row>
+    <row r="179" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A179" s="14"/>
+      <c r="B179" s="14"/>
+      <c r="C179" s="14"/>
+      <c r="D179" s="14"/>
+      <c r="E179" s="14"/>
+      <c r="F179" s="12"/>
+      <c r="G179" s="12"/>
+    </row>
+    <row r="180" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A180" s="14"/>
+      <c r="B180" s="14"/>
+      <c r="C180" s="14"/>
+      <c r="D180" s="14"/>
+      <c r="E180" s="14"/>
+      <c r="F180" s="12"/>
+      <c r="G180" s="12"/>
+    </row>
+    <row r="181" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A181" s="14"/>
+      <c r="B181" s="14"/>
+      <c r="C181" s="14"/>
+      <c r="D181" s="14"/>
+      <c r="E181" s="14"/>
+      <c r="F181" s="12"/>
+      <c r="G181" s="12"/>
+    </row>
+    <row r="182" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A182" s="14"/>
+      <c r="B182" s="14"/>
+      <c r="C182" s="14"/>
+      <c r="D182" s="14"/>
+      <c r="E182" s="14"/>
+      <c r="F182" s="12"/>
+      <c r="G182" s="12"/>
+    </row>
+    <row r="183" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A183" s="14"/>
+      <c r="B183" s="14"/>
+      <c r="C183" s="14"/>
+      <c r="D183" s="14"/>
+      <c r="E183" s="14"/>
+      <c r="F183" s="12"/>
+      <c r="G183" s="12"/>
+    </row>
+    <row r="184" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A184" s="14"/>
+      <c r="B184" s="14"/>
+      <c r="C184" s="14"/>
+      <c r="D184" s="14"/>
+      <c r="E184" s="14"/>
+      <c r="F184" s="12"/>
+      <c r="G184" s="12"/>
+    </row>
+    <row r="185" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A185" s="14"/>
+      <c r="B185" s="14"/>
+      <c r="C185" s="14"/>
+      <c r="D185" s="14"/>
+      <c r="E185" s="14"/>
+      <c r="F185" s="12"/>
+      <c r="G185" s="12"/>
+    </row>
+    <row r="186" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A186" s="14"/>
+      <c r="B186" s="14"/>
+      <c r="C186" s="14"/>
+      <c r="D186" s="14"/>
+      <c r="E186" s="14"/>
+      <c r="F186" s="12"/>
+      <c r="G186" s="12"/>
+    </row>
+    <row r="187" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A187" s="14"/>
+      <c r="B187" s="14"/>
+      <c r="C187" s="14"/>
+      <c r="D187" s="14"/>
+      <c r="E187" s="14"/>
+      <c r="F187" s="12"/>
+      <c r="G187" s="12"/>
+    </row>
+    <row r="188" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A188" s="14"/>
+      <c r="B188" s="14"/>
+      <c r="C188" s="14"/>
+      <c r="D188" s="14"/>
+      <c r="E188" s="14"/>
+      <c r="F188" s="12"/>
+      <c r="G188" s="12"/>
+    </row>
+    <row r="189" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A189" s="14"/>
+      <c r="B189" s="14"/>
+      <c r="C189" s="14"/>
+      <c r="D189" s="14"/>
+      <c r="E189" s="14"/>
+      <c r="F189" s="12"/>
+      <c r="G189" s="12"/>
+    </row>
+    <row r="190" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A190" s="14"/>
+      <c r="B190" s="14"/>
+      <c r="C190" s="14"/>
+      <c r="D190" s="14"/>
+      <c r="E190" s="14"/>
+      <c r="F190" s="12"/>
+      <c r="G190" s="12"/>
+    </row>
+    <row r="191" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A191" s="14"/>
+      <c r="B191" s="14"/>
+      <c r="C191" s="14"/>
+      <c r="D191" s="14"/>
+      <c r="E191" s="14"/>
+      <c r="F191" s="12"/>
+      <c r="G191" s="12"/>
+    </row>
+    <row r="192" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A192" s="14"/>
+      <c r="B192" s="14"/>
+      <c r="C192" s="14"/>
+      <c r="D192" s="14"/>
+      <c r="E192" s="14"/>
+      <c r="F192" s="12"/>
+      <c r="G192" s="12"/>
+    </row>
+    <row r="193" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A193" s="14"/>
+      <c r="B193" s="14"/>
+      <c r="C193" s="14"/>
+      <c r="D193" s="14"/>
+      <c r="E193" s="14"/>
+      <c r="F193" s="12"/>
+      <c r="G193" s="12"/>
+    </row>
+    <row r="194" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A194" s="14"/>
+      <c r="B194" s="14"/>
+      <c r="C194" s="14"/>
+      <c r="D194" s="14"/>
+      <c r="E194" s="14"/>
+      <c r="F194" s="12"/>
+      <c r="G194" s="12"/>
+    </row>
+    <row r="195" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A195" s="14"/>
+      <c r="B195" s="14"/>
+      <c r="C195" s="14"/>
+      <c r="D195" s="14"/>
+      <c r="E195" s="14"/>
+      <c r="F195" s="12"/>
+      <c r="G195" s="12"/>
+    </row>
+    <row r="196" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A196" s="14"/>
+      <c r="B196" s="14"/>
+      <c r="C196" s="14"/>
+      <c r="D196" s="14"/>
+      <c r="E196" s="14"/>
+      <c r="F196" s="12"/>
+      <c r="G196" s="12"/>
+    </row>
+    <row r="197" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A197" s="14"/>
+      <c r="B197" s="14"/>
+      <c r="C197" s="14"/>
+      <c r="D197" s="14"/>
+      <c r="E197" s="14"/>
+      <c r="F197" s="12"/>
+      <c r="G197" s="12"/>
+    </row>
+    <row r="198" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A198" s="14"/>
+      <c r="B198" s="14"/>
+      <c r="C198" s="14"/>
+      <c r="D198" s="14"/>
+      <c r="E198" s="14"/>
+      <c r="F198" s="12"/>
+      <c r="G198" s="12"/>
+    </row>
+    <row r="199" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A199" s="14"/>
+      <c r="B199" s="14"/>
+      <c r="C199" s="14"/>
+      <c r="D199" s="14"/>
+      <c r="E199" s="14"/>
+      <c r="F199" s="12"/>
+      <c r="G199" s="12"/>
+    </row>
+    <row r="200" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A200" s="14"/>
+      <c r="B200" s="14"/>
+      <c r="C200" s="14"/>
+      <c r="D200" s="14"/>
+      <c r="E200" s="14"/>
+      <c r="F200" s="12"/>
+      <c r="G200" s="12"/>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="B3:B200">
+    <cfRule type="expression" dxfId="12" priority="1">
+      <formula>$F3="A"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C3:C200">
+    <cfRule type="expression" dxfId="13" priority="2">
+      <formula>$F3="B"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D3:D200">
+    <cfRule type="expression" dxfId="14" priority="3">
+      <formula>$F3="C"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E3:E200">
+    <cfRule type="expression" dxfId="15" priority="4">
+      <formula>$F3="D"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="4">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="warning" errorTitle="Valor no previsto" error="Elige un valor de la lista." sqref="F10:F200">
+      <formula1>"A,B,C,D"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="warning" errorTitle="Valor no previsto" error="Elige un valor de la lista." sqref="F3:F200">
+      <formula1>"A,B,C,D"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" errorStyle="warning" errorTitle="Valor no previsto" error="Elige un valor de la lista." sqref="G10:G200">
+      <formula1>Concurso!$B$3:$B$100</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" errorStyle="warning" errorTitle="Valor no previsto" error="Elige un valor de la lista." sqref="G3:G200">
+      <formula1>Concurso!$B$3:$B$100</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <tabColor rgb="FF6A1B9A"/>
+  </sheetPr>
+  <dimension ref="A1:A200"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="70" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1" spans="1:1" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="10" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="2" ht="42" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2" s="11" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3" s="14" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A4" s="14" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A5" s="14" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A6" s="14" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A7" s="14" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A8" s="14" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A9" s="14" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A10" s="14" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A11" s="14"/>
+    </row>
+    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A12" s="14"/>
+    </row>
+    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A13" s="14"/>
+    </row>
+    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A14" s="14"/>
+    </row>
+    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A15" s="14"/>
+    </row>
+    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A16" s="14"/>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A17" s="14"/>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A18" s="14"/>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A19" s="14"/>
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A20" s="14"/>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A21" s="14"/>
+    </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A22" s="14"/>
+    </row>
+    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A23" s="14"/>
+    </row>
+    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A24" s="14"/>
+    </row>
+    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A25" s="14"/>
+    </row>
+    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A26" s="14"/>
+    </row>
+    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A27" s="14"/>
+    </row>
+    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A28" s="14"/>
+    </row>
+    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A29" s="14"/>
+    </row>
+    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A30" s="14"/>
+    </row>
+    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A31" s="14"/>
+    </row>
+    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A32" s="14"/>
+    </row>
+    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A33" s="14"/>
+    </row>
+    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A34" s="14"/>
+    </row>
+    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A35" s="14"/>
+    </row>
+    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A36" s="14"/>
+    </row>
+    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A37" s="14"/>
+    </row>
+    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A38" s="14"/>
+    </row>
+    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A39" s="14"/>
+    </row>
+    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A40" s="14"/>
+    </row>
+    <row r="41" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A41" s="14"/>
+    </row>
+    <row r="42" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A42" s="14"/>
+    </row>
+    <row r="43" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A43" s="14"/>
+    </row>
+    <row r="44" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A44" s="14"/>
+    </row>
+    <row r="45" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A45" s="14"/>
+    </row>
+    <row r="46" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A46" s="14"/>
+    </row>
+    <row r="47" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A47" s="14"/>
+    </row>
+    <row r="48" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A48" s="14"/>
+    </row>
+    <row r="49" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A49" s="14"/>
+    </row>
+    <row r="50" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A50" s="14"/>
+    </row>
+    <row r="51" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A51" s="14"/>
+    </row>
+    <row r="52" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A52" s="14"/>
+    </row>
+    <row r="53" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A53" s="14"/>
+    </row>
+    <row r="54" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A54" s="14"/>
+    </row>
+    <row r="55" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A55" s="14"/>
+    </row>
+    <row r="56" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A56" s="14"/>
+    </row>
+    <row r="57" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A57" s="14"/>
+    </row>
+    <row r="58" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A58" s="14"/>
+    </row>
+    <row r="59" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A59" s="14"/>
+    </row>
+    <row r="60" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A60" s="14"/>
+    </row>
+    <row r="61" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A61" s="14"/>
+    </row>
+    <row r="62" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A62" s="14"/>
+    </row>
+    <row r="63" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A63" s="14"/>
+    </row>
+    <row r="64" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A64" s="14"/>
+    </row>
+    <row r="65" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A65" s="14"/>
+    </row>
+    <row r="66" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A66" s="14"/>
+    </row>
+    <row r="67" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A67" s="14"/>
+    </row>
+    <row r="68" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A68" s="14"/>
+    </row>
+    <row r="69" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A69" s="14"/>
+    </row>
+    <row r="70" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A70" s="14"/>
+    </row>
+    <row r="71" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A71" s="14"/>
+    </row>
+    <row r="72" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A72" s="14"/>
+    </row>
+    <row r="73" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A73" s="14"/>
+    </row>
+    <row r="74" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A74" s="14"/>
+    </row>
+    <row r="75" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A75" s="14"/>
+    </row>
+    <row r="76" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A76" s="14"/>
+    </row>
+    <row r="77" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A77" s="14"/>
+    </row>
+    <row r="78" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A78" s="14"/>
+    </row>
+    <row r="79" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A79" s="14"/>
+    </row>
+    <row r="80" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A80" s="14"/>
+    </row>
+    <row r="81" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A81" s="14"/>
+    </row>
+    <row r="82" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A82" s="14"/>
+    </row>
+    <row r="83" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A83" s="14"/>
+    </row>
+    <row r="84" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A84" s="14"/>
+    </row>
+    <row r="85" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A85" s="14"/>
+    </row>
+    <row r="86" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A86" s="14"/>
+    </row>
+    <row r="87" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A87" s="14"/>
+    </row>
+    <row r="88" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A88" s="14"/>
+    </row>
+    <row r="89" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A89" s="14"/>
+    </row>
+    <row r="90" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A90" s="14"/>
+    </row>
+    <row r="91" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A91" s="14"/>
+    </row>
+    <row r="92" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A92" s="14"/>
+    </row>
+    <row r="93" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A93" s="14"/>
+    </row>
+    <row r="94" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A94" s="14"/>
+    </row>
+    <row r="95" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A95" s="14"/>
+    </row>
+    <row r="96" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A96" s="14"/>
+    </row>
+    <row r="97" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A97" s="14"/>
+    </row>
+    <row r="98" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A98" s="14"/>
+    </row>
+    <row r="99" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A99" s="14"/>
+    </row>
+    <row r="100" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A100" s="14"/>
+    </row>
+    <row r="101" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A101" s="14"/>
+    </row>
+    <row r="102" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A102" s="14"/>
+    </row>
+    <row r="103" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A103" s="14"/>
+    </row>
+    <row r="104" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A104" s="14"/>
+    </row>
+    <row r="105" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A105" s="14"/>
+    </row>
+    <row r="106" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A106" s="14"/>
+    </row>
+    <row r="107" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A107" s="14"/>
+    </row>
+    <row r="108" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A108" s="14"/>
+    </row>
+    <row r="109" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A109" s="14"/>
+    </row>
+    <row r="110" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A110" s="14"/>
+    </row>
+    <row r="111" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A111" s="14"/>
+    </row>
+    <row r="112" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A112" s="14"/>
+    </row>
+    <row r="113" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A113" s="14"/>
+    </row>
+    <row r="114" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A114" s="14"/>
+    </row>
+    <row r="115" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A115" s="14"/>
+    </row>
+    <row r="116" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A116" s="14"/>
+    </row>
+    <row r="117" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A117" s="14"/>
+    </row>
+    <row r="118" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A118" s="14"/>
+    </row>
+    <row r="119" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A119" s="14"/>
+    </row>
+    <row r="120" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A120" s="14"/>
+    </row>
+    <row r="121" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A121" s="14"/>
+    </row>
+    <row r="122" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A122" s="14"/>
+    </row>
+    <row r="123" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A123" s="14"/>
+    </row>
+    <row r="124" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A124" s="14"/>
+    </row>
+    <row r="125" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A125" s="14"/>
+    </row>
+    <row r="126" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A126" s="14"/>
+    </row>
+    <row r="127" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A127" s="14"/>
+    </row>
+    <row r="128" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A128" s="14"/>
+    </row>
+    <row r="129" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A129" s="14"/>
+    </row>
+    <row r="130" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A130" s="14"/>
+    </row>
+    <row r="131" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A131" s="14"/>
+    </row>
+    <row r="132" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A132" s="14"/>
+    </row>
+    <row r="133" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A133" s="14"/>
+    </row>
+    <row r="134" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A134" s="14"/>
+    </row>
+    <row r="135" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A135" s="14"/>
+    </row>
+    <row r="136" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A136" s="14"/>
+    </row>
+    <row r="137" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A137" s="14"/>
+    </row>
+    <row r="138" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A138" s="14"/>
+    </row>
+    <row r="139" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A139" s="14"/>
+    </row>
+    <row r="140" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A140" s="14"/>
+    </row>
+    <row r="141" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A141" s="14"/>
+    </row>
+    <row r="142" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A142" s="14"/>
+    </row>
+    <row r="143" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A143" s="14"/>
+    </row>
+    <row r="144" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A144" s="14"/>
+    </row>
+    <row r="145" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A145" s="14"/>
+    </row>
+    <row r="146" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A146" s="14"/>
+    </row>
+    <row r="147" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A147" s="14"/>
+    </row>
+    <row r="148" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A148" s="14"/>
+    </row>
+    <row r="149" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A149" s="14"/>
+    </row>
+    <row r="150" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A150" s="14"/>
+    </row>
+    <row r="151" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A151" s="14"/>
+    </row>
+    <row r="152" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A152" s="14"/>
+    </row>
+    <row r="153" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A153" s="14"/>
+    </row>
+    <row r="154" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A154" s="14"/>
+    </row>
+    <row r="155" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A155" s="14"/>
+    </row>
+    <row r="156" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A156" s="14"/>
+    </row>
+    <row r="157" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A157" s="14"/>
+    </row>
+    <row r="158" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A158" s="14"/>
+    </row>
+    <row r="159" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A159" s="14"/>
+    </row>
+    <row r="160" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A160" s="14"/>
+    </row>
+    <row r="161" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A161" s="14"/>
+    </row>
+    <row r="162" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A162" s="14"/>
+    </row>
+    <row r="163" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A163" s="14"/>
+    </row>
+    <row r="164" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A164" s="14"/>
+    </row>
+    <row r="165" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A165" s="14"/>
+    </row>
+    <row r="166" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A166" s="14"/>
+    </row>
+    <row r="167" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A167" s="14"/>
+    </row>
+    <row r="168" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A168" s="14"/>
+    </row>
+    <row r="169" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A169" s="14"/>
+    </row>
+    <row r="170" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A170" s="14"/>
+    </row>
+    <row r="171" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A171" s="14"/>
+    </row>
+    <row r="172" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A172" s="14"/>
+    </row>
+    <row r="173" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A173" s="14"/>
+    </row>
+    <row r="174" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A174" s="14"/>
+    </row>
+    <row r="175" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A175" s="14"/>
+    </row>
+    <row r="176" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A176" s="14"/>
+    </row>
+    <row r="177" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A177" s="14"/>
+    </row>
+    <row r="178" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A178" s="14"/>
+    </row>
+    <row r="179" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A179" s="14"/>
+    </row>
+    <row r="180" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A180" s="14"/>
+    </row>
+    <row r="181" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A181" s="14"/>
+    </row>
+    <row r="182" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A182" s="14"/>
+    </row>
+    <row r="183" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A183" s="14"/>
+    </row>
+    <row r="184" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A184" s="14"/>
+    </row>
+    <row r="185" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A185" s="14"/>
+    </row>
+    <row r="186" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A186" s="14"/>
+    </row>
+    <row r="187" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A187" s="14"/>
+    </row>
+    <row r="188" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A188" s="14"/>
+    </row>
+    <row r="189" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A189" s="14"/>
+    </row>
+    <row r="190" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A190" s="14"/>
+    </row>
+    <row r="191" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A191" s="14"/>
+    </row>
+    <row r="192" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A192" s="14"/>
+    </row>
+    <row r="193" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A193" s="14"/>
+    </row>
+    <row r="194" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A194" s="14"/>
+    </row>
+    <row r="195" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A195" s="14"/>
+    </row>
+    <row r="196" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A196" s="14"/>
+    </row>
+    <row r="197" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A197" s="14"/>
+    </row>
+    <row r="198" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A198" s="14"/>
+    </row>
+    <row r="199" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A199" s="14"/>
+    </row>
+    <row r="200" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A200" s="14"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
@@ -7024,60 +12575,60 @@
   <sheetData>
     <row r="1" ht="30" customHeight="1" spans="1:9" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="10" t="s">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="B1" s="10" t="s">
-        <v>45</v>
+        <v>56</v>
       </c>
       <c r="C1" s="10" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D1" s="10" t="s">
-        <v>46</v>
+        <v>57</v>
       </c>
       <c r="E1" s="10" t="s">
-        <v>47</v>
+        <v>58</v>
       </c>
       <c r="F1" s="10" t="s">
-        <v>48</v>
+        <v>59</v>
       </c>
       <c r="G1" s="10" t="s">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="H1" s="10" t="s">
-        <v>50</v>
+        <v>61</v>
       </c>
       <c r="I1" s="10" t="s">
-        <v>51</v>
+        <v>62</v>
       </c>
     </row>
     <row r="2" ht="42" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="11" t="s">
-        <v>52</v>
+        <v>63</v>
       </c>
       <c r="B2" s="11" t="s">
-        <v>53</v>
+        <v>64</v>
       </c>
       <c r="C2" s="11" t="s">
-        <v>54</v>
+        <v>65</v>
       </c>
       <c r="D2" s="11" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="E2" s="11" t="s">
-        <v>56</v>
+        <v>67</v>
       </c>
       <c r="F2" s="11" t="s">
-        <v>57</v>
+        <v>68</v>
       </c>
       <c r="G2" s="11" t="s">
-        <v>58</v>
+        <v>69</v>
       </c>
       <c r="H2" s="11" t="s">
-        <v>59</v>
+        <v>70</v>
       </c>
       <c r="I2" s="11" t="s">
-        <v>60</v>
+        <v>71</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
@@ -7085,23 +12636,23 @@
         <v>1</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>61</v>
+        <v>72</v>
       </c>
       <c r="C3" s="12" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D3" s="13" t="str">
-        <f>IF(C3="","",IFERROR("→ "&amp;INDEX({"Pulsador","Test","Verdad o mentira","Dos verdades","Votación","Estimación","Contador","Reflejos","Libre"},MATCH(C3,{"Pulsador","Test","Verdad o mentira","Dos verdades y una mentira","Votación","Estimación","Parar el contador","Duelo de reflejos","Libre"},0)),"¿tipo?"))</f>
+        <f>IF(C3="","",IFERROR("→ "&amp;INDEX({"Pulsador","Test","Verdad o mentira","Dos verdades","Votación","Estimación","Contador","Reflejos","Libre","Palabras","Agitar","Apuesta"},MATCH(C3,{"Pulsador","Test","Verdad o mentira","Dos verdades y una mentira","Votación","Estimación","Parar el contador","Duelo de reflejos","Libre","Palabras secretas","Agita el móvil","La gran apuesta"},0)),"¿tipo?"))</f>
         <v>→ Pulsador</v>
       </c>
       <c r="E3" s="14" t="s">
-        <v>62</v>
+        <v>73</v>
       </c>
       <c r="F3" s="12">
         <v>1</v>
       </c>
       <c r="G3" s="12" t="s">
-        <v>63</v>
+        <v>74</v>
       </c>
       <c r="H3" s="12"/>
       <c r="I3" s="12"/>
@@ -7111,20 +12662,20 @@
         <v>2</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>64</v>
+        <v>75</v>
       </c>
       <c r="C4" s="12" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D4" s="13" t="str">
-        <f>IF(C4="","",IFERROR("→ "&amp;INDEX({"Pulsador","Test","Verdad o mentira","Dos verdades","Votación","Estimación","Contador","Reflejos","Libre"},MATCH(C4,{"Pulsador","Test","Verdad o mentira","Dos verdades y una mentira","Votación","Estimación","Parar el contador","Duelo de reflejos","Libre"},0)),"¿tipo?"))</f>
+        <f>IF(C4="","",IFERROR("→ "&amp;INDEX({"Pulsador","Test","Verdad o mentira","Dos verdades","Votación","Estimación","Contador","Reflejos","Libre","Palabras","Agitar","Apuesta"},MATCH(C4,{"Pulsador","Test","Verdad o mentira","Dos verdades y una mentira","Votación","Estimación","Parar el contador","Duelo de reflejos","Libre","Palabras secretas","Agita el móvil","La gran apuesta"},0)),"¿tipo?"))</f>
         <v>→ Test</v>
       </c>
       <c r="E4" s="14" t="s">
-        <v>65</v>
+        <v>76</v>
       </c>
       <c r="F4" s="12" t="s">
-        <v>66</v>
+        <v>77</v>
       </c>
       <c r="G4" s="12"/>
       <c r="H4" s="12"/>
@@ -7135,17 +12686,17 @@
         <v>3</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>67</v>
+        <v>78</v>
       </c>
       <c r="C5" s="12" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D5" s="13" t="str">
-        <f>IF(C5="","",IFERROR("→ "&amp;INDEX({"Pulsador","Test","Verdad o mentira","Dos verdades","Votación","Estimación","Contador","Reflejos","Libre"},MATCH(C5,{"Pulsador","Test","Verdad o mentira","Dos verdades y una mentira","Votación","Estimación","Parar el contador","Duelo de reflejos","Libre"},0)),"¿tipo?"))</f>
+        <f>IF(C5="","",IFERROR("→ "&amp;INDEX({"Pulsador","Test","Verdad o mentira","Dos verdades","Votación","Estimación","Contador","Reflejos","Libre","Palabras","Agitar","Apuesta"},MATCH(C5,{"Pulsador","Test","Verdad o mentira","Dos verdades y una mentira","Votación","Estimación","Parar el contador","Duelo de reflejos","Libre","Palabras secretas","Agita el móvil","La gran apuesta"},0)),"¿tipo?"))</f>
         <v>→ Verdad o mentira</v>
       </c>
       <c r="E5" s="14" t="s">
-        <v>68</v>
+        <v>79</v>
       </c>
       <c r="F5" s="12">
         <v>1</v>
@@ -7159,17 +12710,17 @@
         <v>4</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>69</v>
+        <v>46</v>
       </c>
       <c r="C6" s="12" t="s">
-        <v>29</v>
+        <v>46</v>
       </c>
       <c r="D6" s="13" t="str">
-        <f>IF(C6="","",IFERROR("→ "&amp;INDEX({"Pulsador","Test","Verdad o mentira","Dos verdades","Votación","Estimación","Contador","Reflejos","Libre"},MATCH(C6,{"Pulsador","Test","Verdad o mentira","Dos verdades y una mentira","Votación","Estimación","Parar el contador","Duelo de reflejos","Libre"},0)),"¿tipo?"))</f>
-        <v>→ Votación</v>
+        <f>IF(C6="","",IFERROR("→ "&amp;INDEX({"Pulsador","Test","Verdad o mentira","Dos verdades","Votación","Estimación","Contador","Reflejos","Libre","Palabras","Agitar","Apuesta"},MATCH(C6,{"Pulsador","Test","Verdad o mentira","Dos verdades y una mentira","Votación","Estimación","Parar el contador","Duelo de reflejos","Libre","Palabras secretas","Agita el móvil","La gran apuesta"},0)),"¿tipo?"))</f>
+        <v>→ Palabras</v>
       </c>
       <c r="E6" s="14" t="s">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="F6" s="12">
         <v>1</v>
@@ -7183,20 +12734,20 @@
         <v>5</v>
       </c>
       <c r="B7" s="12" t="s">
-        <v>71</v>
+        <v>81</v>
       </c>
       <c r="C7" s="12" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D7" s="13" t="str">
-        <f>IF(C7="","",IFERROR("→ "&amp;INDEX({"Pulsador","Test","Verdad o mentira","Dos verdades","Votación","Estimación","Contador","Reflejos","Libre"},MATCH(C7,{"Pulsador","Test","Verdad o mentira","Dos verdades y una mentira","Votación","Estimación","Parar el contador","Duelo de reflejos","Libre"},0)),"¿tipo?"))</f>
-        <v>→ Estimación</v>
+        <f>IF(C7="","",IFERROR("→ "&amp;INDEX({"Pulsador","Test","Verdad o mentira","Dos verdades","Votación","Estimación","Contador","Reflejos","Libre","Palabras","Agitar","Apuesta"},MATCH(C7,{"Pulsador","Test","Verdad o mentira","Dos verdades y una mentira","Votación","Estimación","Parar el contador","Duelo de reflejos","Libre","Palabras secretas","Agita el móvil","La gran apuesta"},0)),"¿tipo?"))</f>
+        <v>→ Votación</v>
       </c>
       <c r="E7" s="14" t="s">
-        <v>72</v>
-      </c>
-      <c r="F7" s="12" t="s">
-        <v>73</v>
+        <v>82</v>
+      </c>
+      <c r="F7" s="12">
+        <v>1</v>
       </c>
       <c r="G7" s="12"/>
       <c r="H7" s="12"/>
@@ -7207,20 +12758,20 @@
         <v>6</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="C8" s="12" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D8" s="13" t="str">
-        <f>IF(C8="","",IFERROR("→ "&amp;INDEX({"Pulsador","Test","Verdad o mentira","Dos verdades","Votación","Estimación","Contador","Reflejos","Libre"},MATCH(C8,{"Pulsador","Test","Verdad o mentira","Dos verdades y una mentira","Votación","Estimación","Parar el contador","Duelo de reflejos","Libre"},0)),"¿tipo?"))</f>
-        <v>→ Contador</v>
+        <f>IF(C8="","",IFERROR("→ "&amp;INDEX({"Pulsador","Test","Verdad o mentira","Dos verdades","Votación","Estimación","Contador","Reflejos","Libre","Palabras","Agitar","Apuesta"},MATCH(C8,{"Pulsador","Test","Verdad o mentira","Dos verdades y una mentira","Votación","Estimación","Parar el contador","Duelo de reflejos","Libre","Palabras secretas","Agita el móvil","La gran apuesta"},0)),"¿tipo?"))</f>
+        <v>→ Estimación</v>
       </c>
       <c r="E8" s="14" t="s">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="F8" s="12" t="s">
-        <v>73</v>
+        <v>85</v>
       </c>
       <c r="G8" s="12"/>
       <c r="H8" s="12"/>
@@ -7231,22 +12782,24 @@
         <v>7</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>76</v>
+        <v>49</v>
       </c>
       <c r="C9" s="12" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="D9" s="13" t="str">
-        <f>IF(C9="","",IFERROR("→ "&amp;INDEX({"Pulsador","Test","Verdad o mentira","Dos verdades","Votación","Estimación","Contador","Reflejos","Libre"},MATCH(C9,{"Pulsador","Test","Verdad o mentira","Dos verdades y una mentira","Votación","Estimación","Parar el contador","Duelo de reflejos","Libre"},0)),"¿tipo?"))</f>
-        <v>→ Reflejos</v>
+        <f>IF(C9="","",IFERROR("→ "&amp;INDEX({"Pulsador","Test","Verdad o mentira","Dos verdades","Votación","Estimación","Contador","Reflejos","Libre","Palabras","Agitar","Apuesta"},MATCH(C9,{"Pulsador","Test","Verdad o mentira","Dos verdades y una mentira","Votación","Estimación","Parar el contador","Duelo de reflejos","Libre","Palabras secretas","Agita el móvil","La gran apuesta"},0)),"¿tipo?"))</f>
+        <v>→ Agitar</v>
       </c>
       <c r="E9" s="14" t="s">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="F9" s="12" t="s">
-        <v>73</v>
-      </c>
-      <c r="G9" s="12"/>
+        <v>85</v>
+      </c>
+      <c r="G9" s="12" t="s">
+        <v>87</v>
+      </c>
       <c r="H9" s="12"/>
       <c r="I9" s="12"/>
     </row>
@@ -7255,20 +12808,20 @@
         <v>8</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>26</v>
+        <v>88</v>
       </c>
       <c r="C10" s="12" t="s">
-        <v>26</v>
+        <v>37</v>
       </c>
       <c r="D10" s="13" t="str">
-        <f>IF(C10="","",IFERROR("→ "&amp;INDEX({"Pulsador","Test","Verdad o mentira","Dos verdades","Votación","Estimación","Contador","Reflejos","Libre"},MATCH(C10,{"Pulsador","Test","Verdad o mentira","Dos verdades y una mentira","Votación","Estimación","Parar el contador","Duelo de reflejos","Libre"},0)),"¿tipo?"))</f>
-        <v>→ Dos verdades</v>
+        <f>IF(C10="","",IFERROR("→ "&amp;INDEX({"Pulsador","Test","Verdad o mentira","Dos verdades","Votación","Estimación","Contador","Reflejos","Libre","Palabras","Agitar","Apuesta"},MATCH(C10,{"Pulsador","Test","Verdad o mentira","Dos verdades y una mentira","Votación","Estimación","Parar el contador","Duelo de reflejos","Libre","Palabras secretas","Agita el móvil","La gran apuesta"},0)),"¿tipo?"))</f>
+        <v>→ Contador</v>
       </c>
       <c r="E10" s="14" t="s">
-        <v>78</v>
-      </c>
-      <c r="F10" s="12">
-        <v>1</v>
+        <v>89</v>
+      </c>
+      <c r="F10" s="12" t="s">
+        <v>85</v>
       </c>
       <c r="G10" s="12"/>
       <c r="H10" s="12"/>
@@ -7279,66 +12832,94 @@
         <v>9</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="C11" s="12" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D11" s="13" t="str">
-        <f>IF(C11="","",IFERROR("→ "&amp;INDEX({"Pulsador","Test","Verdad o mentira","Dos verdades","Votación","Estimación","Contador","Reflejos","Libre"},MATCH(C11,{"Pulsador","Test","Verdad o mentira","Dos verdades y una mentira","Votación","Estimación","Parar el contador","Duelo de reflejos","Libre"},0)),"¿tipo?"))</f>
-        <v>→ Libre</v>
+        <f>IF(C11="","",IFERROR("→ "&amp;INDEX({"Pulsador","Test","Verdad o mentira","Dos verdades","Votación","Estimación","Contador","Reflejos","Libre","Palabras","Agitar","Apuesta"},MATCH(C11,{"Pulsador","Test","Verdad o mentira","Dos verdades y una mentira","Votación","Estimación","Parar el contador","Duelo de reflejos","Libre","Palabras secretas","Agita el móvil","La gran apuesta"},0)),"¿tipo?"))</f>
+        <v>→ Reflejos</v>
       </c>
       <c r="E11" s="14" t="s">
-        <v>80</v>
-      </c>
-      <c r="F11" s="12">
-        <v>3</v>
-      </c>
-      <c r="G11" s="12" t="s">
-        <v>81</v>
-      </c>
+        <v>91</v>
+      </c>
+      <c r="F11" s="12" t="s">
+        <v>85</v>
+      </c>
+      <c r="G11" s="12"/>
       <c r="H11" s="12"/>
-      <c r="I11" s="12" t="s">
-        <v>82</v>
-      </c>
+      <c r="I11" s="12"/>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A12" s="12"/>
-      <c r="B12" s="12"/>
-      <c r="C12" s="12"/>
+      <c r="A12" s="12">
+        <v>10</v>
+      </c>
+      <c r="B12" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="C12" s="12" t="s">
+        <v>28</v>
+      </c>
       <c r="D12" s="13" t="str">
-        <f>IF(C12="","",IFERROR("→ "&amp;INDEX({"Pulsador","Test","Verdad o mentira","Dos verdades","Votación","Estimación","Contador","Reflejos","Libre"},MATCH(C12,{"Pulsador","Test","Verdad o mentira","Dos verdades y una mentira","Votación","Estimación","Parar el contador","Duelo de reflejos","Libre"},0)),"¿tipo?"))</f>
-        <v/>
-      </c>
-      <c r="E12" s="14"/>
-      <c r="F12" s="12"/>
+        <f>IF(C12="","",IFERROR("→ "&amp;INDEX({"Pulsador","Test","Verdad o mentira","Dos verdades","Votación","Estimación","Contador","Reflejos","Libre","Palabras","Agitar","Apuesta"},MATCH(C12,{"Pulsador","Test","Verdad o mentira","Dos verdades y una mentira","Votación","Estimación","Parar el contador","Duelo de reflejos","Libre","Palabras secretas","Agita el móvil","La gran apuesta"},0)),"¿tipo?"))</f>
+        <v>→ Dos verdades</v>
+      </c>
+      <c r="E12" s="14" t="s">
+        <v>92</v>
+      </c>
+      <c r="F12" s="12">
+        <v>1</v>
+      </c>
       <c r="G12" s="12"/>
       <c r="H12" s="12"/>
       <c r="I12" s="12"/>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A13" s="12"/>
-      <c r="B13" s="12"/>
-      <c r="C13" s="12"/>
+      <c r="A13" s="12">
+        <v>11</v>
+      </c>
+      <c r="B13" s="12" t="s">
+        <v>93</v>
+      </c>
+      <c r="C13" s="12" t="s">
+        <v>43</v>
+      </c>
       <c r="D13" s="13" t="str">
-        <f>IF(C13="","",IFERROR("→ "&amp;INDEX({"Pulsador","Test","Verdad o mentira","Dos verdades","Votación","Estimación","Contador","Reflejos","Libre"},MATCH(C13,{"Pulsador","Test","Verdad o mentira","Dos verdades y una mentira","Votación","Estimación","Parar el contador","Duelo de reflejos","Libre"},0)),"¿tipo?"))</f>
-        <v/>
-      </c>
-      <c r="E13" s="14"/>
-      <c r="F13" s="12"/>
-      <c r="G13" s="12"/>
+        <f>IF(C13="","",IFERROR("→ "&amp;INDEX({"Pulsador","Test","Verdad o mentira","Dos verdades","Votación","Estimación","Contador","Reflejos","Libre","Palabras","Agitar","Apuesta"},MATCH(C13,{"Pulsador","Test","Verdad o mentira","Dos verdades y una mentira","Votación","Estimación","Parar el contador","Duelo de reflejos","Libre","Palabras secretas","Agita el móvil","La gran apuesta"},0)),"¿tipo?"))</f>
+        <v>→ Libre</v>
+      </c>
+      <c r="E13" s="14" t="s">
+        <v>94</v>
+      </c>
+      <c r="F13" s="12">
+        <v>3</v>
+      </c>
+      <c r="G13" s="12" t="s">
+        <v>87</v>
+      </c>
       <c r="H13" s="12"/>
-      <c r="I13" s="12"/>
+      <c r="I13" s="12" t="s">
+        <v>95</v>
+      </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A14" s="12"/>
-      <c r="B14" s="12"/>
-      <c r="C14" s="12"/>
+      <c r="A14" s="12">
+        <v>12</v>
+      </c>
+      <c r="B14" s="12" t="s">
+        <v>52</v>
+      </c>
+      <c r="C14" s="12" t="s">
+        <v>52</v>
+      </c>
       <c r="D14" s="13" t="str">
-        <f>IF(C14="","",IFERROR("→ "&amp;INDEX({"Pulsador","Test","Verdad o mentira","Dos verdades","Votación","Estimación","Contador","Reflejos","Libre"},MATCH(C14,{"Pulsador","Test","Verdad o mentira","Dos verdades y una mentira","Votación","Estimación","Parar el contador","Duelo de reflejos","Libre"},0)),"¿tipo?"))</f>
-        <v/>
-      </c>
-      <c r="E14" s="14"/>
+        <f>IF(C14="","",IFERROR("→ "&amp;INDEX({"Pulsador","Test","Verdad o mentira","Dos verdades","Votación","Estimación","Contador","Reflejos","Libre","Palabras","Agitar","Apuesta"},MATCH(C14,{"Pulsador","Test","Verdad o mentira","Dos verdades y una mentira","Votación","Estimación","Parar el contador","Duelo de reflejos","Libre","Palabras secretas","Agita el móvil","La gran apuesta"},0)),"¿tipo?"))</f>
+        <v>→ Apuesta</v>
+      </c>
+      <c r="E14" s="14" t="s">
+        <v>96</v>
+      </c>
       <c r="F14" s="12"/>
       <c r="G14" s="12"/>
       <c r="H14" s="12"/>
@@ -7349,7 +12930,7 @@
       <c r="B15" s="12"/>
       <c r="C15" s="12"/>
       <c r="D15" s="13" t="str">
-        <f>IF(C15="","",IFERROR("→ "&amp;INDEX({"Pulsador","Test","Verdad o mentira","Dos verdades","Votación","Estimación","Contador","Reflejos","Libre"},MATCH(C15,{"Pulsador","Test","Verdad o mentira","Dos verdades y una mentira","Votación","Estimación","Parar el contador","Duelo de reflejos","Libre"},0)),"¿tipo?"))</f>
+        <f>IF(C15="","",IFERROR("→ "&amp;INDEX({"Pulsador","Test","Verdad o mentira","Dos verdades","Votación","Estimación","Contador","Reflejos","Libre","Palabras","Agitar","Apuesta"},MATCH(C15,{"Pulsador","Test","Verdad o mentira","Dos verdades y una mentira","Votación","Estimación","Parar el contador","Duelo de reflejos","Libre","Palabras secretas","Agita el móvil","La gran apuesta"},0)),"¿tipo?"))</f>
         <v/>
       </c>
       <c r="E15" s="14"/>
@@ -7363,7 +12944,7 @@
       <c r="B16" s="12"/>
       <c r="C16" s="12"/>
       <c r="D16" s="13" t="str">
-        <f>IF(C16="","",IFERROR("→ "&amp;INDEX({"Pulsador","Test","Verdad o mentira","Dos verdades","Votación","Estimación","Contador","Reflejos","Libre"},MATCH(C16,{"Pulsador","Test","Verdad o mentira","Dos verdades y una mentira","Votación","Estimación","Parar el contador","Duelo de reflejos","Libre"},0)),"¿tipo?"))</f>
+        <f>IF(C16="","",IFERROR("→ "&amp;INDEX({"Pulsador","Test","Verdad o mentira","Dos verdades","Votación","Estimación","Contador","Reflejos","Libre","Palabras","Agitar","Apuesta"},MATCH(C16,{"Pulsador","Test","Verdad o mentira","Dos verdades y una mentira","Votación","Estimación","Parar el contador","Duelo de reflejos","Libre","Palabras secretas","Agita el móvil","La gran apuesta"},0)),"¿tipo?"))</f>
         <v/>
       </c>
       <c r="E16" s="14"/>
@@ -7377,7 +12958,7 @@
       <c r="B17" s="12"/>
       <c r="C17" s="12"/>
       <c r="D17" s="13" t="str">
-        <f>IF(C17="","",IFERROR("→ "&amp;INDEX({"Pulsador","Test","Verdad o mentira","Dos verdades","Votación","Estimación","Contador","Reflejos","Libre"},MATCH(C17,{"Pulsador","Test","Verdad o mentira","Dos verdades y una mentira","Votación","Estimación","Parar el contador","Duelo de reflejos","Libre"},0)),"¿tipo?"))</f>
+        <f>IF(C17="","",IFERROR("→ "&amp;INDEX({"Pulsador","Test","Verdad o mentira","Dos verdades","Votación","Estimación","Contador","Reflejos","Libre","Palabras","Agitar","Apuesta"},MATCH(C17,{"Pulsador","Test","Verdad o mentira","Dos verdades y una mentira","Votación","Estimación","Parar el contador","Duelo de reflejos","Libre","Palabras secretas","Agita el móvil","La gran apuesta"},0)),"¿tipo?"))</f>
         <v/>
       </c>
       <c r="E17" s="14"/>
@@ -7391,7 +12972,7 @@
       <c r="B18" s="12"/>
       <c r="C18" s="12"/>
       <c r="D18" s="13" t="str">
-        <f>IF(C18="","",IFERROR("→ "&amp;INDEX({"Pulsador","Test","Verdad o mentira","Dos verdades","Votación","Estimación","Contador","Reflejos","Libre"},MATCH(C18,{"Pulsador","Test","Verdad o mentira","Dos verdades y una mentira","Votación","Estimación","Parar el contador","Duelo de reflejos","Libre"},0)),"¿tipo?"))</f>
+        <f>IF(C18="","",IFERROR("→ "&amp;INDEX({"Pulsador","Test","Verdad o mentira","Dos verdades","Votación","Estimación","Contador","Reflejos","Libre","Palabras","Agitar","Apuesta"},MATCH(C18,{"Pulsador","Test","Verdad o mentira","Dos verdades y una mentira","Votación","Estimación","Parar el contador","Duelo de reflejos","Libre","Palabras secretas","Agita el móvil","La gran apuesta"},0)),"¿tipo?"))</f>
         <v/>
       </c>
       <c r="E18" s="14"/>
@@ -7405,7 +12986,7 @@
       <c r="B19" s="12"/>
       <c r="C19" s="12"/>
       <c r="D19" s="13" t="str">
-        <f>IF(C19="","",IFERROR("→ "&amp;INDEX({"Pulsador","Test","Verdad o mentira","Dos verdades","Votación","Estimación","Contador","Reflejos","Libre"},MATCH(C19,{"Pulsador","Test","Verdad o mentira","Dos verdades y una mentira","Votación","Estimación","Parar el contador","Duelo de reflejos","Libre"},0)),"¿tipo?"))</f>
+        <f>IF(C19="","",IFERROR("→ "&amp;INDEX({"Pulsador","Test","Verdad o mentira","Dos verdades","Votación","Estimación","Contador","Reflejos","Libre","Palabras","Agitar","Apuesta"},MATCH(C19,{"Pulsador","Test","Verdad o mentira","Dos verdades y una mentira","Votación","Estimación","Parar el contador","Duelo de reflejos","Libre","Palabras secretas","Agita el móvil","La gran apuesta"},0)),"¿tipo?"))</f>
         <v/>
       </c>
       <c r="E19" s="14"/>
@@ -7419,7 +13000,7 @@
       <c r="B20" s="12"/>
       <c r="C20" s="12"/>
       <c r="D20" s="13" t="str">
-        <f>IF(C20="","",IFERROR("→ "&amp;INDEX({"Pulsador","Test","Verdad o mentira","Dos verdades","Votación","Estimación","Contador","Reflejos","Libre"},MATCH(C20,{"Pulsador","Test","Verdad o mentira","Dos verdades y una mentira","Votación","Estimación","Parar el contador","Duelo de reflejos","Libre"},0)),"¿tipo?"))</f>
+        <f>IF(C20="","",IFERROR("→ "&amp;INDEX({"Pulsador","Test","Verdad o mentira","Dos verdades","Votación","Estimación","Contador","Reflejos","Libre","Palabras","Agitar","Apuesta"},MATCH(C20,{"Pulsador","Test","Verdad o mentira","Dos verdades y una mentira","Votación","Estimación","Parar el contador","Duelo de reflejos","Libre","Palabras secretas","Agita el móvil","La gran apuesta"},0)),"¿tipo?"))</f>
         <v/>
       </c>
       <c r="E20" s="14"/>
@@ -7433,7 +13014,7 @@
       <c r="B21" s="12"/>
       <c r="C21" s="12"/>
       <c r="D21" s="13" t="str">
-        <f>IF(C21="","",IFERROR("→ "&amp;INDEX({"Pulsador","Test","Verdad o mentira","Dos verdades","Votación","Estimación","Contador","Reflejos","Libre"},MATCH(C21,{"Pulsador","Test","Verdad o mentira","Dos verdades y una mentira","Votación","Estimación","Parar el contador","Duelo de reflejos","Libre"},0)),"¿tipo?"))</f>
+        <f>IF(C21="","",IFERROR("→ "&amp;INDEX({"Pulsador","Test","Verdad o mentira","Dos verdades","Votación","Estimación","Contador","Reflejos","Libre","Palabras","Agitar","Apuesta"},MATCH(C21,{"Pulsador","Test","Verdad o mentira","Dos verdades y una mentira","Votación","Estimación","Parar el contador","Duelo de reflejos","Libre","Palabras secretas","Agita el móvil","La gran apuesta"},0)),"¿tipo?"))</f>
         <v/>
       </c>
       <c r="E21" s="14"/>
@@ -7447,7 +13028,7 @@
       <c r="B22" s="12"/>
       <c r="C22" s="12"/>
       <c r="D22" s="13" t="str">
-        <f>IF(C22="","",IFERROR("→ "&amp;INDEX({"Pulsador","Test","Verdad o mentira","Dos verdades","Votación","Estimación","Contador","Reflejos","Libre"},MATCH(C22,{"Pulsador","Test","Verdad o mentira","Dos verdades y una mentira","Votación","Estimación","Parar el contador","Duelo de reflejos","Libre"},0)),"¿tipo?"))</f>
+        <f>IF(C22="","",IFERROR("→ "&amp;INDEX({"Pulsador","Test","Verdad o mentira","Dos verdades","Votación","Estimación","Contador","Reflejos","Libre","Palabras","Agitar","Apuesta"},MATCH(C22,{"Pulsador","Test","Verdad o mentira","Dos verdades y una mentira","Votación","Estimación","Parar el contador","Duelo de reflejos","Libre","Palabras secretas","Agita el móvil","La gran apuesta"},0)),"¿tipo?"))</f>
         <v/>
       </c>
       <c r="E22" s="14"/>
@@ -7461,7 +13042,7 @@
       <c r="B23" s="12"/>
       <c r="C23" s="12"/>
       <c r="D23" s="13" t="str">
-        <f>IF(C23="","",IFERROR("→ "&amp;INDEX({"Pulsador","Test","Verdad o mentira","Dos verdades","Votación","Estimación","Contador","Reflejos","Libre"},MATCH(C23,{"Pulsador","Test","Verdad o mentira","Dos verdades y una mentira","Votación","Estimación","Parar el contador","Duelo de reflejos","Libre"},0)),"¿tipo?"))</f>
+        <f>IF(C23="","",IFERROR("→ "&amp;INDEX({"Pulsador","Test","Verdad o mentira","Dos verdades","Votación","Estimación","Contador","Reflejos","Libre","Palabras","Agitar","Apuesta"},MATCH(C23,{"Pulsador","Test","Verdad o mentira","Dos verdades y una mentira","Votación","Estimación","Parar el contador","Duelo de reflejos","Libre","Palabras secretas","Agita el móvil","La gran apuesta"},0)),"¿tipo?"))</f>
         <v/>
       </c>
       <c r="E23" s="14"/>
@@ -7475,7 +13056,7 @@
       <c r="B24" s="12"/>
       <c r="C24" s="12"/>
       <c r="D24" s="13" t="str">
-        <f>IF(C24="","",IFERROR("→ "&amp;INDEX({"Pulsador","Test","Verdad o mentira","Dos verdades","Votación","Estimación","Contador","Reflejos","Libre"},MATCH(C24,{"Pulsador","Test","Verdad o mentira","Dos verdades y una mentira","Votación","Estimación","Parar el contador","Duelo de reflejos","Libre"},0)),"¿tipo?"))</f>
+        <f>IF(C24="","",IFERROR("→ "&amp;INDEX({"Pulsador","Test","Verdad o mentira","Dos verdades","Votación","Estimación","Contador","Reflejos","Libre","Palabras","Agitar","Apuesta"},MATCH(C24,{"Pulsador","Test","Verdad o mentira","Dos verdades y una mentira","Votación","Estimación","Parar el contador","Duelo de reflejos","Libre","Palabras secretas","Agita el móvil","La gran apuesta"},0)),"¿tipo?"))</f>
         <v/>
       </c>
       <c r="E24" s="14"/>
@@ -7489,7 +13070,7 @@
       <c r="B25" s="12"/>
       <c r="C25" s="12"/>
       <c r="D25" s="13" t="str">
-        <f>IF(C25="","",IFERROR("→ "&amp;INDEX({"Pulsador","Test","Verdad o mentira","Dos verdades","Votación","Estimación","Contador","Reflejos","Libre"},MATCH(C25,{"Pulsador","Test","Verdad o mentira","Dos verdades y una mentira","Votación","Estimación","Parar el contador","Duelo de reflejos","Libre"},0)),"¿tipo?"))</f>
+        <f>IF(C25="","",IFERROR("→ "&amp;INDEX({"Pulsador","Test","Verdad o mentira","Dos verdades","Votación","Estimación","Contador","Reflejos","Libre","Palabras","Agitar","Apuesta"},MATCH(C25,{"Pulsador","Test","Verdad o mentira","Dos verdades y una mentira","Votación","Estimación","Parar el contador","Duelo de reflejos","Libre","Palabras secretas","Agita el móvil","La gran apuesta"},0)),"¿tipo?"))</f>
         <v/>
       </c>
       <c r="E25" s="14"/>
@@ -7503,7 +13084,7 @@
       <c r="B26" s="12"/>
       <c r="C26" s="12"/>
       <c r="D26" s="13" t="str">
-        <f>IF(C26="","",IFERROR("→ "&amp;INDEX({"Pulsador","Test","Verdad o mentira","Dos verdades","Votación","Estimación","Contador","Reflejos","Libre"},MATCH(C26,{"Pulsador","Test","Verdad o mentira","Dos verdades y una mentira","Votación","Estimación","Parar el contador","Duelo de reflejos","Libre"},0)),"¿tipo?"))</f>
+        <f>IF(C26="","",IFERROR("→ "&amp;INDEX({"Pulsador","Test","Verdad o mentira","Dos verdades","Votación","Estimación","Contador","Reflejos","Libre","Palabras","Agitar","Apuesta"},MATCH(C26,{"Pulsador","Test","Verdad o mentira","Dos verdades y una mentira","Votación","Estimación","Parar el contador","Duelo de reflejos","Libre","Palabras secretas","Agita el móvil","La gran apuesta"},0)),"¿tipo?"))</f>
         <v/>
       </c>
       <c r="E26" s="14"/>
@@ -7517,7 +13098,7 @@
       <c r="B27" s="12"/>
       <c r="C27" s="12"/>
       <c r="D27" s="13" t="str">
-        <f>IF(C27="","",IFERROR("→ "&amp;INDEX({"Pulsador","Test","Verdad o mentira","Dos verdades","Votación","Estimación","Contador","Reflejos","Libre"},MATCH(C27,{"Pulsador","Test","Verdad o mentira","Dos verdades y una mentira","Votación","Estimación","Parar el contador","Duelo de reflejos","Libre"},0)),"¿tipo?"))</f>
+        <f>IF(C27="","",IFERROR("→ "&amp;INDEX({"Pulsador","Test","Verdad o mentira","Dos verdades","Votación","Estimación","Contador","Reflejos","Libre","Palabras","Agitar","Apuesta"},MATCH(C27,{"Pulsador","Test","Verdad o mentira","Dos verdades y una mentira","Votación","Estimación","Parar el contador","Duelo de reflejos","Libre","Palabras secretas","Agita el móvil","La gran apuesta"},0)),"¿tipo?"))</f>
         <v/>
       </c>
       <c r="E27" s="14"/>
@@ -7531,7 +13112,7 @@
       <c r="B28" s="12"/>
       <c r="C28" s="12"/>
       <c r="D28" s="13" t="str">
-        <f>IF(C28="","",IFERROR("→ "&amp;INDEX({"Pulsador","Test","Verdad o mentira","Dos verdades","Votación","Estimación","Contador","Reflejos","Libre"},MATCH(C28,{"Pulsador","Test","Verdad o mentira","Dos verdades y una mentira","Votación","Estimación","Parar el contador","Duelo de reflejos","Libre"},0)),"¿tipo?"))</f>
+        <f>IF(C28="","",IFERROR("→ "&amp;INDEX({"Pulsador","Test","Verdad o mentira","Dos verdades","Votación","Estimación","Contador","Reflejos","Libre","Palabras","Agitar","Apuesta"},MATCH(C28,{"Pulsador","Test","Verdad o mentira","Dos verdades y una mentira","Votación","Estimación","Parar el contador","Duelo de reflejos","Libre","Palabras secretas","Agita el móvil","La gran apuesta"},0)),"¿tipo?"))</f>
         <v/>
       </c>
       <c r="E28" s="14"/>
@@ -7545,7 +13126,7 @@
       <c r="B29" s="12"/>
       <c r="C29" s="12"/>
       <c r="D29" s="13" t="str">
-        <f>IF(C29="","",IFERROR("→ "&amp;INDEX({"Pulsador","Test","Verdad o mentira","Dos verdades","Votación","Estimación","Contador","Reflejos","Libre"},MATCH(C29,{"Pulsador","Test","Verdad o mentira","Dos verdades y una mentira","Votación","Estimación","Parar el contador","Duelo de reflejos","Libre"},0)),"¿tipo?"))</f>
+        <f>IF(C29="","",IFERROR("→ "&amp;INDEX({"Pulsador","Test","Verdad o mentira","Dos verdades","Votación","Estimación","Contador","Reflejos","Libre","Palabras","Agitar","Apuesta"},MATCH(C29,{"Pulsador","Test","Verdad o mentira","Dos verdades y una mentira","Votación","Estimación","Parar el contador","Duelo de reflejos","Libre","Palabras secretas","Agita el móvil","La gran apuesta"},0)),"¿tipo?"))</f>
         <v/>
       </c>
       <c r="E29" s="14"/>
@@ -7559,7 +13140,7 @@
       <c r="B30" s="12"/>
       <c r="C30" s="12"/>
       <c r="D30" s="13" t="str">
-        <f>IF(C30="","",IFERROR("→ "&amp;INDEX({"Pulsador","Test","Verdad o mentira","Dos verdades","Votación","Estimación","Contador","Reflejos","Libre"},MATCH(C30,{"Pulsador","Test","Verdad o mentira","Dos verdades y una mentira","Votación","Estimación","Parar el contador","Duelo de reflejos","Libre"},0)),"¿tipo?"))</f>
+        <f>IF(C30="","",IFERROR("→ "&amp;INDEX({"Pulsador","Test","Verdad o mentira","Dos verdades","Votación","Estimación","Contador","Reflejos","Libre","Palabras","Agitar","Apuesta"},MATCH(C30,{"Pulsador","Test","Verdad o mentira","Dos verdades y una mentira","Votación","Estimación","Parar el contador","Duelo de reflejos","Libre","Palabras secretas","Agita el móvil","La gran apuesta"},0)),"¿tipo?"))</f>
         <v/>
       </c>
       <c r="E30" s="14"/>
@@ -7573,7 +13154,7 @@
       <c r="B31" s="12"/>
       <c r="C31" s="12"/>
       <c r="D31" s="13" t="str">
-        <f>IF(C31="","",IFERROR("→ "&amp;INDEX({"Pulsador","Test","Verdad o mentira","Dos verdades","Votación","Estimación","Contador","Reflejos","Libre"},MATCH(C31,{"Pulsador","Test","Verdad o mentira","Dos verdades y una mentira","Votación","Estimación","Parar el contador","Duelo de reflejos","Libre"},0)),"¿tipo?"))</f>
+        <f>IF(C31="","",IFERROR("→ "&amp;INDEX({"Pulsador","Test","Verdad o mentira","Dos verdades","Votación","Estimación","Contador","Reflejos","Libre","Palabras","Agitar","Apuesta"},MATCH(C31,{"Pulsador","Test","Verdad o mentira","Dos verdades y una mentira","Votación","Estimación","Parar el contador","Duelo de reflejos","Libre","Palabras secretas","Agita el móvil","La gran apuesta"},0)),"¿tipo?"))</f>
         <v/>
       </c>
       <c r="E31" s="14"/>
@@ -7587,7 +13168,7 @@
       <c r="B32" s="12"/>
       <c r="C32" s="12"/>
       <c r="D32" s="13" t="str">
-        <f>IF(C32="","",IFERROR("→ "&amp;INDEX({"Pulsador","Test","Verdad o mentira","Dos verdades","Votación","Estimación","Contador","Reflejos","Libre"},MATCH(C32,{"Pulsador","Test","Verdad o mentira","Dos verdades y una mentira","Votación","Estimación","Parar el contador","Duelo de reflejos","Libre"},0)),"¿tipo?"))</f>
+        <f>IF(C32="","",IFERROR("→ "&amp;INDEX({"Pulsador","Test","Verdad o mentira","Dos verdades","Votación","Estimación","Contador","Reflejos","Libre","Palabras","Agitar","Apuesta"},MATCH(C32,{"Pulsador","Test","Verdad o mentira","Dos verdades y una mentira","Votación","Estimación","Parar el contador","Duelo de reflejos","Libre","Palabras secretas","Agita el móvil","La gran apuesta"},0)),"¿tipo?"))</f>
         <v/>
       </c>
       <c r="E32" s="14"/>
@@ -7601,7 +13182,7 @@
       <c r="B33" s="12"/>
       <c r="C33" s="12"/>
       <c r="D33" s="13" t="str">
-        <f>IF(C33="","",IFERROR("→ "&amp;INDEX({"Pulsador","Test","Verdad o mentira","Dos verdades","Votación","Estimación","Contador","Reflejos","Libre"},MATCH(C33,{"Pulsador","Test","Verdad o mentira","Dos verdades y una mentira","Votación","Estimación","Parar el contador","Duelo de reflejos","Libre"},0)),"¿tipo?"))</f>
+        <f>IF(C33="","",IFERROR("→ "&amp;INDEX({"Pulsador","Test","Verdad o mentira","Dos verdades","Votación","Estimación","Contador","Reflejos","Libre","Palabras","Agitar","Apuesta"},MATCH(C33,{"Pulsador","Test","Verdad o mentira","Dos verdades y una mentira","Votación","Estimación","Parar el contador","Duelo de reflejos","Libre","Palabras secretas","Agita el móvil","La gran apuesta"},0)),"¿tipo?"))</f>
         <v/>
       </c>
       <c r="E33" s="14"/>
@@ -7615,7 +13196,7 @@
       <c r="B34" s="12"/>
       <c r="C34" s="12"/>
       <c r="D34" s="13" t="str">
-        <f>IF(C34="","",IFERROR("→ "&amp;INDEX({"Pulsador","Test","Verdad o mentira","Dos verdades","Votación","Estimación","Contador","Reflejos","Libre"},MATCH(C34,{"Pulsador","Test","Verdad o mentira","Dos verdades y una mentira","Votación","Estimación","Parar el contador","Duelo de reflejos","Libre"},0)),"¿tipo?"))</f>
+        <f>IF(C34="","",IFERROR("→ "&amp;INDEX({"Pulsador","Test","Verdad o mentira","Dos verdades","Votación","Estimación","Contador","Reflejos","Libre","Palabras","Agitar","Apuesta"},MATCH(C34,{"Pulsador","Test","Verdad o mentira","Dos verdades y una mentira","Votación","Estimación","Parar el contador","Duelo de reflejos","Libre","Palabras secretas","Agita el móvil","La gran apuesta"},0)),"¿tipo?"))</f>
         <v/>
       </c>
       <c r="E34" s="14"/>
@@ -7629,7 +13210,7 @@
       <c r="B35" s="12"/>
       <c r="C35" s="12"/>
       <c r="D35" s="13" t="str">
-        <f>IF(C35="","",IFERROR("→ "&amp;INDEX({"Pulsador","Test","Verdad o mentira","Dos verdades","Votación","Estimación","Contador","Reflejos","Libre"},MATCH(C35,{"Pulsador","Test","Verdad o mentira","Dos verdades y una mentira","Votación","Estimación","Parar el contador","Duelo de reflejos","Libre"},0)),"¿tipo?"))</f>
+        <f>IF(C35="","",IFERROR("→ "&amp;INDEX({"Pulsador","Test","Verdad o mentira","Dos verdades","Votación","Estimación","Contador","Reflejos","Libre","Palabras","Agitar","Apuesta"},MATCH(C35,{"Pulsador","Test","Verdad o mentira","Dos verdades y una mentira","Votación","Estimación","Parar el contador","Duelo de reflejos","Libre","Palabras secretas","Agita el móvil","La gran apuesta"},0)),"¿tipo?"))</f>
         <v/>
       </c>
       <c r="E35" s="14"/>
@@ -7643,7 +13224,7 @@
       <c r="B36" s="12"/>
       <c r="C36" s="12"/>
       <c r="D36" s="13" t="str">
-        <f>IF(C36="","",IFERROR("→ "&amp;INDEX({"Pulsador","Test","Verdad o mentira","Dos verdades","Votación","Estimación","Contador","Reflejos","Libre"},MATCH(C36,{"Pulsador","Test","Verdad o mentira","Dos verdades y una mentira","Votación","Estimación","Parar el contador","Duelo de reflejos","Libre"},0)),"¿tipo?"))</f>
+        <f>IF(C36="","",IFERROR("→ "&amp;INDEX({"Pulsador","Test","Verdad o mentira","Dos verdades","Votación","Estimación","Contador","Reflejos","Libre","Palabras","Agitar","Apuesta"},MATCH(C36,{"Pulsador","Test","Verdad o mentira","Dos verdades y una mentira","Votación","Estimación","Parar el contador","Duelo de reflejos","Libre","Palabras secretas","Agita el móvil","La gran apuesta"},0)),"¿tipo?"))</f>
         <v/>
       </c>
       <c r="E36" s="14"/>
@@ -7657,7 +13238,7 @@
       <c r="B37" s="12"/>
       <c r="C37" s="12"/>
       <c r="D37" s="13" t="str">
-        <f>IF(C37="","",IFERROR("→ "&amp;INDEX({"Pulsador","Test","Verdad o mentira","Dos verdades","Votación","Estimación","Contador","Reflejos","Libre"},MATCH(C37,{"Pulsador","Test","Verdad o mentira","Dos verdades y una mentira","Votación","Estimación","Parar el contador","Duelo de reflejos","Libre"},0)),"¿tipo?"))</f>
+        <f>IF(C37="","",IFERROR("→ "&amp;INDEX({"Pulsador","Test","Verdad o mentira","Dos verdades","Votación","Estimación","Contador","Reflejos","Libre","Palabras","Agitar","Apuesta"},MATCH(C37,{"Pulsador","Test","Verdad o mentira","Dos verdades y una mentira","Votación","Estimación","Parar el contador","Duelo de reflejos","Libre","Palabras secretas","Agita el móvil","La gran apuesta"},0)),"¿tipo?"))</f>
         <v/>
       </c>
       <c r="E37" s="14"/>
@@ -7671,7 +13252,7 @@
       <c r="B38" s="12"/>
       <c r="C38" s="12"/>
       <c r="D38" s="13" t="str">
-        <f>IF(C38="","",IFERROR("→ "&amp;INDEX({"Pulsador","Test","Verdad o mentira","Dos verdades","Votación","Estimación","Contador","Reflejos","Libre"},MATCH(C38,{"Pulsador","Test","Verdad o mentira","Dos verdades y una mentira","Votación","Estimación","Parar el contador","Duelo de reflejos","Libre"},0)),"¿tipo?"))</f>
+        <f>IF(C38="","",IFERROR("→ "&amp;INDEX({"Pulsador","Test","Verdad o mentira","Dos verdades","Votación","Estimación","Contador","Reflejos","Libre","Palabras","Agitar","Apuesta"},MATCH(C38,{"Pulsador","Test","Verdad o mentira","Dos verdades y una mentira","Votación","Estimación","Parar el contador","Duelo de reflejos","Libre","Palabras secretas","Agita el móvil","La gran apuesta"},0)),"¿tipo?"))</f>
         <v/>
       </c>
       <c r="E38" s="14"/>
@@ -7685,7 +13266,7 @@
       <c r="B39" s="12"/>
       <c r="C39" s="12"/>
       <c r="D39" s="13" t="str">
-        <f>IF(C39="","",IFERROR("→ "&amp;INDEX({"Pulsador","Test","Verdad o mentira","Dos verdades","Votación","Estimación","Contador","Reflejos","Libre"},MATCH(C39,{"Pulsador","Test","Verdad o mentira","Dos verdades y una mentira","Votación","Estimación","Parar el contador","Duelo de reflejos","Libre"},0)),"¿tipo?"))</f>
+        <f>IF(C39="","",IFERROR("→ "&amp;INDEX({"Pulsador","Test","Verdad o mentira","Dos verdades","Votación","Estimación","Contador","Reflejos","Libre","Palabras","Agitar","Apuesta"},MATCH(C39,{"Pulsador","Test","Verdad o mentira","Dos verdades y una mentira","Votación","Estimación","Parar el contador","Duelo de reflejos","Libre","Palabras secretas","Agita el móvil","La gran apuesta"},0)),"¿tipo?"))</f>
         <v/>
       </c>
       <c r="E39" s="14"/>
@@ -7699,7 +13280,7 @@
       <c r="B40" s="12"/>
       <c r="C40" s="12"/>
       <c r="D40" s="13" t="str">
-        <f>IF(C40="","",IFERROR("→ "&amp;INDEX({"Pulsador","Test","Verdad o mentira","Dos verdades","Votación","Estimación","Contador","Reflejos","Libre"},MATCH(C40,{"Pulsador","Test","Verdad o mentira","Dos verdades y una mentira","Votación","Estimación","Parar el contador","Duelo de reflejos","Libre"},0)),"¿tipo?"))</f>
+        <f>IF(C40="","",IFERROR("→ "&amp;INDEX({"Pulsador","Test","Verdad o mentira","Dos verdades","Votación","Estimación","Contador","Reflejos","Libre","Palabras","Agitar","Apuesta"},MATCH(C40,{"Pulsador","Test","Verdad o mentira","Dos verdades y una mentira","Votación","Estimación","Parar el contador","Duelo de reflejos","Libre","Palabras secretas","Agita el móvil","La gran apuesta"},0)),"¿tipo?"))</f>
         <v/>
       </c>
       <c r="E40" s="14"/>
@@ -7713,7 +13294,7 @@
       <c r="B41" s="12"/>
       <c r="C41" s="12"/>
       <c r="D41" s="13" t="str">
-        <f>IF(C41="","",IFERROR("→ "&amp;INDEX({"Pulsador","Test","Verdad o mentira","Dos verdades","Votación","Estimación","Contador","Reflejos","Libre"},MATCH(C41,{"Pulsador","Test","Verdad o mentira","Dos verdades y una mentira","Votación","Estimación","Parar el contador","Duelo de reflejos","Libre"},0)),"¿tipo?"))</f>
+        <f>IF(C41="","",IFERROR("→ "&amp;INDEX({"Pulsador","Test","Verdad o mentira","Dos verdades","Votación","Estimación","Contador","Reflejos","Libre","Palabras","Agitar","Apuesta"},MATCH(C41,{"Pulsador","Test","Verdad o mentira","Dos verdades y una mentira","Votación","Estimación","Parar el contador","Duelo de reflejos","Libre","Palabras secretas","Agita el móvil","La gran apuesta"},0)),"¿tipo?"))</f>
         <v/>
       </c>
       <c r="E41" s="14"/>
@@ -7727,7 +13308,7 @@
       <c r="B42" s="12"/>
       <c r="C42" s="12"/>
       <c r="D42" s="13" t="str">
-        <f>IF(C42="","",IFERROR("→ "&amp;INDEX({"Pulsador","Test","Verdad o mentira","Dos verdades","Votación","Estimación","Contador","Reflejos","Libre"},MATCH(C42,{"Pulsador","Test","Verdad o mentira","Dos verdades y una mentira","Votación","Estimación","Parar el contador","Duelo de reflejos","Libre"},0)),"¿tipo?"))</f>
+        <f>IF(C42="","",IFERROR("→ "&amp;INDEX({"Pulsador","Test","Verdad o mentira","Dos verdades","Votación","Estimación","Contador","Reflejos","Libre","Palabras","Agitar","Apuesta"},MATCH(C42,{"Pulsador","Test","Verdad o mentira","Dos verdades y una mentira","Votación","Estimación","Parar el contador","Duelo de reflejos","Libre","Palabras secretas","Agita el móvil","La gran apuesta"},0)),"¿tipo?"))</f>
         <v/>
       </c>
       <c r="E42" s="14"/>
@@ -7741,7 +13322,7 @@
       <c r="B43" s="12"/>
       <c r="C43" s="12"/>
       <c r="D43" s="13" t="str">
-        <f>IF(C43="","",IFERROR("→ "&amp;INDEX({"Pulsador","Test","Verdad o mentira","Dos verdades","Votación","Estimación","Contador","Reflejos","Libre"},MATCH(C43,{"Pulsador","Test","Verdad o mentira","Dos verdades y una mentira","Votación","Estimación","Parar el contador","Duelo de reflejos","Libre"},0)),"¿tipo?"))</f>
+        <f>IF(C43="","",IFERROR("→ "&amp;INDEX({"Pulsador","Test","Verdad o mentira","Dos verdades","Votación","Estimación","Contador","Reflejos","Libre","Palabras","Agitar","Apuesta"},MATCH(C43,{"Pulsador","Test","Verdad o mentira","Dos verdades y una mentira","Votación","Estimación","Parar el contador","Duelo de reflejos","Libre","Palabras secretas","Agita el móvil","La gran apuesta"},0)),"¿tipo?"))</f>
         <v/>
       </c>
       <c r="E43" s="14"/>
@@ -7755,7 +13336,7 @@
       <c r="B44" s="12"/>
       <c r="C44" s="12"/>
       <c r="D44" s="13" t="str">
-        <f>IF(C44="","",IFERROR("→ "&amp;INDEX({"Pulsador","Test","Verdad o mentira","Dos verdades","Votación","Estimación","Contador","Reflejos","Libre"},MATCH(C44,{"Pulsador","Test","Verdad o mentira","Dos verdades y una mentira","Votación","Estimación","Parar el contador","Duelo de reflejos","Libre"},0)),"¿tipo?"))</f>
+        <f>IF(C44="","",IFERROR("→ "&amp;INDEX({"Pulsador","Test","Verdad o mentira","Dos verdades","Votación","Estimación","Contador","Reflejos","Libre","Palabras","Agitar","Apuesta"},MATCH(C44,{"Pulsador","Test","Verdad o mentira","Dos verdades y una mentira","Votación","Estimación","Parar el contador","Duelo de reflejos","Libre","Palabras secretas","Agita el móvil","La gran apuesta"},0)),"¿tipo?"))</f>
         <v/>
       </c>
       <c r="E44" s="14"/>
@@ -7769,7 +13350,7 @@
       <c r="B45" s="12"/>
       <c r="C45" s="12"/>
       <c r="D45" s="13" t="str">
-        <f>IF(C45="","",IFERROR("→ "&amp;INDEX({"Pulsador","Test","Verdad o mentira","Dos verdades","Votación","Estimación","Contador","Reflejos","Libre"},MATCH(C45,{"Pulsador","Test","Verdad o mentira","Dos verdades y una mentira","Votación","Estimación","Parar el contador","Duelo de reflejos","Libre"},0)),"¿tipo?"))</f>
+        <f>IF(C45="","",IFERROR("→ "&amp;INDEX({"Pulsador","Test","Verdad o mentira","Dos verdades","Votación","Estimación","Contador","Reflejos","Libre","Palabras","Agitar","Apuesta"},MATCH(C45,{"Pulsador","Test","Verdad o mentira","Dos verdades y una mentira","Votación","Estimación","Parar el contador","Duelo de reflejos","Libre","Palabras secretas","Agita el móvil","La gran apuesta"},0)),"¿tipo?"))</f>
         <v/>
       </c>
       <c r="E45" s="14"/>
@@ -7783,7 +13364,7 @@
       <c r="B46" s="12"/>
       <c r="C46" s="12"/>
       <c r="D46" s="13" t="str">
-        <f>IF(C46="","",IFERROR("→ "&amp;INDEX({"Pulsador","Test","Verdad o mentira","Dos verdades","Votación","Estimación","Contador","Reflejos","Libre"},MATCH(C46,{"Pulsador","Test","Verdad o mentira","Dos verdades y una mentira","Votación","Estimación","Parar el contador","Duelo de reflejos","Libre"},0)),"¿tipo?"))</f>
+        <f>IF(C46="","",IFERROR("→ "&amp;INDEX({"Pulsador","Test","Verdad o mentira","Dos verdades","Votación","Estimación","Contador","Reflejos","Libre","Palabras","Agitar","Apuesta"},MATCH(C46,{"Pulsador","Test","Verdad o mentira","Dos verdades y una mentira","Votación","Estimación","Parar el contador","Duelo de reflejos","Libre","Palabras secretas","Agita el móvil","La gran apuesta"},0)),"¿tipo?"))</f>
         <v/>
       </c>
       <c r="E46" s="14"/>
@@ -7797,7 +13378,7 @@
       <c r="B47" s="12"/>
       <c r="C47" s="12"/>
       <c r="D47" s="13" t="str">
-        <f>IF(C47="","",IFERROR("→ "&amp;INDEX({"Pulsador","Test","Verdad o mentira","Dos verdades","Votación","Estimación","Contador","Reflejos","Libre"},MATCH(C47,{"Pulsador","Test","Verdad o mentira","Dos verdades y una mentira","Votación","Estimación","Parar el contador","Duelo de reflejos","Libre"},0)),"¿tipo?"))</f>
+        <f>IF(C47="","",IFERROR("→ "&amp;INDEX({"Pulsador","Test","Verdad o mentira","Dos verdades","Votación","Estimación","Contador","Reflejos","Libre","Palabras","Agitar","Apuesta"},MATCH(C47,{"Pulsador","Test","Verdad o mentira","Dos verdades y una mentira","Votación","Estimación","Parar el contador","Duelo de reflejos","Libre","Palabras secretas","Agita el móvil","La gran apuesta"},0)),"¿tipo?"))</f>
         <v/>
       </c>
       <c r="E47" s="14"/>
@@ -7811,7 +13392,7 @@
       <c r="B48" s="12"/>
       <c r="C48" s="12"/>
       <c r="D48" s="13" t="str">
-        <f>IF(C48="","",IFERROR("→ "&amp;INDEX({"Pulsador","Test","Verdad o mentira","Dos verdades","Votación","Estimación","Contador","Reflejos","Libre"},MATCH(C48,{"Pulsador","Test","Verdad o mentira","Dos verdades y una mentira","Votación","Estimación","Parar el contador","Duelo de reflejos","Libre"},0)),"¿tipo?"))</f>
+        <f>IF(C48="","",IFERROR("→ "&amp;INDEX({"Pulsador","Test","Verdad o mentira","Dos verdades","Votación","Estimación","Contador","Reflejos","Libre","Palabras","Agitar","Apuesta"},MATCH(C48,{"Pulsador","Test","Verdad o mentira","Dos verdades y una mentira","Votación","Estimación","Parar el contador","Duelo de reflejos","Libre","Palabras secretas","Agita el móvil","La gran apuesta"},0)),"¿tipo?"))</f>
         <v/>
       </c>
       <c r="E48" s="14"/>
@@ -7825,7 +13406,7 @@
       <c r="B49" s="12"/>
       <c r="C49" s="12"/>
       <c r="D49" s="13" t="str">
-        <f>IF(C49="","",IFERROR("→ "&amp;INDEX({"Pulsador","Test","Verdad o mentira","Dos verdades","Votación","Estimación","Contador","Reflejos","Libre"},MATCH(C49,{"Pulsador","Test","Verdad o mentira","Dos verdades y una mentira","Votación","Estimación","Parar el contador","Duelo de reflejos","Libre"},0)),"¿tipo?"))</f>
+        <f>IF(C49="","",IFERROR("→ "&amp;INDEX({"Pulsador","Test","Verdad o mentira","Dos verdades","Votación","Estimación","Contador","Reflejos","Libre","Palabras","Agitar","Apuesta"},MATCH(C49,{"Pulsador","Test","Verdad o mentira","Dos verdades y una mentira","Votación","Estimación","Parar el contador","Duelo de reflejos","Libre","Palabras secretas","Agita el móvil","La gran apuesta"},0)),"¿tipo?"))</f>
         <v/>
       </c>
       <c r="E49" s="14"/>
@@ -7839,7 +13420,7 @@
       <c r="B50" s="12"/>
       <c r="C50" s="12"/>
       <c r="D50" s="13" t="str">
-        <f>IF(C50="","",IFERROR("→ "&amp;INDEX({"Pulsador","Test","Verdad o mentira","Dos verdades","Votación","Estimación","Contador","Reflejos","Libre"},MATCH(C50,{"Pulsador","Test","Verdad o mentira","Dos verdades y una mentira","Votación","Estimación","Parar el contador","Duelo de reflejos","Libre"},0)),"¿tipo?"))</f>
+        <f>IF(C50="","",IFERROR("→ "&amp;INDEX({"Pulsador","Test","Verdad o mentira","Dos verdades","Votación","Estimación","Contador","Reflejos","Libre","Palabras","Agitar","Apuesta"},MATCH(C50,{"Pulsador","Test","Verdad o mentira","Dos verdades y una mentira","Votación","Estimación","Parar el contador","Duelo de reflejos","Libre","Palabras secretas","Agita el móvil","La gran apuesta"},0)),"¿tipo?"))</f>
         <v/>
       </c>
       <c r="E50" s="14"/>
@@ -7853,7 +13434,7 @@
       <c r="B51" s="12"/>
       <c r="C51" s="12"/>
       <c r="D51" s="13" t="str">
-        <f>IF(C51="","",IFERROR("→ "&amp;INDEX({"Pulsador","Test","Verdad o mentira","Dos verdades","Votación","Estimación","Contador","Reflejos","Libre"},MATCH(C51,{"Pulsador","Test","Verdad o mentira","Dos verdades y una mentira","Votación","Estimación","Parar el contador","Duelo de reflejos","Libre"},0)),"¿tipo?"))</f>
+        <f>IF(C51="","",IFERROR("→ "&amp;INDEX({"Pulsador","Test","Verdad o mentira","Dos verdades","Votación","Estimación","Contador","Reflejos","Libre","Palabras","Agitar","Apuesta"},MATCH(C51,{"Pulsador","Test","Verdad o mentira","Dos verdades y una mentira","Votación","Estimación","Parar el contador","Duelo de reflejos","Libre","Palabras secretas","Agita el móvil","La gran apuesta"},0)),"¿tipo?"))</f>
         <v/>
       </c>
       <c r="E51" s="14"/>
@@ -7867,7 +13448,7 @@
       <c r="B52" s="12"/>
       <c r="C52" s="12"/>
       <c r="D52" s="13" t="str">
-        <f>IF(C52="","",IFERROR("→ "&amp;INDEX({"Pulsador","Test","Verdad o mentira","Dos verdades","Votación","Estimación","Contador","Reflejos","Libre"},MATCH(C52,{"Pulsador","Test","Verdad o mentira","Dos verdades y una mentira","Votación","Estimación","Parar el contador","Duelo de reflejos","Libre"},0)),"¿tipo?"))</f>
+        <f>IF(C52="","",IFERROR("→ "&amp;INDEX({"Pulsador","Test","Verdad o mentira","Dos verdades","Votación","Estimación","Contador","Reflejos","Libre","Palabras","Agitar","Apuesta"},MATCH(C52,{"Pulsador","Test","Verdad o mentira","Dos verdades y una mentira","Votación","Estimación","Parar el contador","Duelo de reflejos","Libre","Palabras secretas","Agita el móvil","La gran apuesta"},0)),"¿tipo?"))</f>
         <v/>
       </c>
       <c r="E52" s="14"/>
@@ -7881,7 +13462,7 @@
       <c r="B53" s="12"/>
       <c r="C53" s="12"/>
       <c r="D53" s="13" t="str">
-        <f>IF(C53="","",IFERROR("→ "&amp;INDEX({"Pulsador","Test","Verdad o mentira","Dos verdades","Votación","Estimación","Contador","Reflejos","Libre"},MATCH(C53,{"Pulsador","Test","Verdad o mentira","Dos verdades y una mentira","Votación","Estimación","Parar el contador","Duelo de reflejos","Libre"},0)),"¿tipo?"))</f>
+        <f>IF(C53="","",IFERROR("→ "&amp;INDEX({"Pulsador","Test","Verdad o mentira","Dos verdades","Votación","Estimación","Contador","Reflejos","Libre","Palabras","Agitar","Apuesta"},MATCH(C53,{"Pulsador","Test","Verdad o mentira","Dos verdades y una mentira","Votación","Estimación","Parar el contador","Duelo de reflejos","Libre","Palabras secretas","Agita el móvil","La gran apuesta"},0)),"¿tipo?"))</f>
         <v/>
       </c>
       <c r="E53" s="14"/>
@@ -7895,7 +13476,7 @@
       <c r="B54" s="12"/>
       <c r="C54" s="12"/>
       <c r="D54" s="13" t="str">
-        <f>IF(C54="","",IFERROR("→ "&amp;INDEX({"Pulsador","Test","Verdad o mentira","Dos verdades","Votación","Estimación","Contador","Reflejos","Libre"},MATCH(C54,{"Pulsador","Test","Verdad o mentira","Dos verdades y una mentira","Votación","Estimación","Parar el contador","Duelo de reflejos","Libre"},0)),"¿tipo?"))</f>
+        <f>IF(C54="","",IFERROR("→ "&amp;INDEX({"Pulsador","Test","Verdad o mentira","Dos verdades","Votación","Estimación","Contador","Reflejos","Libre","Palabras","Agitar","Apuesta"},MATCH(C54,{"Pulsador","Test","Verdad o mentira","Dos verdades y una mentira","Votación","Estimación","Parar el contador","Duelo de reflejos","Libre","Palabras secretas","Agita el móvil","La gran apuesta"},0)),"¿tipo?"))</f>
         <v/>
       </c>
       <c r="E54" s="14"/>
@@ -7909,7 +13490,7 @@
       <c r="B55" s="12"/>
       <c r="C55" s="12"/>
       <c r="D55" s="13" t="str">
-        <f>IF(C55="","",IFERROR("→ "&amp;INDEX({"Pulsador","Test","Verdad o mentira","Dos verdades","Votación","Estimación","Contador","Reflejos","Libre"},MATCH(C55,{"Pulsador","Test","Verdad o mentira","Dos verdades y una mentira","Votación","Estimación","Parar el contador","Duelo de reflejos","Libre"},0)),"¿tipo?"))</f>
+        <f>IF(C55="","",IFERROR("→ "&amp;INDEX({"Pulsador","Test","Verdad o mentira","Dos verdades","Votación","Estimación","Contador","Reflejos","Libre","Palabras","Agitar","Apuesta"},MATCH(C55,{"Pulsador","Test","Verdad o mentira","Dos verdades y una mentira","Votación","Estimación","Parar el contador","Duelo de reflejos","Libre","Palabras secretas","Agita el móvil","La gran apuesta"},0)),"¿tipo?"))</f>
         <v/>
       </c>
       <c r="E55" s="14"/>
@@ -7923,7 +13504,7 @@
       <c r="B56" s="12"/>
       <c r="C56" s="12"/>
       <c r="D56" s="13" t="str">
-        <f>IF(C56="","",IFERROR("→ "&amp;INDEX({"Pulsador","Test","Verdad o mentira","Dos verdades","Votación","Estimación","Contador","Reflejos","Libre"},MATCH(C56,{"Pulsador","Test","Verdad o mentira","Dos verdades y una mentira","Votación","Estimación","Parar el contador","Duelo de reflejos","Libre"},0)),"¿tipo?"))</f>
+        <f>IF(C56="","",IFERROR("→ "&amp;INDEX({"Pulsador","Test","Verdad o mentira","Dos verdades","Votación","Estimación","Contador","Reflejos","Libre","Palabras","Agitar","Apuesta"},MATCH(C56,{"Pulsador","Test","Verdad o mentira","Dos verdades y una mentira","Votación","Estimación","Parar el contador","Duelo de reflejos","Libre","Palabras secretas","Agita el móvil","La gran apuesta"},0)),"¿tipo?"))</f>
         <v/>
       </c>
       <c r="E56" s="14"/>
@@ -7937,7 +13518,7 @@
       <c r="B57" s="12"/>
       <c r="C57" s="12"/>
       <c r="D57" s="13" t="str">
-        <f>IF(C57="","",IFERROR("→ "&amp;INDEX({"Pulsador","Test","Verdad o mentira","Dos verdades","Votación","Estimación","Contador","Reflejos","Libre"},MATCH(C57,{"Pulsador","Test","Verdad o mentira","Dos verdades y una mentira","Votación","Estimación","Parar el contador","Duelo de reflejos","Libre"},0)),"¿tipo?"))</f>
+        <f>IF(C57="","",IFERROR("→ "&amp;INDEX({"Pulsador","Test","Verdad o mentira","Dos verdades","Votación","Estimación","Contador","Reflejos","Libre","Palabras","Agitar","Apuesta"},MATCH(C57,{"Pulsador","Test","Verdad o mentira","Dos verdades y una mentira","Votación","Estimación","Parar el contador","Duelo de reflejos","Libre","Palabras secretas","Agita el móvil","La gran apuesta"},0)),"¿tipo?"))</f>
         <v/>
       </c>
       <c r="E57" s="14"/>
@@ -7951,7 +13532,7 @@
       <c r="B58" s="12"/>
       <c r="C58" s="12"/>
       <c r="D58" s="13" t="str">
-        <f>IF(C58="","",IFERROR("→ "&amp;INDEX({"Pulsador","Test","Verdad o mentira","Dos verdades","Votación","Estimación","Contador","Reflejos","Libre"},MATCH(C58,{"Pulsador","Test","Verdad o mentira","Dos verdades y una mentira","Votación","Estimación","Parar el contador","Duelo de reflejos","Libre"},0)),"¿tipo?"))</f>
+        <f>IF(C58="","",IFERROR("→ "&amp;INDEX({"Pulsador","Test","Verdad o mentira","Dos verdades","Votación","Estimación","Contador","Reflejos","Libre","Palabras","Agitar","Apuesta"},MATCH(C58,{"Pulsador","Test","Verdad o mentira","Dos verdades y una mentira","Votación","Estimación","Parar el contador","Duelo de reflejos","Libre","Palabras secretas","Agita el móvil","La gran apuesta"},0)),"¿tipo?"))</f>
         <v/>
       </c>
       <c r="E58" s="14"/>
@@ -7965,7 +13546,7 @@
       <c r="B59" s="12"/>
       <c r="C59" s="12"/>
       <c r="D59" s="13" t="str">
-        <f>IF(C59="","",IFERROR("→ "&amp;INDEX({"Pulsador","Test","Verdad o mentira","Dos verdades","Votación","Estimación","Contador","Reflejos","Libre"},MATCH(C59,{"Pulsador","Test","Verdad o mentira","Dos verdades y una mentira","Votación","Estimación","Parar el contador","Duelo de reflejos","Libre"},0)),"¿tipo?"))</f>
+        <f>IF(C59="","",IFERROR("→ "&amp;INDEX({"Pulsador","Test","Verdad o mentira","Dos verdades","Votación","Estimación","Contador","Reflejos","Libre","Palabras","Agitar","Apuesta"},MATCH(C59,{"Pulsador","Test","Verdad o mentira","Dos verdades y una mentira","Votación","Estimación","Parar el contador","Duelo de reflejos","Libre","Palabras secretas","Agita el móvil","La gran apuesta"},0)),"¿tipo?"))</f>
         <v/>
       </c>
       <c r="E59" s="14"/>
@@ -7979,7 +13560,7 @@
       <c r="B60" s="12"/>
       <c r="C60" s="12"/>
       <c r="D60" s="13" t="str">
-        <f>IF(C60="","",IFERROR("→ "&amp;INDEX({"Pulsador","Test","Verdad o mentira","Dos verdades","Votación","Estimación","Contador","Reflejos","Libre"},MATCH(C60,{"Pulsador","Test","Verdad o mentira","Dos verdades y una mentira","Votación","Estimación","Parar el contador","Duelo de reflejos","Libre"},0)),"¿tipo?"))</f>
+        <f>IF(C60="","",IFERROR("→ "&amp;INDEX({"Pulsador","Test","Verdad o mentira","Dos verdades","Votación","Estimación","Contador","Reflejos","Libre","Palabras","Agitar","Apuesta"},MATCH(C60,{"Pulsador","Test","Verdad o mentira","Dos verdades y una mentira","Votación","Estimación","Parar el contador","Duelo de reflejos","Libre","Palabras secretas","Agita el móvil","La gran apuesta"},0)),"¿tipo?"))</f>
         <v/>
       </c>
       <c r="E60" s="14"/>
@@ -7993,7 +13574,7 @@
       <c r="B61" s="12"/>
       <c r="C61" s="12"/>
       <c r="D61" s="13" t="str">
-        <f>IF(C61="","",IFERROR("→ "&amp;INDEX({"Pulsador","Test","Verdad o mentira","Dos verdades","Votación","Estimación","Contador","Reflejos","Libre"},MATCH(C61,{"Pulsador","Test","Verdad o mentira","Dos verdades y una mentira","Votación","Estimación","Parar el contador","Duelo de reflejos","Libre"},0)),"¿tipo?"))</f>
+        <f>IF(C61="","",IFERROR("→ "&amp;INDEX({"Pulsador","Test","Verdad o mentira","Dos verdades","Votación","Estimación","Contador","Reflejos","Libre","Palabras","Agitar","Apuesta"},MATCH(C61,{"Pulsador","Test","Verdad o mentira","Dos verdades y una mentira","Votación","Estimación","Parar el contador","Duelo de reflejos","Libre","Palabras secretas","Agita el móvil","La gran apuesta"},0)),"¿tipo?"))</f>
         <v/>
       </c>
       <c r="E61" s="14"/>
@@ -8007,7 +13588,7 @@
       <c r="B62" s="12"/>
       <c r="C62" s="12"/>
       <c r="D62" s="13" t="str">
-        <f>IF(C62="","",IFERROR("→ "&amp;INDEX({"Pulsador","Test","Verdad o mentira","Dos verdades","Votación","Estimación","Contador","Reflejos","Libre"},MATCH(C62,{"Pulsador","Test","Verdad o mentira","Dos verdades y una mentira","Votación","Estimación","Parar el contador","Duelo de reflejos","Libre"},0)),"¿tipo?"))</f>
+        <f>IF(C62="","",IFERROR("→ "&amp;INDEX({"Pulsador","Test","Verdad o mentira","Dos verdades","Votación","Estimación","Contador","Reflejos","Libre","Palabras","Agitar","Apuesta"},MATCH(C62,{"Pulsador","Test","Verdad o mentira","Dos verdades y una mentira","Votación","Estimación","Parar el contador","Duelo de reflejos","Libre","Palabras secretas","Agita el móvil","La gran apuesta"},0)),"¿tipo?"))</f>
         <v/>
       </c>
       <c r="E62" s="14"/>
@@ -8021,7 +13602,7 @@
       <c r="B63" s="12"/>
       <c r="C63" s="12"/>
       <c r="D63" s="13" t="str">
-        <f>IF(C63="","",IFERROR("→ "&amp;INDEX({"Pulsador","Test","Verdad o mentira","Dos verdades","Votación","Estimación","Contador","Reflejos","Libre"},MATCH(C63,{"Pulsador","Test","Verdad o mentira","Dos verdades y una mentira","Votación","Estimación","Parar el contador","Duelo de reflejos","Libre"},0)),"¿tipo?"))</f>
+        <f>IF(C63="","",IFERROR("→ "&amp;INDEX({"Pulsador","Test","Verdad o mentira","Dos verdades","Votación","Estimación","Contador","Reflejos","Libre","Palabras","Agitar","Apuesta"},MATCH(C63,{"Pulsador","Test","Verdad o mentira","Dos verdades y una mentira","Votación","Estimación","Parar el contador","Duelo de reflejos","Libre","Palabras secretas","Agita el móvil","La gran apuesta"},0)),"¿tipo?"))</f>
         <v/>
       </c>
       <c r="E63" s="14"/>
@@ -8035,7 +13616,7 @@
       <c r="B64" s="12"/>
       <c r="C64" s="12"/>
       <c r="D64" s="13" t="str">
-        <f>IF(C64="","",IFERROR("→ "&amp;INDEX({"Pulsador","Test","Verdad o mentira","Dos verdades","Votación","Estimación","Contador","Reflejos","Libre"},MATCH(C64,{"Pulsador","Test","Verdad o mentira","Dos verdades y una mentira","Votación","Estimación","Parar el contador","Duelo de reflejos","Libre"},0)),"¿tipo?"))</f>
+        <f>IF(C64="","",IFERROR("→ "&amp;INDEX({"Pulsador","Test","Verdad o mentira","Dos verdades","Votación","Estimación","Contador","Reflejos","Libre","Palabras","Agitar","Apuesta"},MATCH(C64,{"Pulsador","Test","Verdad o mentira","Dos verdades y una mentira","Votación","Estimación","Parar el contador","Duelo de reflejos","Libre","Palabras secretas","Agita el móvil","La gran apuesta"},0)),"¿tipo?"))</f>
         <v/>
       </c>
       <c r="E64" s="14"/>
@@ -8049,7 +13630,7 @@
       <c r="B65" s="12"/>
       <c r="C65" s="12"/>
       <c r="D65" s="13" t="str">
-        <f>IF(C65="","",IFERROR("→ "&amp;INDEX({"Pulsador","Test","Verdad o mentira","Dos verdades","Votación","Estimación","Contador","Reflejos","Libre"},MATCH(C65,{"Pulsador","Test","Verdad o mentira","Dos verdades y una mentira","Votación","Estimación","Parar el contador","Duelo de reflejos","Libre"},0)),"¿tipo?"))</f>
+        <f>IF(C65="","",IFERROR("→ "&amp;INDEX({"Pulsador","Test","Verdad o mentira","Dos verdades","Votación","Estimación","Contador","Reflejos","Libre","Palabras","Agitar","Apuesta"},MATCH(C65,{"Pulsador","Test","Verdad o mentira","Dos verdades y una mentira","Votación","Estimación","Parar el contador","Duelo de reflejos","Libre","Palabras secretas","Agita el móvil","La gran apuesta"},0)),"¿tipo?"))</f>
         <v/>
       </c>
       <c r="E65" s="14"/>
@@ -8063,7 +13644,7 @@
       <c r="B66" s="12"/>
       <c r="C66" s="12"/>
       <c r="D66" s="13" t="str">
-        <f>IF(C66="","",IFERROR("→ "&amp;INDEX({"Pulsador","Test","Verdad o mentira","Dos verdades","Votación","Estimación","Contador","Reflejos","Libre"},MATCH(C66,{"Pulsador","Test","Verdad o mentira","Dos verdades y una mentira","Votación","Estimación","Parar el contador","Duelo de reflejos","Libre"},0)),"¿tipo?"))</f>
+        <f>IF(C66="","",IFERROR("→ "&amp;INDEX({"Pulsador","Test","Verdad o mentira","Dos verdades","Votación","Estimación","Contador","Reflejos","Libre","Palabras","Agitar","Apuesta"},MATCH(C66,{"Pulsador","Test","Verdad o mentira","Dos verdades y una mentira","Votación","Estimación","Parar el contador","Duelo de reflejos","Libre","Palabras secretas","Agita el móvil","La gran apuesta"},0)),"¿tipo?"))</f>
         <v/>
       </c>
       <c r="E66" s="14"/>
@@ -8077,7 +13658,7 @@
       <c r="B67" s="12"/>
       <c r="C67" s="12"/>
       <c r="D67" s="13" t="str">
-        <f>IF(C67="","",IFERROR("→ "&amp;INDEX({"Pulsador","Test","Verdad o mentira","Dos verdades","Votación","Estimación","Contador","Reflejos","Libre"},MATCH(C67,{"Pulsador","Test","Verdad o mentira","Dos verdades y una mentira","Votación","Estimación","Parar el contador","Duelo de reflejos","Libre"},0)),"¿tipo?"))</f>
+        <f>IF(C67="","",IFERROR("→ "&amp;INDEX({"Pulsador","Test","Verdad o mentira","Dos verdades","Votación","Estimación","Contador","Reflejos","Libre","Palabras","Agitar","Apuesta"},MATCH(C67,{"Pulsador","Test","Verdad o mentira","Dos verdades y una mentira","Votación","Estimación","Parar el contador","Duelo de reflejos","Libre","Palabras secretas","Agita el móvil","La gran apuesta"},0)),"¿tipo?"))</f>
         <v/>
       </c>
       <c r="E67" s="14"/>
@@ -8091,7 +13672,7 @@
       <c r="B68" s="12"/>
       <c r="C68" s="12"/>
       <c r="D68" s="13" t="str">
-        <f>IF(C68="","",IFERROR("→ "&amp;INDEX({"Pulsador","Test","Verdad o mentira","Dos verdades","Votación","Estimación","Contador","Reflejos","Libre"},MATCH(C68,{"Pulsador","Test","Verdad o mentira","Dos verdades y una mentira","Votación","Estimación","Parar el contador","Duelo de reflejos","Libre"},0)),"¿tipo?"))</f>
+        <f>IF(C68="","",IFERROR("→ "&amp;INDEX({"Pulsador","Test","Verdad o mentira","Dos verdades","Votación","Estimación","Contador","Reflejos","Libre","Palabras","Agitar","Apuesta"},MATCH(C68,{"Pulsador","Test","Verdad o mentira","Dos verdades y una mentira","Votación","Estimación","Parar el contador","Duelo de reflejos","Libre","Palabras secretas","Agita el móvil","La gran apuesta"},0)),"¿tipo?"))</f>
         <v/>
       </c>
       <c r="E68" s="14"/>
@@ -8105,7 +13686,7 @@
       <c r="B69" s="12"/>
       <c r="C69" s="12"/>
       <c r="D69" s="13" t="str">
-        <f>IF(C69="","",IFERROR("→ "&amp;INDEX({"Pulsador","Test","Verdad o mentira","Dos verdades","Votación","Estimación","Contador","Reflejos","Libre"},MATCH(C69,{"Pulsador","Test","Verdad o mentira","Dos verdades y una mentira","Votación","Estimación","Parar el contador","Duelo de reflejos","Libre"},0)),"¿tipo?"))</f>
+        <f>IF(C69="","",IFERROR("→ "&amp;INDEX({"Pulsador","Test","Verdad o mentira","Dos verdades","Votación","Estimación","Contador","Reflejos","Libre","Palabras","Agitar","Apuesta"},MATCH(C69,{"Pulsador","Test","Verdad o mentira","Dos verdades y una mentira","Votación","Estimación","Parar el contador","Duelo de reflejos","Libre","Palabras secretas","Agita el móvil","La gran apuesta"},0)),"¿tipo?"))</f>
         <v/>
       </c>
       <c r="E69" s="14"/>
@@ -8119,7 +13700,7 @@
       <c r="B70" s="12"/>
       <c r="C70" s="12"/>
       <c r="D70" s="13" t="str">
-        <f>IF(C70="","",IFERROR("→ "&amp;INDEX({"Pulsador","Test","Verdad o mentira","Dos verdades","Votación","Estimación","Contador","Reflejos","Libre"},MATCH(C70,{"Pulsador","Test","Verdad o mentira","Dos verdades y una mentira","Votación","Estimación","Parar el contador","Duelo de reflejos","Libre"},0)),"¿tipo?"))</f>
+        <f>IF(C70="","",IFERROR("→ "&amp;INDEX({"Pulsador","Test","Verdad o mentira","Dos verdades","Votación","Estimación","Contador","Reflejos","Libre","Palabras","Agitar","Apuesta"},MATCH(C70,{"Pulsador","Test","Verdad o mentira","Dos verdades y una mentira","Votación","Estimación","Parar el contador","Duelo de reflejos","Libre","Palabras secretas","Agita el móvil","La gran apuesta"},0)),"¿tipo?"))</f>
         <v/>
       </c>
       <c r="E70" s="14"/>
@@ -8133,7 +13714,7 @@
       <c r="B71" s="12"/>
       <c r="C71" s="12"/>
       <c r="D71" s="13" t="str">
-        <f>IF(C71="","",IFERROR("→ "&amp;INDEX({"Pulsador","Test","Verdad o mentira","Dos verdades","Votación","Estimación","Contador","Reflejos","Libre"},MATCH(C71,{"Pulsador","Test","Verdad o mentira","Dos verdades y una mentira","Votación","Estimación","Parar el contador","Duelo de reflejos","Libre"},0)),"¿tipo?"))</f>
+        <f>IF(C71="","",IFERROR("→ "&amp;INDEX({"Pulsador","Test","Verdad o mentira","Dos verdades","Votación","Estimación","Contador","Reflejos","Libre","Palabras","Agitar","Apuesta"},MATCH(C71,{"Pulsador","Test","Verdad o mentira","Dos verdades y una mentira","Votación","Estimación","Parar el contador","Duelo de reflejos","Libre","Palabras secretas","Agita el móvil","La gran apuesta"},0)),"¿tipo?"))</f>
         <v/>
       </c>
       <c r="E71" s="14"/>
@@ -8147,7 +13728,7 @@
       <c r="B72" s="12"/>
       <c r="C72" s="12"/>
       <c r="D72" s="13" t="str">
-        <f>IF(C72="","",IFERROR("→ "&amp;INDEX({"Pulsador","Test","Verdad o mentira","Dos verdades","Votación","Estimación","Contador","Reflejos","Libre"},MATCH(C72,{"Pulsador","Test","Verdad o mentira","Dos verdades y una mentira","Votación","Estimación","Parar el contador","Duelo de reflejos","Libre"},0)),"¿tipo?"))</f>
+        <f>IF(C72="","",IFERROR("→ "&amp;INDEX({"Pulsador","Test","Verdad o mentira","Dos verdades","Votación","Estimación","Contador","Reflejos","Libre","Palabras","Agitar","Apuesta"},MATCH(C72,{"Pulsador","Test","Verdad o mentira","Dos verdades y una mentira","Votación","Estimación","Parar el contador","Duelo de reflejos","Libre","Palabras secretas","Agita el móvil","La gran apuesta"},0)),"¿tipo?"))</f>
         <v/>
       </c>
       <c r="E72" s="14"/>
@@ -8161,7 +13742,7 @@
       <c r="B73" s="12"/>
       <c r="C73" s="12"/>
       <c r="D73" s="13" t="str">
-        <f>IF(C73="","",IFERROR("→ "&amp;INDEX({"Pulsador","Test","Verdad o mentira","Dos verdades","Votación","Estimación","Contador","Reflejos","Libre"},MATCH(C73,{"Pulsador","Test","Verdad o mentira","Dos verdades y una mentira","Votación","Estimación","Parar el contador","Duelo de reflejos","Libre"},0)),"¿tipo?"))</f>
+        <f>IF(C73="","",IFERROR("→ "&amp;INDEX({"Pulsador","Test","Verdad o mentira","Dos verdades","Votación","Estimación","Contador","Reflejos","Libre","Palabras","Agitar","Apuesta"},MATCH(C73,{"Pulsador","Test","Verdad o mentira","Dos verdades y una mentira","Votación","Estimación","Parar el contador","Duelo de reflejos","Libre","Palabras secretas","Agita el móvil","La gran apuesta"},0)),"¿tipo?"))</f>
         <v/>
       </c>
       <c r="E73" s="14"/>
@@ -8175,7 +13756,7 @@
       <c r="B74" s="12"/>
       <c r="C74" s="12"/>
       <c r="D74" s="13" t="str">
-        <f>IF(C74="","",IFERROR("→ "&amp;INDEX({"Pulsador","Test","Verdad o mentira","Dos verdades","Votación","Estimación","Contador","Reflejos","Libre"},MATCH(C74,{"Pulsador","Test","Verdad o mentira","Dos verdades y una mentira","Votación","Estimación","Parar el contador","Duelo de reflejos","Libre"},0)),"¿tipo?"))</f>
+        <f>IF(C74="","",IFERROR("→ "&amp;INDEX({"Pulsador","Test","Verdad o mentira","Dos verdades","Votación","Estimación","Contador","Reflejos","Libre","Palabras","Agitar","Apuesta"},MATCH(C74,{"Pulsador","Test","Verdad o mentira","Dos verdades y una mentira","Votación","Estimación","Parar el contador","Duelo de reflejos","Libre","Palabras secretas","Agita el móvil","La gran apuesta"},0)),"¿tipo?"))</f>
         <v/>
       </c>
       <c r="E74" s="14"/>
@@ -8189,7 +13770,7 @@
       <c r="B75" s="12"/>
       <c r="C75" s="12"/>
       <c r="D75" s="13" t="str">
-        <f>IF(C75="","",IFERROR("→ "&amp;INDEX({"Pulsador","Test","Verdad o mentira","Dos verdades","Votación","Estimación","Contador","Reflejos","Libre"},MATCH(C75,{"Pulsador","Test","Verdad o mentira","Dos verdades y una mentira","Votación","Estimación","Parar el contador","Duelo de reflejos","Libre"},0)),"¿tipo?"))</f>
+        <f>IF(C75="","",IFERROR("→ "&amp;INDEX({"Pulsador","Test","Verdad o mentira","Dos verdades","Votación","Estimación","Contador","Reflejos","Libre","Palabras","Agitar","Apuesta"},MATCH(C75,{"Pulsador","Test","Verdad o mentira","Dos verdades y una mentira","Votación","Estimación","Parar el contador","Duelo de reflejos","Libre","Palabras secretas","Agita el móvil","La gran apuesta"},0)),"¿tipo?"))</f>
         <v/>
       </c>
       <c r="E75" s="14"/>
@@ -8203,7 +13784,7 @@
       <c r="B76" s="12"/>
       <c r="C76" s="12"/>
       <c r="D76" s="13" t="str">
-        <f>IF(C76="","",IFERROR("→ "&amp;INDEX({"Pulsador","Test","Verdad o mentira","Dos verdades","Votación","Estimación","Contador","Reflejos","Libre"},MATCH(C76,{"Pulsador","Test","Verdad o mentira","Dos verdades y una mentira","Votación","Estimación","Parar el contador","Duelo de reflejos","Libre"},0)),"¿tipo?"))</f>
+        <f>IF(C76="","",IFERROR("→ "&amp;INDEX({"Pulsador","Test","Verdad o mentira","Dos verdades","Votación","Estimación","Contador","Reflejos","Libre","Palabras","Agitar","Apuesta"},MATCH(C76,{"Pulsador","Test","Verdad o mentira","Dos verdades y una mentira","Votación","Estimación","Parar el contador","Duelo de reflejos","Libre","Palabras secretas","Agita el móvil","La gran apuesta"},0)),"¿tipo?"))</f>
         <v/>
       </c>
       <c r="E76" s="14"/>
@@ -8217,7 +13798,7 @@
       <c r="B77" s="12"/>
       <c r="C77" s="12"/>
       <c r="D77" s="13" t="str">
-        <f>IF(C77="","",IFERROR("→ "&amp;INDEX({"Pulsador","Test","Verdad o mentira","Dos verdades","Votación","Estimación","Contador","Reflejos","Libre"},MATCH(C77,{"Pulsador","Test","Verdad o mentira","Dos verdades y una mentira","Votación","Estimación","Parar el contador","Duelo de reflejos","Libre"},0)),"¿tipo?"))</f>
+        <f>IF(C77="","",IFERROR("→ "&amp;INDEX({"Pulsador","Test","Verdad o mentira","Dos verdades","Votación","Estimación","Contador","Reflejos","Libre","Palabras","Agitar","Apuesta"},MATCH(C77,{"Pulsador","Test","Verdad o mentira","Dos verdades y una mentira","Votación","Estimación","Parar el contador","Duelo de reflejos","Libre","Palabras secretas","Agita el móvil","La gran apuesta"},0)),"¿tipo?"))</f>
         <v/>
       </c>
       <c r="E77" s="14"/>
@@ -8231,7 +13812,7 @@
       <c r="B78" s="12"/>
       <c r="C78" s="12"/>
       <c r="D78" s="13" t="str">
-        <f>IF(C78="","",IFERROR("→ "&amp;INDEX({"Pulsador","Test","Verdad o mentira","Dos verdades","Votación","Estimación","Contador","Reflejos","Libre"},MATCH(C78,{"Pulsador","Test","Verdad o mentira","Dos verdades y una mentira","Votación","Estimación","Parar el contador","Duelo de reflejos","Libre"},0)),"¿tipo?"))</f>
+        <f>IF(C78="","",IFERROR("→ "&amp;INDEX({"Pulsador","Test","Verdad o mentira","Dos verdades","Votación","Estimación","Contador","Reflejos","Libre","Palabras","Agitar","Apuesta"},MATCH(C78,{"Pulsador","Test","Verdad o mentira","Dos verdades y una mentira","Votación","Estimación","Parar el contador","Duelo de reflejos","Libre","Palabras secretas","Agita el móvil","La gran apuesta"},0)),"¿tipo?"))</f>
         <v/>
       </c>
       <c r="E78" s="14"/>
@@ -8245,7 +13826,7 @@
       <c r="B79" s="12"/>
       <c r="C79" s="12"/>
       <c r="D79" s="13" t="str">
-        <f>IF(C79="","",IFERROR("→ "&amp;INDEX({"Pulsador","Test","Verdad o mentira","Dos verdades","Votación","Estimación","Contador","Reflejos","Libre"},MATCH(C79,{"Pulsador","Test","Verdad o mentira","Dos verdades y una mentira","Votación","Estimación","Parar el contador","Duelo de reflejos","Libre"},0)),"¿tipo?"))</f>
+        <f>IF(C79="","",IFERROR("→ "&amp;INDEX({"Pulsador","Test","Verdad o mentira","Dos verdades","Votación","Estimación","Contador","Reflejos","Libre","Palabras","Agitar","Apuesta"},MATCH(C79,{"Pulsador","Test","Verdad o mentira","Dos verdades y una mentira","Votación","Estimación","Parar el contador","Duelo de reflejos","Libre","Palabras secretas","Agita el móvil","La gran apuesta"},0)),"¿tipo?"))</f>
         <v/>
       </c>
       <c r="E79" s="14"/>
@@ -8259,7 +13840,7 @@
       <c r="B80" s="12"/>
       <c r="C80" s="12"/>
       <c r="D80" s="13" t="str">
-        <f>IF(C80="","",IFERROR("→ "&amp;INDEX({"Pulsador","Test","Verdad o mentira","Dos verdades","Votación","Estimación","Contador","Reflejos","Libre"},MATCH(C80,{"Pulsador","Test","Verdad o mentira","Dos verdades y una mentira","Votación","Estimación","Parar el contador","Duelo de reflejos","Libre"},0)),"¿tipo?"))</f>
+        <f>IF(C80="","",IFERROR("→ "&amp;INDEX({"Pulsador","Test","Verdad o mentira","Dos verdades","Votación","Estimación","Contador","Reflejos","Libre","Palabras","Agitar","Apuesta"},MATCH(C80,{"Pulsador","Test","Verdad o mentira","Dos verdades y una mentira","Votación","Estimación","Parar el contador","Duelo de reflejos","Libre","Palabras secretas","Agita el móvil","La gran apuesta"},0)),"¿tipo?"))</f>
         <v/>
       </c>
       <c r="E80" s="14"/>
@@ -8273,7 +13854,7 @@
       <c r="B81" s="12"/>
       <c r="C81" s="12"/>
       <c r="D81" s="13" t="str">
-        <f>IF(C81="","",IFERROR("→ "&amp;INDEX({"Pulsador","Test","Verdad o mentira","Dos verdades","Votación","Estimación","Contador","Reflejos","Libre"},MATCH(C81,{"Pulsador","Test","Verdad o mentira","Dos verdades y una mentira","Votación","Estimación","Parar el contador","Duelo de reflejos","Libre"},0)),"¿tipo?"))</f>
+        <f>IF(C81="","",IFERROR("→ "&amp;INDEX({"Pulsador","Test","Verdad o mentira","Dos verdades","Votación","Estimación","Contador","Reflejos","Libre","Palabras","Agitar","Apuesta"},MATCH(C81,{"Pulsador","Test","Verdad o mentira","Dos verdades y una mentira","Votación","Estimación","Parar el contador","Duelo de reflejos","Libre","Palabras secretas","Agita el móvil","La gran apuesta"},0)),"¿tipo?"))</f>
         <v/>
       </c>
       <c r="E81" s="14"/>
@@ -8287,7 +13868,7 @@
       <c r="B82" s="12"/>
       <c r="C82" s="12"/>
       <c r="D82" s="13" t="str">
-        <f>IF(C82="","",IFERROR("→ "&amp;INDEX({"Pulsador","Test","Verdad o mentira","Dos verdades","Votación","Estimación","Contador","Reflejos","Libre"},MATCH(C82,{"Pulsador","Test","Verdad o mentira","Dos verdades y una mentira","Votación","Estimación","Parar el contador","Duelo de reflejos","Libre"},0)),"¿tipo?"))</f>
+        <f>IF(C82="","",IFERROR("→ "&amp;INDEX({"Pulsador","Test","Verdad o mentira","Dos verdades","Votación","Estimación","Contador","Reflejos","Libre","Palabras","Agitar","Apuesta"},MATCH(C82,{"Pulsador","Test","Verdad o mentira","Dos verdades y una mentira","Votación","Estimación","Parar el contador","Duelo de reflejos","Libre","Palabras secretas","Agita el móvil","La gran apuesta"},0)),"¿tipo?"))</f>
         <v/>
       </c>
       <c r="E82" s="14"/>
@@ -8301,7 +13882,7 @@
       <c r="B83" s="12"/>
       <c r="C83" s="12"/>
       <c r="D83" s="13" t="str">
-        <f>IF(C83="","",IFERROR("→ "&amp;INDEX({"Pulsador","Test","Verdad o mentira","Dos verdades","Votación","Estimación","Contador","Reflejos","Libre"},MATCH(C83,{"Pulsador","Test","Verdad o mentira","Dos verdades y una mentira","Votación","Estimación","Parar el contador","Duelo de reflejos","Libre"},0)),"¿tipo?"))</f>
+        <f>IF(C83="","",IFERROR("→ "&amp;INDEX({"Pulsador","Test","Verdad o mentira","Dos verdades","Votación","Estimación","Contador","Reflejos","Libre","Palabras","Agitar","Apuesta"},MATCH(C83,{"Pulsador","Test","Verdad o mentira","Dos verdades y una mentira","Votación","Estimación","Parar el contador","Duelo de reflejos","Libre","Palabras secretas","Agita el móvil","La gran apuesta"},0)),"¿tipo?"))</f>
         <v/>
       </c>
       <c r="E83" s="14"/>
@@ -8315,7 +13896,7 @@
       <c r="B84" s="12"/>
       <c r="C84" s="12"/>
       <c r="D84" s="13" t="str">
-        <f>IF(C84="","",IFERROR("→ "&amp;INDEX({"Pulsador","Test","Verdad o mentira","Dos verdades","Votación","Estimación","Contador","Reflejos","Libre"},MATCH(C84,{"Pulsador","Test","Verdad o mentira","Dos verdades y una mentira","Votación","Estimación","Parar el contador","Duelo de reflejos","Libre"},0)),"¿tipo?"))</f>
+        <f>IF(C84="","",IFERROR("→ "&amp;INDEX({"Pulsador","Test","Verdad o mentira","Dos verdades","Votación","Estimación","Contador","Reflejos","Libre","Palabras","Agitar","Apuesta"},MATCH(C84,{"Pulsador","Test","Verdad o mentira","Dos verdades y una mentira","Votación","Estimación","Parar el contador","Duelo de reflejos","Libre","Palabras secretas","Agita el móvil","La gran apuesta"},0)),"¿tipo?"))</f>
         <v/>
       </c>
       <c r="E84" s="14"/>
@@ -8329,7 +13910,7 @@
       <c r="B85" s="12"/>
       <c r="C85" s="12"/>
       <c r="D85" s="13" t="str">
-        <f>IF(C85="","",IFERROR("→ "&amp;INDEX({"Pulsador","Test","Verdad o mentira","Dos verdades","Votación","Estimación","Contador","Reflejos","Libre"},MATCH(C85,{"Pulsador","Test","Verdad o mentira","Dos verdades y una mentira","Votación","Estimación","Parar el contador","Duelo de reflejos","Libre"},0)),"¿tipo?"))</f>
+        <f>IF(C85="","",IFERROR("→ "&amp;INDEX({"Pulsador","Test","Verdad o mentira","Dos verdades","Votación","Estimación","Contador","Reflejos","Libre","Palabras","Agitar","Apuesta"},MATCH(C85,{"Pulsador","Test","Verdad o mentira","Dos verdades y una mentira","Votación","Estimación","Parar el contador","Duelo de reflejos","Libre","Palabras secretas","Agita el móvil","La gran apuesta"},0)),"¿tipo?"))</f>
         <v/>
       </c>
       <c r="E85" s="14"/>
@@ -8343,7 +13924,7 @@
       <c r="B86" s="12"/>
       <c r="C86" s="12"/>
       <c r="D86" s="13" t="str">
-        <f>IF(C86="","",IFERROR("→ "&amp;INDEX({"Pulsador","Test","Verdad o mentira","Dos verdades","Votación","Estimación","Contador","Reflejos","Libre"},MATCH(C86,{"Pulsador","Test","Verdad o mentira","Dos verdades y una mentira","Votación","Estimación","Parar el contador","Duelo de reflejos","Libre"},0)),"¿tipo?"))</f>
+        <f>IF(C86="","",IFERROR("→ "&amp;INDEX({"Pulsador","Test","Verdad o mentira","Dos verdades","Votación","Estimación","Contador","Reflejos","Libre","Palabras","Agitar","Apuesta"},MATCH(C86,{"Pulsador","Test","Verdad o mentira","Dos verdades y una mentira","Votación","Estimación","Parar el contador","Duelo de reflejos","Libre","Palabras secretas","Agita el móvil","La gran apuesta"},0)),"¿tipo?"))</f>
         <v/>
       </c>
       <c r="E86" s="14"/>
@@ -8357,7 +13938,7 @@
       <c r="B87" s="12"/>
       <c r="C87" s="12"/>
       <c r="D87" s="13" t="str">
-        <f>IF(C87="","",IFERROR("→ "&amp;INDEX({"Pulsador","Test","Verdad o mentira","Dos verdades","Votación","Estimación","Contador","Reflejos","Libre"},MATCH(C87,{"Pulsador","Test","Verdad o mentira","Dos verdades y una mentira","Votación","Estimación","Parar el contador","Duelo de reflejos","Libre"},0)),"¿tipo?"))</f>
+        <f>IF(C87="","",IFERROR("→ "&amp;INDEX({"Pulsador","Test","Verdad o mentira","Dos verdades","Votación","Estimación","Contador","Reflejos","Libre","Palabras","Agitar","Apuesta"},MATCH(C87,{"Pulsador","Test","Verdad o mentira","Dos verdades y una mentira","Votación","Estimación","Parar el contador","Duelo de reflejos","Libre","Palabras secretas","Agita el móvil","La gran apuesta"},0)),"¿tipo?"))</f>
         <v/>
       </c>
       <c r="E87" s="14"/>
@@ -8371,7 +13952,7 @@
       <c r="B88" s="12"/>
       <c r="C88" s="12"/>
       <c r="D88" s="13" t="str">
-        <f>IF(C88="","",IFERROR("→ "&amp;INDEX({"Pulsador","Test","Verdad o mentira","Dos verdades","Votación","Estimación","Contador","Reflejos","Libre"},MATCH(C88,{"Pulsador","Test","Verdad o mentira","Dos verdades y una mentira","Votación","Estimación","Parar el contador","Duelo de reflejos","Libre"},0)),"¿tipo?"))</f>
+        <f>IF(C88="","",IFERROR("→ "&amp;INDEX({"Pulsador","Test","Verdad o mentira","Dos verdades","Votación","Estimación","Contador","Reflejos","Libre","Palabras","Agitar","Apuesta"},MATCH(C88,{"Pulsador","Test","Verdad o mentira","Dos verdades y una mentira","Votación","Estimación","Parar el contador","Duelo de reflejos","Libre","Palabras secretas","Agita el móvil","La gran apuesta"},0)),"¿tipo?"))</f>
         <v/>
       </c>
       <c r="E88" s="14"/>
@@ -8385,7 +13966,7 @@
       <c r="B89" s="12"/>
       <c r="C89" s="12"/>
       <c r="D89" s="13" t="str">
-        <f>IF(C89="","",IFERROR("→ "&amp;INDEX({"Pulsador","Test","Verdad o mentira","Dos verdades","Votación","Estimación","Contador","Reflejos","Libre"},MATCH(C89,{"Pulsador","Test","Verdad o mentira","Dos verdades y una mentira","Votación","Estimación","Parar el contador","Duelo de reflejos","Libre"},0)),"¿tipo?"))</f>
+        <f>IF(C89="","",IFERROR("→ "&amp;INDEX({"Pulsador","Test","Verdad o mentira","Dos verdades","Votación","Estimación","Contador","Reflejos","Libre","Palabras","Agitar","Apuesta"},MATCH(C89,{"Pulsador","Test","Verdad o mentira","Dos verdades y una mentira","Votación","Estimación","Parar el contador","Duelo de reflejos","Libre","Palabras secretas","Agita el móvil","La gran apuesta"},0)),"¿tipo?"))</f>
         <v/>
       </c>
       <c r="E89" s="14"/>
@@ -8399,7 +13980,7 @@
       <c r="B90" s="12"/>
       <c r="C90" s="12"/>
       <c r="D90" s="13" t="str">
-        <f>IF(C90="","",IFERROR("→ "&amp;INDEX({"Pulsador","Test","Verdad o mentira","Dos verdades","Votación","Estimación","Contador","Reflejos","Libre"},MATCH(C90,{"Pulsador","Test","Verdad o mentira","Dos verdades y una mentira","Votación","Estimación","Parar el contador","Duelo de reflejos","Libre"},0)),"¿tipo?"))</f>
+        <f>IF(C90="","",IFERROR("→ "&amp;INDEX({"Pulsador","Test","Verdad o mentira","Dos verdades","Votación","Estimación","Contador","Reflejos","Libre","Palabras","Agitar","Apuesta"},MATCH(C90,{"Pulsador","Test","Verdad o mentira","Dos verdades y una mentira","Votación","Estimación","Parar el contador","Duelo de reflejos","Libre","Palabras secretas","Agita el móvil","La gran apuesta"},0)),"¿tipo?"))</f>
         <v/>
       </c>
       <c r="E90" s="14"/>
@@ -8413,7 +13994,7 @@
       <c r="B91" s="12"/>
       <c r="C91" s="12"/>
       <c r="D91" s="13" t="str">
-        <f>IF(C91="","",IFERROR("→ "&amp;INDEX({"Pulsador","Test","Verdad o mentira","Dos verdades","Votación","Estimación","Contador","Reflejos","Libre"},MATCH(C91,{"Pulsador","Test","Verdad o mentira","Dos verdades y una mentira","Votación","Estimación","Parar el contador","Duelo de reflejos","Libre"},0)),"¿tipo?"))</f>
+        <f>IF(C91="","",IFERROR("→ "&amp;INDEX({"Pulsador","Test","Verdad o mentira","Dos verdades","Votación","Estimación","Contador","Reflejos","Libre","Palabras","Agitar","Apuesta"},MATCH(C91,{"Pulsador","Test","Verdad o mentira","Dos verdades y una mentira","Votación","Estimación","Parar el contador","Duelo de reflejos","Libre","Palabras secretas","Agita el móvil","La gran apuesta"},0)),"¿tipo?"))</f>
         <v/>
       </c>
       <c r="E91" s="14"/>
@@ -8427,7 +14008,7 @@
       <c r="B92" s="12"/>
       <c r="C92" s="12"/>
       <c r="D92" s="13" t="str">
-        <f>IF(C92="","",IFERROR("→ "&amp;INDEX({"Pulsador","Test","Verdad o mentira","Dos verdades","Votación","Estimación","Contador","Reflejos","Libre"},MATCH(C92,{"Pulsador","Test","Verdad o mentira","Dos verdades y una mentira","Votación","Estimación","Parar el contador","Duelo de reflejos","Libre"},0)),"¿tipo?"))</f>
+        <f>IF(C92="","",IFERROR("→ "&amp;INDEX({"Pulsador","Test","Verdad o mentira","Dos verdades","Votación","Estimación","Contador","Reflejos","Libre","Palabras","Agitar","Apuesta"},MATCH(C92,{"Pulsador","Test","Verdad o mentira","Dos verdades y una mentira","Votación","Estimación","Parar el contador","Duelo de reflejos","Libre","Palabras secretas","Agita el móvil","La gran apuesta"},0)),"¿tipo?"))</f>
         <v/>
       </c>
       <c r="E92" s="14"/>
@@ -8441,7 +14022,7 @@
       <c r="B93" s="12"/>
       <c r="C93" s="12"/>
       <c r="D93" s="13" t="str">
-        <f>IF(C93="","",IFERROR("→ "&amp;INDEX({"Pulsador","Test","Verdad o mentira","Dos verdades","Votación","Estimación","Contador","Reflejos","Libre"},MATCH(C93,{"Pulsador","Test","Verdad o mentira","Dos verdades y una mentira","Votación","Estimación","Parar el contador","Duelo de reflejos","Libre"},0)),"¿tipo?"))</f>
+        <f>IF(C93="","",IFERROR("→ "&amp;INDEX({"Pulsador","Test","Verdad o mentira","Dos verdades","Votación","Estimación","Contador","Reflejos","Libre","Palabras","Agitar","Apuesta"},MATCH(C93,{"Pulsador","Test","Verdad o mentira","Dos verdades y una mentira","Votación","Estimación","Parar el contador","Duelo de reflejos","Libre","Palabras secretas","Agita el móvil","La gran apuesta"},0)),"¿tipo?"))</f>
         <v/>
       </c>
       <c r="E93" s="14"/>
@@ -8455,7 +14036,7 @@
       <c r="B94" s="12"/>
       <c r="C94" s="12"/>
       <c r="D94" s="13" t="str">
-        <f>IF(C94="","",IFERROR("→ "&amp;INDEX({"Pulsador","Test","Verdad o mentira","Dos verdades","Votación","Estimación","Contador","Reflejos","Libre"},MATCH(C94,{"Pulsador","Test","Verdad o mentira","Dos verdades y una mentira","Votación","Estimación","Parar el contador","Duelo de reflejos","Libre"},0)),"¿tipo?"))</f>
+        <f>IF(C94="","",IFERROR("→ "&amp;INDEX({"Pulsador","Test","Verdad o mentira","Dos verdades","Votación","Estimación","Contador","Reflejos","Libre","Palabras","Agitar","Apuesta"},MATCH(C94,{"Pulsador","Test","Verdad o mentira","Dos verdades y una mentira","Votación","Estimación","Parar el contador","Duelo de reflejos","Libre","Palabras secretas","Agita el móvil","La gran apuesta"},0)),"¿tipo?"))</f>
         <v/>
       </c>
       <c r="E94" s="14"/>
@@ -8469,7 +14050,7 @@
       <c r="B95" s="12"/>
       <c r="C95" s="12"/>
       <c r="D95" s="13" t="str">
-        <f>IF(C95="","",IFERROR("→ "&amp;INDEX({"Pulsador","Test","Verdad o mentira","Dos verdades","Votación","Estimación","Contador","Reflejos","Libre"},MATCH(C95,{"Pulsador","Test","Verdad o mentira","Dos verdades y una mentira","Votación","Estimación","Parar el contador","Duelo de reflejos","Libre"},0)),"¿tipo?"))</f>
+        <f>IF(C95="","",IFERROR("→ "&amp;INDEX({"Pulsador","Test","Verdad o mentira","Dos verdades","Votación","Estimación","Contador","Reflejos","Libre","Palabras","Agitar","Apuesta"},MATCH(C95,{"Pulsador","Test","Verdad o mentira","Dos verdades y una mentira","Votación","Estimación","Parar el contador","Duelo de reflejos","Libre","Palabras secretas","Agita el móvil","La gran apuesta"},0)),"¿tipo?"))</f>
         <v/>
       </c>
       <c r="E95" s="14"/>
@@ -8483,7 +14064,7 @@
       <c r="B96" s="12"/>
       <c r="C96" s="12"/>
       <c r="D96" s="13" t="str">
-        <f>IF(C96="","",IFERROR("→ "&amp;INDEX({"Pulsador","Test","Verdad o mentira","Dos verdades","Votación","Estimación","Contador","Reflejos","Libre"},MATCH(C96,{"Pulsador","Test","Verdad o mentira","Dos verdades y una mentira","Votación","Estimación","Parar el contador","Duelo de reflejos","Libre"},0)),"¿tipo?"))</f>
+        <f>IF(C96="","",IFERROR("→ "&amp;INDEX({"Pulsador","Test","Verdad o mentira","Dos verdades","Votación","Estimación","Contador","Reflejos","Libre","Palabras","Agitar","Apuesta"},MATCH(C96,{"Pulsador","Test","Verdad o mentira","Dos verdades y una mentira","Votación","Estimación","Parar el contador","Duelo de reflejos","Libre","Palabras secretas","Agita el móvil","La gran apuesta"},0)),"¿tipo?"))</f>
         <v/>
       </c>
       <c r="E96" s="14"/>
@@ -8497,7 +14078,7 @@
       <c r="B97" s="12"/>
       <c r="C97" s="12"/>
       <c r="D97" s="13" t="str">
-        <f>IF(C97="","",IFERROR("→ "&amp;INDEX({"Pulsador","Test","Verdad o mentira","Dos verdades","Votación","Estimación","Contador","Reflejos","Libre"},MATCH(C97,{"Pulsador","Test","Verdad o mentira","Dos verdades y una mentira","Votación","Estimación","Parar el contador","Duelo de reflejos","Libre"},0)),"¿tipo?"))</f>
+        <f>IF(C97="","",IFERROR("→ "&amp;INDEX({"Pulsador","Test","Verdad o mentira","Dos verdades","Votación","Estimación","Contador","Reflejos","Libre","Palabras","Agitar","Apuesta"},MATCH(C97,{"Pulsador","Test","Verdad o mentira","Dos verdades y una mentira","Votación","Estimación","Parar el contador","Duelo de reflejos","Libre","Palabras secretas","Agita el móvil","La gran apuesta"},0)),"¿tipo?"))</f>
         <v/>
       </c>
       <c r="E97" s="14"/>
@@ -8511,7 +14092,7 @@
       <c r="B98" s="12"/>
       <c r="C98" s="12"/>
       <c r="D98" s="13" t="str">
-        <f>IF(C98="","",IFERROR("→ "&amp;INDEX({"Pulsador","Test","Verdad o mentira","Dos verdades","Votación","Estimación","Contador","Reflejos","Libre"},MATCH(C98,{"Pulsador","Test","Verdad o mentira","Dos verdades y una mentira","Votación","Estimación","Parar el contador","Duelo de reflejos","Libre"},0)),"¿tipo?"))</f>
+        <f>IF(C98="","",IFERROR("→ "&amp;INDEX({"Pulsador","Test","Verdad o mentira","Dos verdades","Votación","Estimación","Contador","Reflejos","Libre","Palabras","Agitar","Apuesta"},MATCH(C98,{"Pulsador","Test","Verdad o mentira","Dos verdades y una mentira","Votación","Estimación","Parar el contador","Duelo de reflejos","Libre","Palabras secretas","Agita el móvil","La gran apuesta"},0)),"¿tipo?"))</f>
         <v/>
       </c>
       <c r="E98" s="14"/>
@@ -8525,7 +14106,7 @@
       <c r="B99" s="12"/>
       <c r="C99" s="12"/>
       <c r="D99" s="13" t="str">
-        <f>IF(C99="","",IFERROR("→ "&amp;INDEX({"Pulsador","Test","Verdad o mentira","Dos verdades","Votación","Estimación","Contador","Reflejos","Libre"},MATCH(C99,{"Pulsador","Test","Verdad o mentira","Dos verdades y una mentira","Votación","Estimación","Parar el contador","Duelo de reflejos","Libre"},0)),"¿tipo?"))</f>
+        <f>IF(C99="","",IFERROR("→ "&amp;INDEX({"Pulsador","Test","Verdad o mentira","Dos verdades","Votación","Estimación","Contador","Reflejos","Libre","Palabras","Agitar","Apuesta"},MATCH(C99,{"Pulsador","Test","Verdad o mentira","Dos verdades y una mentira","Votación","Estimación","Parar el contador","Duelo de reflejos","Libre","Palabras secretas","Agita el móvil","La gran apuesta"},0)),"¿tipo?"))</f>
         <v/>
       </c>
       <c r="E99" s="14"/>
@@ -8539,7 +14120,7 @@
       <c r="B100" s="12"/>
       <c r="C100" s="12"/>
       <c r="D100" s="13" t="str">
-        <f>IF(C100="","",IFERROR("→ "&amp;INDEX({"Pulsador","Test","Verdad o mentira","Dos verdades","Votación","Estimación","Contador","Reflejos","Libre"},MATCH(C100,{"Pulsador","Test","Verdad o mentira","Dos verdades y una mentira","Votación","Estimación","Parar el contador","Duelo de reflejos","Libre"},0)),"¿tipo?"))</f>
+        <f>IF(C100="","",IFERROR("→ "&amp;INDEX({"Pulsador","Test","Verdad o mentira","Dos verdades","Votación","Estimación","Contador","Reflejos","Libre","Palabras","Agitar","Apuesta"},MATCH(C100,{"Pulsador","Test","Verdad o mentira","Dos verdades y una mentira","Votación","Estimación","Parar el contador","Duelo de reflejos","Libre","Palabras secretas","Agita el móvil","La gran apuesta"},0)),"¿tipo?"))</f>
         <v/>
       </c>
       <c r="E100" s="14"/>
@@ -9651,10 +15232,10 @@
   </sheetData>
   <dataValidations count="6">
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="warning" errorTitle="Valor no previsto" error="Elige un valor de la lista." sqref="C10:C200">
-      <formula1>"Pulsador,Test,Verdad o mentira,Dos verdades y una mentira,Votación,Estimación,Parar el contador,Duelo de reflejos,Libre"</formula1>
+      <formula1>"Pulsador,Test,Verdad o mentira,Dos verdades y una mentira,Votación,Estimación,Parar el contador,Duelo de reflejos,Libre,Palabras secretas,Agita el móvil,La gran apuesta"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="warning" errorTitle="Valor no previsto" error="Elige un valor de la lista." sqref="C3:C200">
-      <formula1>"Pulsador,Test,Verdad o mentira,Dos verdades y una mentira,Votación,Estimación,Parar el contador,Duelo de reflejos,Libre"</formula1>
+      <formula1>"Pulsador,Test,Verdad o mentira,Dos verdades y una mentira,Votación,Estimación,Parar el contador,Duelo de reflejos,Libre,Palabras secretas,Agita el móvil,La gran apuesta"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="warning" errorTitle="Valor no previsto" error="Elige un valor de la lista." sqref="G10:H200">
       <formula1>"Sí,No"</formula1>
@@ -9688,34 +15269,34 @@
   <sheetData>
     <row r="1" ht="30" customHeight="1" spans="1:2" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="10" t="s">
-        <v>83</v>
+        <v>97</v>
       </c>
       <c r="B1" s="10" t="s">
-        <v>84</v>
+        <v>98</v>
       </c>
     </row>
     <row r="2" ht="42" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="11" t="s">
-        <v>85</v>
+        <v>99</v>
       </c>
       <c r="B2" s="11" t="s">
-        <v>86</v>
+        <v>100</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="12" t="s">
-        <v>87</v>
+        <v>101</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>88</v>
+        <v>102</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="12" t="s">
-        <v>89</v>
+        <v>103</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>90</v>
+        <v>104</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
@@ -10531,123 +16112,135 @@
   <sheetData>
     <row r="1" ht="30" customHeight="1" spans="1:3" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="10" t="s">
-        <v>91</v>
+        <v>105</v>
       </c>
       <c r="B1" s="10" t="s">
-        <v>92</v>
+        <v>106</v>
       </c>
       <c r="C1" s="10" t="s">
-        <v>93</v>
+        <v>107</v>
       </c>
     </row>
     <row r="2" ht="42" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="11" t="s">
-        <v>94</v>
+        <v>108</v>
       </c>
       <c r="B2" s="11" t="s">
-        <v>95</v>
+        <v>109</v>
       </c>
       <c r="C2" s="11" t="s">
-        <v>96</v>
+        <v>110</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="12" t="s">
-        <v>97</v>
+        <v>111</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="C3" s="14" t="s">
-        <v>99</v>
+        <v>113</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="12" t="s">
-        <v>100</v>
+        <v>114</v>
       </c>
       <c r="B4" s="12">
         <v>1</v>
       </c>
       <c r="C4" s="14" t="s">
-        <v>101</v>
+        <v>115</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="12" t="s">
-        <v>102</v>
+        <v>116</v>
       </c>
       <c r="B5" s="12">
         <v>1</v>
       </c>
       <c r="C5" s="14" t="s">
-        <v>103</v>
+        <v>117</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="12" t="s">
-        <v>104</v>
+        <v>118</v>
       </c>
       <c r="B6" s="12">
         <v>1</v>
       </c>
       <c r="C6" s="14" t="s">
-        <v>105</v>
+        <v>119</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="12" t="s">
-        <v>106</v>
+        <v>120</v>
       </c>
       <c r="B7" s="12">
         <v>1</v>
       </c>
       <c r="C7" s="14" t="s">
-        <v>107</v>
+        <v>121</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="12" t="s">
-        <v>108</v>
+        <v>122</v>
       </c>
       <c r="B8" s="12">
         <v>0</v>
       </c>
       <c r="C8" s="14" t="s">
-        <v>109</v>
+        <v>123</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="12" t="s">
-        <v>110</v>
+        <v>124</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="C9" s="14" t="s">
-        <v>111</v>
+        <v>125</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="12" t="s">
-        <v>112</v>
+        <v>126</v>
       </c>
       <c r="B10" s="12">
         <v>20</v>
       </c>
       <c r="C10" s="14" t="s">
-        <v>113</v>
+        <v>127</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A11" s="12"/>
-      <c r="B11" s="12"/>
-      <c r="C11" s="14"/>
+      <c r="A11" s="12" t="s">
+        <v>128</v>
+      </c>
+      <c r="B11" s="12">
+        <v>60</v>
+      </c>
+      <c r="C11" s="14" t="s">
+        <v>129</v>
+      </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A12" s="12"/>
-      <c r="B12" s="12"/>
-      <c r="C12" s="14"/>
+      <c r="A12" s="12" t="s">
+        <v>130</v>
+      </c>
+      <c r="B12" s="12">
+        <v>2</v>
+      </c>
+      <c r="C12" s="14" t="s">
+        <v>131</v>
+      </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="12"/>
@@ -11612,119 +17205,163 @@
   <sheetData>
     <row r="1" ht="30" customHeight="1" spans="1:5" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="10" t="s">
-        <v>114</v>
+        <v>132</v>
       </c>
       <c r="B1" s="10" t="s">
-        <v>115</v>
+        <v>133</v>
       </c>
       <c r="C1" s="10" t="s">
-        <v>116</v>
+        <v>134</v>
       </c>
       <c r="D1" s="10" t="s">
-        <v>117</v>
+        <v>135</v>
       </c>
       <c r="E1" s="10" t="s">
-        <v>45</v>
+        <v>56</v>
       </c>
     </row>
     <row r="2" ht="42" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="11" t="s">
-        <v>118</v>
+        <v>136</v>
       </c>
       <c r="B2" s="11" t="s">
-        <v>119</v>
+        <v>137</v>
       </c>
       <c r="C2" s="11" t="s">
-        <v>120</v>
+        <v>138</v>
       </c>
       <c r="D2" s="11" t="s">
-        <v>121</v>
+        <v>139</v>
       </c>
       <c r="E2" s="11" t="s">
-        <v>122</v>
+        <v>140</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="14" t="s">
-        <v>123</v>
+        <v>141</v>
       </c>
       <c r="B3" s="14" t="s">
-        <v>124</v>
+        <v>142</v>
       </c>
       <c r="C3" s="12" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="D3" s="14"/>
       <c r="E3" s="12"/>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="14" t="s">
-        <v>125</v>
+        <v>143</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>126</v>
+        <v>144</v>
       </c>
       <c r="C4" s="12" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="D4" s="14"/>
       <c r="E4" s="12"/>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="14" t="s">
-        <v>127</v>
+        <v>145</v>
       </c>
       <c r="B5" s="14" t="s">
-        <v>128</v>
+        <v>146</v>
       </c>
       <c r="C5" s="12" t="s">
-        <v>81</v>
-      </c>
-      <c r="D5" s="14" t="s">
-        <v>129</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="D5" s="14"/>
       <c r="E5" s="12"/>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" s="14"/>
-      <c r="B6" s="14"/>
-      <c r="C6" s="12"/>
+      <c r="A6" s="14" t="s">
+        <v>147</v>
+      </c>
+      <c r="B6" s="14" t="s">
+        <v>148</v>
+      </c>
+      <c r="C6" s="12" t="s">
+        <v>87</v>
+      </c>
       <c r="D6" s="14"/>
       <c r="E6" s="12"/>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" s="14"/>
-      <c r="B7" s="14"/>
-      <c r="C7" s="12"/>
-      <c r="D7" s="14"/>
+      <c r="A7" s="14" t="s">
+        <v>149</v>
+      </c>
+      <c r="B7" s="14" t="s">
+        <v>150</v>
+      </c>
+      <c r="C7" s="12" t="s">
+        <v>87</v>
+      </c>
+      <c r="D7" s="14" t="s">
+        <v>151</v>
+      </c>
       <c r="E7" s="12"/>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A8" s="14"/>
-      <c r="B8" s="14"/>
-      <c r="C8" s="12"/>
-      <c r="D8" s="14"/>
+      <c r="A8" s="14" t="s">
+        <v>152</v>
+      </c>
+      <c r="B8" s="14" t="s">
+        <v>153</v>
+      </c>
+      <c r="C8" s="12" t="s">
+        <v>87</v>
+      </c>
+      <c r="D8" s="14" t="s">
+        <v>154</v>
+      </c>
       <c r="E8" s="12"/>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A9" s="14"/>
-      <c r="B9" s="14"/>
-      <c r="C9" s="12"/>
-      <c r="D9" s="14"/>
+      <c r="A9" s="14" t="s">
+        <v>155</v>
+      </c>
+      <c r="B9" s="14" t="s">
+        <v>156</v>
+      </c>
+      <c r="C9" s="12" t="s">
+        <v>87</v>
+      </c>
+      <c r="D9" s="14" t="s">
+        <v>157</v>
+      </c>
       <c r="E9" s="12"/>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A10" s="14"/>
-      <c r="B10" s="14"/>
-      <c r="C10" s="12"/>
-      <c r="D10" s="14"/>
+      <c r="A10" s="14" t="s">
+        <v>158</v>
+      </c>
+      <c r="B10" s="14" t="s">
+        <v>159</v>
+      </c>
+      <c r="C10" s="12" t="s">
+        <v>87</v>
+      </c>
+      <c r="D10" s="14" t="s">
+        <v>160</v>
+      </c>
       <c r="E10" s="12"/>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A11" s="14"/>
-      <c r="B11" s="14"/>
-      <c r="C11" s="12"/>
-      <c r="D11" s="14"/>
+      <c r="A11" s="14" t="s">
+        <v>161</v>
+      </c>
+      <c r="B11" s="14" t="s">
+        <v>162</v>
+      </c>
+      <c r="C11" s="12" t="s">
+        <v>87</v>
+      </c>
+      <c r="D11" s="14" t="s">
+        <v>160</v>
+      </c>
       <c r="E11" s="12"/>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
@@ -13088,275 +18725,359 @@
   <sheetData>
     <row r="1" ht="30" customHeight="1" spans="1:9" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="10" t="s">
-        <v>114</v>
+        <v>132</v>
       </c>
       <c r="B1" s="10" t="s">
-        <v>130</v>
+        <v>163</v>
       </c>
       <c r="C1" s="10" t="s">
-        <v>131</v>
+        <v>164</v>
       </c>
       <c r="D1" s="10" t="s">
-        <v>132</v>
+        <v>165</v>
       </c>
       <c r="E1" s="10" t="s">
-        <v>133</v>
+        <v>166</v>
       </c>
       <c r="F1" s="10" t="s">
-        <v>134</v>
+        <v>167</v>
       </c>
       <c r="G1" s="10" t="s">
-        <v>135</v>
+        <v>168</v>
       </c>
       <c r="H1" s="10" t="s">
-        <v>136</v>
+        <v>169</v>
       </c>
       <c r="I1" s="10" t="s">
-        <v>45</v>
+        <v>56</v>
       </c>
     </row>
     <row r="2" ht="42" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="11" t="s">
-        <v>137</v>
+        <v>170</v>
       </c>
       <c r="B2" s="11" t="s">
-        <v>138</v>
+        <v>171</v>
       </c>
       <c r="C2" s="11" t="s">
-        <v>139</v>
+        <v>172</v>
       </c>
       <c r="D2" s="11" t="s">
+        <v>173</v>
+      </c>
+      <c r="E2" s="11" t="s">
+        <v>174</v>
+      </c>
+      <c r="F2" s="11" t="s">
+        <v>175</v>
+      </c>
+      <c r="G2" s="11" t="s">
+        <v>176</v>
+      </c>
+      <c r="H2" s="11" t="s">
+        <v>177</v>
+      </c>
+      <c r="I2" s="11" t="s">
         <v>140</v>
-      </c>
-      <c r="E2" s="11" t="s">
-        <v>141</v>
-      </c>
-      <c r="F2" s="11" t="s">
-        <v>142</v>
-      </c>
-      <c r="G2" s="11" t="s">
-        <v>143</v>
-      </c>
-      <c r="H2" s="11" t="s">
-        <v>144</v>
-      </c>
-      <c r="I2" s="11" t="s">
-        <v>122</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="14" t="s">
-        <v>145</v>
+        <v>178</v>
       </c>
       <c r="B3" s="14" t="s">
-        <v>146</v>
+        <v>179</v>
       </c>
       <c r="C3" s="14" t="s">
-        <v>147</v>
+        <v>180</v>
       </c>
       <c r="D3" s="14" t="s">
-        <v>148</v>
+        <v>181</v>
       </c>
       <c r="E3" s="14" t="s">
-        <v>126</v>
+        <v>142</v>
       </c>
       <c r="F3" s="12" t="s">
-        <v>131</v>
+        <v>164</v>
       </c>
       <c r="G3" s="12" t="s">
-        <v>149</v>
+        <v>182</v>
       </c>
       <c r="H3" s="12"/>
       <c r="I3" s="12"/>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="14" t="s">
-        <v>150</v>
+        <v>183</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>151</v>
+        <v>184</v>
       </c>
       <c r="C4" s="14" t="s">
-        <v>152</v>
+        <v>185</v>
       </c>
       <c r="D4" s="14" t="s">
-        <v>153</v>
+        <v>186</v>
       </c>
       <c r="E4" s="14" t="s">
-        <v>154</v>
+        <v>187</v>
       </c>
       <c r="F4" s="12" t="s">
-        <v>132</v>
+        <v>163</v>
       </c>
       <c r="G4" s="12" t="s">
-        <v>149</v>
+        <v>182</v>
       </c>
       <c r="H4" s="12"/>
       <c r="I4" s="12"/>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="14" t="s">
-        <v>155</v>
+        <v>188</v>
       </c>
       <c r="B5" s="14" t="s">
-        <v>156</v>
+        <v>189</v>
       </c>
       <c r="C5" s="14" t="s">
-        <v>157</v>
+        <v>190</v>
       </c>
       <c r="D5" s="14" t="s">
-        <v>158</v>
+        <v>191</v>
       </c>
       <c r="E5" s="14" t="s">
-        <v>159</v>
+        <v>192</v>
       </c>
       <c r="F5" s="12" t="s">
-        <v>131</v>
+        <v>164</v>
       </c>
       <c r="G5" s="12" t="s">
-        <v>160</v>
+        <v>182</v>
       </c>
       <c r="H5" s="12"/>
       <c r="I5" s="12"/>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="14" t="s">
-        <v>161</v>
+        <v>193</v>
       </c>
       <c r="B6" s="14" t="s">
-        <v>162</v>
+        <v>194</v>
       </c>
       <c r="C6" s="14" t="s">
-        <v>163</v>
+        <v>195</v>
       </c>
       <c r="D6" s="14" t="s">
-        <v>164</v>
+        <v>196</v>
       </c>
       <c r="E6" s="14" t="s">
+        <v>197</v>
+      </c>
+      <c r="F6" s="12" t="s">
         <v>165</v>
       </c>
-      <c r="F6" s="12" t="s">
-        <v>132</v>
-      </c>
       <c r="G6" s="12" t="s">
-        <v>160</v>
+        <v>182</v>
       </c>
       <c r="H6" s="12"/>
       <c r="I6" s="12"/>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="14" t="s">
-        <v>166</v>
+        <v>198</v>
       </c>
       <c r="B7" s="14" t="s">
-        <v>167</v>
+        <v>199</v>
       </c>
       <c r="C7" s="14" t="s">
-        <v>168</v>
+        <v>200</v>
       </c>
       <c r="D7" s="14" t="s">
-        <v>169</v>
+        <v>201</v>
       </c>
       <c r="E7" s="14" t="s">
-        <v>170</v>
+        <v>202</v>
       </c>
       <c r="F7" s="12" t="s">
-        <v>133</v>
+        <v>164</v>
       </c>
       <c r="G7" s="12" t="s">
-        <v>171</v>
+        <v>203</v>
       </c>
       <c r="H7" s="12"/>
       <c r="I7" s="12"/>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" s="14" t="s">
-        <v>172</v>
+        <v>204</v>
       </c>
       <c r="B8" s="14" t="s">
-        <v>173</v>
+        <v>205</v>
       </c>
       <c r="C8" s="14" t="s">
-        <v>174</v>
+        <v>206</v>
       </c>
       <c r="D8" s="14" t="s">
-        <v>175</v>
+        <v>191</v>
       </c>
       <c r="E8" s="14" t="s">
-        <v>176</v>
+        <v>207</v>
       </c>
       <c r="F8" s="12" t="s">
-        <v>130</v>
+        <v>165</v>
       </c>
       <c r="G8" s="12" t="s">
-        <v>171</v>
+        <v>203</v>
       </c>
       <c r="H8" s="12"/>
       <c r="I8" s="12"/>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A9" s="14"/>
-      <c r="B9" s="14"/>
-      <c r="C9" s="14"/>
-      <c r="D9" s="14"/>
-      <c r="E9" s="14"/>
-      <c r="F9" s="12"/>
-      <c r="G9" s="12"/>
+      <c r="A9" s="14" t="s">
+        <v>208</v>
+      </c>
+      <c r="B9" s="14" t="s">
+        <v>209</v>
+      </c>
+      <c r="C9" s="14" t="s">
+        <v>210</v>
+      </c>
+      <c r="D9" s="14" t="s">
+        <v>211</v>
+      </c>
+      <c r="E9" s="14" t="s">
+        <v>212</v>
+      </c>
+      <c r="F9" s="12" t="s">
+        <v>164</v>
+      </c>
+      <c r="G9" s="12" t="s">
+        <v>203</v>
+      </c>
       <c r="H9" s="12"/>
       <c r="I9" s="12"/>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A10" s="14"/>
-      <c r="B10" s="14"/>
-      <c r="C10" s="14"/>
-      <c r="D10" s="14"/>
-      <c r="E10" s="14"/>
-      <c r="F10" s="12"/>
-      <c r="G10" s="12"/>
+      <c r="A10" s="14" t="s">
+        <v>213</v>
+      </c>
+      <c r="B10" s="14" t="s">
+        <v>214</v>
+      </c>
+      <c r="C10" s="14" t="s">
+        <v>215</v>
+      </c>
+      <c r="D10" s="14" t="s">
+        <v>216</v>
+      </c>
+      <c r="E10" s="14" t="s">
+        <v>217</v>
+      </c>
+      <c r="F10" s="12" t="s">
+        <v>166</v>
+      </c>
+      <c r="G10" s="12" t="s">
+        <v>203</v>
+      </c>
       <c r="H10" s="12"/>
       <c r="I10" s="12"/>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A11" s="14"/>
-      <c r="B11" s="14"/>
-      <c r="C11" s="14"/>
-      <c r="D11" s="14"/>
-      <c r="E11" s="14"/>
-      <c r="F11" s="12"/>
-      <c r="G11" s="12"/>
+      <c r="A11" s="14" t="s">
+        <v>218</v>
+      </c>
+      <c r="B11" s="14" t="s">
+        <v>219</v>
+      </c>
+      <c r="C11" s="14" t="s">
+        <v>220</v>
+      </c>
+      <c r="D11" s="14" t="s">
+        <v>221</v>
+      </c>
+      <c r="E11" s="14" t="s">
+        <v>222</v>
+      </c>
+      <c r="F11" s="12" t="s">
+        <v>166</v>
+      </c>
+      <c r="G11" s="12" t="s">
+        <v>223</v>
+      </c>
       <c r="H11" s="12"/>
       <c r="I11" s="12"/>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A12" s="14"/>
-      <c r="B12" s="14"/>
-      <c r="C12" s="14"/>
-      <c r="D12" s="14"/>
-      <c r="E12" s="14"/>
-      <c r="F12" s="12"/>
-      <c r="G12" s="12"/>
+      <c r="A12" s="14" t="s">
+        <v>224</v>
+      </c>
+      <c r="B12" s="14" t="s">
+        <v>225</v>
+      </c>
+      <c r="C12" s="14" t="s">
+        <v>226</v>
+      </c>
+      <c r="D12" s="14" t="s">
+        <v>227</v>
+      </c>
+      <c r="E12" s="14" t="s">
+        <v>228</v>
+      </c>
+      <c r="F12" s="12" t="s">
+        <v>163</v>
+      </c>
+      <c r="G12" s="12" t="s">
+        <v>223</v>
+      </c>
       <c r="H12" s="12"/>
       <c r="I12" s="12"/>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A13" s="14"/>
-      <c r="B13" s="14"/>
-      <c r="C13" s="14"/>
-      <c r="D13" s="14"/>
-      <c r="E13" s="14"/>
-      <c r="F13" s="12"/>
-      <c r="G13" s="12"/>
+      <c r="A13" s="14" t="s">
+        <v>229</v>
+      </c>
+      <c r="B13" s="14" t="s">
+        <v>230</v>
+      </c>
+      <c r="C13" s="14" t="s">
+        <v>231</v>
+      </c>
+      <c r="D13" s="14" t="s">
+        <v>232</v>
+      </c>
+      <c r="E13" s="14" t="s">
+        <v>233</v>
+      </c>
+      <c r="F13" s="12" t="s">
+        <v>164</v>
+      </c>
+      <c r="G13" s="12" t="s">
+        <v>223</v>
+      </c>
       <c r="H13" s="12"/>
       <c r="I13" s="12"/>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A14" s="14"/>
-      <c r="B14" s="14"/>
-      <c r="C14" s="14"/>
-      <c r="D14" s="14"/>
-      <c r="E14" s="14"/>
-      <c r="F14" s="12"/>
-      <c r="G14" s="12"/>
+      <c r="A14" s="14" t="s">
+        <v>234</v>
+      </c>
+      <c r="B14" s="14" t="s">
+        <v>235</v>
+      </c>
+      <c r="C14" s="14" t="s">
+        <v>236</v>
+      </c>
+      <c r="D14" s="14" t="s">
+        <v>237</v>
+      </c>
+      <c r="E14" s="14" t="s">
+        <v>238</v>
+      </c>
+      <c r="F14" s="12" t="s">
+        <v>164</v>
+      </c>
+      <c r="G14" s="12" t="s">
+        <v>223</v>
+      </c>
       <c r="H14" s="12"/>
       <c r="I14" s="12"/>
     </row>
@@ -15482,72 +21203,96 @@
   <sheetData>
     <row r="1" ht="30" customHeight="1" spans="1:3" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="10" t="s">
-        <v>177</v>
+        <v>239</v>
       </c>
       <c r="B1" s="10" t="s">
-        <v>115</v>
+        <v>133</v>
       </c>
       <c r="C1" s="10" t="s">
-        <v>45</v>
+        <v>56</v>
       </c>
     </row>
     <row r="2" ht="42" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="11" t="s">
-        <v>178</v>
+        <v>240</v>
       </c>
       <c r="B2" s="11" t="s">
-        <v>179</v>
+        <v>241</v>
       </c>
       <c r="C2" s="11" t="s">
-        <v>122</v>
+        <v>140</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="14" t="s">
-        <v>180</v>
+        <v>242</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>181</v>
+        <v>243</v>
       </c>
       <c r="C3" s="12"/>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="14" t="s">
-        <v>182</v>
+        <v>244</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>183</v>
+        <v>245</v>
       </c>
       <c r="C4" s="12"/>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" s="14"/>
-      <c r="B5" s="12"/>
+      <c r="A5" s="14" t="s">
+        <v>246</v>
+      </c>
+      <c r="B5" s="12" t="s">
+        <v>245</v>
+      </c>
       <c r="C5" s="12"/>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" s="14"/>
-      <c r="B6" s="12"/>
+      <c r="A6" s="14" t="s">
+        <v>247</v>
+      </c>
+      <c r="B6" s="12" t="s">
+        <v>243</v>
+      </c>
       <c r="C6" s="12"/>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" s="14"/>
-      <c r="B7" s="12"/>
+      <c r="A7" s="14" t="s">
+        <v>248</v>
+      </c>
+      <c r="B7" s="12" t="s">
+        <v>243</v>
+      </c>
       <c r="C7" s="12"/>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" s="14"/>
-      <c r="B8" s="12"/>
+      <c r="A8" s="14" t="s">
+        <v>249</v>
+      </c>
+      <c r="B8" s="12" t="s">
+        <v>243</v>
+      </c>
       <c r="C8" s="12"/>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" s="14"/>
-      <c r="B9" s="12"/>
+      <c r="A9" s="14" t="s">
+        <v>250</v>
+      </c>
+      <c r="B9" s="12" t="s">
+        <v>245</v>
+      </c>
       <c r="C9" s="12"/>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10" s="14"/>
-      <c r="B10" s="12"/>
+      <c r="A10" s="14" t="s">
+        <v>251</v>
+      </c>
+      <c r="B10" s="12" t="s">
+        <v>245</v>
+      </c>
       <c r="C10" s="12"/>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
@@ -16545,56 +22290,56 @@
   <sheetData>
     <row r="1" ht="30" customHeight="1" spans="1:6" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="10" t="s">
-        <v>184</v>
+        <v>252</v>
       </c>
       <c r="B1" s="10" t="s">
-        <v>185</v>
+        <v>253</v>
       </c>
       <c r="C1" s="10" t="s">
-        <v>186</v>
+        <v>254</v>
       </c>
       <c r="D1" s="10" t="s">
-        <v>187</v>
+        <v>255</v>
       </c>
       <c r="E1" s="10" t="s">
-        <v>183</v>
+        <v>245</v>
       </c>
       <c r="F1" s="10" t="s">
-        <v>45</v>
+        <v>56</v>
       </c>
     </row>
     <row r="2" ht="42" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="11" t="s">
-        <v>188</v>
+        <v>256</v>
       </c>
       <c r="B2" s="11" t="s">
-        <v>189</v>
+        <v>257</v>
       </c>
       <c r="C2" s="11" t="s">
-        <v>190</v>
+        <v>258</v>
       </c>
       <c r="D2" s="11" t="s">
-        <v>191</v>
+        <v>259</v>
       </c>
       <c r="E2" s="11" t="s">
-        <v>192</v>
+        <v>260</v>
       </c>
       <c r="F2" s="11" t="s">
-        <v>122</v>
+        <v>140</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="12" t="s">
-        <v>193</v>
+        <v>261</v>
       </c>
       <c r="B3" s="14" t="s">
-        <v>194</v>
+        <v>262</v>
       </c>
       <c r="C3" s="14" t="s">
-        <v>195</v>
+        <v>263</v>
       </c>
       <c r="D3" s="14" t="s">
-        <v>196</v>
+        <v>264</v>
       </c>
       <c r="E3" s="12">
         <v>2</v>
@@ -16602,51 +22347,111 @@
       <c r="F3" s="12"/>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="12"/>
-      <c r="B4" s="14"/>
-      <c r="C4" s="14"/>
-      <c r="D4" s="14"/>
-      <c r="E4" s="12"/>
+      <c r="A4" s="12" t="s">
+        <v>265</v>
+      </c>
+      <c r="B4" s="14" t="s">
+        <v>266</v>
+      </c>
+      <c r="C4" s="14" t="s">
+        <v>267</v>
+      </c>
+      <c r="D4" s="14" t="s">
+        <v>268</v>
+      </c>
+      <c r="E4" s="12">
+        <v>3</v>
+      </c>
       <c r="F4" s="12"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="12"/>
-      <c r="B5" s="14"/>
-      <c r="C5" s="14"/>
-      <c r="D5" s="14"/>
-      <c r="E5" s="12"/>
+      <c r="A5" s="12" t="s">
+        <v>269</v>
+      </c>
+      <c r="B5" s="14" t="s">
+        <v>270</v>
+      </c>
+      <c r="C5" s="14" t="s">
+        <v>271</v>
+      </c>
+      <c r="D5" s="14" t="s">
+        <v>272</v>
+      </c>
+      <c r="E5" s="12">
+        <v>1</v>
+      </c>
       <c r="F5" s="12"/>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="12"/>
-      <c r="B6" s="14"/>
-      <c r="C6" s="14"/>
-      <c r="D6" s="14"/>
-      <c r="E6" s="12"/>
+      <c r="A6" s="12" t="s">
+        <v>273</v>
+      </c>
+      <c r="B6" s="14" t="s">
+        <v>274</v>
+      </c>
+      <c r="C6" s="14" t="s">
+        <v>275</v>
+      </c>
+      <c r="D6" s="14" t="s">
+        <v>276</v>
+      </c>
+      <c r="E6" s="12">
+        <v>2</v>
+      </c>
       <c r="F6" s="12"/>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="12"/>
-      <c r="B7" s="14"/>
-      <c r="C7" s="14"/>
-      <c r="D7" s="14"/>
-      <c r="E7" s="12"/>
+      <c r="A7" s="12" t="s">
+        <v>277</v>
+      </c>
+      <c r="B7" s="14" t="s">
+        <v>278</v>
+      </c>
+      <c r="C7" s="14" t="s">
+        <v>279</v>
+      </c>
+      <c r="D7" s="14" t="s">
+        <v>280</v>
+      </c>
+      <c r="E7" s="12">
+        <v>3</v>
+      </c>
       <c r="F7" s="12"/>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="12"/>
-      <c r="B8" s="14"/>
-      <c r="C8" s="14"/>
-      <c r="D8" s="14"/>
-      <c r="E8" s="12"/>
+      <c r="A8" s="12" t="s">
+        <v>162</v>
+      </c>
+      <c r="B8" s="14" t="s">
+        <v>281</v>
+      </c>
+      <c r="C8" s="14" t="s">
+        <v>282</v>
+      </c>
+      <c r="D8" s="14" t="s">
+        <v>283</v>
+      </c>
+      <c r="E8" s="12">
+        <v>2</v>
+      </c>
       <c r="F8" s="12"/>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="12"/>
-      <c r="B9" s="14"/>
-      <c r="C9" s="14"/>
-      <c r="D9" s="14"/>
-      <c r="E9" s="12"/>
+      <c r="A9" s="12" t="s">
+        <v>284</v>
+      </c>
+      <c r="B9" s="14" t="s">
+        <v>285</v>
+      </c>
+      <c r="C9" s="14" t="s">
+        <v>286</v>
+      </c>
+      <c r="D9" s="14" t="s">
+        <v>287</v>
+      </c>
+      <c r="E9" s="12">
+        <v>2</v>
+      </c>
       <c r="F9" s="12"/>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
@@ -18226,54 +24031,66 @@
   <sheetData>
     <row r="1" ht="30" customHeight="1" spans="1:2" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="10" t="s">
-        <v>114</v>
+        <v>132</v>
       </c>
       <c r="B1" s="10" t="s">
-        <v>45</v>
+        <v>56</v>
       </c>
     </row>
     <row r="2" ht="42" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="11" t="s">
-        <v>197</v>
+        <v>288</v>
       </c>
       <c r="B2" s="11" t="s">
-        <v>122</v>
+        <v>140</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="14" t="s">
-        <v>198</v>
+        <v>289</v>
       </c>
       <c r="B3" s="12"/>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="14" t="s">
-        <v>199</v>
+        <v>290</v>
       </c>
       <c r="B4" s="12"/>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" s="14"/>
+      <c r="A5" s="14" t="s">
+        <v>291</v>
+      </c>
       <c r="B5" s="12"/>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" s="14"/>
+      <c r="A6" s="14" t="s">
+        <v>292</v>
+      </c>
       <c r="B6" s="12"/>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" s="14"/>
+      <c r="A7" s="14" t="s">
+        <v>293</v>
+      </c>
       <c r="B7" s="12"/>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" s="14"/>
+      <c r="A8" s="14" t="s">
+        <v>294</v>
+      </c>
       <c r="B8" s="12"/>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" s="14"/>
+      <c r="A9" s="14" t="s">
+        <v>295</v>
+      </c>
       <c r="B9" s="12"/>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" s="14"/>
+      <c r="A10" s="14" t="s">
+        <v>296</v>
+      </c>
       <c r="B10" s="12"/>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
